--- a/Versão5/SIS/Ontologia_Hidrossanitaria.xlsx
+++ b/Versão5/SIS/Ontologia_Hidrossanitaria.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\HIDS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\SIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53CE202D-AF85-49C5-80FE-D438782C0C65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C74E98C-D129-4C8E-BB18-D50654DBD375}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1218" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1346" uniqueCount="285">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -473,12 +473,6 @@
     <t>"Sistema de Esgoto da coluna 1 do Predio"</t>
   </si>
   <si>
-    <t>Sistema.Sanitário</t>
-  </si>
-  <si>
-    <t>Sistema.Hidráulico</t>
-  </si>
-  <si>
     <t>Tubulação.Reuso</t>
   </si>
   <si>
@@ -530,24 +524,9 @@
     <t>Cisterna Intermediária</t>
   </si>
   <si>
-    <t>Sistema de Esgoto Predial</t>
-  </si>
-  <si>
-    <t>Sistema de Água Quente Predial</t>
-  </si>
-  <si>
-    <t>Sistema de Água Fria Predial</t>
-  </si>
-  <si>
     <t>Ventilação de Esgoto</t>
   </si>
   <si>
-    <t>Sistema de Desague Predial</t>
-  </si>
-  <si>
-    <t>Sistema de Água Caliente Predial</t>
-  </si>
-  <si>
     <t>Ventilación de Esgoto</t>
   </si>
   <si>
@@ -861,6 +840,93 @@
   </si>
   <si>
     <t>"[ IfcPipeSegment : IfcPipeFitting ]"</t>
+  </si>
+  <si>
+    <t>Sistemas.Sanitários</t>
+  </si>
+  <si>
+    <t>Sistemas.Hidráulicos</t>
+  </si>
+  <si>
+    <t>Sistema.VEN</t>
+  </si>
+  <si>
+    <t>[ IfcDistributionSystemVENT ]</t>
+  </si>
+  <si>
+    <t>Sistema de ventilación de desagües.</t>
+  </si>
+  <si>
+    <t>Sistema de desagües del edificio.</t>
+  </si>
+  <si>
+    <t>Sistema de agua fria del edificio.</t>
+  </si>
+  <si>
+    <t>Sistema de agua caliente del edificio.</t>
+  </si>
+  <si>
+    <t>Sistema.PLU</t>
+  </si>
+  <si>
+    <t>Sistema de desagüe pluvial.</t>
+  </si>
+  <si>
+    <t>Sistema de ventilação do esgoto predial.</t>
+  </si>
+  <si>
+    <t>Sistema de esgoto predial.</t>
+  </si>
+  <si>
+    <t>Sistema de água fria predial.</t>
+  </si>
+  <si>
+    <t>Sistema de água quente predial.</t>
+  </si>
+  <si>
+    <t>Sistemas.Pluviais</t>
+  </si>
+  <si>
+    <t>Projeto</t>
+  </si>
+  <si>
+    <t>De.Tubulações</t>
+  </si>
+  <si>
+    <t>Esgoto</t>
+  </si>
+  <si>
+    <t>AF</t>
+  </si>
+  <si>
+    <t>AQ</t>
+  </si>
+  <si>
+    <t>Pluvial</t>
+  </si>
+  <si>
+    <t>Elementos.de.Instalações</t>
+  </si>
+  <si>
+    <t>Instalação.De</t>
+  </si>
+  <si>
+    <t>Ventilação</t>
+  </si>
+  <si>
+    <t>Ventilação de la instalação de desague.</t>
+  </si>
+  <si>
+    <t>Instalação de Esgoto</t>
+  </si>
+  <si>
+    <t>Instalação de água fria</t>
+  </si>
+  <si>
+    <t>Instalação de água caliente</t>
+  </si>
+  <si>
+    <t>Instalação de águas pluviais.</t>
   </si>
 </sst>
 </file>
@@ -1384,7 +1450,25 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="27">
+  <dxfs count="28">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1461,14 +1545,6 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -1476,6 +1552,14 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -1634,14 +1718,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2076,15 +2152,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="54" customWidth="1"/>
-    <col min="2" max="2" width="40.140625" style="54" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="40" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="54"/>
+    <col min="1" max="1" width="8.69140625" style="54" customWidth="1"/>
+    <col min="2" max="2" width="40.15234375" style="54" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="40" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.15234375" style="54"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="11" t="s">
         <v>44</v>
       </c>
@@ -2095,7 +2171,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="12" t="s">
         <v>46</v>
       </c>
@@ -2106,18 +2182,18 @@
         <v>90</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="12" t="s">
         <v>48</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="C3" s="39" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="13" t="s">
         <v>49</v>
       </c>
@@ -2128,7 +2204,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="13" t="s">
         <v>50</v>
       </c>
@@ -2140,7 +2216,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="13" t="s">
         <v>51</v>
       </c>
@@ -2152,7 +2228,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="13" t="s">
         <v>52</v>
       </c>
@@ -2163,7 +2239,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="37" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" s="37" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="36" t="s">
         <v>54</v>
       </c>
@@ -2174,7 +2250,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="13" t="s">
         <v>55</v>
       </c>
@@ -2185,7 +2261,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="13" t="s">
         <v>57</v>
       </c>
@@ -2196,7 +2272,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="13" t="s">
         <v>59</v>
       </c>
@@ -2207,7 +2283,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="13" t="s">
         <v>60</v>
       </c>
@@ -2218,7 +2294,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="13" t="s">
         <v>61</v>
       </c>
@@ -2229,7 +2305,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="13" t="s">
         <v>62</v>
       </c>
@@ -2240,7 +2316,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="13" t="s">
         <v>63</v>
       </c>
@@ -2251,7 +2327,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="13" t="s">
         <v>64</v>
       </c>
@@ -2262,30 +2338,30 @@
         <v>90</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="13" t="s">
         <v>65</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="C17" s="39" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="13" t="s">
         <v>66</v>
       </c>
       <c r="B18" s="14">
         <f ca="1">NOW()</f>
-        <v>46244.671326851851</v>
+        <v>46249.439659837961</v>
       </c>
       <c r="C18" s="39" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="13" t="s">
         <v>67</v>
       </c>
@@ -2296,7 +2372,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="13" t="s">
         <v>69</v>
       </c>
@@ -2307,7 +2383,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="13" t="s">
         <v>70</v>
       </c>
@@ -2318,29 +2394,29 @@
         <v>90</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="13" t="s">
         <v>71</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="C22" s="39" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="13" t="s">
         <v>72</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="C23" s="39" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="37" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" s="37" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="13" t="s">
         <v>88</v>
       </c>
@@ -2360,36 +2436,36 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96052D63-9637-42D9-866B-0BB924A50D8C}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AA40"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AA47"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.7109375" style="52" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.85546875" style="52" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" style="52" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.28515625" style="52" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.140625" style="59" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="8" style="52" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.85546875" style="52" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.7109375" style="52" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.28515625" style="52" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.140625" style="52" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="64.5703125" style="52" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="41" style="52" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="3.85546875" style="52" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.7109375" style="52" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="6.85546875" style="52" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.28515625" style="52" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8.5703125" style="52" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.7109375" style="52" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="43.85546875" style="52" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="19.28515625" style="53" customWidth="1"/>
-    <col min="26" max="26" width="7.28515625" style="52" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="67.7109375" style="52" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="52"/>
+    <col min="1" max="1" width="2.07421875" customWidth="1"/>
+    <col min="2" max="2" width="4.23046875" style="52" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.15234375" style="52" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.23046875" style="52" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.4609375" style="52" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.69140625" style="59" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="6.4609375" style="52" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.15234375" style="52" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.23046875" style="52" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.53515625" style="52" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.69140625" style="52" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="31.61328125" style="52" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="29.4609375" style="52" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="3.69140625" style="52" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.07421875" style="52" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.765625" style="52" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.4609375" style="52" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.921875" style="52" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.61328125" style="52" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="52.3046875" style="52" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="19.15234375" style="53" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="5" style="52" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="26.53515625" style="52" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.15234375" style="52"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" ht="38.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="42" t="s">
         <v>93</v>
       </c>
@@ -2472,24 +2548,24 @@
         <v>86</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="56">
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C2" s="41" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D2" s="41" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="E2" s="41" t="s">
-        <v>133</v>
+        <v>256</v>
       </c>
       <c r="F2" s="41" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="G2" s="58" t="s">
         <v>9</v>
@@ -2507,79 +2583,79 @@
         <v>9</v>
       </c>
       <c r="L2" s="32" t="str">
-        <f t="shared" ref="L2:L32" si="0">CONCATENATE("", C2)</f>
+        <f t="shared" ref="L2:L3" si="0">CONCATENATE("", C2)</f>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M2" s="32" t="str">
-        <f t="shared" ref="M2:M32" si="1">CONCATENATE("", D2)</f>
+        <f t="shared" ref="M2:M3" si="1">CONCATENATE("", D2)</f>
         <v>Sistemas.Hidrossanitários</v>
       </c>
       <c r="N2" s="32" t="str">
-        <f t="shared" ref="N2:N32" si="2">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E2),"."," ")," De "," de "))</f>
-        <v>Sistema Sanitário</v>
+        <f t="shared" ref="N2:N3" si="2">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E2),"."," ")," De "," de "))</f>
+        <v>Sistemas Sanitários</v>
       </c>
       <c r="O2" s="29" t="str">
-        <f t="shared" ref="O2:O40" si="3">IF(ISNUMBER(FIND("Ifc",F2)),CONCATENATE("Classe IFC:   ",F2),CONCATENATE("",F2))</f>
+        <f t="shared" ref="O2:O3" si="3">IF(ISNUMBER(FIND("Ifc",F2)),CONCATENATE("Classe IFC:   ",F2),CONCATENATE("",F2))</f>
         <v>Sistema.ESG</v>
       </c>
       <c r="P2" s="51" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q2" s="51" t="s">
+        <v>261</v>
+      </c>
+      <c r="R2" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="S2" s="29" t="s">
+        <v>153</v>
+      </c>
+      <c r="T2" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="Q2" s="51" t="s">
-        <v>156</v>
-      </c>
-      <c r="R2" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="S2" s="29" t="s">
-        <v>160</v>
-      </c>
-      <c r="T2" s="29" t="s">
-        <v>159</v>
-      </c>
       <c r="U2" s="29" t="str">
-        <f t="shared" ref="U2:U32" si="4">SUBSTITUTE(E2, "_", " ")</f>
-        <v>Sistema.Sanitário</v>
+        <f t="shared" ref="U2:U3" si="4">SUBSTITUTE(E2, "_", " ")</f>
+        <v>Sistemas.Sanitários</v>
       </c>
       <c r="V2" s="29" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="W2" s="57" t="str">
-        <f t="shared" ref="W2:W40" si="5">CONCATENATE("Key-HIDR-",A2)</f>
+        <f t="shared" ref="W2:W42" si="5">CONCATENATE("Key-HIDR-",A2)</f>
         <v>Key-HIDR-2</v>
       </c>
       <c r="X2" s="28" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="Y2" s="28" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="Z2" s="29" t="s">
         <v>128</v>
       </c>
       <c r="AA2" s="29" t="str">
         <f>_xlfn.TRANSLATE(P2,"pt","en")</f>
-        <v>Building Sewer System</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>Building sewer system.</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="56">
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C3" s="41" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D3" s="41" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="E3" s="41" t="s">
-        <v>134</v>
+        <v>256</v>
       </c>
       <c r="F3" s="41" t="s">
-        <v>228</v>
+        <v>258</v>
       </c>
       <c r="G3" s="58" t="s">
         <v>9</v>
@@ -2597,79 +2673,79 @@
         <v>9</v>
       </c>
       <c r="L3" s="32" t="str">
-        <f t="shared" ref="L3:L12" si="6">CONCATENATE("", C3)</f>
+        <f t="shared" si="0"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M3" s="32" t="str">
-        <f t="shared" ref="M3:M12" si="7">CONCATENATE("", D3)</f>
+        <f t="shared" si="1"/>
         <v>Sistemas.Hidrossanitários</v>
       </c>
       <c r="N3" s="32" t="str">
-        <f t="shared" ref="N3:N12" si="8">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E3),"."," ")," De "," de "))</f>
-        <v>Sistema Hidráulico</v>
+        <f t="shared" si="2"/>
+        <v>Sistemas Sanitários</v>
       </c>
       <c r="O3" s="29" t="str">
         <f t="shared" si="3"/>
-        <v>Sistema.AFR</v>
+        <v>Sistema.VEN</v>
       </c>
       <c r="P3" s="51" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q3" s="51" t="s">
+        <v>260</v>
+      </c>
+      <c r="R3" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="S3" s="29" t="s">
+        <v>153</v>
+      </c>
+      <c r="T3" s="29" t="s">
+        <v>152</v>
+      </c>
+      <c r="U3" s="29" t="str">
+        <f t="shared" si="4"/>
+        <v>Sistemas.Sanitários</v>
+      </c>
+      <c r="V3" s="29" t="s">
         <v>154</v>
       </c>
-      <c r="Q3" s="51" t="s">
-        <v>154</v>
-      </c>
-      <c r="R3" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="S3" s="29" t="s">
-        <v>160</v>
-      </c>
-      <c r="T3" s="29" t="s">
-        <v>159</v>
-      </c>
-      <c r="U3" s="29" t="str">
-        <f t="shared" ref="U3:U12" si="9">SUBSTITUTE(E3, "_", " ")</f>
-        <v>Sistema.Hidráulico</v>
-      </c>
-      <c r="V3" s="29" t="s">
-        <v>161</v>
-      </c>
       <c r="W3" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="W3" si="6">CONCATENATE("Key-HIDR-",A3)</f>
         <v>Key-HIDR-3</v>
       </c>
       <c r="X3" s="28" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="Y3" s="28" t="s">
-        <v>233</v>
+        <v>259</v>
       </c>
       <c r="Z3" s="29" t="s">
-        <v>163</v>
+        <v>128</v>
       </c>
       <c r="AA3" s="29" t="str">
         <f>_xlfn.TRANSLATE(P3,"pt","en")</f>
-        <v>Building Cold Water System</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>Building sewer ventilation system.</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="56">
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C4" s="41" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D4" s="41" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="E4" s="41" t="s">
-        <v>134</v>
+        <v>257</v>
       </c>
       <c r="F4" s="41" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="G4" s="58" t="s">
         <v>9</v>
@@ -2687,79 +2763,79 @@
         <v>9</v>
       </c>
       <c r="L4" s="32" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="L4:L14" si="7">CONCATENATE("", C4)</f>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M4" s="32" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="M4:M14" si="8">CONCATENATE("", D4)</f>
         <v>Sistemas.Hidrossanitários</v>
       </c>
       <c r="N4" s="32" t="str">
-        <f t="shared" si="8"/>
-        <v>Sistema Hidráulico</v>
+        <f t="shared" ref="N4:N14" si="9">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E4),"."," ")," De "," de "))</f>
+        <v>Sistemas Hidráulicos</v>
       </c>
       <c r="O4" s="29" t="str">
-        <f t="shared" si="3"/>
-        <v>Sistema.AQT</v>
+        <f t="shared" ref="O4:O42" si="10">IF(ISNUMBER(FIND("Ifc",F4)),CONCATENATE("Classe IFC:   ",F4),CONCATENATE("",F4))</f>
+        <v>Sistema.AFR</v>
       </c>
       <c r="P4" s="51" t="s">
+        <v>268</v>
+      </c>
+      <c r="Q4" s="51" t="s">
+        <v>262</v>
+      </c>
+      <c r="R4" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="S4" s="29" t="s">
         <v>153</v>
       </c>
-      <c r="Q4" s="51" t="s">
-        <v>157</v>
-      </c>
-      <c r="R4" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="S4" s="29" t="s">
-        <v>160</v>
-      </c>
       <c r="T4" s="29" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="U4" s="29" t="str">
-        <f t="shared" si="9"/>
-        <v>Sistema.Hidráulico</v>
+        <f t="shared" ref="U4:U14" si="11">SUBSTITUTE(E4, "_", " ")</f>
+        <v>Sistemas.Hidráulicos</v>
       </c>
       <c r="V4" s="29" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="W4" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-4</v>
       </c>
       <c r="X4" s="28" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="Y4" s="28" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="Z4" s="29" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="AA4" s="29" t="str">
         <f>_xlfn.TRANSLATE(P4,"pt","en")</f>
-        <v>Building Hot Water System</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>Building cold water system.</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="56">
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C5" s="41" t="s">
-        <v>253</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>254</v>
+        <v>246</v>
+      </c>
+      <c r="D5" s="41" t="s">
+        <v>248</v>
       </c>
       <c r="E5" s="41" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
       <c r="F5" s="41" t="s">
-        <v>171</v>
+        <v>222</v>
       </c>
       <c r="G5" s="58" t="s">
         <v>9</v>
@@ -2777,42 +2853,42 @@
         <v>9</v>
       </c>
       <c r="L5" s="32" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M5" s="32" t="str">
-        <f t="shared" si="7"/>
-        <v>Elementos.Hidráulicos</v>
+        <f t="shared" si="8"/>
+        <v>Sistemas.Hidrossanitários</v>
       </c>
       <c r="N5" s="32" t="str">
-        <f t="shared" si="8"/>
-        <v>Peças Hidráulicas</v>
+        <f t="shared" si="9"/>
+        <v>Sistemas Hidráulicos</v>
       </c>
       <c r="O5" s="29" t="str">
-        <f t="shared" si="3"/>
-        <v>Torneira</v>
+        <f t="shared" si="10"/>
+        <v>Sistema.AQT</v>
       </c>
       <c r="P5" s="51" t="s">
-        <v>171</v>
-      </c>
-      <c r="Q5" s="29" t="s">
-        <v>183</v>
+        <v>269</v>
+      </c>
+      <c r="Q5" s="51" t="s">
+        <v>263</v>
       </c>
       <c r="R5" s="29" t="s">
         <v>9</v>
       </c>
       <c r="S5" s="29" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="T5" s="29" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="U5" s="29" t="str">
-        <f t="shared" si="9"/>
-        <v>Peças.Hidráulicas</v>
+        <f t="shared" si="11"/>
+        <v>Sistemas.Hidráulicos</v>
       </c>
       <c r="V5" s="29" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="W5" s="57" t="str">
         <f t="shared" si="5"/>
@@ -2822,34 +2898,34 @@
         <v>190</v>
       </c>
       <c r="Y5" s="28" t="s">
-        <v>192</v>
+        <v>227</v>
       </c>
       <c r="Z5" s="29" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="AA5" s="29" t="str">
-        <f t="shared" ref="AA5:AA12" si="10">_xlfn.TRANSLATE(P5,"pt","en")</f>
-        <v>Tap</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <f>_xlfn.TRANSLATE(P5,"pt","en")</f>
+        <v>Building hot water system.</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="56">
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C6" s="41" t="s">
-        <v>253</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>254</v>
+        <v>246</v>
+      </c>
+      <c r="D6" s="41" t="s">
+        <v>248</v>
       </c>
       <c r="E6" s="41" t="s">
-        <v>227</v>
+        <v>270</v>
       </c>
       <c r="F6" s="41" t="s">
-        <v>172</v>
+        <v>264</v>
       </c>
       <c r="G6" s="58" t="s">
         <v>9</v>
@@ -2867,80 +2943,79 @@
         <v>9</v>
       </c>
       <c r="L6" s="32" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M6" s="32" t="str">
-        <f t="shared" si="7"/>
-        <v>Elementos.Hidráulicos</v>
+        <f t="shared" si="8"/>
+        <v>Sistemas.Hidrossanitários</v>
       </c>
       <c r="N6" s="32" t="str">
-        <f t="shared" si="8"/>
-        <v>Peças Hidráulicas</v>
+        <f t="shared" si="9"/>
+        <v>Sistemas Pluviais</v>
       </c>
       <c r="O6" s="29" t="str">
-        <f t="shared" si="3"/>
-        <v>Misturador</v>
+        <f t="shared" ref="O6" si="12">IF(ISNUMBER(FIND("Ifc",F6)),CONCATENATE("Classe IFC:   ",F6),CONCATENATE("",F6))</f>
+        <v>Sistema.PLU</v>
       </c>
       <c r="P6" s="51" t="s">
-        <v>172</v>
-      </c>
-      <c r="Q6" s="29" t="str">
-        <f t="shared" ref="Q6:Q12" si="11">_xlfn.TRANSLATE(P6,"pt","es")</f>
-        <v>Mezclador</v>
+        <v>265</v>
+      </c>
+      <c r="Q6" s="51" t="s">
+        <v>265</v>
       </c>
       <c r="R6" s="29" t="s">
         <v>9</v>
       </c>
       <c r="S6" s="29" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="T6" s="29" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="U6" s="29" t="str">
-        <f t="shared" si="9"/>
-        <v>Peças.Hidráulicas</v>
+        <f t="shared" si="11"/>
+        <v>Sistemas.Pluviais</v>
       </c>
       <c r="V6" s="29" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="W6" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="W6" si="13">CONCATENATE("Key-HIDR-",A6)</f>
         <v>Key-HIDR-6</v>
       </c>
       <c r="X6" s="28" t="s">
         <v>190</v>
       </c>
       <c r="Y6" s="28" t="s">
-        <v>192</v>
+        <v>259</v>
       </c>
       <c r="Z6" s="29" t="s">
-        <v>163</v>
+        <v>128</v>
       </c>
       <c r="AA6" s="29" t="str">
-        <f t="shared" si="10"/>
-        <v>Mixer</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <f>_xlfn.TRANSLATE(P6,"pt","en")</f>
+        <v>Rainwater drainage system.</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="56">
         <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C7" s="41" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E7" s="41" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="F7" s="41" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="G7" s="58" t="s">
         <v>9</v>
@@ -2958,80 +3033,79 @@
         <v>9</v>
       </c>
       <c r="L7" s="32" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M7" s="32" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N7" s="32" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Peças Hidráulicas</v>
       </c>
       <c r="O7" s="29" t="str">
-        <f t="shared" si="3"/>
-        <v>Registro</v>
+        <f t="shared" si="10"/>
+        <v>Torneira</v>
       </c>
       <c r="P7" s="51" t="s">
-        <v>174</v>
-      </c>
-      <c r="Q7" s="29" t="str">
+        <v>164</v>
+      </c>
+      <c r="Q7" s="29" t="s">
+        <v>176</v>
+      </c>
+      <c r="R7" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="S7" s="29" t="s">
+        <v>153</v>
+      </c>
+      <c r="T7" s="29" t="s">
+        <v>152</v>
+      </c>
+      <c r="U7" s="29" t="str">
         <f t="shared" si="11"/>
-        <v>Registro</v>
-      </c>
-      <c r="R7" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="S7" s="29" t="s">
-        <v>160</v>
-      </c>
-      <c r="T7" s="29" t="s">
-        <v>159</v>
-      </c>
-      <c r="U7" s="29" t="str">
-        <f t="shared" si="9"/>
         <v>Peças.Hidráulicas</v>
       </c>
       <c r="V7" s="29" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="W7" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-7</v>
       </c>
       <c r="X7" s="28" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="Y7" s="28" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="Z7" s="29" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="AA7" s="29" t="str">
-        <f t="shared" si="10"/>
-        <v>Registration</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" ref="AA7:AA14" si="14">_xlfn.TRANSLATE(P7,"pt","en")</f>
+        <v>Tap</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="56">
         <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C8" s="41" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E8" s="41" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="F8" s="41" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="G8" s="58" t="s">
         <v>9</v>
@@ -3049,171 +3123,171 @@
         <v>9</v>
       </c>
       <c r="L8" s="32" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M8" s="32" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N8" s="32" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Peças Hidráulicas</v>
       </c>
       <c r="O8" s="29" t="str">
-        <f t="shared" si="3"/>
-        <v>Válvula</v>
+        <f t="shared" si="10"/>
+        <v>Misturador</v>
       </c>
       <c r="P8" s="51" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="Q8" s="29" t="str">
+        <f t="shared" ref="Q8:Q14" si="15">_xlfn.TRANSLATE(P8,"pt","es")</f>
+        <v>Mezclador</v>
+      </c>
+      <c r="R8" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="S8" s="29" t="s">
+        <v>153</v>
+      </c>
+      <c r="T8" s="29" t="s">
+        <v>152</v>
+      </c>
+      <c r="U8" s="29" t="str">
         <f t="shared" si="11"/>
-        <v>Válvula</v>
-      </c>
-      <c r="R8" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="S8" s="29" t="s">
-        <v>160</v>
-      </c>
-      <c r="T8" s="29" t="s">
-        <v>159</v>
-      </c>
-      <c r="U8" s="29" t="str">
-        <f t="shared" si="9"/>
         <v>Peças.Hidráulicas</v>
       </c>
       <c r="V8" s="29" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="W8" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-8</v>
       </c>
       <c r="X8" s="28" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="Y8" s="28" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="Z8" s="29" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="AA8" s="29" t="str">
+        <f t="shared" si="14"/>
+        <v>Mixer</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="56">
+        <v>9</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="C9" s="41" t="s">
+        <v>246</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="E9" s="41" t="s">
+        <v>220</v>
+      </c>
+      <c r="F9" s="41" t="s">
+        <v>167</v>
+      </c>
+      <c r="G9" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H9" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I9" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J9" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K9" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="L9" s="32" t="str">
+        <f t="shared" si="7"/>
+        <v>Sistemas.Prediais</v>
+      </c>
+      <c r="M9" s="32" t="str">
+        <f t="shared" si="8"/>
+        <v>Elementos.Hidráulicos</v>
+      </c>
+      <c r="N9" s="32" t="str">
+        <f t="shared" si="9"/>
+        <v>Peças Hidráulicas</v>
+      </c>
+      <c r="O9" s="29" t="str">
         <f t="shared" si="10"/>
-        <v>Valve</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="56">
-        <v>9</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="C9" s="41" t="s">
-        <v>253</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="E9" s="41" t="s">
-        <v>227</v>
-      </c>
-      <c r="F9" s="41" t="s">
-        <v>170</v>
-      </c>
-      <c r="G9" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="H9" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="I9" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="J9" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="K9" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="L9" s="32" t="str">
-        <f t="shared" ref="L9:L11" si="12">CONCATENATE("", C9)</f>
-        <v>Sistemas.Prediais</v>
-      </c>
-      <c r="M9" s="32" t="str">
-        <f t="shared" ref="M9:M11" si="13">CONCATENATE("", D9)</f>
-        <v>Elementos.Hidráulicos</v>
-      </c>
-      <c r="N9" s="32" t="str">
-        <f t="shared" ref="N9:N11" si="14">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E9),"."," ")," De "," de "))</f>
-        <v>Peças Hidráulicas</v>
-      </c>
-      <c r="O9" s="29" t="str">
-        <f t="shared" si="3"/>
-        <v>Chuveiro</v>
+        <v>Registro</v>
       </c>
       <c r="P9" s="51" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="Q9" s="29" t="str">
+        <f t="shared" si="15"/>
+        <v>Registro</v>
+      </c>
+      <c r="R9" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="S9" s="29" t="s">
+        <v>153</v>
+      </c>
+      <c r="T9" s="29" t="s">
+        <v>152</v>
+      </c>
+      <c r="U9" s="29" t="str">
         <f t="shared" si="11"/>
-        <v>Ducha</v>
-      </c>
-      <c r="R9" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="S9" s="29" t="s">
-        <v>160</v>
-      </c>
-      <c r="T9" s="29" t="s">
-        <v>159</v>
-      </c>
-      <c r="U9" s="29" t="str">
-        <f t="shared" ref="U9:U11" si="15">SUBSTITUTE(E9, "_", " ")</f>
         <v>Peças.Hidráulicas</v>
       </c>
       <c r="V9" s="29" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="W9" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-9</v>
       </c>
       <c r="X9" s="28" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="Y9" s="28" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="Z9" s="29" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="AA9" s="29" t="str">
-        <f t="shared" ref="AA9:AA10" si="16">_xlfn.TRANSLATE(P9,"pt","en")</f>
-        <v>Shower</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="14"/>
+        <v>Registration</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="56">
         <v>10</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C10" s="41" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E10" s="41" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="F10" s="41" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="G10" s="58" t="s">
         <v>9</v>
@@ -3231,80 +3305,80 @@
         <v>9</v>
       </c>
       <c r="L10" s="32" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="7"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M10" s="32" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="8"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N10" s="32" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>Peças Hidráulicas</v>
       </c>
       <c r="O10" s="29" t="str">
-        <f t="shared" si="3"/>
-        <v>Ducha</v>
+        <f t="shared" si="10"/>
+        <v>Válvula</v>
       </c>
       <c r="P10" s="51" t="s">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="Q10" s="29" t="str">
-        <f t="shared" ref="Q10" si="17">_xlfn.TRANSLATE(P10,"pt","es")</f>
-        <v>Ducha manual</v>
+        <f t="shared" si="15"/>
+        <v>Válvula</v>
       </c>
       <c r="R10" s="29" t="s">
         <v>9</v>
       </c>
       <c r="S10" s="29" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="T10" s="29" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="U10" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="11"/>
         <v>Peças.Hidráulicas</v>
       </c>
       <c r="V10" s="29" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="W10" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-10</v>
       </c>
       <c r="X10" s="28" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="Y10" s="28" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="Z10" s="29" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="AA10" s="29" t="str">
-        <f t="shared" si="16"/>
-        <v>Manual shower</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="14"/>
+        <v>Valve</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="56">
         <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C11" s="41" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E11" s="41" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="F11" s="41" t="s">
-        <v>239</v>
+        <v>163</v>
       </c>
       <c r="G11" s="58" t="s">
         <v>9</v>
@@ -3322,78 +3396,80 @@
         <v>9</v>
       </c>
       <c r="L11" s="32" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="L11:L13" si="16">CONCATENATE("", C11)</f>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M11" s="32" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="M11:M13" si="17">CONCATENATE("", D11)</f>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N11" s="32" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="N11:N13" si="18">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E11),"."," ")," De "," de "))</f>
         <v>Peças Hidráulicas</v>
       </c>
       <c r="O11" s="29" t="str">
-        <f t="shared" si="3"/>
-        <v>Medidor.de.Água</v>
+        <f t="shared" si="10"/>
+        <v>Chuveiro</v>
       </c>
       <c r="P11" s="51" t="s">
-        <v>240</v>
-      </c>
-      <c r="Q11" s="51" t="s">
-        <v>241</v>
+        <v>163</v>
+      </c>
+      <c r="Q11" s="29" t="str">
+        <f t="shared" si="15"/>
+        <v>Ducha</v>
       </c>
       <c r="R11" s="29" t="s">
         <v>9</v>
       </c>
       <c r="S11" s="29" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="T11" s="29" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="U11" s="29" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" ref="U11:U13" si="19">SUBSTITUTE(E11, "_", " ")</f>
         <v>Peças.Hidráulicas</v>
       </c>
       <c r="V11" s="29" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="W11" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-11</v>
       </c>
       <c r="X11" s="28" t="s">
-        <v>249</v>
+        <v>183</v>
       </c>
       <c r="Y11" s="28" t="s">
-        <v>238</v>
+        <v>184</v>
       </c>
       <c r="Z11" s="29" t="s">
-        <v>163</v>
-      </c>
-      <c r="AA11" s="29" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+      <c r="AA11" s="29" t="str">
+        <f t="shared" ref="AA11:AA12" si="20">_xlfn.TRANSLATE(P11,"pt","en")</f>
+        <v>Shower</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="56">
         <v>12</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C12" s="41" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E12" s="41" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="F12" s="41" t="s">
-        <v>220</v>
+        <v>174</v>
       </c>
       <c r="G12" s="58" t="s">
         <v>9</v>
@@ -3411,80 +3487,80 @@
         <v>9</v>
       </c>
       <c r="L12" s="32" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="16"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M12" s="32" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="17"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N12" s="32" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="18"/>
         <v>Peças Hidráulicas</v>
       </c>
       <c r="O12" s="29" t="str">
-        <f t="shared" si="3"/>
-        <v>Acessório.Hidraúlico</v>
+        <f t="shared" si="10"/>
+        <v>Ducha</v>
       </c>
       <c r="P12" s="51" t="s">
-        <v>231</v>
+        <v>175</v>
       </c>
       <c r="Q12" s="29" t="str">
-        <f t="shared" si="11"/>
-        <v>Accesorios para sistemas de agua como soportes, ganchos, pedestales, etc.</v>
+        <f t="shared" ref="Q12" si="21">_xlfn.TRANSLATE(P12,"pt","es")</f>
+        <v>Ducha manual</v>
       </c>
       <c r="R12" s="29" t="s">
         <v>9</v>
       </c>
       <c r="S12" s="29" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="T12" s="29" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="U12" s="29" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="19"/>
         <v>Peças.Hidráulicas</v>
       </c>
       <c r="V12" s="29" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="W12" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-12</v>
       </c>
       <c r="X12" s="28" t="s">
-        <v>244</v>
+        <v>183</v>
       </c>
       <c r="Y12" s="28" t="s">
-        <v>243</v>
+        <v>184</v>
       </c>
       <c r="Z12" s="29" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="AA12" s="29" t="str">
-        <f t="shared" si="10"/>
-        <v>Water system accessory like brackets, hooks, pedestals, etc.</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="20"/>
+        <v>Manual shower</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="56">
         <v>13</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C13" s="41" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E13" s="41" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F13" s="41" t="s">
-        <v>136</v>
+        <v>232</v>
       </c>
       <c r="G13" s="58" t="s">
         <v>9</v>
@@ -3502,80 +3578,78 @@
         <v>9</v>
       </c>
       <c r="L13" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="16"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M13" s="32" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="17"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N13" s="32" t="str">
-        <f t="shared" si="2"/>
-        <v>Tubulação Agua Fria</v>
+        <f t="shared" si="18"/>
+        <v>Peças Hidráulicas</v>
       </c>
       <c r="O13" s="29" t="str">
-        <f t="shared" si="3"/>
-        <v>Cisterna.Superior</v>
+        <f t="shared" si="10"/>
+        <v>Medidor.de.Água</v>
       </c>
       <c r="P13" s="51" t="s">
-        <v>142</v>
-      </c>
-      <c r="Q13" s="29" t="str">
-        <f>_xlfn.TRANSLATE(P13,"pt","es")</f>
-        <v>Cisterna Superior</v>
+        <v>233</v>
+      </c>
+      <c r="Q13" s="51" t="s">
+        <v>234</v>
       </c>
       <c r="R13" s="29" t="s">
         <v>9</v>
       </c>
       <c r="S13" s="29" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="T13" s="29" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="U13" s="29" t="str">
-        <f t="shared" si="4"/>
-        <v>Tubulação.Agua.Fria</v>
+        <f t="shared" si="19"/>
+        <v>Peças.Hidráulicas</v>
       </c>
       <c r="V13" s="29" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="W13" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-13</v>
       </c>
       <c r="X13" s="28" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="Y13" s="28" t="s">
-        <v>193</v>
+        <v>231</v>
       </c>
       <c r="Z13" s="29" t="s">
-        <v>163</v>
-      </c>
-      <c r="AA13" s="29" t="str">
-        <f t="shared" ref="AA13:AA27" si="18">_xlfn.TRANSLATE(P13,"pt","en")</f>
-        <v>Upper Cistern</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+      <c r="AA13" s="29" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="56">
         <v>14</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C14" s="41" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E14" s="41" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F14" s="41" t="s">
-        <v>237</v>
+        <v>213</v>
       </c>
       <c r="G14" s="58" t="s">
         <v>9</v>
@@ -3593,80 +3667,80 @@
         <v>9</v>
       </c>
       <c r="L14" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M14" s="32" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="8"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N14" s="32" t="str">
-        <f t="shared" si="2"/>
-        <v>Tubulação Agua Fria</v>
+        <f t="shared" si="9"/>
+        <v>Peças Hidráulicas</v>
       </c>
       <c r="O14" s="29" t="str">
-        <f t="shared" si="3"/>
-        <v>Cisterna.Intermediária</v>
+        <f t="shared" si="10"/>
+        <v>Acessório.Hidraúlico</v>
       </c>
       <c r="P14" s="51" t="s">
-        <v>151</v>
+        <v>224</v>
       </c>
       <c r="Q14" s="29" t="str">
-        <f t="shared" ref="Q14:Q20" si="19">_xlfn.TRANSLATE(P14,"pt","es")</f>
-        <v>Cisterna intermedia</v>
+        <f t="shared" si="15"/>
+        <v>Accesorios para sistemas de agua como soportes, ganchos, pedestales, etc.</v>
       </c>
       <c r="R14" s="29" t="s">
         <v>9</v>
       </c>
       <c r="S14" s="29" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="T14" s="29" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="U14" s="29" t="str">
-        <f t="shared" si="4"/>
-        <v>Tubulação.Agua.Fria</v>
+        <f t="shared" si="11"/>
+        <v>Peças.Hidráulicas</v>
       </c>
       <c r="V14" s="29" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="W14" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-14</v>
       </c>
       <c r="X14" s="28" t="s">
-        <v>256</v>
+        <v>237</v>
       </c>
       <c r="Y14" s="28" t="s">
-        <v>193</v>
+        <v>236</v>
       </c>
       <c r="Z14" s="29" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="AA14" s="29" t="str">
-        <f t="shared" si="18"/>
-        <v>Intermediate Cistern</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="14"/>
+        <v>Water system accessory like brackets, hooks, pedestals, etc.</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="56">
         <v>15</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C15" s="41" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E15" s="41" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="F15" s="41" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="G15" s="58" t="s">
         <v>9</v>
@@ -3684,80 +3758,80 @@
         <v>9</v>
       </c>
       <c r="L15" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="L15:L34" si="22">CONCATENATE("", C15)</f>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M15" s="32" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="M15:M34" si="23">CONCATENATE("", D15)</f>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N15" s="32" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="N15:N34" si="24">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E15),"."," ")," De "," de "))</f>
         <v>Tubulação Agua Fria</v>
       </c>
       <c r="O15" s="29" t="str">
-        <f t="shared" si="3"/>
-        <v>Cisterna.Inferior</v>
+        <f t="shared" si="10"/>
+        <v>Cisterna.Superior</v>
       </c>
       <c r="P15" s="51" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="Q15" s="29" t="str">
-        <f t="shared" si="19"/>
-        <v>Cisterna Inferior</v>
+        <f>_xlfn.TRANSLATE(P15,"pt","es")</f>
+        <v>Cisterna Superior</v>
       </c>
       <c r="R15" s="29" t="s">
         <v>9</v>
       </c>
       <c r="S15" s="29" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="T15" s="29" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="U15" s="29" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="U15:U34" si="25">SUBSTITUTE(E15, "_", " ")</f>
         <v>Tubulação.Agua.Fria</v>
       </c>
       <c r="V15" s="29" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="W15" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-15</v>
       </c>
       <c r="X15" s="28" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="Y15" s="28" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="Z15" s="29" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="AA15" s="29" t="str">
-        <f t="shared" si="18"/>
-        <v>Lower Cistern</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" ref="AA15:AA29" si="26">_xlfn.TRANSLATE(P15,"pt","en")</f>
+        <v>Upper Cistern</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="56">
         <v>16</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C16" s="41" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E16" s="41" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="F16" s="41" t="s">
-        <v>141</v>
+        <v>230</v>
       </c>
       <c r="G16" s="58" t="s">
         <v>9</v>
@@ -3775,80 +3849,80 @@
         <v>9</v>
       </c>
       <c r="L16" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="22"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M16" s="32" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="23"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N16" s="32" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="24"/>
         <v>Tubulação Agua Fria</v>
       </c>
       <c r="O16" s="29" t="str">
-        <f t="shared" si="3"/>
-        <v>Tubulação.AF</v>
+        <f t="shared" si="10"/>
+        <v>Cisterna.Intermediária</v>
       </c>
       <c r="P16" s="51" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="Q16" s="29" t="str">
-        <f t="shared" si="19"/>
-        <v>Tubería de agua fría</v>
+        <f t="shared" ref="Q16:Q22" si="27">_xlfn.TRANSLATE(P16,"pt","es")</f>
+        <v>Cisterna intermedia</v>
       </c>
       <c r="R16" s="29" t="s">
         <v>9</v>
       </c>
       <c r="S16" s="29" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="T16" s="29" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="U16" s="29" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="25"/>
         <v>Tubulação.Agua.Fria</v>
       </c>
       <c r="V16" s="29" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="W16" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-16</v>
       </c>
       <c r="X16" s="28" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="Y16" s="28" t="s">
-        <v>257</v>
+        <v>186</v>
       </c>
       <c r="Z16" s="29" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="AA16" s="29" t="str">
-        <f t="shared" si="18"/>
-        <v>Cold Water Pipe</v>
-      </c>
-    </row>
-    <row r="17" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="26"/>
+        <v>Intermediate Cistern</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="56">
         <v>17</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C17" s="41" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E17" s="41" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="F17" s="41" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="G17" s="58" t="s">
         <v>9</v>
@@ -3866,79 +3940,80 @@
         <v>9</v>
       </c>
       <c r="L17" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="22"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M17" s="32" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="23"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N17" s="32" t="str">
-        <f t="shared" si="2"/>
-        <v>Tubulação Agua Quente</v>
+        <f t="shared" si="24"/>
+        <v>Tubulação Agua Fria</v>
       </c>
       <c r="O17" s="29" t="str">
-        <f t="shared" si="3"/>
-        <v>Aquecedor.de.Agua</v>
+        <f t="shared" si="10"/>
+        <v>Cisterna.Inferior</v>
       </c>
       <c r="P17" s="51" t="s">
-        <v>145</v>
-      </c>
-      <c r="Q17" s="29" t="s">
-        <v>150</v>
+        <v>141</v>
+      </c>
+      <c r="Q17" s="29" t="str">
+        <f t="shared" si="27"/>
+        <v>Cisterna Inferior</v>
       </c>
       <c r="R17" s="29" t="s">
         <v>9</v>
       </c>
       <c r="S17" s="29" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="T17" s="29" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="U17" s="29" t="str">
-        <f t="shared" si="4"/>
-        <v>Tubulação.Agua.Quente</v>
+        <f t="shared" si="25"/>
+        <v>Tubulação.Agua.Fria</v>
       </c>
       <c r="V17" s="29" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="W17" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-17</v>
       </c>
       <c r="X17" s="28" t="s">
-        <v>190</v>
+        <v>249</v>
       </c>
       <c r="Y17" s="28" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="Z17" s="29" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="AA17" s="29" t="str">
-        <f t="shared" si="18"/>
-        <v>Water heater</v>
-      </c>
-    </row>
-    <row r="18" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="26"/>
+        <v>Lower Cistern</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="56">
         <v>18</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C18" s="41" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E18" s="41" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="F18" s="41" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G18" s="58" t="s">
         <v>9</v>
@@ -3956,79 +4031,80 @@
         <v>9</v>
       </c>
       <c r="L18" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="22"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M18" s="32" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="23"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N18" s="32" t="str">
-        <f t="shared" si="2"/>
-        <v>Tubulação Agua Quente</v>
+        <f t="shared" si="24"/>
+        <v>Tubulação Agua Fria</v>
       </c>
       <c r="O18" s="29" t="str">
-        <f t="shared" si="3"/>
-        <v>Boiler</v>
+        <f t="shared" si="10"/>
+        <v>Tubulação.AF</v>
       </c>
       <c r="P18" s="51" t="s">
-        <v>138</v>
-      </c>
-      <c r="Q18" s="29" t="s">
-        <v>138</v>
+        <v>144</v>
+      </c>
+      <c r="Q18" s="29" t="str">
+        <f t="shared" si="27"/>
+        <v>Tubería de agua fría</v>
       </c>
       <c r="R18" s="29" t="s">
         <v>9</v>
       </c>
       <c r="S18" s="29" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="T18" s="29" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="U18" s="29" t="str">
-        <f t="shared" si="4"/>
-        <v>Tubulação.Agua.Quente</v>
+        <f t="shared" si="25"/>
+        <v>Tubulação.Agua.Fria</v>
       </c>
       <c r="V18" s="29" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="W18" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-18</v>
       </c>
       <c r="X18" s="28" t="s">
-        <v>190</v>
+        <v>249</v>
       </c>
       <c r="Y18" s="28" t="s">
-        <v>194</v>
+        <v>250</v>
       </c>
       <c r="Z18" s="29" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="AA18" s="29" t="str">
-        <f t="shared" si="18"/>
-        <v>Boiler</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="26"/>
+        <v>Cold Water Pipe</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="56">
         <v>19</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C19" s="41" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E19" s="41" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="F19" s="41" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="G19" s="58" t="s">
         <v>9</v>
@@ -4046,80 +4122,79 @@
         <v>9</v>
       </c>
       <c r="L19" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="22"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M19" s="32" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="23"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N19" s="32" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="24"/>
         <v>Tubulação Agua Quente</v>
       </c>
       <c r="O19" s="29" t="str">
-        <f t="shared" si="3"/>
-        <v>Caldeira</v>
+        <f t="shared" si="10"/>
+        <v>Aquecedor.de.Agua</v>
       </c>
       <c r="P19" s="51" t="s">
-        <v>139</v>
-      </c>
-      <c r="Q19" s="29" t="str">
-        <f t="shared" si="19"/>
-        <v>Caldera</v>
+        <v>143</v>
+      </c>
+      <c r="Q19" s="29" t="s">
+        <v>148</v>
       </c>
       <c r="R19" s="29" t="s">
         <v>9</v>
       </c>
       <c r="S19" s="29" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="T19" s="29" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="U19" s="29" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="25"/>
         <v>Tubulação.Agua.Quente</v>
       </c>
       <c r="V19" s="29" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="W19" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-19</v>
       </c>
       <c r="X19" s="28" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="Y19" s="28" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="Z19" s="29" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="AA19" s="29" t="str">
-        <f t="shared" si="18"/>
-        <v>Boiler</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="26"/>
+        <v>Water heater</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="56">
         <v>20</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C20" s="41" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E20" s="41" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="F20" s="41" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="G20" s="58" t="s">
         <v>9</v>
@@ -4137,80 +4212,79 @@
         <v>9</v>
       </c>
       <c r="L20" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="22"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M20" s="32" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="23"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N20" s="32" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="24"/>
         <v>Tubulação Agua Quente</v>
       </c>
       <c r="O20" s="29" t="str">
-        <f t="shared" si="3"/>
-        <v>Tubulação.AQ</v>
+        <f t="shared" si="10"/>
+        <v>Boiler</v>
       </c>
       <c r="P20" s="51" t="s">
-        <v>147</v>
-      </c>
-      <c r="Q20" s="29" t="str">
-        <f t="shared" si="19"/>
-        <v>Tubería de agua caliente</v>
+        <v>136</v>
+      </c>
+      <c r="Q20" s="29" t="s">
+        <v>136</v>
       </c>
       <c r="R20" s="29" t="s">
         <v>9</v>
       </c>
       <c r="S20" s="29" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="T20" s="29" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="U20" s="29" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="25"/>
         <v>Tubulação.Agua.Quente</v>
       </c>
       <c r="V20" s="29" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="W20" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-20</v>
       </c>
       <c r="X20" s="28" t="s">
-        <v>256</v>
+        <v>183</v>
       </c>
       <c r="Y20" s="28" t="s">
-        <v>257</v>
+        <v>187</v>
       </c>
       <c r="Z20" s="29" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="AA20" s="29" t="str">
-        <f t="shared" si="18"/>
-        <v>Hot Water Pipe</v>
-      </c>
-    </row>
-    <row r="21" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="26"/>
+        <v>Boiler</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="56">
         <v>21</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C21" s="41" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E21" s="41" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="F21" s="41" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G21" s="58" t="s">
         <v>9</v>
@@ -4228,79 +4302,80 @@
         <v>9</v>
       </c>
       <c r="L21" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="22"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M21" s="32" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="23"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N21" s="32" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="24"/>
         <v>Tubulação Agua Quente</v>
       </c>
       <c r="O21" s="29" t="str">
-        <f t="shared" si="3"/>
-        <v>Tubulação.Reuso</v>
+        <f t="shared" si="10"/>
+        <v>Caldeira</v>
       </c>
       <c r="P21" s="51" t="s">
-        <v>148</v>
-      </c>
-      <c r="Q21" s="51" t="s">
-        <v>149</v>
+        <v>137</v>
+      </c>
+      <c r="Q21" s="29" t="str">
+        <f t="shared" si="27"/>
+        <v>Caldera</v>
       </c>
       <c r="R21" s="29" t="s">
         <v>9</v>
       </c>
       <c r="S21" s="29" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="T21" s="29" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="U21" s="29" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="25"/>
         <v>Tubulação.Agua.Quente</v>
       </c>
       <c r="V21" s="29" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="W21" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-21</v>
       </c>
       <c r="X21" s="28" t="s">
-        <v>256</v>
+        <v>183</v>
       </c>
       <c r="Y21" s="28" t="s">
-        <v>257</v>
+        <v>188</v>
       </c>
       <c r="Z21" s="29" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="AA21" s="29" t="str">
-        <f t="shared" si="18"/>
-        <v>Reuse Water Pipe</v>
-      </c>
-    </row>
-    <row r="22" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="26"/>
+        <v>Boiler</v>
+      </c>
+    </row>
+    <row r="22" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="56">
         <v>22</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C22" s="41" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E22" s="41" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="F22" s="41" t="s">
-        <v>177</v>
+        <v>138</v>
       </c>
       <c r="G22" s="58" t="s">
         <v>9</v>
@@ -4318,79 +4393,80 @@
         <v>9</v>
       </c>
       <c r="L22" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="22"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M22" s="32" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="23"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N22" s="32" t="str">
-        <f t="shared" si="2"/>
-        <v>Peças Sanitárias</v>
+        <f t="shared" si="24"/>
+        <v>Tubulação Agua Quente</v>
       </c>
       <c r="O22" s="29" t="str">
-        <f t="shared" si="3"/>
-        <v>Vaso.Sanitário</v>
+        <f t="shared" si="10"/>
+        <v>Tubulação.AQ</v>
       </c>
       <c r="P22" s="51" t="s">
-        <v>184</v>
-      </c>
-      <c r="Q22" s="29" t="s">
-        <v>187</v>
+        <v>145</v>
+      </c>
+      <c r="Q22" s="29" t="str">
+        <f t="shared" si="27"/>
+        <v>Tubería de agua caliente</v>
       </c>
       <c r="R22" s="29" t="s">
         <v>9</v>
       </c>
       <c r="S22" s="29" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="T22" s="29" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="U22" s="29" t="str">
-        <f t="shared" si="4"/>
-        <v>Peças.Sanitárias</v>
+        <f t="shared" si="25"/>
+        <v>Tubulação.Agua.Quente</v>
       </c>
       <c r="V22" s="29" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="W22" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-22</v>
       </c>
       <c r="X22" s="28" t="s">
-        <v>190</v>
+        <v>249</v>
       </c>
       <c r="Y22" s="28" t="s">
-        <v>191</v>
+        <v>250</v>
       </c>
       <c r="Z22" s="29" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="AA22" s="29" t="str">
-        <f t="shared" si="18"/>
-        <v>Toilet</v>
-      </c>
-    </row>
-    <row r="23" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="26"/>
+        <v>Hot Water Pipe</v>
+      </c>
+    </row>
+    <row r="23" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="56">
         <v>23</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C23" s="41" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E23" s="41" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="F23" s="41" t="s">
-        <v>176</v>
+        <v>133</v>
       </c>
       <c r="G23" s="58" t="s">
         <v>9</v>
@@ -4408,80 +4484,79 @@
         <v>9</v>
       </c>
       <c r="L23" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="22"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M23" s="32" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="23"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N23" s="32" t="str">
-        <f t="shared" si="2"/>
-        <v>Peças Sanitárias</v>
+        <f t="shared" si="24"/>
+        <v>Tubulação Agua Quente</v>
       </c>
       <c r="O23" s="29" t="str">
-        <f t="shared" si="3"/>
-        <v>Bidet</v>
+        <f t="shared" si="10"/>
+        <v>Tubulação.Reuso</v>
       </c>
       <c r="P23" s="51" t="s">
-        <v>176</v>
-      </c>
-      <c r="Q23" s="29" t="str">
-        <f t="shared" ref="Q23:Q27" si="20">_xlfn.TRANSLATE(P23,"pt","es")</f>
-        <v>Bidé</v>
+        <v>146</v>
+      </c>
+      <c r="Q23" s="51" t="s">
+        <v>147</v>
       </c>
       <c r="R23" s="29" t="s">
         <v>9</v>
       </c>
       <c r="S23" s="29" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="T23" s="29" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="U23" s="29" t="str">
-        <f t="shared" si="4"/>
-        <v>Peças.Sanitárias</v>
+        <f t="shared" si="25"/>
+        <v>Tubulação.Agua.Quente</v>
       </c>
       <c r="V23" s="29" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="W23" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-23</v>
       </c>
       <c r="X23" s="28" t="s">
-        <v>190</v>
+        <v>249</v>
       </c>
       <c r="Y23" s="28" t="s">
-        <v>191</v>
+        <v>250</v>
       </c>
       <c r="Z23" s="29" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="AA23" s="29" t="str">
-        <f t="shared" si="18"/>
-        <v>Bidet</v>
-      </c>
-    </row>
-    <row r="24" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="26"/>
+        <v>Reuse Water Pipe</v>
+      </c>
+    </row>
+    <row r="24" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="56">
         <v>24</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C24" s="41" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E24" s="41" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="F24" s="41" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="G24" s="58" t="s">
         <v>9</v>
@@ -4499,79 +4574,79 @@
         <v>9</v>
       </c>
       <c r="L24" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="22"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M24" s="32" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="23"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N24" s="32" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="24"/>
         <v>Peças Sanitárias</v>
       </c>
       <c r="O24" s="29" t="str">
-        <f t="shared" si="3"/>
-        <v>Pia.Sanitária</v>
+        <f t="shared" si="10"/>
+        <v>Vaso.Sanitário</v>
       </c>
       <c r="P24" s="51" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="Q24" s="29" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="R24" s="29" t="s">
         <v>9</v>
       </c>
       <c r="S24" s="29" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="T24" s="29" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="U24" s="29" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="25"/>
         <v>Peças.Sanitárias</v>
       </c>
       <c r="V24" s="29" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="W24" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-24</v>
       </c>
       <c r="X24" s="28" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="Y24" s="28" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="Z24" s="29" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="AA24" s="29" t="str">
-        <f t="shared" si="18"/>
-        <v>Sanitary Sink</v>
-      </c>
-    </row>
-    <row r="25" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="26"/>
+        <v>Toilet</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="56">
         <v>25</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C25" s="41" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E25" s="41" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="F25" s="41" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="G25" s="58" t="s">
         <v>9</v>
@@ -4589,170 +4664,170 @@
         <v>9</v>
       </c>
       <c r="L25" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="22"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M25" s="32" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="23"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N25" s="32" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="24"/>
         <v>Peças Sanitárias</v>
       </c>
       <c r="O25" s="29" t="str">
-        <f t="shared" si="3"/>
-        <v>Lavatório</v>
+        <f t="shared" si="10"/>
+        <v>Bidet</v>
       </c>
       <c r="P25" s="51" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="Q25" s="29" t="str">
-        <f t="shared" si="20"/>
-        <v>Lavabo</v>
+        <f t="shared" ref="Q25:Q29" si="28">_xlfn.TRANSLATE(P25,"pt","es")</f>
+        <v>Bidé</v>
       </c>
       <c r="R25" s="29" t="s">
         <v>9</v>
       </c>
       <c r="S25" s="29" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="T25" s="29" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="U25" s="29" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="25"/>
         <v>Peças.Sanitárias</v>
       </c>
       <c r="V25" s="29" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="W25" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-25</v>
       </c>
       <c r="X25" s="28" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="Y25" s="28" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="Z25" s="29" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="AA25" s="29" t="str">
-        <f t="shared" si="18"/>
-        <v>Washbasin</v>
-      </c>
-    </row>
-    <row r="26" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="26"/>
+        <v>Bidet</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="56">
         <v>26</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C26" s="41" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E26" s="41" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="F26" s="41" t="s">
+        <v>172</v>
+      </c>
+      <c r="G26" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H26" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I26" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J26" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K26" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="L26" s="32" t="str">
+        <f t="shared" si="22"/>
+        <v>Sistemas.Prediais</v>
+      </c>
+      <c r="M26" s="32" t="str">
+        <f t="shared" si="23"/>
+        <v>Elementos.Hidráulicos</v>
+      </c>
+      <c r="N26" s="32" t="str">
+        <f t="shared" si="24"/>
+        <v>Peças Sanitárias</v>
+      </c>
+      <c r="O26" s="29" t="str">
+        <f t="shared" si="10"/>
+        <v>Pia.Sanitária</v>
+      </c>
+      <c r="P26" s="51" t="s">
         <v>178</v>
       </c>
-      <c r="G26" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="H26" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="I26" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="J26" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="K26" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="L26" s="32" t="str">
-        <f t="shared" ref="L26" si="21">CONCATENATE("", C26)</f>
-        <v>Sistemas.Prediais</v>
-      </c>
-      <c r="M26" s="32" t="str">
-        <f t="shared" ref="M26" si="22">CONCATENATE("", D26)</f>
-        <v>Elementos.Hidráulicos</v>
-      </c>
-      <c r="N26" s="32" t="str">
-        <f t="shared" ref="N26" si="23">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E26),"."," ")," De "," de "))</f>
-        <v>Peças Sanitárias</v>
-      </c>
-      <c r="O26" s="29" t="str">
-        <f t="shared" si="3"/>
-        <v>Cuba.Sanitária</v>
-      </c>
-      <c r="P26" s="51" t="s">
-        <v>186</v>
-      </c>
       <c r="Q26" s="29" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="R26" s="29" t="s">
         <v>9</v>
       </c>
       <c r="S26" s="29" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="T26" s="29" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="U26" s="29" t="str">
-        <f t="shared" ref="U26" si="24">SUBSTITUTE(E26, "_", " ")</f>
+        <f t="shared" si="25"/>
         <v>Peças.Sanitárias</v>
       </c>
       <c r="V26" s="29" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="W26" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-26</v>
       </c>
       <c r="X26" s="28" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="Y26" s="28" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="Z26" s="29" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="AA26" s="29" t="str">
-        <f t="shared" ref="AA26" si="25">_xlfn.TRANSLATE(P26,"pt","en")</f>
-        <v>Sanitary Bowl</v>
-      </c>
-    </row>
-    <row r="27" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="26"/>
+        <v>Sanitary Sink</v>
+      </c>
+    </row>
+    <row r="27" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="56">
         <v>27</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C27" s="41" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E27" s="41" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="F27" s="41" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="G27" s="58" t="s">
         <v>9</v>
@@ -4770,80 +4845,80 @@
         <v>9</v>
       </c>
       <c r="L27" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="22"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M27" s="32" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="23"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N27" s="32" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="24"/>
         <v>Peças Sanitárias</v>
       </c>
       <c r="O27" s="29" t="str">
-        <f t="shared" si="3"/>
-        <v>Banheira</v>
+        <f t="shared" si="10"/>
+        <v>Lavatório</v>
       </c>
       <c r="P27" s="51" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="Q27" s="29" t="str">
-        <f t="shared" si="20"/>
-        <v>Bañera</v>
+        <f t="shared" si="28"/>
+        <v>Lavabo</v>
       </c>
       <c r="R27" s="29" t="s">
         <v>9</v>
       </c>
       <c r="S27" s="29" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="T27" s="29" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="U27" s="29" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="25"/>
         <v>Peças.Sanitárias</v>
       </c>
       <c r="V27" s="29" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="W27" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-27</v>
       </c>
       <c r="X27" s="28" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="Y27" s="28" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="Z27" s="29" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="AA27" s="29" t="str">
-        <f t="shared" si="18"/>
-        <v>Bathtub</v>
-      </c>
-    </row>
-    <row r="28" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="26"/>
+        <v>Washbasin</v>
+      </c>
+    </row>
+    <row r="28" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="56">
         <v>28</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C28" s="41" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E28" s="41" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="F28" s="41" t="s">
-        <v>109</v>
+        <v>171</v>
       </c>
       <c r="G28" s="58" t="s">
         <v>9</v>
@@ -4861,79 +4936,79 @@
         <v>9</v>
       </c>
       <c r="L28" s="32" t="str">
-        <f t="shared" ref="L28" si="26">CONCATENATE("", C28)</f>
+        <f t="shared" ref="L28" si="29">CONCATENATE("", C28)</f>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M28" s="32" t="str">
-        <f t="shared" ref="M28" si="27">CONCATENATE("", D28)</f>
+        <f t="shared" ref="M28" si="30">CONCATENATE("", D28)</f>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N28" s="32" t="str">
-        <f t="shared" ref="N28" si="28">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E28),"."," ")," De "," de "))</f>
-        <v>Esgoto Coletores</v>
+        <f t="shared" ref="N28" si="31">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E28),"."," ")," De "," de "))</f>
+        <v>Peças Sanitárias</v>
       </c>
       <c r="O28" s="29" t="str">
-        <f t="shared" si="3"/>
-        <v>Ventilação.Esgoto</v>
+        <f t="shared" si="10"/>
+        <v>Cuba.Sanitária</v>
       </c>
       <c r="P28" s="51" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q28" s="51" t="s">
-        <v>158</v>
+        <v>179</v>
+      </c>
+      <c r="Q28" s="29" t="s">
+        <v>181</v>
       </c>
       <c r="R28" s="29" t="s">
         <v>9</v>
       </c>
       <c r="S28" s="29" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="T28" s="29" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="U28" s="29" t="str">
-        <f t="shared" ref="U28" si="29">SUBSTITUTE(E28, "_", " ")</f>
-        <v>Esgoto.Coletores</v>
+        <f t="shared" ref="U28" si="32">SUBSTITUTE(E28, "_", " ")</f>
+        <v>Peças.Sanitárias</v>
       </c>
       <c r="V28" s="29" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="W28" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-28</v>
       </c>
       <c r="X28" s="28" t="s">
-        <v>256</v>
+        <v>183</v>
       </c>
       <c r="Y28" s="28" t="s">
-        <v>257</v>
+        <v>184</v>
       </c>
       <c r="Z28" s="29" t="s">
-        <v>128</v>
+        <v>156</v>
       </c>
       <c r="AA28" s="29" t="str">
-        <f>_xlfn.TRANSLATE(P28,"pt","en")</f>
-        <v>Sewer Ventilation</v>
-      </c>
-    </row>
-    <row r="29" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" ref="AA28" si="33">_xlfn.TRANSLATE(P28,"pt","en")</f>
+        <v>Sanitary Bowl</v>
+      </c>
+    </row>
+    <row r="29" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="56">
         <v>29</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C29" s="41" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E29" s="41" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="F29" s="41" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="G29" s="58" t="s">
         <v>9</v>
@@ -4951,79 +5026,80 @@
         <v>9</v>
       </c>
       <c r="L29" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="22"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M29" s="32" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="23"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N29" s="32" t="str">
-        <f t="shared" si="2"/>
-        <v>Esgoto Coletores</v>
+        <f t="shared" si="24"/>
+        <v>Peças Sanitárias</v>
       </c>
       <c r="O29" s="29" t="str">
-        <f t="shared" si="3"/>
-        <v>Ralo.Seco</v>
+        <f t="shared" si="10"/>
+        <v>Banheira</v>
       </c>
       <c r="P29" s="51" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q29" s="29" t="s">
-        <v>121</v>
+        <v>173</v>
+      </c>
+      <c r="Q29" s="29" t="str">
+        <f t="shared" si="28"/>
+        <v>Bañera</v>
       </c>
       <c r="R29" s="29" t="s">
         <v>9</v>
       </c>
       <c r="S29" s="29" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="T29" s="29" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="U29" s="29" t="str">
-        <f t="shared" si="4"/>
-        <v>Esgoto.Coletores</v>
+        <f t="shared" si="25"/>
+        <v>Peças.Sanitárias</v>
       </c>
       <c r="V29" s="29" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="W29" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-29</v>
       </c>
       <c r="X29" s="28" t="s">
-        <v>256</v>
+        <v>183</v>
       </c>
       <c r="Y29" s="28" t="s">
-        <v>257</v>
+        <v>184</v>
       </c>
       <c r="Z29" s="29" t="s">
-        <v>128</v>
+        <v>156</v>
       </c>
       <c r="AA29" s="29" t="str">
-        <f t="shared" ref="AA29:AA39" si="30">_xlfn.TRANSLATE(P29,"pt","en")</f>
-        <v>Local Collector as a Dry Drain or Basin Valve</v>
-      </c>
-    </row>
-    <row r="30" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="26"/>
+        <v>Bathtub</v>
+      </c>
+    </row>
+    <row r="30" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="56">
         <v>30</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C30" s="41" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E30" s="41" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="F30" s="41" t="s">
-        <v>168</v>
+        <v>109</v>
       </c>
       <c r="G30" s="58" t="s">
         <v>9</v>
@@ -5041,79 +5117,79 @@
         <v>9</v>
       </c>
       <c r="L30" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="L30" si="34">CONCATENATE("", C30)</f>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M30" s="32" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="M30" si="35">CONCATENATE("", D30)</f>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N30" s="32" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="N30" si="36">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E30),"."," ")," De "," de "))</f>
         <v>Esgoto Coletores</v>
       </c>
       <c r="O30" s="29" t="str">
-        <f t="shared" si="3"/>
-        <v>Ralo.Sifonado</v>
+        <f t="shared" si="10"/>
+        <v>Ventilação.Esgoto</v>
       </c>
       <c r="P30" s="51" t="s">
-        <v>110</v>
-      </c>
-      <c r="Q30" s="29" t="s">
-        <v>122</v>
+        <v>150</v>
+      </c>
+      <c r="Q30" s="51" t="s">
+        <v>151</v>
       </c>
       <c r="R30" s="29" t="s">
         <v>9</v>
       </c>
       <c r="S30" s="29" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="T30" s="29" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="U30" s="29" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="U30" si="37">SUBSTITUTE(E30, "_", " ")</f>
         <v>Esgoto.Coletores</v>
       </c>
       <c r="V30" s="29" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="W30" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-30</v>
       </c>
       <c r="X30" s="28" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="Y30" s="28" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="Z30" s="29" t="s">
         <v>128</v>
       </c>
       <c r="AA30" s="29" t="str">
-        <f t="shared" si="30"/>
-        <v>Siphoned Collector as a Siphoned Drain</v>
-      </c>
-    </row>
-    <row r="31" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <f>_xlfn.TRANSLATE(P30,"pt","en")</f>
+        <v>Sewer Ventilation</v>
+      </c>
+    </row>
+    <row r="31" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="56">
         <v>31</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C31" s="41" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E31" s="41" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="F31" s="41" t="s">
-        <v>102</v>
+        <v>162</v>
       </c>
       <c r="G31" s="58" t="s">
         <v>9</v>
@@ -5131,79 +5207,79 @@
         <v>9</v>
       </c>
       <c r="L31" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="22"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M31" s="32" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="23"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N31" s="32" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="24"/>
         <v>Esgoto Coletores</v>
       </c>
       <c r="O31" s="29" t="str">
-        <f t="shared" si="3"/>
-        <v>Coletor.Andar</v>
+        <f t="shared" si="10"/>
+        <v>Ralo.Seco</v>
       </c>
       <c r="P31" s="51" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q31" s="29" t="s">
-        <v>246</v>
+        <v>121</v>
       </c>
       <c r="R31" s="29" t="s">
         <v>9</v>
       </c>
       <c r="S31" s="29" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="T31" s="29" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="U31" s="29" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="25"/>
         <v>Esgoto.Coletores</v>
       </c>
       <c r="V31" s="29" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="W31" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-31</v>
       </c>
       <c r="X31" s="28" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="Y31" s="28" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="Z31" s="29" t="s">
         <v>128</v>
       </c>
       <c r="AA31" s="29" t="str">
-        <f t="shared" si="30"/>
-        <v>Floor Horizontal Collection Branch</v>
-      </c>
-    </row>
-    <row r="32" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" ref="AA31:AA41" si="38">_xlfn.TRANSLATE(P31,"pt","en")</f>
+        <v>Local Collector as a Dry Drain or Basin Valve</v>
+      </c>
+    </row>
+    <row r="32" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="56">
         <v>32</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C32" s="41" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E32" s="41" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="F32" s="41" t="s">
-        <v>101</v>
+        <v>161</v>
       </c>
       <c r="G32" s="58" t="s">
         <v>9</v>
@@ -5221,79 +5297,79 @@
         <v>9</v>
       </c>
       <c r="L32" s="32" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="22"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M32" s="32" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="23"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N32" s="32" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="24"/>
         <v>Esgoto Coletores</v>
       </c>
       <c r="O32" s="29" t="str">
-        <f t="shared" si="3"/>
-        <v>Coletor.Predial</v>
+        <f t="shared" si="10"/>
+        <v>Ralo.Sifonado</v>
       </c>
       <c r="P32" s="51" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="Q32" s="29" t="s">
-        <v>247</v>
+        <v>122</v>
       </c>
       <c r="R32" s="29" t="s">
         <v>9</v>
       </c>
       <c r="S32" s="29" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="T32" s="29" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="U32" s="29" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="25"/>
         <v>Esgoto.Coletores</v>
       </c>
       <c r="V32" s="29" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="W32" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-32</v>
       </c>
       <c r="X32" s="28" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="Y32" s="28" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="Z32" s="29" t="s">
         <v>128</v>
       </c>
       <c r="AA32" s="29" t="str">
-        <f t="shared" si="30"/>
-        <v>Horizontal collection branch of the building</v>
-      </c>
-    </row>
-    <row r="33" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="38"/>
+        <v>Siphoned Collector as a Siphoned Drain</v>
+      </c>
+    </row>
+    <row r="33" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="56">
         <v>33</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C33" s="41" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E33" s="41" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="F33" s="41" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G33" s="58" t="s">
         <v>9</v>
@@ -5311,79 +5387,79 @@
         <v>9</v>
       </c>
       <c r="L33" s="32" t="str">
-        <f t="shared" ref="L33" si="31">CONCATENATE("", C33)</f>
+        <f t="shared" si="22"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M33" s="32" t="str">
-        <f t="shared" ref="M33" si="32">CONCATENATE("", D33)</f>
+        <f t="shared" si="23"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N33" s="32" t="str">
-        <f t="shared" ref="N33" si="33">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E33),"."," ")," De "," de "))</f>
+        <f t="shared" si="24"/>
         <v>Esgoto Coletores</v>
       </c>
       <c r="O33" s="29" t="str">
-        <f t="shared" si="3"/>
-        <v>Tubo.de.Queda</v>
+        <f t="shared" si="10"/>
+        <v>Coletor.Andar</v>
       </c>
       <c r="P33" s="51" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="Q33" s="29" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="R33" s="29" t="s">
         <v>9</v>
       </c>
       <c r="S33" s="29" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="T33" s="29" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="U33" s="29" t="str">
-        <f t="shared" ref="U33" si="34">SUBSTITUTE(E33, "_", " ")</f>
+        <f t="shared" si="25"/>
         <v>Esgoto.Coletores</v>
       </c>
       <c r="V33" s="29" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="W33" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-33</v>
       </c>
       <c r="X33" s="28" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="Y33" s="28" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="Z33" s="29" t="s">
         <v>128</v>
       </c>
       <c r="AA33" s="29" t="str">
-        <f t="shared" si="30"/>
-        <v>Downpipe</v>
-      </c>
-    </row>
-    <row r="34" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="38"/>
+        <v>Floor Horizontal Collection Branch</v>
+      </c>
+    </row>
+    <row r="34" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="56">
         <v>34</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C34" s="41" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E34" s="41" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="F34" s="41" t="s">
-        <v>219</v>
+        <v>101</v>
       </c>
       <c r="G34" s="58" t="s">
         <v>9</v>
@@ -5401,79 +5477,79 @@
         <v>9</v>
       </c>
       <c r="L34" s="32" t="str">
-        <f t="shared" ref="L34" si="35">CONCATENATE("", C34)</f>
+        <f t="shared" si="22"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M34" s="32" t="str">
-        <f t="shared" ref="M34" si="36">CONCATENATE("", D34)</f>
+        <f t="shared" si="23"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N34" s="32" t="str">
-        <f t="shared" ref="N34" si="37">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E34),"."," ")," De "," de "))</f>
+        <f t="shared" si="24"/>
         <v>Esgoto Coletores</v>
       </c>
       <c r="O34" s="29" t="str">
-        <f t="shared" si="3"/>
-        <v>Fecho.Hidráulico</v>
+        <f t="shared" si="10"/>
+        <v>Coletor.Predial</v>
       </c>
       <c r="P34" s="51" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="Q34" s="29" t="s">
-        <v>123</v>
+        <v>240</v>
       </c>
       <c r="R34" s="29" t="s">
         <v>9</v>
       </c>
       <c r="S34" s="29" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="T34" s="29" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="U34" s="29" t="str">
-        <f t="shared" ref="U34" si="38">SUBSTITUTE(E34, "_", " ")</f>
+        <f t="shared" si="25"/>
         <v>Esgoto.Coletores</v>
       </c>
       <c r="V34" s="29" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="W34" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-34</v>
       </c>
       <c r="X34" s="28" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="Y34" s="28" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="Z34" s="29" t="s">
         <v>128</v>
       </c>
       <c r="AA34" s="29" t="str">
-        <f t="shared" si="30"/>
-        <v>Siphons</v>
-      </c>
-    </row>
-    <row r="35" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="38"/>
+        <v>Horizontal collection branch of the building</v>
+      </c>
+    </row>
+    <row r="35" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="56">
         <v>35</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C35" s="41" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E35" s="41" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="F35" s="41" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="G35" s="58" t="s">
         <v>9</v>
@@ -5491,79 +5567,79 @@
         <v>9</v>
       </c>
       <c r="L35" s="32" t="str">
-        <f t="shared" ref="L35:L39" si="39">CONCATENATE("", C35)</f>
+        <f t="shared" ref="L35" si="39">CONCATENATE("", C35)</f>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M35" s="32" t="str">
-        <f t="shared" ref="M35:M39" si="40">CONCATENATE("", D35)</f>
+        <f t="shared" ref="M35" si="40">CONCATENATE("", D35)</f>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N35" s="32" t="str">
-        <f t="shared" ref="N35:N39" si="41">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E35),"."," ")," De "," de "))</f>
-        <v>Esgoto Visitas</v>
+        <f t="shared" ref="N35" si="41">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E35),"."," ")," De "," de "))</f>
+        <v>Esgoto Coletores</v>
       </c>
       <c r="O35" s="29" t="str">
-        <f t="shared" si="3"/>
-        <v>Caixa.de.Areia</v>
+        <f t="shared" si="10"/>
+        <v>Tubo.de.Queda</v>
       </c>
       <c r="P35" s="51" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="Q35" s="29" t="s">
-        <v>124</v>
+        <v>241</v>
       </c>
       <c r="R35" s="29" t="s">
         <v>9</v>
       </c>
       <c r="S35" s="29" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="T35" s="29" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="U35" s="29" t="str">
-        <f t="shared" ref="U35:U39" si="42">SUBSTITUTE(E35, "_", " ")</f>
-        <v>Esgoto.Visitas</v>
+        <f t="shared" ref="U35" si="42">SUBSTITUTE(E35, "_", " ")</f>
+        <v>Esgoto.Coletores</v>
       </c>
       <c r="V35" s="29" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="W35" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-35</v>
       </c>
       <c r="X35" s="28" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="Y35" s="28" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="Z35" s="29" t="s">
         <v>128</v>
       </c>
       <c r="AA35" s="29" t="str">
-        <f t="shared" si="30"/>
-        <v>Sandboxes</v>
-      </c>
-    </row>
-    <row r="36" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="38"/>
+        <v>Downpipe</v>
+      </c>
+    </row>
+    <row r="36" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="56">
         <v>36</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C36" s="41" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E36" s="41" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="F36" s="41" t="s">
-        <v>106</v>
+        <v>212</v>
       </c>
       <c r="G36" s="58" t="s">
         <v>9</v>
@@ -5581,79 +5657,79 @@
         <v>9</v>
       </c>
       <c r="L36" s="32" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" ref="L36" si="43">CONCATENATE("", C36)</f>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M36" s="32" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" ref="M36" si="44">CONCATENATE("", D36)</f>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N36" s="32" t="str">
-        <f t="shared" si="41"/>
-        <v>Esgoto Visitas</v>
+        <f t="shared" ref="N36" si="45">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E36),"."," ")," De "," de "))</f>
+        <v>Esgoto Coletores</v>
       </c>
       <c r="O36" s="29" t="str">
-        <f t="shared" si="3"/>
-        <v>Caixa.de.Gordura</v>
+        <f t="shared" si="10"/>
+        <v>Fecho.Hidráulico</v>
       </c>
       <c r="P36" s="51" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="Q36" s="29" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="R36" s="29" t="s">
         <v>9</v>
       </c>
       <c r="S36" s="29" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="T36" s="29" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="U36" s="29" t="str">
-        <f t="shared" si="42"/>
-        <v>Esgoto.Visitas</v>
+        <f t="shared" ref="U36" si="46">SUBSTITUTE(E36, "_", " ")</f>
+        <v>Esgoto.Coletores</v>
       </c>
       <c r="V36" s="29" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="W36" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-36</v>
       </c>
       <c r="X36" s="28" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="Y36" s="28" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="Z36" s="29" t="s">
         <v>128</v>
       </c>
       <c r="AA36" s="29" t="str">
-        <f t="shared" si="30"/>
-        <v>Grease Traps</v>
-      </c>
-    </row>
-    <row r="37" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="38"/>
+        <v>Siphons</v>
+      </c>
+    </row>
+    <row r="37" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="56">
         <v>37</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C37" s="41" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E37" s="41" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F37" s="41" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="G37" s="58" t="s">
         <v>9</v>
@@ -5671,79 +5747,79 @@
         <v>9</v>
       </c>
       <c r="L37" s="32" t="str">
-        <f t="shared" ref="L37:L38" si="43">CONCATENATE("", C37)</f>
+        <f t="shared" ref="L37:L41" si="47">CONCATENATE("", C37)</f>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M37" s="32" t="str">
-        <f t="shared" ref="M37:M38" si="44">CONCATENATE("", D37)</f>
+        <f t="shared" ref="M37:M41" si="48">CONCATENATE("", D37)</f>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N37" s="32" t="str">
-        <f t="shared" ref="N37:N38" si="45">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E37),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N37:N41" si="49">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E37),"."," ")," De "," de "))</f>
         <v>Esgoto Visitas</v>
       </c>
       <c r="O37" s="29" t="str">
-        <f t="shared" si="3"/>
-        <v>Caixa.de.Inspeção</v>
+        <f t="shared" si="10"/>
+        <v>Caixa.de.Areia</v>
       </c>
       <c r="P37" s="51" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="Q37" s="29" t="s">
-        <v>245</v>
+        <v>124</v>
       </c>
       <c r="R37" s="29" t="s">
         <v>9</v>
       </c>
       <c r="S37" s="29" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="T37" s="29" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="U37" s="29" t="str">
-        <f t="shared" ref="U37:U38" si="46">SUBSTITUTE(E37, "_", " ")</f>
+        <f t="shared" ref="U37:U41" si="50">SUBSTITUTE(E37, "_", " ")</f>
         <v>Esgoto.Visitas</v>
       </c>
       <c r="V37" s="29" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="W37" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-37</v>
       </c>
       <c r="X37" s="28" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="Y37" s="28" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="Z37" s="29" t="s">
         <v>128</v>
       </c>
       <c r="AA37" s="29" t="str">
-        <f t="shared" si="30"/>
-        <v>Manholes</v>
-      </c>
-    </row>
-    <row r="38" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="38"/>
+        <v>Sandboxes</v>
+      </c>
+    </row>
+    <row r="38" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="56">
         <v>38</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C38" s="41" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E38" s="41" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F38" s="41" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G38" s="58" t="s">
         <v>9</v>
@@ -5761,79 +5837,79 @@
         <v>9</v>
       </c>
       <c r="L38" s="32" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="47"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M38" s="32" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N38" s="32" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="49"/>
         <v>Esgoto Visitas</v>
       </c>
       <c r="O38" s="29" t="str">
-        <f t="shared" si="3"/>
-        <v>Caixa.Sifonada</v>
+        <f t="shared" si="10"/>
+        <v>Caixa.de.Gordura</v>
       </c>
       <c r="P38" s="51" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="Q38" s="29" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="R38" s="29" t="s">
         <v>9</v>
       </c>
       <c r="S38" s="29" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="T38" s="29" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="U38" s="29" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="50"/>
         <v>Esgoto.Visitas</v>
       </c>
       <c r="V38" s="29" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="W38" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-38</v>
       </c>
       <c r="X38" s="28" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="Y38" s="28" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="Z38" s="29" t="s">
         <v>128</v>
       </c>
       <c r="AA38" s="29" t="str">
-        <f t="shared" si="30"/>
-        <v>Siphon Boxes</v>
-      </c>
-    </row>
-    <row r="39" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="38"/>
+        <v>Grease Traps</v>
+      </c>
+    </row>
+    <row r="39" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="56">
         <v>39</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C39" s="41" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E39" s="41" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="F39" s="41" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G39" s="58" t="s">
         <v>9</v>
@@ -5851,79 +5927,79 @@
         <v>9</v>
       </c>
       <c r="L39" s="32" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" ref="L39:L40" si="51">CONCATENATE("", C39)</f>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M39" s="32" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" ref="M39:M40" si="52">CONCATENATE("", D39)</f>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N39" s="32" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" ref="N39:N40" si="53">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E39),"."," ")," De "," de "))</f>
         <v>Esgoto Visitas</v>
       </c>
       <c r="O39" s="29" t="str">
-        <f t="shared" si="3"/>
-        <v>Poço.de.Visita</v>
+        <f t="shared" si="10"/>
+        <v>Caixa.de.Inspeção</v>
       </c>
       <c r="P39" s="51" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q39" s="29" t="s">
-        <v>127</v>
+        <v>238</v>
       </c>
       <c r="R39" s="29" t="s">
         <v>9</v>
       </c>
       <c r="S39" s="29" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="T39" s="29" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="U39" s="29" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" ref="U39:U40" si="54">SUBSTITUTE(E39, "_", " ")</f>
         <v>Esgoto.Visitas</v>
       </c>
       <c r="V39" s="29" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="W39" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-39</v>
       </c>
       <c r="X39" s="28" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="Y39" s="28" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="Z39" s="29" t="s">
         <v>128</v>
       </c>
       <c r="AA39" s="29" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>Manholes</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="56">
         <v>40</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C40" s="41" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E40" s="41" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="F40" s="41" t="s">
-        <v>164</v>
+        <v>108</v>
       </c>
       <c r="G40" s="58" t="s">
         <v>9</v>
@@ -5941,124 +6017,765 @@
         <v>9</v>
       </c>
       <c r="L40" s="32" t="str">
-        <f t="shared" ref="L40" si="47">CONCATENATE("", C40)</f>
+        <f t="shared" si="51"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M40" s="32" t="str">
-        <f t="shared" ref="M40" si="48">CONCATENATE("", D40)</f>
+        <f t="shared" si="52"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N40" s="32" t="str">
-        <f t="shared" ref="N40" si="49">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E40),"."," ")," De "," de "))</f>
-        <v>Esgoto Acessórios</v>
+        <f t="shared" si="53"/>
+        <v>Esgoto Visitas</v>
       </c>
       <c r="O40" s="29" t="str">
-        <f t="shared" si="3"/>
-        <v>Acessório.Sanitário</v>
+        <f t="shared" si="10"/>
+        <v>Caixa.Sifonada</v>
       </c>
       <c r="P40" s="51" t="s">
-        <v>232</v>
-      </c>
-      <c r="Q40" s="51" t="s">
-        <v>165</v>
+        <v>119</v>
+      </c>
+      <c r="Q40" s="29" t="s">
+        <v>126</v>
       </c>
       <c r="R40" s="29" t="s">
         <v>9</v>
       </c>
       <c r="S40" s="29" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="T40" s="29" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="U40" s="29" t="str">
-        <f t="shared" ref="U40" si="50">SUBSTITUTE(E40, "_", " ")</f>
-        <v>Esgoto.Acessórios</v>
+        <f t="shared" si="54"/>
+        <v>Esgoto.Visitas</v>
       </c>
       <c r="V40" s="29" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="W40" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-40</v>
       </c>
       <c r="X40" s="28" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="Y40" s="28" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="Z40" s="29" t="s">
         <v>128</v>
       </c>
       <c r="AA40" s="29" t="str">
-        <f t="shared" ref="AA40" si="51">_xlfn.TRANSLATE(P40,"pt","en")</f>
+        <f t="shared" si="38"/>
+        <v>Siphon Boxes</v>
+      </c>
+    </row>
+    <row r="41" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A41" s="56">
+        <v>41</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="C41" s="41" t="s">
+        <v>246</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="E41" s="41" t="s">
+        <v>218</v>
+      </c>
+      <c r="F41" s="41" t="s">
+        <v>105</v>
+      </c>
+      <c r="G41" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H41" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I41" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J41" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K41" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="L41" s="32" t="str">
+        <f t="shared" si="47"/>
+        <v>Sistemas.Prediais</v>
+      </c>
+      <c r="M41" s="32" t="str">
+        <f t="shared" si="48"/>
+        <v>Elementos.Hidráulicos</v>
+      </c>
+      <c r="N41" s="32" t="str">
+        <f t="shared" si="49"/>
+        <v>Esgoto Visitas</v>
+      </c>
+      <c r="O41" s="29" t="str">
+        <f t="shared" si="10"/>
+        <v>Poço.de.Visita</v>
+      </c>
+      <c r="P41" s="51" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q41" s="29" t="s">
+        <v>127</v>
+      </c>
+      <c r="R41" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="S41" s="29" t="s">
+        <v>153</v>
+      </c>
+      <c r="T41" s="29" t="s">
+        <v>152</v>
+      </c>
+      <c r="U41" s="29" t="str">
+        <f t="shared" si="50"/>
+        <v>Esgoto.Visitas</v>
+      </c>
+      <c r="V41" s="29" t="s">
+        <v>154</v>
+      </c>
+      <c r="W41" s="57" t="str">
+        <f t="shared" si="5"/>
+        <v>Key-HIDR-41</v>
+      </c>
+      <c r="X41" s="28" t="s">
+        <v>249</v>
+      </c>
+      <c r="Y41" s="28" t="s">
+        <v>250</v>
+      </c>
+      <c r="Z41" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA41" s="29" t="str">
+        <f t="shared" si="38"/>
+        <v>Manholes</v>
+      </c>
+    </row>
+    <row r="42" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A42" s="56">
+        <v>42</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="C42" s="41" t="s">
+        <v>246</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="E42" s="41" t="s">
+        <v>219</v>
+      </c>
+      <c r="F42" s="41" t="s">
+        <v>157</v>
+      </c>
+      <c r="G42" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H42" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I42" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J42" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K42" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="L42" s="32" t="str">
+        <f t="shared" ref="L42" si="55">CONCATENATE("", C42)</f>
+        <v>Sistemas.Prediais</v>
+      </c>
+      <c r="M42" s="32" t="str">
+        <f t="shared" ref="M42" si="56">CONCATENATE("", D42)</f>
+        <v>Elementos.Hidráulicos</v>
+      </c>
+      <c r="N42" s="32" t="str">
+        <f t="shared" ref="N42" si="57">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E42),"."," ")," De "," de "))</f>
+        <v>Esgoto Acessórios</v>
+      </c>
+      <c r="O42" s="29" t="str">
+        <f t="shared" si="10"/>
+        <v>Acessório.Sanitário</v>
+      </c>
+      <c r="P42" s="51" t="s">
+        <v>225</v>
+      </c>
+      <c r="Q42" s="51" t="s">
+        <v>158</v>
+      </c>
+      <c r="R42" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="S42" s="29" t="s">
+        <v>153</v>
+      </c>
+      <c r="T42" s="29" t="s">
+        <v>152</v>
+      </c>
+      <c r="U42" s="29" t="str">
+        <f t="shared" ref="U42" si="58">SUBSTITUTE(E42, "_", " ")</f>
+        <v>Esgoto.Acessórios</v>
+      </c>
+      <c r="V42" s="29" t="s">
+        <v>154</v>
+      </c>
+      <c r="W42" s="57" t="str">
+        <f t="shared" si="5"/>
+        <v>Key-HIDR-42</v>
+      </c>
+      <c r="X42" s="28" t="s">
+        <v>237</v>
+      </c>
+      <c r="Y42" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="Z42" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA42" s="29" t="str">
+        <f t="shared" ref="AA42" si="59">_xlfn.TRANSLATE(P42,"pt","en")</f>
         <v>Sanitary sewer system accessory like brackets, hooks, pedestals, etc.</v>
       </c>
     </row>
+    <row r="43" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A43" s="56">
+        <v>43</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="C43" s="41" t="s">
+        <v>272</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="E43" s="41" t="s">
+        <v>278</v>
+      </c>
+      <c r="F43" s="41" t="s">
+        <v>273</v>
+      </c>
+      <c r="G43" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H43" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I43" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J43" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K43" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="L43" s="32" t="str">
+        <f t="shared" ref="L43" si="60">CONCATENATE("", C43)</f>
+        <v>De.Tubulações</v>
+      </c>
+      <c r="M43" s="32" t="str">
+        <f t="shared" ref="M43" si="61">CONCATENATE("", D43)</f>
+        <v>Elementos.de.Instalações</v>
+      </c>
+      <c r="N43" s="32" t="str">
+        <f t="shared" ref="N43" si="62">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E43),"."," ")," De "," de "))</f>
+        <v>Instalação De</v>
+      </c>
+      <c r="O43" s="29" t="str">
+        <f t="shared" ref="O43:P43" si="63">IF(ISNUMBER(FIND("Ifc",F43)),CONCATENATE("Classe IFC:   ",F43),CONCATENATE("",F43))</f>
+        <v>Esgoto</v>
+      </c>
+      <c r="P43" s="51" t="s">
+        <v>281</v>
+      </c>
+      <c r="Q43" s="51" t="str">
+        <f>_xlfn.TRANSLATE(P43,"pt","es")</f>
+        <v>Instalación de alcantarillado</v>
+      </c>
+      <c r="R43" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="S43" s="29" t="s">
+        <v>153</v>
+      </c>
+      <c r="T43" s="29" t="s">
+        <v>152</v>
+      </c>
+      <c r="U43" s="29" t="str">
+        <f t="shared" ref="U43" si="64">SUBSTITUTE(E43, "_", " ")</f>
+        <v>Instalação.De</v>
+      </c>
+      <c r="V43" s="29" t="s">
+        <v>154</v>
+      </c>
+      <c r="W43" s="57" t="str">
+        <f t="shared" ref="W43" si="65">CONCATENATE("Key-HIDR-",A43)</f>
+        <v>Key-HIDR-43</v>
+      </c>
+      <c r="X43" s="28" t="s">
+        <v>249</v>
+      </c>
+      <c r="Y43" s="28" t="s">
+        <v>250</v>
+      </c>
+      <c r="Z43" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA43" s="29" t="str">
+        <f t="shared" ref="AA43" si="66">_xlfn.TRANSLATE(P43,"pt","en")</f>
+        <v>Sewer Installation</v>
+      </c>
+    </row>
+    <row r="44" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="56">
+        <v>44</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="C44" s="41" t="s">
+        <v>272</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="E44" s="41" t="s">
+        <v>278</v>
+      </c>
+      <c r="F44" s="41" t="s">
+        <v>274</v>
+      </c>
+      <c r="G44" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H44" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I44" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J44" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K44" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="L44" s="32" t="str">
+        <f t="shared" ref="L44:L46" si="67">CONCATENATE("", C44)</f>
+        <v>De.Tubulações</v>
+      </c>
+      <c r="M44" s="32" t="str">
+        <f t="shared" ref="M44:M46" si="68">CONCATENATE("", D44)</f>
+        <v>Elementos.de.Instalações</v>
+      </c>
+      <c r="N44" s="32" t="str">
+        <f t="shared" ref="N44:N46" si="69">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E44),"."," ")," De "," de "))</f>
+        <v>Instalação De</v>
+      </c>
+      <c r="O44" s="29" t="str">
+        <f t="shared" ref="O44:P46" si="70">IF(ISNUMBER(FIND("Ifc",F44)),CONCATENATE("Classe IFC:   ",F44),CONCATENATE("",F44))</f>
+        <v>AF</v>
+      </c>
+      <c r="P44" s="51" t="s">
+        <v>282</v>
+      </c>
+      <c r="Q44" s="51" t="str">
+        <f t="shared" ref="Q44:Q47" si="71">_xlfn.TRANSLATE(P44,"pt","es")</f>
+        <v>Instalación de agua fría</v>
+      </c>
+      <c r="R44" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="S44" s="29" t="s">
+        <v>153</v>
+      </c>
+      <c r="T44" s="29" t="s">
+        <v>152</v>
+      </c>
+      <c r="U44" s="29" t="str">
+        <f t="shared" ref="U44:U46" si="72">SUBSTITUTE(E44, "_", " ")</f>
+        <v>Instalação.De</v>
+      </c>
+      <c r="V44" s="29" t="s">
+        <v>154</v>
+      </c>
+      <c r="W44" s="57" t="str">
+        <f t="shared" ref="W44:W46" si="73">CONCATENATE("Key-HIDR-",A44)</f>
+        <v>Key-HIDR-44</v>
+      </c>
+      <c r="X44" s="28" t="s">
+        <v>249</v>
+      </c>
+      <c r="Y44" s="28" t="s">
+        <v>250</v>
+      </c>
+      <c r="Z44" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="AA44" s="29" t="str">
+        <f t="shared" ref="AA44:AA46" si="74">_xlfn.TRANSLATE(P44,"pt","en")</f>
+        <v>Cold water installation</v>
+      </c>
+    </row>
+    <row r="45" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A45" s="56">
+        <v>45</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="C45" s="41" t="s">
+        <v>272</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="E45" s="41" t="s">
+        <v>278</v>
+      </c>
+      <c r="F45" s="41" t="s">
+        <v>275</v>
+      </c>
+      <c r="G45" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H45" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I45" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J45" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K45" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="L45" s="32" t="str">
+        <f t="shared" si="67"/>
+        <v>De.Tubulações</v>
+      </c>
+      <c r="M45" s="32" t="str">
+        <f t="shared" si="68"/>
+        <v>Elementos.de.Instalações</v>
+      </c>
+      <c r="N45" s="32" t="str">
+        <f t="shared" si="69"/>
+        <v>Instalação De</v>
+      </c>
+      <c r="O45" s="29" t="str">
+        <f t="shared" si="70"/>
+        <v>AQ</v>
+      </c>
+      <c r="P45" s="51" t="s">
+        <v>283</v>
+      </c>
+      <c r="Q45" s="51" t="str">
+        <f t="shared" si="71"/>
+        <v>Instalación de agua caliente</v>
+      </c>
+      <c r="R45" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="S45" s="29" t="s">
+        <v>153</v>
+      </c>
+      <c r="T45" s="29" t="s">
+        <v>152</v>
+      </c>
+      <c r="U45" s="29" t="str">
+        <f t="shared" si="72"/>
+        <v>Instalação.De</v>
+      </c>
+      <c r="V45" s="29" t="s">
+        <v>154</v>
+      </c>
+      <c r="W45" s="57" t="str">
+        <f t="shared" si="73"/>
+        <v>Key-HIDR-45</v>
+      </c>
+      <c r="X45" s="28" t="s">
+        <v>249</v>
+      </c>
+      <c r="Y45" s="28" t="s">
+        <v>250</v>
+      </c>
+      <c r="Z45" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="AA45" s="29" t="str">
+        <f t="shared" si="74"/>
+        <v>Installation of hot water</v>
+      </c>
+    </row>
+    <row r="46" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A46" s="56">
+        <v>46</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="C46" s="41" t="s">
+        <v>272</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="E46" s="41" t="s">
+        <v>278</v>
+      </c>
+      <c r="F46" s="41" t="s">
+        <v>276</v>
+      </c>
+      <c r="G46" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H46" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I46" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J46" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K46" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="L46" s="32" t="str">
+        <f t="shared" si="67"/>
+        <v>De.Tubulações</v>
+      </c>
+      <c r="M46" s="32" t="str">
+        <f t="shared" si="68"/>
+        <v>Elementos.de.Instalações</v>
+      </c>
+      <c r="N46" s="32" t="str">
+        <f t="shared" si="69"/>
+        <v>Instalação De</v>
+      </c>
+      <c r="O46" s="29" t="str">
+        <f t="shared" si="70"/>
+        <v>Pluvial</v>
+      </c>
+      <c r="P46" s="51" t="s">
+        <v>284</v>
+      </c>
+      <c r="Q46" s="51" t="str">
+        <f t="shared" si="71"/>
+        <v>Instalación de agua de lluvia.</v>
+      </c>
+      <c r="R46" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="S46" s="29" t="s">
+        <v>153</v>
+      </c>
+      <c r="T46" s="29" t="s">
+        <v>152</v>
+      </c>
+      <c r="U46" s="29" t="str">
+        <f t="shared" si="72"/>
+        <v>Instalação.De</v>
+      </c>
+      <c r="V46" s="29" t="s">
+        <v>154</v>
+      </c>
+      <c r="W46" s="57" t="str">
+        <f t="shared" si="73"/>
+        <v>Key-HIDR-46</v>
+      </c>
+      <c r="X46" s="28" t="s">
+        <v>249</v>
+      </c>
+      <c r="Y46" s="28" t="s">
+        <v>250</v>
+      </c>
+      <c r="Z46" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA46" s="29" t="str">
+        <f t="shared" si="74"/>
+        <v>Rainwater installation.</v>
+      </c>
+    </row>
+    <row r="47" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A47" s="56">
+        <v>47</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="C47" s="41" t="s">
+        <v>272</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="E47" s="41" t="s">
+        <v>278</v>
+      </c>
+      <c r="F47" s="41" t="s">
+        <v>279</v>
+      </c>
+      <c r="G47" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H47" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I47" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J47" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K47" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="L47" s="32" t="str">
+        <f t="shared" ref="L47" si="75">CONCATENATE("", C47)</f>
+        <v>De.Tubulações</v>
+      </c>
+      <c r="M47" s="32" t="str">
+        <f t="shared" ref="M47" si="76">CONCATENATE("", D47)</f>
+        <v>Elementos.de.Instalações</v>
+      </c>
+      <c r="N47" s="32" t="str">
+        <f t="shared" ref="N47" si="77">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E47),"."," ")," De "," de "))</f>
+        <v>Instalação De</v>
+      </c>
+      <c r="O47" s="29" t="str">
+        <f t="shared" ref="O47:P47" si="78">IF(ISNUMBER(FIND("Ifc",F47)),CONCATENATE("Classe IFC:   ",F47),CONCATENATE("",F47))</f>
+        <v>Ventilação</v>
+      </c>
+      <c r="P47" s="51" t="s">
+        <v>280</v>
+      </c>
+      <c r="Q47" s="51" t="str">
+        <f t="shared" si="71"/>
+        <v>Ventilación de la instalación del desagüe.</v>
+      </c>
+      <c r="R47" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="S47" s="29" t="s">
+        <v>153</v>
+      </c>
+      <c r="T47" s="29" t="s">
+        <v>152</v>
+      </c>
+      <c r="U47" s="29" t="str">
+        <f t="shared" ref="U47" si="79">SUBSTITUTE(E47, "_", " ")</f>
+        <v>Instalação.De</v>
+      </c>
+      <c r="V47" s="29" t="s">
+        <v>154</v>
+      </c>
+      <c r="W47" s="57" t="str">
+        <f t="shared" ref="W47" si="80">CONCATENATE("Key-HIDR-",A47)</f>
+        <v>Key-HIDR-47</v>
+      </c>
+      <c r="X47" s="28" t="s">
+        <v>249</v>
+      </c>
+      <c r="Y47" s="28" t="s">
+        <v>250</v>
+      </c>
+      <c r="Z47" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA47" s="29" t="str">
+        <f t="shared" ref="AA47" si="81">_xlfn.TRANSLATE(P47,"pt","en")</f>
+        <v>Ventilation of the drain installation.</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AA931">
-    <sortCondition ref="F2:F931"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:AA933">
+    <sortCondition ref="F4:F933"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="AA2:AA40 A2:B40">
-    <cfRule type="cellIs" dxfId="26" priority="6" operator="equal">
+  <conditionalFormatting sqref="AA2:AA47 A2:B47">
+    <cfRule type="cellIs" dxfId="0" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="25" priority="1494"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="1496"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F1048576">
-    <cfRule type="duplicateValues" dxfId="24" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="24"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F11">
-    <cfRule type="duplicateValues" dxfId="23" priority="24"/>
+  <conditionalFormatting sqref="F13">
+    <cfRule type="duplicateValues" dxfId="25" priority="26"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F30">
-    <cfRule type="duplicateValues" dxfId="22" priority="44"/>
+  <conditionalFormatting sqref="F32">
+    <cfRule type="duplicateValues" dxfId="24" priority="46"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F33 F35:F1048576 F12:F28 F1:F10">
-    <cfRule type="duplicateValues" dxfId="21" priority="46"/>
+  <conditionalFormatting sqref="F35 F14:F30 F37:F1048576 F1:F12">
+    <cfRule type="duplicateValues" dxfId="23" priority="48"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F41:F1048576">
-    <cfRule type="duplicateValues" dxfId="20" priority="251"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="253"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="1466"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="1487"/>
+  <conditionalFormatting sqref="F48:F1048576">
+    <cfRule type="duplicateValues" dxfId="22" priority="253"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="255"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="1468"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="1489"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:O1 A1:D1 Q1:X1">
-    <cfRule type="cellIs" dxfId="16" priority="58" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="60" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P4">
-    <cfRule type="duplicateValues" dxfId="15" priority="29"/>
+  <conditionalFormatting sqref="P7:P12 P14:P23">
+    <cfRule type="duplicateValues" dxfId="17" priority="1509"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P5:P10 P12:P21">
-    <cfRule type="duplicateValues" dxfId="14" priority="1507"/>
+  <conditionalFormatting sqref="P24:P29">
+    <cfRule type="duplicateValues" dxfId="16" priority="29"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P22:P27">
-    <cfRule type="duplicateValues" dxfId="13" priority="27"/>
+  <conditionalFormatting sqref="P30">
+    <cfRule type="duplicateValues" dxfId="15" priority="1502"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P28">
-    <cfRule type="duplicateValues" dxfId="12" priority="1500"/>
+  <conditionalFormatting sqref="Q2:Q5">
+    <cfRule type="duplicateValues" dxfId="14" priority="30"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q4">
-    <cfRule type="duplicateValues" dxfId="11" priority="28"/>
+  <conditionalFormatting sqref="Q23">
+    <cfRule type="duplicateValues" dxfId="13" priority="32"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q21">
-    <cfRule type="duplicateValues" dxfId="10" priority="30"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q28">
-    <cfRule type="duplicateValues" dxfId="9" priority="1501"/>
+  <conditionalFormatting sqref="Q30">
+    <cfRule type="duplicateValues" dxfId="12" priority="1503"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z1:AA1">
-    <cfRule type="cellIs" dxfId="8" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="25" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="Q6">
+    <cfRule type="duplicateValues" dxfId="10" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P2:P6">
+    <cfRule type="duplicateValues" dxfId="1" priority="1521"/>
+  </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -6066,15 +6783,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" style="9" customWidth="1"/>
-    <col min="2" max="10" width="6.5703125" style="10" customWidth="1"/>
-    <col min="11" max="21" width="6.5703125" style="8" customWidth="1"/>
-    <col min="22" max="16384" width="11.140625" style="8"/>
+    <col min="1" max="1" width="2.84375" style="9" customWidth="1"/>
+    <col min="2" max="10" width="6.53515625" style="10" customWidth="1"/>
+    <col min="11" max="21" width="6.53515625" style="8" customWidth="1"/>
+    <col min="22" max="16384" width="11.15234375" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -6139,7 +6856,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -6206,7 +6923,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6222,30 +6939,30 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38CB0525-EDFB-44CB-9009-6752AEDD7340}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:S19"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.85546875" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.3046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.3046875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.69140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.84375" customWidth="1"/>
     <col min="6" max="6" width="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="60.140625" customWidth="1"/>
+    <col min="7" max="7" width="60.15234375" customWidth="1"/>
     <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.42578125" customWidth="1"/>
-    <col min="10" max="10" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.3828125" customWidth="1"/>
+    <col min="10" max="10" width="8.3046875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.84375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.3828125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="24" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="23.85546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.3828125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="23.84375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.69140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="19.69140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.3046875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.3828125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="14.7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="16" t="s">
         <v>10</v>
       </c>
@@ -6304,7 +7021,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="19">
         <v>1</v>
       </c>
@@ -6312,7 +7029,7 @@
         <v>96</v>
       </c>
       <c r="C2" s="41" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D2" s="49" t="s">
         <v>9</v>
@@ -6324,7 +7041,7 @@
         <v>77</v>
       </c>
       <c r="G2" s="22" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="H2" s="48" t="s">
         <v>9</v>
@@ -6363,15 +7080,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="19">
         <v>2</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="C3" s="41" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="D3" s="49" t="s">
         <v>82</v>
@@ -6383,7 +7100,7 @@
         <v>77</v>
       </c>
       <c r="G3" s="22" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="H3" s="48" t="s">
         <v>77</v>
@@ -6407,7 +7124,7 @@
         <v>9</v>
       </c>
       <c r="O3" s="23" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="P3" s="48" t="s">
         <v>9</v>
@@ -6422,15 +7139,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="19">
         <v>3</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="C4" s="41" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="D4" s="49" t="s">
         <v>82</v>
@@ -6442,7 +7159,7 @@
         <v>77</v>
       </c>
       <c r="G4" s="22" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="H4" s="48" t="s">
         <v>77</v>
@@ -6466,7 +7183,7 @@
         <v>9</v>
       </c>
       <c r="O4" s="23" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="P4" s="48" t="s">
         <v>9</v>
@@ -6481,15 +7198,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="19">
         <v>4</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="C5" s="41" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="D5" s="49" t="s">
         <v>82</v>
@@ -6501,7 +7218,7 @@
         <v>77</v>
       </c>
       <c r="G5" s="22" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="H5" s="48" t="s">
         <v>77</v>
@@ -6525,7 +7242,7 @@
         <v>9</v>
       </c>
       <c r="O5" s="23" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="P5" s="48" t="s">
         <v>9</v>
@@ -6540,27 +7257,27 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="19">
         <v>5</v>
       </c>
       <c r="B6" s="46" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="C6" s="41" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="D6" s="49" t="s">
         <v>131</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="F6" s="21" t="s">
         <v>77</v>
       </c>
       <c r="G6" s="22" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="H6" s="48" t="s">
         <v>9</v>
@@ -6569,13 +7286,13 @@
         <v>9</v>
       </c>
       <c r="J6" s="48" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="K6" s="23" t="s">
         <v>129</v>
       </c>
       <c r="L6" s="48" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="M6" s="23" t="s">
         <v>98</v>
@@ -6584,13 +7301,13 @@
         <v>100</v>
       </c>
       <c r="O6" s="23" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="P6" s="48" t="s">
         <v>99</v>
       </c>
       <c r="Q6" s="23" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="R6" s="48" t="s">
         <v>97</v>
@@ -6599,27 +7316,27 @@
         <v>130</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="19">
         <v>6</v>
       </c>
       <c r="B7" s="46" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="C7" s="41" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="D7" s="49" t="s">
         <v>131</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="F7" s="21" t="s">
         <v>77</v>
       </c>
       <c r="G7" s="22" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="H7" s="48" t="s">
         <v>9</v>
@@ -6628,13 +7345,13 @@
         <v>9</v>
       </c>
       <c r="J7" s="48" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="K7" s="23" t="s">
         <v>129</v>
       </c>
       <c r="L7" s="48" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="M7" s="23" t="s">
         <v>98</v>
@@ -6643,13 +7360,13 @@
         <v>100</v>
       </c>
       <c r="O7" s="23" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="P7" s="48" t="s">
         <v>99</v>
       </c>
       <c r="Q7" s="23" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="R7" s="48" t="s">
         <v>97</v>
@@ -6658,27 +7375,27 @@
         <v>130</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="19">
         <v>7</v>
       </c>
       <c r="B8" s="46" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="C8" s="41" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="D8" s="49" t="s">
         <v>131</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="F8" s="21" t="s">
         <v>77</v>
       </c>
       <c r="G8" s="22" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="H8" s="48" t="s">
         <v>9</v>
@@ -6687,13 +7404,13 @@
         <v>9</v>
       </c>
       <c r="J8" s="48" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="K8" s="23" t="s">
         <v>129</v>
       </c>
       <c r="L8" s="48" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="M8" s="23" t="s">
         <v>98</v>
@@ -6702,42 +7419,42 @@
         <v>100</v>
       </c>
       <c r="O8" s="23" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="P8" s="48" t="s">
         <v>99</v>
       </c>
       <c r="Q8" s="23" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="R8" s="48" t="s">
         <v>97</v>
       </c>
       <c r="S8" s="23" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="19">
         <v>8</v>
       </c>
       <c r="B9" s="46" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="C9" s="41" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="D9" s="49" t="s">
         <v>131</v>
       </c>
       <c r="E9" s="33" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="F9" s="21" t="s">
         <v>77</v>
       </c>
       <c r="G9" s="22" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="H9" s="48" t="s">
         <v>9</v>
@@ -6746,13 +7463,13 @@
         <v>9</v>
       </c>
       <c r="J9" s="48" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="K9" s="23" t="s">
         <v>129</v>
       </c>
       <c r="L9" s="48" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="M9" s="23" t="s">
         <v>98</v>
@@ -6761,42 +7478,42 @@
         <v>100</v>
       </c>
       <c r="O9" s="23" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="P9" s="48" t="s">
         <v>99</v>
       </c>
       <c r="Q9" s="23" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="R9" s="48" t="s">
         <v>97</v>
       </c>
       <c r="S9" s="23" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="19">
         <v>9</v>
       </c>
       <c r="B10" s="46" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="C10" s="41" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="D10" s="49" t="s">
         <v>131</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="F10" s="21" t="s">
         <v>77</v>
       </c>
       <c r="G10" s="22" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="H10" s="48" t="s">
         <v>9</v>
@@ -6805,13 +7522,13 @@
         <v>9</v>
       </c>
       <c r="J10" s="48" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="K10" s="23" t="s">
         <v>129</v>
       </c>
       <c r="L10" s="48" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="M10" s="23" t="s">
         <v>98</v>
@@ -6820,42 +7537,42 @@
         <v>100</v>
       </c>
       <c r="O10" s="23" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="P10" s="48" t="s">
         <v>99</v>
       </c>
       <c r="Q10" s="23" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="R10" s="48" t="s">
         <v>97</v>
       </c>
       <c r="S10" s="23" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="19">
         <v>10</v>
       </c>
       <c r="B11" s="46" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="C11" s="41" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="D11" s="49" t="s">
         <v>131</v>
       </c>
       <c r="E11" s="33" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="F11" s="21" t="s">
         <v>77</v>
       </c>
       <c r="G11" s="22" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="H11" s="48" t="s">
         <v>9</v>
@@ -6864,13 +7581,13 @@
         <v>9</v>
       </c>
       <c r="J11" s="48" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="K11" s="23" t="s">
         <v>129</v>
       </c>
       <c r="L11" s="48" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="M11" s="23" t="s">
         <v>98</v>
@@ -6879,42 +7596,42 @@
         <v>100</v>
       </c>
       <c r="O11" s="23" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="P11" s="48" t="s">
         <v>99</v>
       </c>
       <c r="Q11" s="23" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="R11" s="48" t="s">
         <v>97</v>
       </c>
       <c r="S11" s="23" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="19">
         <v>11</v>
       </c>
       <c r="B12" s="46" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="C12" s="41" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="D12" s="49" t="s">
         <v>131</v>
       </c>
       <c r="E12" s="33" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="F12" s="21" t="s">
         <v>77</v>
       </c>
       <c r="G12" s="22" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="H12" s="48" t="s">
         <v>9</v>
@@ -6923,13 +7640,13 @@
         <v>9</v>
       </c>
       <c r="J12" s="48" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="K12" s="23" t="s">
         <v>129</v>
       </c>
       <c r="L12" s="48" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="M12" s="23" t="s">
         <v>98</v>
@@ -6938,42 +7655,42 @@
         <v>100</v>
       </c>
       <c r="O12" s="23" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="P12" s="48" t="s">
         <v>99</v>
       </c>
       <c r="Q12" s="23" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="R12" s="48" t="s">
         <v>97</v>
       </c>
       <c r="S12" s="23" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="19">
         <v>12</v>
       </c>
       <c r="B13" s="46" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="C13" s="41" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="D13" s="49" t="s">
         <v>131</v>
       </c>
       <c r="E13" s="33" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="F13" s="21" t="s">
         <v>77</v>
       </c>
       <c r="G13" s="22" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="H13" s="48" t="s">
         <v>9</v>
@@ -6982,13 +7699,13 @@
         <v>9</v>
       </c>
       <c r="J13" s="48" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="K13" s="23" t="s">
         <v>129</v>
       </c>
       <c r="L13" s="48" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="M13" s="23" t="s">
         <v>98</v>
@@ -6997,42 +7714,42 @@
         <v>100</v>
       </c>
       <c r="O13" s="23" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="P13" s="48" t="s">
         <v>99</v>
       </c>
       <c r="Q13" s="23" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="R13" s="48" t="s">
         <v>97</v>
       </c>
       <c r="S13" s="23" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="19">
         <v>13</v>
       </c>
       <c r="B14" s="46" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="C14" s="41" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="D14" s="49" t="s">
         <v>131</v>
       </c>
       <c r="E14" s="33" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="F14" s="21" t="s">
         <v>77</v>
       </c>
       <c r="G14" s="22" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="H14" s="48" t="s">
         <v>9</v>
@@ -7041,13 +7758,13 @@
         <v>9</v>
       </c>
       <c r="J14" s="48" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="K14" s="23" t="s">
         <v>129</v>
       </c>
       <c r="L14" s="48" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="M14" s="23" t="s">
         <v>98</v>
@@ -7056,42 +7773,42 @@
         <v>100</v>
       </c>
       <c r="O14" s="23" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="P14" s="48" t="s">
         <v>99</v>
       </c>
       <c r="Q14" s="23" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="R14" s="48" t="s">
         <v>97</v>
       </c>
       <c r="S14" s="23" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="19">
         <v>14</v>
       </c>
       <c r="B15" s="46" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="C15" s="41" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="D15" s="49" t="s">
         <v>131</v>
       </c>
       <c r="E15" s="33" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="F15" s="21" t="s">
         <v>77</v>
       </c>
       <c r="G15" s="22" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="H15" s="48" t="s">
         <v>9</v>
@@ -7100,13 +7817,13 @@
         <v>9</v>
       </c>
       <c r="J15" s="48" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="K15" s="23" t="s">
         <v>129</v>
       </c>
       <c r="L15" s="48" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="M15" s="23" t="s">
         <v>98</v>
@@ -7115,42 +7832,42 @@
         <v>100</v>
       </c>
       <c r="O15" s="23" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="P15" s="48" t="s">
         <v>99</v>
       </c>
       <c r="Q15" s="23" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="R15" s="48" t="s">
         <v>97</v>
       </c>
       <c r="S15" s="23" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="19">
         <v>15</v>
       </c>
       <c r="B16" s="46" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="C16" s="41" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="D16" s="49" t="s">
         <v>131</v>
       </c>
       <c r="E16" s="33" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="F16" s="21" t="s">
         <v>77</v>
       </c>
       <c r="G16" s="22" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="H16" s="48" t="s">
         <v>9</v>
@@ -7159,13 +7876,13 @@
         <v>9</v>
       </c>
       <c r="J16" s="48" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="K16" s="23" t="s">
         <v>129</v>
       </c>
       <c r="L16" s="48" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="M16" s="23" t="s">
         <v>98</v>
@@ -7174,42 +7891,42 @@
         <v>100</v>
       </c>
       <c r="O16" s="23" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="P16" s="48" t="s">
         <v>99</v>
       </c>
       <c r="Q16" s="23" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="R16" s="48" t="s">
         <v>97</v>
       </c>
       <c r="S16" s="23" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="19">
         <v>16</v>
       </c>
       <c r="B17" s="46" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="C17" s="41" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="D17" s="49" t="s">
         <v>131</v>
       </c>
       <c r="E17" s="33" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="F17" s="21" t="s">
         <v>77</v>
       </c>
       <c r="G17" s="22" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="H17" s="48" t="s">
         <v>9</v>
@@ -7218,13 +7935,13 @@
         <v>9</v>
       </c>
       <c r="J17" s="48" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="K17" s="23" t="s">
         <v>129</v>
       </c>
       <c r="L17" s="48" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="M17" s="23" t="s">
         <v>98</v>
@@ -7233,42 +7950,42 @@
         <v>100</v>
       </c>
       <c r="O17" s="23" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="P17" s="48" t="s">
         <v>99</v>
       </c>
       <c r="Q17" s="23" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="R17" s="48" t="s">
         <v>97</v>
       </c>
       <c r="S17" s="23" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="19">
         <v>17</v>
       </c>
       <c r="B18" s="46" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="C18" s="41" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="D18" s="49" t="s">
         <v>131</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="F18" s="21" t="s">
         <v>77</v>
       </c>
       <c r="G18" s="22" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="H18" s="48" t="s">
         <v>9</v>
@@ -7277,13 +7994,13 @@
         <v>9</v>
       </c>
       <c r="J18" s="48" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="K18" s="23" t="s">
         <v>129</v>
       </c>
       <c r="L18" s="48" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="M18" s="23" t="s">
         <v>98</v>
@@ -7292,42 +8009,42 @@
         <v>100</v>
       </c>
       <c r="O18" s="23" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="P18" s="48" t="s">
         <v>99</v>
       </c>
       <c r="Q18" s="23" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="R18" s="48" t="s">
         <v>97</v>
       </c>
       <c r="S18" s="23" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="19">
         <v>18</v>
       </c>
       <c r="B19" s="46" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="C19" s="41" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="D19" s="49" t="s">
         <v>131</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="F19" s="21" t="s">
         <v>77</v>
       </c>
       <c r="G19" s="22" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="H19" s="48" t="s">
         <v>9</v>
@@ -7336,13 +8053,13 @@
         <v>9</v>
       </c>
       <c r="J19" s="48" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="K19" s="23" t="s">
         <v>129</v>
       </c>
       <c r="L19" s="48" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="M19" s="23" t="s">
         <v>98</v>
@@ -7351,25 +8068,25 @@
         <v>100</v>
       </c>
       <c r="O19" s="23" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="P19" s="48" t="s">
         <v>99</v>
       </c>
       <c r="Q19" s="23" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="R19" s="48" t="s">
         <v>97</v>
       </c>
       <c r="S19" s="23" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C3:C5">
-    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7379,15 +8096,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5FE5EC8-1387-4A67-960C-C64BD1326958}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.140625" style="25" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" style="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" style="24" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.85546875" style="24" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.15234375" style="25" customWidth="1"/>
+    <col min="2" max="2" width="5.84375" style="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.3046875" style="24" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.84375" style="24" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="30">
         <v>0</v>
       </c>
@@ -7410,7 +8127,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="31">
         <v>2</v>
       </c>
@@ -7439,22 +8156,22 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:G1 B3:G1048576">
-    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="7" priority="5" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" dxfId="4" priority="1449"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="1450"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="1449"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="1450"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 A1:B1">
-    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 B1">
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:G2">
-    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",B2)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/SIS/Ontologia_Hidrossanitaria.xlsx
+++ b/Versão5/SIS/Ontologia_Hidrossanitaria.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\SIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C74E98C-D129-4C8E-BB18-D50654DBD375}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB479118-CACE-4A09-891C-2E29A7E6996C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1346" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1505" uniqueCount="343">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -321,12 +321,6 @@
     <t>é.dentro.de</t>
   </si>
   <si>
-    <t>CategoriaRvt</t>
-  </si>
-  <si>
-    <t>ClasseIfc</t>
-  </si>
-  <si>
     <t>ABNT</t>
   </si>
   <si>
@@ -927,6 +921,186 @@
   </si>
   <si>
     <t>Instalação de águas pluviais.</t>
+  </si>
+  <si>
+    <t>Mezclador</t>
+  </si>
+  <si>
+    <t>Accesorios para sistemas de agua como soportes, ganchos, pedestales, etc.</t>
+  </si>
+  <si>
+    <t>Cisterna intermedia</t>
+  </si>
+  <si>
+    <t>Tubería de agua fría</t>
+  </si>
+  <si>
+    <t>Caldera</t>
+  </si>
+  <si>
+    <t>Tubería de agua caliente</t>
+  </si>
+  <si>
+    <t>Bidé</t>
+  </si>
+  <si>
+    <t>Lavabo</t>
+  </si>
+  <si>
+    <t>Bañera</t>
+  </si>
+  <si>
+    <t>Instalación de alcantarillado</t>
+  </si>
+  <si>
+    <t>Instalación de agua fría</t>
+  </si>
+  <si>
+    <t>Instalación de agua caliente</t>
+  </si>
+  <si>
+    <t>Instalación de agua de lluvia.</t>
+  </si>
+  <si>
+    <t>Ventilación de la instalación del desagüe.</t>
+  </si>
+  <si>
+    <t>Building sewer system.</t>
+  </si>
+  <si>
+    <t>Building sewer ventilation system.</t>
+  </si>
+  <si>
+    <t>Building cold water system.</t>
+  </si>
+  <si>
+    <t>Building hot water system.</t>
+  </si>
+  <si>
+    <t>Rainwater drainage system.</t>
+  </si>
+  <si>
+    <t>Tap</t>
+  </si>
+  <si>
+    <t>Mixer</t>
+  </si>
+  <si>
+    <t>Registration</t>
+  </si>
+  <si>
+    <t>Valve</t>
+  </si>
+  <si>
+    <t>Shower</t>
+  </si>
+  <si>
+    <t>Manual shower</t>
+  </si>
+  <si>
+    <t>Water system accessory like brackets, hooks, pedestals, etc.</t>
+  </si>
+  <si>
+    <t>Upper Cistern</t>
+  </si>
+  <si>
+    <t>Intermediate Cistern</t>
+  </si>
+  <si>
+    <t>Lower Cistern</t>
+  </si>
+  <si>
+    <t>Cold Water Pipe</t>
+  </si>
+  <si>
+    <t>Water heater</t>
+  </si>
+  <si>
+    <t>Hot Water Pipe</t>
+  </si>
+  <si>
+    <t>Reuse Water Pipe</t>
+  </si>
+  <si>
+    <t>Toilet</t>
+  </si>
+  <si>
+    <t>Sanitary Sink</t>
+  </si>
+  <si>
+    <t>Washbasin</t>
+  </si>
+  <si>
+    <t>Sanitary Bowl</t>
+  </si>
+  <si>
+    <t>Bathtub</t>
+  </si>
+  <si>
+    <t>Sewer Ventilation</t>
+  </si>
+  <si>
+    <t>Local Collector as a Dry Drain or Basin Valve</t>
+  </si>
+  <si>
+    <t>Siphoned Collector as a Siphoned Drain</t>
+  </si>
+  <si>
+    <t>Floor Horizontal Collection Branch</t>
+  </si>
+  <si>
+    <t>Horizontal collection branch of the building</t>
+  </si>
+  <si>
+    <t>Downpipe</t>
+  </si>
+  <si>
+    <t>Siphons</t>
+  </si>
+  <si>
+    <t>Sandboxes</t>
+  </si>
+  <si>
+    <t>Grease Traps</t>
+  </si>
+  <si>
+    <t>Manholes</t>
+  </si>
+  <si>
+    <t>Siphon Boxes</t>
+  </si>
+  <si>
+    <t>Sanitary sewer system accessory like brackets, hooks, pedestals, etc.</t>
+  </si>
+  <si>
+    <t>Sewer Installation</t>
+  </si>
+  <si>
+    <t>Cold water installation</t>
+  </si>
+  <si>
+    <t>Installation of hot water</t>
+  </si>
+  <si>
+    <t>Rainwater installation.</t>
+  </si>
+  <si>
+    <t>Ventilation of the drain installation.</t>
+  </si>
+  <si>
+    <t>Atributo IFC</t>
+  </si>
+  <si>
+    <t>Classe IFC</t>
+  </si>
+  <si>
+    <t>[ - ]</t>
+  </si>
+  <si>
+    <t>Categoria Rvt</t>
+  </si>
+  <si>
+    <t>Parâmetro Rvt</t>
   </si>
 </sst>
 </file>
@@ -1450,25 +1624,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="28">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="30">
     <dxf>
       <font>
         <b val="0"/>
@@ -1545,6 +1701,30 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -1555,11 +1735,13 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
+        <color rgb="FF9C0006"/>
       </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -1718,6 +1900,14 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2168,7 +2358,7 @@
         <v>45</v>
       </c>
       <c r="C1" s="38" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2179,7 +2369,7 @@
         <v>47</v>
       </c>
       <c r="C2" s="39" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2187,10 +2377,10 @@
         <v>48</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C3" s="39" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2201,7 +2391,7 @@
         <v>32</v>
       </c>
       <c r="C4" s="39" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2213,7 +2403,7 @@
         <v>BIMProp</v>
       </c>
       <c r="C5" s="39" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2225,7 +2415,7 @@
         <v>BIMData</v>
       </c>
       <c r="C6" s="39" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2236,7 +2426,7 @@
         <v>53</v>
       </c>
       <c r="C7" s="39" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:3" s="37" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2244,10 +2434,10 @@
         <v>54</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C8" s="39" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2258,7 +2448,7 @@
         <v>56</v>
       </c>
       <c r="C9" s="39" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2269,7 +2459,7 @@
         <v>58</v>
       </c>
       <c r="C10" s="39" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2280,7 +2470,7 @@
         <v>58</v>
       </c>
       <c r="C11" s="39" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2291,7 +2481,7 @@
         <v>58</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2302,7 +2492,7 @@
         <v>58</v>
       </c>
       <c r="C13" s="39" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2313,7 +2503,7 @@
         <v>58</v>
       </c>
       <c r="C14" s="39" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2324,7 +2514,7 @@
         <v>58</v>
       </c>
       <c r="C15" s="39" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2335,7 +2525,7 @@
         <v>58</v>
       </c>
       <c r="C16" s="39" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2343,10 +2533,10 @@
         <v>65</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C17" s="39" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2355,10 +2545,10 @@
       </c>
       <c r="B18" s="14">
         <f ca="1">NOW()</f>
-        <v>46249.439659837961</v>
+        <v>46253.811862037037</v>
       </c>
       <c r="C18" s="39" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2369,7 +2559,7 @@
         <v>68</v>
       </c>
       <c r="C19" s="39" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2380,7 +2570,7 @@
         <v>58</v>
       </c>
       <c r="C20" s="39" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2391,7 +2581,7 @@
         <v>58</v>
       </c>
       <c r="C21" s="39" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2399,10 +2589,10 @@
         <v>71</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C22" s="39" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
@@ -2410,22 +2600,22 @@
         <v>72</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C23" s="39" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="24" spans="1:3" s="37" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="13" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B24" s="15" t="str">
         <f>_xlfn.TRANSLATE(B22,"pt","en")</f>
         <v>Formalize elements of the BIM project. Specific Objects of Hydraulics and Sanitary Sewer</v>
       </c>
       <c r="C24" s="39" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -2436,38 +2626,40 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96052D63-9637-42D9-866B-0BB924A50D8C}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AA47"/>
+  <dimension ref="A1:AC47"/>
   <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.07421875" customWidth="1"/>
+    <col min="1" max="1" width="1.4609375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="4.23046875" style="52" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.15234375" style="52" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.23046875" style="52" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.4609375" style="52" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.07421875" style="52" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" style="52" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.23046875" style="52" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.69140625" style="59" bestFit="1" customWidth="1"/>
     <col min="7" max="11" width="6.4609375" style="52" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.15234375" style="52" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.23046875" style="52" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.53515625" style="52" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.07421875" style="52" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10" style="52" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.3828125" style="52" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="8.69140625" style="52" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="31.61328125" style="52" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="29.4609375" style="52" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="3.69140625" style="52" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6.07421875" style="52" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="4.765625" style="52" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.4609375" style="52" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="4.921875" style="52" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="5.61328125" style="52" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="52.3046875" style="52" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="19.15234375" style="53" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="5" style="52" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="26.53515625" style="52" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.15234375" style="52"/>
+    <col min="16" max="16" width="31.3828125" style="52" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="29.3046875" style="52" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="26.4609375" style="52" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.69140625" style="52" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6" style="52" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="4.69140625" style="52" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.23046875" style="52" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="4.921875" style="52" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.61328125" style="52" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="52.3046875" style="52" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.765625" style="52" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="19.15234375" style="53" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6" style="52" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="5" style="52" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.15234375" style="52"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="38.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:29" ht="38.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="42" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B1" s="43" t="s">
         <v>42</v>
@@ -2500,7 +2692,7 @@
         <v>4</v>
       </c>
       <c r="L1" s="34" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="M1" s="34" t="s">
         <v>5</v>
@@ -2517,55 +2709,61 @@
       <c r="Q1" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="R1" s="34" t="s">
-        <v>95</v>
+      <c r="R1" s="35" t="s">
+        <v>84</v>
       </c>
       <c r="S1" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="T1" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="T1" s="34" t="s">
+      <c r="U1" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="U1" s="45" t="s">
+      <c r="V1" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="V1" s="34" t="s">
+      <c r="W1" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="W1" s="55" t="s">
+      <c r="X1" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="X1" s="34" t="s">
+      <c r="Y1" s="34" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z1" s="34" t="s">
+        <v>342</v>
+      </c>
+      <c r="AA1" s="34" t="s">
+        <v>339</v>
+      </c>
+      <c r="AB1" s="34" t="s">
+        <v>338</v>
+      </c>
+      <c r="AC1" s="34" t="s">
         <v>83</v>
       </c>
-      <c r="Y1" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="Z1" s="34" t="s">
-        <v>85</v>
-      </c>
-      <c r="AA1" s="35" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="2" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="56">
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C2" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="D2" s="41" t="s">
         <v>246</v>
       </c>
-      <c r="D2" s="41" t="s">
-        <v>248</v>
-      </c>
       <c r="E2" s="41" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F2" s="41" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G2" s="58" t="s">
         <v>9</v>
@@ -2599,63 +2797,68 @@
         <v>Sistema.ESG</v>
       </c>
       <c r="P2" s="51" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="Q2" s="51" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="R2" s="29" t="s">
-        <v>9</v>
+        <v>297</v>
       </c>
       <c r="S2" s="29" t="s">
-        <v>153</v>
+        <v>9</v>
       </c>
       <c r="T2" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="U2" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="V2" s="29" t="str">
+        <f t="shared" ref="V2:V3" si="4">SUBSTITUTE(E2, "_", " ")</f>
+        <v>Sistemas.Sanitários</v>
+      </c>
+      <c r="W2" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="U2" s="29" t="str">
-        <f t="shared" ref="U2:U3" si="4">SUBSTITUTE(E2, "_", " ")</f>
-        <v>Sistemas.Sanitários</v>
-      </c>
-      <c r="V2" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="W2" s="57" t="str">
-        <f t="shared" ref="W2:W42" si="5">CONCATENATE("Key-HIDR-",A2)</f>
+      <c r="X2" s="57" t="str">
+        <f t="shared" ref="X2:X42" si="5">CONCATENATE("Key-HIDR-",A2)</f>
         <v>Key-HIDR-2</v>
       </c>
-      <c r="X2" s="28" t="s">
-        <v>190</v>
-      </c>
       <c r="Y2" s="28" t="s">
-        <v>228</v>
-      </c>
-      <c r="Z2" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="AA2" s="29" t="str">
-        <f>_xlfn.TRANSLATE(P2,"pt","en")</f>
-        <v>Building sewer system.</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>188</v>
+      </c>
+      <c r="Z2" s="28" t="s">
+        <v>340</v>
+      </c>
+      <c r="AA2" s="28" t="s">
+        <v>226</v>
+      </c>
+      <c r="AB2" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="AC2" s="29" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="56">
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C3" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="D3" s="41" t="s">
         <v>246</v>
       </c>
-      <c r="D3" s="41" t="s">
-        <v>248</v>
-      </c>
       <c r="E3" s="41" t="s">
+        <v>254</v>
+      </c>
+      <c r="F3" s="41" t="s">
         <v>256</v>
-      </c>
-      <c r="F3" s="41" t="s">
-        <v>258</v>
       </c>
       <c r="G3" s="58" t="s">
         <v>9</v>
@@ -2689,63 +2892,68 @@
         <v>Sistema.VEN</v>
       </c>
       <c r="P3" s="51" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="Q3" s="51" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="R3" s="29" t="s">
-        <v>9</v>
+        <v>298</v>
       </c>
       <c r="S3" s="29" t="s">
-        <v>153</v>
+        <v>9</v>
       </c>
       <c r="T3" s="29" t="s">
-        <v>152</v>
-      </c>
-      <c r="U3" s="29" t="str">
+        <v>151</v>
+      </c>
+      <c r="U3" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="V3" s="29" t="str">
         <f t="shared" si="4"/>
         <v>Sistemas.Sanitários</v>
       </c>
-      <c r="V3" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="W3" s="57" t="str">
-        <f t="shared" ref="W3" si="6">CONCATENATE("Key-HIDR-",A3)</f>
+      <c r="W3" s="29" t="s">
+        <v>152</v>
+      </c>
+      <c r="X3" s="57" t="str">
+        <f t="shared" ref="X3" si="6">CONCATENATE("Key-HIDR-",A3)</f>
         <v>Key-HIDR-3</v>
       </c>
-      <c r="X3" s="28" t="s">
-        <v>190</v>
-      </c>
       <c r="Y3" s="28" t="s">
-        <v>259</v>
-      </c>
-      <c r="Z3" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="AA3" s="29" t="str">
-        <f>_xlfn.TRANSLATE(P3,"pt","en")</f>
-        <v>Building sewer ventilation system.</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>188</v>
+      </c>
+      <c r="Z3" s="28" t="s">
+        <v>340</v>
+      </c>
+      <c r="AA3" s="28" t="s">
+        <v>257</v>
+      </c>
+      <c r="AB3" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="AC3" s="29" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="56">
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C4" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="D4" s="41" t="s">
         <v>246</v>
       </c>
-      <c r="D4" s="41" t="s">
-        <v>248</v>
-      </c>
       <c r="E4" s="41" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F4" s="41" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G4" s="58" t="s">
         <v>9</v>
@@ -2779,63 +2987,68 @@
         <v>Sistema.AFR</v>
       </c>
       <c r="P4" s="51" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="Q4" s="51" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="R4" s="29" t="s">
-        <v>9</v>
+        <v>299</v>
       </c>
       <c r="S4" s="29" t="s">
-        <v>153</v>
+        <v>9</v>
       </c>
       <c r="T4" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="U4" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="V4" s="29" t="str">
+        <f t="shared" ref="V4:V14" si="11">SUBSTITUTE(E4, "_", " ")</f>
+        <v>Sistemas.Hidráulicos</v>
+      </c>
+      <c r="W4" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="U4" s="29" t="str">
-        <f t="shared" ref="U4:U14" si="11">SUBSTITUTE(E4, "_", " ")</f>
-        <v>Sistemas.Hidráulicos</v>
-      </c>
-      <c r="V4" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="W4" s="57" t="str">
+      <c r="X4" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-4</v>
       </c>
-      <c r="X4" s="28" t="s">
-        <v>190</v>
-      </c>
       <c r="Y4" s="28" t="s">
-        <v>226</v>
-      </c>
-      <c r="Z4" s="29" t="s">
-        <v>156</v>
-      </c>
-      <c r="AA4" s="29" t="str">
-        <f>_xlfn.TRANSLATE(P4,"pt","en")</f>
-        <v>Building cold water system.</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>188</v>
+      </c>
+      <c r="Z4" s="28" t="s">
+        <v>340</v>
+      </c>
+      <c r="AA4" s="28" t="s">
+        <v>224</v>
+      </c>
+      <c r="AB4" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="AC4" s="29" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="56">
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C5" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="D5" s="41" t="s">
         <v>246</v>
       </c>
-      <c r="D5" s="41" t="s">
-        <v>248</v>
-      </c>
       <c r="E5" s="41" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F5" s="41" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G5" s="58" t="s">
         <v>9</v>
@@ -2869,63 +3082,68 @@
         <v>Sistema.AQT</v>
       </c>
       <c r="P5" s="51" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="Q5" s="51" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="R5" s="29" t="s">
-        <v>9</v>
+        <v>300</v>
       </c>
       <c r="S5" s="29" t="s">
-        <v>153</v>
+        <v>9</v>
       </c>
       <c r="T5" s="29" t="s">
-        <v>152</v>
-      </c>
-      <c r="U5" s="29" t="str">
+        <v>151</v>
+      </c>
+      <c r="U5" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="V5" s="29" t="str">
         <f t="shared" si="11"/>
         <v>Sistemas.Hidráulicos</v>
       </c>
-      <c r="V5" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="W5" s="57" t="str">
+      <c r="W5" s="29" t="s">
+        <v>152</v>
+      </c>
+      <c r="X5" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-5</v>
       </c>
-      <c r="X5" s="28" t="s">
-        <v>190</v>
-      </c>
       <c r="Y5" s="28" t="s">
-        <v>227</v>
-      </c>
-      <c r="Z5" s="29" t="s">
-        <v>156</v>
-      </c>
-      <c r="AA5" s="29" t="str">
-        <f>_xlfn.TRANSLATE(P5,"pt","en")</f>
-        <v>Building hot water system.</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>188</v>
+      </c>
+      <c r="Z5" s="28" t="s">
+        <v>340</v>
+      </c>
+      <c r="AA5" s="28" t="s">
+        <v>225</v>
+      </c>
+      <c r="AB5" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="AC5" s="29" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="56">
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C6" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="D6" s="41" t="s">
         <v>246</v>
       </c>
-      <c r="D6" s="41" t="s">
-        <v>248</v>
-      </c>
       <c r="E6" s="41" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="F6" s="41" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="G6" s="58" t="s">
         <v>9</v>
@@ -2959,63 +3177,68 @@
         <v>Sistema.PLU</v>
       </c>
       <c r="P6" s="51" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="Q6" s="51" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="R6" s="29" t="s">
-        <v>9</v>
+        <v>301</v>
       </c>
       <c r="S6" s="29" t="s">
-        <v>153</v>
+        <v>9</v>
       </c>
       <c r="T6" s="29" t="s">
-        <v>152</v>
-      </c>
-      <c r="U6" s="29" t="str">
+        <v>151</v>
+      </c>
+      <c r="U6" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="V6" s="29" t="str">
         <f t="shared" si="11"/>
         <v>Sistemas.Pluviais</v>
       </c>
-      <c r="V6" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="W6" s="57" t="str">
-        <f t="shared" ref="W6" si="13">CONCATENATE("Key-HIDR-",A6)</f>
+      <c r="W6" s="29" t="s">
+        <v>152</v>
+      </c>
+      <c r="X6" s="57" t="str">
+        <f t="shared" ref="X6" si="13">CONCATENATE("Key-HIDR-",A6)</f>
         <v>Key-HIDR-6</v>
       </c>
-      <c r="X6" s="28" t="s">
-        <v>190</v>
-      </c>
       <c r="Y6" s="28" t="s">
-        <v>259</v>
-      </c>
-      <c r="Z6" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="AA6" s="29" t="str">
-        <f>_xlfn.TRANSLATE(P6,"pt","en")</f>
-        <v>Rainwater drainage system.</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>188</v>
+      </c>
+      <c r="Z6" s="28" t="s">
+        <v>340</v>
+      </c>
+      <c r="AA6" s="28" t="s">
+        <v>257</v>
+      </c>
+      <c r="AB6" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="AC6" s="29" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="56">
         <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C7" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C7" s="41" t="s">
-        <v>246</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="E7" s="41" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F7" s="41" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G7" s="58" t="s">
         <v>9</v>
@@ -3049,63 +3272,68 @@
         <v>Torneira</v>
       </c>
       <c r="P7" s="51" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="Q7" s="29" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="R7" s="29" t="s">
-        <v>9</v>
+        <v>302</v>
       </c>
       <c r="S7" s="29" t="s">
-        <v>153</v>
+        <v>9</v>
       </c>
       <c r="T7" s="29" t="s">
-        <v>152</v>
-      </c>
-      <c r="U7" s="29" t="str">
+        <v>151</v>
+      </c>
+      <c r="U7" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="V7" s="29" t="str">
         <f t="shared" si="11"/>
         <v>Peças.Hidráulicas</v>
       </c>
-      <c r="V7" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="W7" s="57" t="str">
+      <c r="W7" s="29" t="s">
+        <v>152</v>
+      </c>
+      <c r="X7" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-7</v>
       </c>
-      <c r="X7" s="28" t="s">
+      <c r="Y7" s="28" t="s">
+        <v>181</v>
+      </c>
+      <c r="Z7" s="28" t="s">
+        <v>340</v>
+      </c>
+      <c r="AA7" s="28" t="s">
         <v>183</v>
       </c>
-      <c r="Y7" s="28" t="s">
-        <v>185</v>
-      </c>
-      <c r="Z7" s="29" t="s">
-        <v>156</v>
-      </c>
-      <c r="AA7" s="29" t="str">
-        <f t="shared" ref="AA7:AA14" si="14">_xlfn.TRANSLATE(P7,"pt","en")</f>
-        <v>Tap</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AB7" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="AC7" s="29" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="56">
         <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C8" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C8" s="41" t="s">
-        <v>246</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="E8" s="41" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F8" s="41" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G8" s="58" t="s">
         <v>9</v>
@@ -3139,64 +3367,68 @@
         <v>Misturador</v>
       </c>
       <c r="P8" s="51" t="s">
-        <v>165</v>
-      </c>
-      <c r="Q8" s="29" t="str">
-        <f t="shared" ref="Q8:Q14" si="15">_xlfn.TRANSLATE(P8,"pt","es")</f>
-        <v>Mezclador</v>
+        <v>163</v>
+      </c>
+      <c r="Q8" s="29" t="s">
+        <v>283</v>
       </c>
       <c r="R8" s="29" t="s">
-        <v>9</v>
+        <v>303</v>
       </c>
       <c r="S8" s="29" t="s">
-        <v>153</v>
+        <v>9</v>
       </c>
       <c r="T8" s="29" t="s">
-        <v>152</v>
-      </c>
-      <c r="U8" s="29" t="str">
+        <v>151</v>
+      </c>
+      <c r="U8" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="V8" s="29" t="str">
         <f t="shared" si="11"/>
         <v>Peças.Hidráulicas</v>
       </c>
-      <c r="V8" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="W8" s="57" t="str">
+      <c r="W8" s="29" t="s">
+        <v>152</v>
+      </c>
+      <c r="X8" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-8</v>
       </c>
-      <c r="X8" s="28" t="s">
+      <c r="Y8" s="28" t="s">
+        <v>181</v>
+      </c>
+      <c r="Z8" s="28" t="s">
+        <v>340</v>
+      </c>
+      <c r="AA8" s="28" t="s">
         <v>183</v>
       </c>
-      <c r="Y8" s="28" t="s">
-        <v>185</v>
-      </c>
-      <c r="Z8" s="29" t="s">
-        <v>156</v>
-      </c>
-      <c r="AA8" s="29" t="str">
-        <f t="shared" si="14"/>
-        <v>Mixer</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AB8" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="AC8" s="29" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="56">
         <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C9" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C9" s="41" t="s">
-        <v>246</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="E9" s="41" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F9" s="41" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="G9" s="58" t="s">
         <v>9</v>
@@ -3230,64 +3462,68 @@
         <v>Registro</v>
       </c>
       <c r="P9" s="51" t="s">
-        <v>167</v>
-      </c>
-      <c r="Q9" s="29" t="str">
-        <f t="shared" si="15"/>
-        <v>Registro</v>
+        <v>165</v>
+      </c>
+      <c r="Q9" s="29" t="s">
+        <v>165</v>
       </c>
       <c r="R9" s="29" t="s">
-        <v>9</v>
+        <v>304</v>
       </c>
       <c r="S9" s="29" t="s">
-        <v>153</v>
+        <v>9</v>
       </c>
       <c r="T9" s="29" t="s">
-        <v>152</v>
-      </c>
-      <c r="U9" s="29" t="str">
+        <v>151</v>
+      </c>
+      <c r="U9" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="V9" s="29" t="str">
         <f t="shared" si="11"/>
         <v>Peças.Hidráulicas</v>
       </c>
-      <c r="V9" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="W9" s="57" t="str">
+      <c r="W9" s="29" t="s">
+        <v>152</v>
+      </c>
+      <c r="X9" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-9</v>
       </c>
-      <c r="X9" s="28" t="s">
+      <c r="Y9" s="28" t="s">
+        <v>181</v>
+      </c>
+      <c r="Z9" s="28" t="s">
+        <v>340</v>
+      </c>
+      <c r="AA9" s="28" t="s">
         <v>183</v>
       </c>
-      <c r="Y9" s="28" t="s">
-        <v>185</v>
-      </c>
-      <c r="Z9" s="29" t="s">
-        <v>156</v>
-      </c>
-      <c r="AA9" s="29" t="str">
-        <f t="shared" si="14"/>
-        <v>Registration</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AB9" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="AC9" s="29" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="56">
         <v>10</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C10" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C10" s="41" t="s">
-        <v>246</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="E10" s="41" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F10" s="41" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G10" s="58" t="s">
         <v>9</v>
@@ -3321,64 +3557,68 @@
         <v>Válvula</v>
       </c>
       <c r="P10" s="51" t="s">
-        <v>166</v>
-      </c>
-      <c r="Q10" s="29" t="str">
-        <f t="shared" si="15"/>
-        <v>Válvula</v>
+        <v>164</v>
+      </c>
+      <c r="Q10" s="29" t="s">
+        <v>164</v>
       </c>
       <c r="R10" s="29" t="s">
-        <v>9</v>
+        <v>305</v>
       </c>
       <c r="S10" s="29" t="s">
-        <v>153</v>
+        <v>9</v>
       </c>
       <c r="T10" s="29" t="s">
-        <v>152</v>
-      </c>
-      <c r="U10" s="29" t="str">
+        <v>151</v>
+      </c>
+      <c r="U10" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="V10" s="29" t="str">
         <f t="shared" si="11"/>
         <v>Peças.Hidráulicas</v>
       </c>
-      <c r="V10" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="W10" s="57" t="str">
+      <c r="W10" s="29" t="s">
+        <v>152</v>
+      </c>
+      <c r="X10" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-10</v>
       </c>
-      <c r="X10" s="28" t="s">
+      <c r="Y10" s="28" t="s">
+        <v>181</v>
+      </c>
+      <c r="Z10" s="28" t="s">
+        <v>340</v>
+      </c>
+      <c r="AA10" s="28" t="s">
         <v>183</v>
       </c>
-      <c r="Y10" s="28" t="s">
-        <v>185</v>
-      </c>
-      <c r="Z10" s="29" t="s">
-        <v>156</v>
-      </c>
-      <c r="AA10" s="29" t="str">
-        <f t="shared" si="14"/>
-        <v>Valve</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AB10" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="AC10" s="29" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="56">
         <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C11" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C11" s="41" t="s">
-        <v>246</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="E11" s="41" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F11" s="41" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="G11" s="58" t="s">
         <v>9</v>
@@ -3396,15 +3636,15 @@
         <v>9</v>
       </c>
       <c r="L11" s="32" t="str">
-        <f t="shared" ref="L11:L13" si="16">CONCATENATE("", C11)</f>
+        <f t="shared" ref="L11:L13" si="14">CONCATENATE("", C11)</f>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M11" s="32" t="str">
-        <f t="shared" ref="M11:M13" si="17">CONCATENATE("", D11)</f>
+        <f t="shared" ref="M11:M13" si="15">CONCATENATE("", D11)</f>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N11" s="32" t="str">
-        <f t="shared" ref="N11:N13" si="18">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E11),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N11:N13" si="16">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E11),"."," ")," De "," de "))</f>
         <v>Peças Hidráulicas</v>
       </c>
       <c r="O11" s="29" t="str">
@@ -3412,64 +3652,68 @@
         <v>Chuveiro</v>
       </c>
       <c r="P11" s="51" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q11" s="29" t="str">
-        <f t="shared" si="15"/>
-        <v>Ducha</v>
+        <v>161</v>
+      </c>
+      <c r="Q11" s="29" t="s">
+        <v>172</v>
       </c>
       <c r="R11" s="29" t="s">
-        <v>9</v>
+        <v>306</v>
       </c>
       <c r="S11" s="29" t="s">
-        <v>153</v>
+        <v>9</v>
       </c>
       <c r="T11" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="U11" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="V11" s="29" t="str">
+        <f t="shared" ref="V11:V13" si="17">SUBSTITUTE(E11, "_", " ")</f>
+        <v>Peças.Hidráulicas</v>
+      </c>
+      <c r="W11" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="U11" s="29" t="str">
-        <f t="shared" ref="U11:U13" si="19">SUBSTITUTE(E11, "_", " ")</f>
-        <v>Peças.Hidráulicas</v>
-      </c>
-      <c r="V11" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="W11" s="57" t="str">
+      <c r="X11" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-11</v>
       </c>
-      <c r="X11" s="28" t="s">
-        <v>183</v>
-      </c>
       <c r="Y11" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="Z11" s="29" t="s">
-        <v>156</v>
-      </c>
-      <c r="AA11" s="29" t="str">
-        <f t="shared" ref="AA11:AA12" si="20">_xlfn.TRANSLATE(P11,"pt","en")</f>
-        <v>Shower</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>181</v>
+      </c>
+      <c r="Z11" s="28" t="s">
+        <v>340</v>
+      </c>
+      <c r="AA11" s="28" t="s">
+        <v>182</v>
+      </c>
+      <c r="AB11" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="AC11" s="29" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="56">
         <v>12</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C12" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C12" s="41" t="s">
-        <v>246</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="E12" s="41" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F12" s="41" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G12" s="58" t="s">
         <v>9</v>
@@ -3487,15 +3731,15 @@
         <v>9</v>
       </c>
       <c r="L12" s="32" t="str">
+        <f t="shared" si="14"/>
+        <v>Sistemas.Prediais</v>
+      </c>
+      <c r="M12" s="32" t="str">
+        <f t="shared" si="15"/>
+        <v>Elementos.Hidráulicos</v>
+      </c>
+      <c r="N12" s="32" t="str">
         <f t="shared" si="16"/>
-        <v>Sistemas.Prediais</v>
-      </c>
-      <c r="M12" s="32" t="str">
-        <f t="shared" si="17"/>
-        <v>Elementos.Hidráulicos</v>
-      </c>
-      <c r="N12" s="32" t="str">
-        <f t="shared" si="18"/>
         <v>Peças Hidráulicas</v>
       </c>
       <c r="O12" s="29" t="str">
@@ -3503,64 +3747,68 @@
         <v>Ducha</v>
       </c>
       <c r="P12" s="51" t="s">
-        <v>175</v>
-      </c>
-      <c r="Q12" s="29" t="str">
-        <f t="shared" ref="Q12" si="21">_xlfn.TRANSLATE(P12,"pt","es")</f>
-        <v>Ducha manual</v>
+        <v>173</v>
+      </c>
+      <c r="Q12" s="29" t="s">
+        <v>173</v>
       </c>
       <c r="R12" s="29" t="s">
-        <v>9</v>
+        <v>307</v>
       </c>
       <c r="S12" s="29" t="s">
-        <v>153</v>
+        <v>9</v>
       </c>
       <c r="T12" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="U12" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="V12" s="29" t="str">
+        <f t="shared" si="17"/>
+        <v>Peças.Hidráulicas</v>
+      </c>
+      <c r="W12" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="U12" s="29" t="str">
-        <f t="shared" si="19"/>
-        <v>Peças.Hidráulicas</v>
-      </c>
-      <c r="V12" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="W12" s="57" t="str">
+      <c r="X12" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-12</v>
       </c>
-      <c r="X12" s="28" t="s">
-        <v>183</v>
-      </c>
       <c r="Y12" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="Z12" s="29" t="s">
-        <v>156</v>
-      </c>
-      <c r="AA12" s="29" t="str">
-        <f t="shared" si="20"/>
-        <v>Manual shower</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>181</v>
+      </c>
+      <c r="Z12" s="28" t="s">
+        <v>340</v>
+      </c>
+      <c r="AA12" s="28" t="s">
+        <v>182</v>
+      </c>
+      <c r="AB12" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="AC12" s="29" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="56">
         <v>13</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C13" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C13" s="41" t="s">
-        <v>246</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="E13" s="41" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F13" s="41" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="G13" s="58" t="s">
         <v>9</v>
@@ -3578,15 +3826,15 @@
         <v>9</v>
       </c>
       <c r="L13" s="32" t="str">
+        <f t="shared" si="14"/>
+        <v>Sistemas.Prediais</v>
+      </c>
+      <c r="M13" s="32" t="str">
+        <f t="shared" si="15"/>
+        <v>Elementos.Hidráulicos</v>
+      </c>
+      <c r="N13" s="32" t="str">
         <f t="shared" si="16"/>
-        <v>Sistemas.Prediais</v>
-      </c>
-      <c r="M13" s="32" t="str">
-        <f t="shared" si="17"/>
-        <v>Elementos.Hidráulicos</v>
-      </c>
-      <c r="N13" s="32" t="str">
-        <f t="shared" si="18"/>
         <v>Peças Hidráulicas</v>
       </c>
       <c r="O13" s="29" t="str">
@@ -3594,62 +3842,68 @@
         <v>Medidor.de.Água</v>
       </c>
       <c r="P13" s="51" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q13" s="51" t="s">
+        <v>232</v>
+      </c>
+      <c r="R13" s="29" t="s">
         <v>233</v>
       </c>
-      <c r="Q13" s="51" t="s">
-        <v>234</v>
-      </c>
-      <c r="R13" s="29" t="s">
-        <v>9</v>
-      </c>
       <c r="S13" s="29" t="s">
-        <v>153</v>
+        <v>9</v>
       </c>
       <c r="T13" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="U13" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="V13" s="29" t="str">
+        <f t="shared" si="17"/>
+        <v>Peças.Hidráulicas</v>
+      </c>
+      <c r="W13" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="U13" s="29" t="str">
-        <f t="shared" si="19"/>
-        <v>Peças.Hidráulicas</v>
-      </c>
-      <c r="V13" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="W13" s="57" t="str">
+      <c r="X13" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-13</v>
       </c>
-      <c r="X13" s="28" t="s">
-        <v>242</v>
-      </c>
       <c r="Y13" s="28" t="s">
-        <v>231</v>
-      </c>
-      <c r="Z13" s="29" t="s">
-        <v>156</v>
-      </c>
-      <c r="AA13" s="29" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>240</v>
+      </c>
+      <c r="Z13" s="28" t="s">
+        <v>340</v>
+      </c>
+      <c r="AA13" s="28" t="s">
+        <v>229</v>
+      </c>
+      <c r="AB13" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="AC13" s="29" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="56">
         <v>14</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C14" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C14" s="41" t="s">
-        <v>246</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="E14" s="41" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F14" s="41" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G14" s="58" t="s">
         <v>9</v>
@@ -3683,64 +3937,68 @@
         <v>Acessório.Hidraúlico</v>
       </c>
       <c r="P14" s="51" t="s">
-        <v>224</v>
-      </c>
-      <c r="Q14" s="29" t="str">
-        <f t="shared" si="15"/>
-        <v>Accesorios para sistemas de agua como soportes, ganchos, pedestales, etc.</v>
+        <v>222</v>
+      </c>
+      <c r="Q14" s="29" t="s">
+        <v>284</v>
       </c>
       <c r="R14" s="29" t="s">
-        <v>9</v>
+        <v>308</v>
       </c>
       <c r="S14" s="29" t="s">
-        <v>153</v>
+        <v>9</v>
       </c>
       <c r="T14" s="29" t="s">
-        <v>152</v>
-      </c>
-      <c r="U14" s="29" t="str">
+        <v>151</v>
+      </c>
+      <c r="U14" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="V14" s="29" t="str">
         <f t="shared" si="11"/>
         <v>Peças.Hidráulicas</v>
       </c>
-      <c r="V14" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="W14" s="57" t="str">
+      <c r="W14" s="29" t="s">
+        <v>152</v>
+      </c>
+      <c r="X14" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-14</v>
       </c>
-      <c r="X14" s="28" t="s">
-        <v>237</v>
-      </c>
       <c r="Y14" s="28" t="s">
-        <v>236</v>
-      </c>
-      <c r="Z14" s="29" t="s">
-        <v>156</v>
-      </c>
-      <c r="AA14" s="29" t="str">
-        <f t="shared" si="14"/>
-        <v>Water system accessory like brackets, hooks, pedestals, etc.</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>235</v>
+      </c>
+      <c r="Z14" s="28" t="s">
+        <v>340</v>
+      </c>
+      <c r="AA14" s="28" t="s">
+        <v>234</v>
+      </c>
+      <c r="AB14" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="AC14" s="29" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="56">
         <v>15</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C15" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C15" s="41" t="s">
-        <v>246</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="E15" s="41" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F15" s="41" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G15" s="58" t="s">
         <v>9</v>
@@ -3758,15 +4016,15 @@
         <v>9</v>
       </c>
       <c r="L15" s="32" t="str">
-        <f t="shared" ref="L15:L34" si="22">CONCATENATE("", C15)</f>
+        <f t="shared" ref="L15:L34" si="18">CONCATENATE("", C15)</f>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M15" s="32" t="str">
-        <f t="shared" ref="M15:M34" si="23">CONCATENATE("", D15)</f>
+        <f t="shared" ref="M15:M34" si="19">CONCATENATE("", D15)</f>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N15" s="32" t="str">
-        <f t="shared" ref="N15:N34" si="24">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E15),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N15:N34" si="20">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E15),"."," ")," De "," de "))</f>
         <v>Tubulação Agua Fria</v>
       </c>
       <c r="O15" s="29" t="str">
@@ -3774,64 +4032,68 @@
         <v>Cisterna.Superior</v>
       </c>
       <c r="P15" s="51" t="s">
-        <v>140</v>
-      </c>
-      <c r="Q15" s="29" t="str">
-        <f>_xlfn.TRANSLATE(P15,"pt","es")</f>
-        <v>Cisterna Superior</v>
+        <v>138</v>
+      </c>
+      <c r="Q15" s="29" t="s">
+        <v>138</v>
       </c>
       <c r="R15" s="29" t="s">
-        <v>9</v>
+        <v>309</v>
       </c>
       <c r="S15" s="29" t="s">
-        <v>153</v>
+        <v>9</v>
       </c>
       <c r="T15" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="U15" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="V15" s="29" t="str">
+        <f t="shared" ref="V15:V34" si="21">SUBSTITUTE(E15, "_", " ")</f>
+        <v>Tubulação.Agua.Fria</v>
+      </c>
+      <c r="W15" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="U15" s="29" t="str">
-        <f t="shared" ref="U15:U34" si="25">SUBSTITUTE(E15, "_", " ")</f>
-        <v>Tubulação.Agua.Fria</v>
-      </c>
-      <c r="V15" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="W15" s="57" t="str">
+      <c r="X15" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-15</v>
       </c>
-      <c r="X15" s="28" t="s">
-        <v>249</v>
-      </c>
       <c r="Y15" s="28" t="s">
-        <v>186</v>
-      </c>
-      <c r="Z15" s="29" t="s">
-        <v>156</v>
-      </c>
-      <c r="AA15" s="29" t="str">
-        <f t="shared" ref="AA15:AA29" si="26">_xlfn.TRANSLATE(P15,"pt","en")</f>
-        <v>Upper Cistern</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>247</v>
+      </c>
+      <c r="Z15" s="28" t="s">
+        <v>340</v>
+      </c>
+      <c r="AA15" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="AB15" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="AC15" s="29" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="56">
         <v>16</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C16" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C16" s="41" t="s">
-        <v>246</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="E16" s="41" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F16" s="41" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="G16" s="58" t="s">
         <v>9</v>
@@ -3849,15 +4111,15 @@
         <v>9</v>
       </c>
       <c r="L16" s="32" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M16" s="32" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="19"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N16" s="32" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v>Tubulação Agua Fria</v>
       </c>
       <c r="O16" s="29" t="str">
@@ -3865,64 +4127,68 @@
         <v>Cisterna.Intermediária</v>
       </c>
       <c r="P16" s="51" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q16" s="29" t="str">
-        <f t="shared" ref="Q16:Q22" si="27">_xlfn.TRANSLATE(P16,"pt","es")</f>
-        <v>Cisterna intermedia</v>
+        <v>147</v>
+      </c>
+      <c r="Q16" s="29" t="s">
+        <v>285</v>
       </c>
       <c r="R16" s="29" t="s">
-        <v>9</v>
+        <v>310</v>
       </c>
       <c r="S16" s="29" t="s">
-        <v>153</v>
+        <v>9</v>
       </c>
       <c r="T16" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="U16" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="V16" s="29" t="str">
+        <f t="shared" si="21"/>
+        <v>Tubulação.Agua.Fria</v>
+      </c>
+      <c r="W16" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="U16" s="29" t="str">
-        <f t="shared" si="25"/>
-        <v>Tubulação.Agua.Fria</v>
-      </c>
-      <c r="V16" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="W16" s="57" t="str">
+      <c r="X16" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-16</v>
       </c>
-      <c r="X16" s="28" t="s">
-        <v>249</v>
-      </c>
       <c r="Y16" s="28" t="s">
-        <v>186</v>
-      </c>
-      <c r="Z16" s="29" t="s">
-        <v>156</v>
-      </c>
-      <c r="AA16" s="29" t="str">
-        <f t="shared" si="26"/>
-        <v>Intermediate Cistern</v>
-      </c>
-    </row>
-    <row r="17" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>247</v>
+      </c>
+      <c r="Z16" s="28" t="s">
+        <v>340</v>
+      </c>
+      <c r="AA16" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="AB16" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="AC16" s="29" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="17" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="56">
         <v>17</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C17" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C17" s="41" t="s">
-        <v>246</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="E17" s="41" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F17" s="41" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G17" s="58" t="s">
         <v>9</v>
@@ -3940,15 +4206,15 @@
         <v>9</v>
       </c>
       <c r="L17" s="32" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M17" s="32" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="19"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N17" s="32" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v>Tubulação Agua Fria</v>
       </c>
       <c r="O17" s="29" t="str">
@@ -3956,64 +4222,68 @@
         <v>Cisterna.Inferior</v>
       </c>
       <c r="P17" s="51" t="s">
-        <v>141</v>
-      </c>
-      <c r="Q17" s="29" t="str">
-        <f t="shared" si="27"/>
-        <v>Cisterna Inferior</v>
+        <v>139</v>
+      </c>
+      <c r="Q17" s="29" t="s">
+        <v>139</v>
       </c>
       <c r="R17" s="29" t="s">
-        <v>9</v>
+        <v>311</v>
       </c>
       <c r="S17" s="29" t="s">
-        <v>153</v>
+        <v>9</v>
       </c>
       <c r="T17" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="U17" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="V17" s="29" t="str">
+        <f t="shared" si="21"/>
+        <v>Tubulação.Agua.Fria</v>
+      </c>
+      <c r="W17" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="U17" s="29" t="str">
-        <f t="shared" si="25"/>
-        <v>Tubulação.Agua.Fria</v>
-      </c>
-      <c r="V17" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="W17" s="57" t="str">
+      <c r="X17" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-17</v>
       </c>
-      <c r="X17" s="28" t="s">
-        <v>249</v>
-      </c>
       <c r="Y17" s="28" t="s">
-        <v>186</v>
-      </c>
-      <c r="Z17" s="29" t="s">
-        <v>156</v>
-      </c>
-      <c r="AA17" s="29" t="str">
-        <f t="shared" si="26"/>
-        <v>Lower Cistern</v>
-      </c>
-    </row>
-    <row r="18" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>247</v>
+      </c>
+      <c r="Z17" s="28" t="s">
+        <v>340</v>
+      </c>
+      <c r="AA17" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="AB17" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="AC17" s="29" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="18" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="56">
         <v>18</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C18" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C18" s="41" t="s">
-        <v>246</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="E18" s="41" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F18" s="41" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G18" s="58" t="s">
         <v>9</v>
@@ -4031,15 +4301,15 @@
         <v>9</v>
       </c>
       <c r="L18" s="32" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M18" s="32" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="19"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N18" s="32" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v>Tubulação Agua Fria</v>
       </c>
       <c r="O18" s="29" t="str">
@@ -4047,64 +4317,68 @@
         <v>Tubulação.AF</v>
       </c>
       <c r="P18" s="51" t="s">
-        <v>144</v>
-      </c>
-      <c r="Q18" s="29" t="str">
-        <f t="shared" si="27"/>
-        <v>Tubería de agua fría</v>
+        <v>142</v>
+      </c>
+      <c r="Q18" s="29" t="s">
+        <v>286</v>
       </c>
       <c r="R18" s="29" t="s">
-        <v>9</v>
+        <v>312</v>
       </c>
       <c r="S18" s="29" t="s">
-        <v>153</v>
+        <v>9</v>
       </c>
       <c r="T18" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="U18" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="V18" s="29" t="str">
+        <f t="shared" si="21"/>
+        <v>Tubulação.Agua.Fria</v>
+      </c>
+      <c r="W18" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="U18" s="29" t="str">
-        <f t="shared" si="25"/>
-        <v>Tubulação.Agua.Fria</v>
-      </c>
-      <c r="V18" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="W18" s="57" t="str">
+      <c r="X18" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-18</v>
       </c>
-      <c r="X18" s="28" t="s">
-        <v>249</v>
-      </c>
       <c r="Y18" s="28" t="s">
-        <v>250</v>
-      </c>
-      <c r="Z18" s="29" t="s">
-        <v>156</v>
-      </c>
-      <c r="AA18" s="29" t="str">
-        <f t="shared" si="26"/>
-        <v>Cold Water Pipe</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>247</v>
+      </c>
+      <c r="Z18" s="28" t="s">
+        <v>340</v>
+      </c>
+      <c r="AA18" s="28" t="s">
+        <v>248</v>
+      </c>
+      <c r="AB18" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="AC18" s="29" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="19" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="56">
         <v>19</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C19" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C19" s="41" t="s">
-        <v>246</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="E19" s="41" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F19" s="41" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G19" s="58" t="s">
         <v>9</v>
@@ -4122,15 +4396,15 @@
         <v>9</v>
       </c>
       <c r="L19" s="32" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M19" s="32" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="19"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N19" s="32" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v>Tubulação Agua Quente</v>
       </c>
       <c r="O19" s="29" t="str">
@@ -4138,63 +4412,68 @@
         <v>Aquecedor.de.Agua</v>
       </c>
       <c r="P19" s="51" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="Q19" s="29" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="R19" s="29" t="s">
-        <v>9</v>
+        <v>313</v>
       </c>
       <c r="S19" s="29" t="s">
-        <v>153</v>
+        <v>9</v>
       </c>
       <c r="T19" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="U19" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="V19" s="29" t="str">
+        <f t="shared" si="21"/>
+        <v>Tubulação.Agua.Quente</v>
+      </c>
+      <c r="W19" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="U19" s="29" t="str">
-        <f t="shared" si="25"/>
-        <v>Tubulação.Agua.Quente</v>
-      </c>
-      <c r="V19" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="W19" s="57" t="str">
+      <c r="X19" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-19</v>
       </c>
-      <c r="X19" s="28" t="s">
-        <v>183</v>
-      </c>
       <c r="Y19" s="28" t="s">
-        <v>187</v>
-      </c>
-      <c r="Z19" s="29" t="s">
-        <v>156</v>
-      </c>
-      <c r="AA19" s="29" t="str">
-        <f t="shared" si="26"/>
-        <v>Water heater</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>181</v>
+      </c>
+      <c r="Z19" s="28" t="s">
+        <v>340</v>
+      </c>
+      <c r="AA19" s="28" t="s">
+        <v>185</v>
+      </c>
+      <c r="AB19" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="AC19" s="29" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="20" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="56">
         <v>20</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C20" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C20" s="41" t="s">
-        <v>246</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="E20" s="41" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F20" s="41" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G20" s="58" t="s">
         <v>9</v>
@@ -4212,15 +4491,15 @@
         <v>9</v>
       </c>
       <c r="L20" s="32" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M20" s="32" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="19"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N20" s="32" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v>Tubulação Agua Quente</v>
       </c>
       <c r="O20" s="29" t="str">
@@ -4228,63 +4507,68 @@
         <v>Boiler</v>
       </c>
       <c r="P20" s="51" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="Q20" s="29" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="R20" s="29" t="s">
-        <v>9</v>
+        <v>134</v>
       </c>
       <c r="S20" s="29" t="s">
-        <v>153</v>
+        <v>9</v>
       </c>
       <c r="T20" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="U20" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="V20" s="29" t="str">
+        <f t="shared" si="21"/>
+        <v>Tubulação.Agua.Quente</v>
+      </c>
+      <c r="W20" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="U20" s="29" t="str">
-        <f t="shared" si="25"/>
-        <v>Tubulação.Agua.Quente</v>
-      </c>
-      <c r="V20" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="W20" s="57" t="str">
+      <c r="X20" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-20</v>
       </c>
-      <c r="X20" s="28" t="s">
-        <v>183</v>
-      </c>
       <c r="Y20" s="28" t="s">
-        <v>187</v>
-      </c>
-      <c r="Z20" s="29" t="s">
-        <v>156</v>
-      </c>
-      <c r="AA20" s="29" t="str">
-        <f t="shared" si="26"/>
-        <v>Boiler</v>
-      </c>
-    </row>
-    <row r="21" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>181</v>
+      </c>
+      <c r="Z20" s="28" t="s">
+        <v>340</v>
+      </c>
+      <c r="AA20" s="28" t="s">
+        <v>185</v>
+      </c>
+      <c r="AB20" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="AC20" s="29" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="21" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="56">
         <v>21</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C21" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C21" s="41" t="s">
-        <v>246</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="E21" s="41" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F21" s="41" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G21" s="58" t="s">
         <v>9</v>
@@ -4302,15 +4586,15 @@
         <v>9</v>
       </c>
       <c r="L21" s="32" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M21" s="32" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="19"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N21" s="32" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v>Tubulação Agua Quente</v>
       </c>
       <c r="O21" s="29" t="str">
@@ -4318,64 +4602,68 @@
         <v>Caldeira</v>
       </c>
       <c r="P21" s="51" t="s">
-        <v>137</v>
-      </c>
-      <c r="Q21" s="29" t="str">
-        <f t="shared" si="27"/>
-        <v>Caldera</v>
+        <v>135</v>
+      </c>
+      <c r="Q21" s="29" t="s">
+        <v>287</v>
       </c>
       <c r="R21" s="29" t="s">
-        <v>9</v>
+        <v>134</v>
       </c>
       <c r="S21" s="29" t="s">
-        <v>153</v>
+        <v>9</v>
       </c>
       <c r="T21" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="U21" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="V21" s="29" t="str">
+        <f t="shared" si="21"/>
+        <v>Tubulação.Agua.Quente</v>
+      </c>
+      <c r="W21" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="U21" s="29" t="str">
-        <f t="shared" si="25"/>
-        <v>Tubulação.Agua.Quente</v>
-      </c>
-      <c r="V21" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="W21" s="57" t="str">
+      <c r="X21" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-21</v>
       </c>
-      <c r="X21" s="28" t="s">
-        <v>183</v>
-      </c>
       <c r="Y21" s="28" t="s">
-        <v>188</v>
-      </c>
-      <c r="Z21" s="29" t="s">
-        <v>156</v>
-      </c>
-      <c r="AA21" s="29" t="str">
-        <f t="shared" si="26"/>
-        <v>Boiler</v>
-      </c>
-    </row>
-    <row r="22" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>181</v>
+      </c>
+      <c r="Z21" s="28" t="s">
+        <v>340</v>
+      </c>
+      <c r="AA21" s="28" t="s">
+        <v>186</v>
+      </c>
+      <c r="AB21" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="AC21" s="29" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="22" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="56">
         <v>22</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C22" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C22" s="41" t="s">
-        <v>246</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="E22" s="41" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F22" s="41" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G22" s="58" t="s">
         <v>9</v>
@@ -4393,15 +4681,15 @@
         <v>9</v>
       </c>
       <c r="L22" s="32" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M22" s="32" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="19"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N22" s="32" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v>Tubulação Agua Quente</v>
       </c>
       <c r="O22" s="29" t="str">
@@ -4409,64 +4697,68 @@
         <v>Tubulação.AQ</v>
       </c>
       <c r="P22" s="51" t="s">
-        <v>145</v>
-      </c>
-      <c r="Q22" s="29" t="str">
-        <f t="shared" si="27"/>
-        <v>Tubería de agua caliente</v>
+        <v>143</v>
+      </c>
+      <c r="Q22" s="29" t="s">
+        <v>288</v>
       </c>
       <c r="R22" s="29" t="s">
-        <v>9</v>
+        <v>314</v>
       </c>
       <c r="S22" s="29" t="s">
-        <v>153</v>
+        <v>9</v>
       </c>
       <c r="T22" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="U22" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="V22" s="29" t="str">
+        <f t="shared" si="21"/>
+        <v>Tubulação.Agua.Quente</v>
+      </c>
+      <c r="W22" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="U22" s="29" t="str">
-        <f t="shared" si="25"/>
-        <v>Tubulação.Agua.Quente</v>
-      </c>
-      <c r="V22" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="W22" s="57" t="str">
+      <c r="X22" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-22</v>
       </c>
-      <c r="X22" s="28" t="s">
-        <v>249</v>
-      </c>
       <c r="Y22" s="28" t="s">
-        <v>250</v>
-      </c>
-      <c r="Z22" s="29" t="s">
-        <v>156</v>
-      </c>
-      <c r="AA22" s="29" t="str">
-        <f t="shared" si="26"/>
-        <v>Hot Water Pipe</v>
-      </c>
-    </row>
-    <row r="23" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>247</v>
+      </c>
+      <c r="Z22" s="28" t="s">
+        <v>340</v>
+      </c>
+      <c r="AA22" s="28" t="s">
+        <v>248</v>
+      </c>
+      <c r="AB22" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="AC22" s="29" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="23" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="56">
         <v>23</v>
       </c>
       <c r="B23" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C23" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C23" s="41" t="s">
-        <v>246</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="E23" s="41" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F23" s="41" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G23" s="58" t="s">
         <v>9</v>
@@ -4484,15 +4776,15 @@
         <v>9</v>
       </c>
       <c r="L23" s="32" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M23" s="32" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="19"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N23" s="32" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v>Tubulação Agua Quente</v>
       </c>
       <c r="O23" s="29" t="str">
@@ -4500,63 +4792,68 @@
         <v>Tubulação.Reuso</v>
       </c>
       <c r="P23" s="51" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="Q23" s="51" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="R23" s="29" t="s">
-        <v>9</v>
+        <v>315</v>
       </c>
       <c r="S23" s="29" t="s">
-        <v>153</v>
+        <v>9</v>
       </c>
       <c r="T23" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="U23" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="V23" s="29" t="str">
+        <f t="shared" si="21"/>
+        <v>Tubulação.Agua.Quente</v>
+      </c>
+      <c r="W23" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="U23" s="29" t="str">
-        <f t="shared" si="25"/>
-        <v>Tubulação.Agua.Quente</v>
-      </c>
-      <c r="V23" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="W23" s="57" t="str">
+      <c r="X23" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-23</v>
       </c>
-      <c r="X23" s="28" t="s">
-        <v>249</v>
-      </c>
       <c r="Y23" s="28" t="s">
-        <v>250</v>
-      </c>
-      <c r="Z23" s="29" t="s">
-        <v>156</v>
-      </c>
-      <c r="AA23" s="29" t="str">
-        <f t="shared" si="26"/>
-        <v>Reuse Water Pipe</v>
-      </c>
-    </row>
-    <row r="24" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>247</v>
+      </c>
+      <c r="Z23" s="28" t="s">
+        <v>340</v>
+      </c>
+      <c r="AA23" s="28" t="s">
+        <v>248</v>
+      </c>
+      <c r="AB23" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="AC23" s="29" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="24" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="56">
         <v>24</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C24" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C24" s="41" t="s">
-        <v>246</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="E24" s="41" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F24" s="41" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G24" s="58" t="s">
         <v>9</v>
@@ -4574,15 +4871,15 @@
         <v>9</v>
       </c>
       <c r="L24" s="32" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M24" s="32" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="19"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N24" s="32" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v>Peças Sanitárias</v>
       </c>
       <c r="O24" s="29" t="str">
@@ -4590,63 +4887,68 @@
         <v>Vaso.Sanitário</v>
       </c>
       <c r="P24" s="51" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="Q24" s="29" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="R24" s="29" t="s">
-        <v>9</v>
+        <v>316</v>
       </c>
       <c r="S24" s="29" t="s">
-        <v>153</v>
+        <v>9</v>
       </c>
       <c r="T24" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="U24" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="V24" s="29" t="str">
+        <f t="shared" si="21"/>
+        <v>Peças.Sanitárias</v>
+      </c>
+      <c r="W24" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="U24" s="29" t="str">
-        <f t="shared" si="25"/>
-        <v>Peças.Sanitárias</v>
-      </c>
-      <c r="V24" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="W24" s="57" t="str">
+      <c r="X24" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-24</v>
       </c>
-      <c r="X24" s="28" t="s">
-        <v>183</v>
-      </c>
       <c r="Y24" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="Z24" s="29" t="s">
-        <v>156</v>
-      </c>
-      <c r="AA24" s="29" t="str">
-        <f t="shared" si="26"/>
-        <v>Toilet</v>
-      </c>
-    </row>
-    <row r="25" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>181</v>
+      </c>
+      <c r="Z24" s="28" t="s">
+        <v>340</v>
+      </c>
+      <c r="AA24" s="28" t="s">
+        <v>182</v>
+      </c>
+      <c r="AB24" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="AC24" s="29" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="25" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="56">
         <v>25</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C25" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C25" s="41" t="s">
-        <v>246</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="E25" s="41" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F25" s="41" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G25" s="58" t="s">
         <v>9</v>
@@ -4664,15 +4966,15 @@
         <v>9</v>
       </c>
       <c r="L25" s="32" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M25" s="32" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="19"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N25" s="32" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v>Peças Sanitárias</v>
       </c>
       <c r="O25" s="29" t="str">
@@ -4680,64 +4982,68 @@
         <v>Bidet</v>
       </c>
       <c r="P25" s="51" t="s">
-        <v>169</v>
-      </c>
-      <c r="Q25" s="29" t="str">
-        <f t="shared" ref="Q25:Q29" si="28">_xlfn.TRANSLATE(P25,"pt","es")</f>
-        <v>Bidé</v>
+        <v>167</v>
+      </c>
+      <c r="Q25" s="29" t="s">
+        <v>289</v>
       </c>
       <c r="R25" s="29" t="s">
-        <v>9</v>
+        <v>167</v>
       </c>
       <c r="S25" s="29" t="s">
-        <v>153</v>
+        <v>9</v>
       </c>
       <c r="T25" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="U25" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="V25" s="29" t="str">
+        <f t="shared" si="21"/>
+        <v>Peças.Sanitárias</v>
+      </c>
+      <c r="W25" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="U25" s="29" t="str">
-        <f t="shared" si="25"/>
-        <v>Peças.Sanitárias</v>
-      </c>
-      <c r="V25" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="W25" s="57" t="str">
+      <c r="X25" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-25</v>
       </c>
-      <c r="X25" s="28" t="s">
-        <v>183</v>
-      </c>
       <c r="Y25" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="Z25" s="29" t="s">
-        <v>156</v>
-      </c>
-      <c r="AA25" s="29" t="str">
-        <f t="shared" si="26"/>
-        <v>Bidet</v>
-      </c>
-    </row>
-    <row r="26" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>181</v>
+      </c>
+      <c r="Z25" s="28" t="s">
+        <v>340</v>
+      </c>
+      <c r="AA25" s="28" t="s">
+        <v>182</v>
+      </c>
+      <c r="AB25" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="AC25" s="29" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="26" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="56">
         <v>26</v>
       </c>
       <c r="B26" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C26" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C26" s="41" t="s">
-        <v>246</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="E26" s="41" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F26" s="41" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G26" s="58" t="s">
         <v>9</v>
@@ -4755,15 +5061,15 @@
         <v>9</v>
       </c>
       <c r="L26" s="32" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M26" s="32" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="19"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N26" s="32" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v>Peças Sanitárias</v>
       </c>
       <c r="O26" s="29" t="str">
@@ -4771,63 +5077,68 @@
         <v>Pia.Sanitária</v>
       </c>
       <c r="P26" s="51" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="Q26" s="29" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="R26" s="29" t="s">
-        <v>9</v>
+        <v>317</v>
       </c>
       <c r="S26" s="29" t="s">
-        <v>153</v>
+        <v>9</v>
       </c>
       <c r="T26" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="U26" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="V26" s="29" t="str">
+        <f t="shared" si="21"/>
+        <v>Peças.Sanitárias</v>
+      </c>
+      <c r="W26" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="U26" s="29" t="str">
-        <f t="shared" si="25"/>
-        <v>Peças.Sanitárias</v>
-      </c>
-      <c r="V26" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="W26" s="57" t="str">
+      <c r="X26" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-26</v>
       </c>
-      <c r="X26" s="28" t="s">
-        <v>183</v>
-      </c>
       <c r="Y26" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="Z26" s="29" t="s">
-        <v>156</v>
-      </c>
-      <c r="AA26" s="29" t="str">
-        <f t="shared" si="26"/>
-        <v>Sanitary Sink</v>
-      </c>
-    </row>
-    <row r="27" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>181</v>
+      </c>
+      <c r="Z26" s="28" t="s">
+        <v>340</v>
+      </c>
+      <c r="AA26" s="28" t="s">
+        <v>182</v>
+      </c>
+      <c r="AB26" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="AC26" s="29" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="27" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="56">
         <v>27</v>
       </c>
       <c r="B27" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C27" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C27" s="41" t="s">
-        <v>246</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="E27" s="41" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F27" s="41" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G27" s="58" t="s">
         <v>9</v>
@@ -4845,15 +5156,15 @@
         <v>9</v>
       </c>
       <c r="L27" s="32" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M27" s="32" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="19"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N27" s="32" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v>Peças Sanitárias</v>
       </c>
       <c r="O27" s="29" t="str">
@@ -4861,64 +5172,68 @@
         <v>Lavatório</v>
       </c>
       <c r="P27" s="51" t="s">
-        <v>168</v>
-      </c>
-      <c r="Q27" s="29" t="str">
-        <f t="shared" si="28"/>
-        <v>Lavabo</v>
+        <v>166</v>
+      </c>
+      <c r="Q27" s="29" t="s">
+        <v>290</v>
       </c>
       <c r="R27" s="29" t="s">
-        <v>9</v>
+        <v>318</v>
       </c>
       <c r="S27" s="29" t="s">
-        <v>153</v>
+        <v>9</v>
       </c>
       <c r="T27" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="U27" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="V27" s="29" t="str">
+        <f t="shared" si="21"/>
+        <v>Peças.Sanitárias</v>
+      </c>
+      <c r="W27" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="U27" s="29" t="str">
-        <f t="shared" si="25"/>
-        <v>Peças.Sanitárias</v>
-      </c>
-      <c r="V27" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="W27" s="57" t="str">
+      <c r="X27" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-27</v>
       </c>
-      <c r="X27" s="28" t="s">
-        <v>183</v>
-      </c>
       <c r="Y27" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="Z27" s="29" t="s">
-        <v>156</v>
-      </c>
-      <c r="AA27" s="29" t="str">
-        <f t="shared" si="26"/>
-        <v>Washbasin</v>
-      </c>
-    </row>
-    <row r="28" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>181</v>
+      </c>
+      <c r="Z27" s="28" t="s">
+        <v>340</v>
+      </c>
+      <c r="AA27" s="28" t="s">
+        <v>182</v>
+      </c>
+      <c r="AB27" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="AC27" s="29" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="28" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="56">
         <v>28</v>
       </c>
       <c r="B28" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C28" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C28" s="41" t="s">
-        <v>246</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="E28" s="41" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F28" s="41" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G28" s="58" t="s">
         <v>9</v>
@@ -4936,15 +5251,15 @@
         <v>9</v>
       </c>
       <c r="L28" s="32" t="str">
-        <f t="shared" ref="L28" si="29">CONCATENATE("", C28)</f>
+        <f t="shared" ref="L28" si="22">CONCATENATE("", C28)</f>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M28" s="32" t="str">
-        <f t="shared" ref="M28" si="30">CONCATENATE("", D28)</f>
+        <f t="shared" ref="M28" si="23">CONCATENATE("", D28)</f>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N28" s="32" t="str">
-        <f t="shared" ref="N28" si="31">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E28),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N28" si="24">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E28),"."," ")," De "," de "))</f>
         <v>Peças Sanitárias</v>
       </c>
       <c r="O28" s="29" t="str">
@@ -4952,63 +5267,68 @@
         <v>Cuba.Sanitária</v>
       </c>
       <c r="P28" s="51" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q28" s="29" t="s">
         <v>179</v>
       </c>
-      <c r="Q28" s="29" t="s">
-        <v>181</v>
-      </c>
       <c r="R28" s="29" t="s">
-        <v>9</v>
+        <v>319</v>
       </c>
       <c r="S28" s="29" t="s">
-        <v>153</v>
+        <v>9</v>
       </c>
       <c r="T28" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="U28" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="V28" s="29" t="str">
+        <f t="shared" ref="V28" si="25">SUBSTITUTE(E28, "_", " ")</f>
+        <v>Peças.Sanitárias</v>
+      </c>
+      <c r="W28" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="U28" s="29" t="str">
-        <f t="shared" ref="U28" si="32">SUBSTITUTE(E28, "_", " ")</f>
-        <v>Peças.Sanitárias</v>
-      </c>
-      <c r="V28" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="W28" s="57" t="str">
+      <c r="X28" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-28</v>
       </c>
-      <c r="X28" s="28" t="s">
-        <v>183</v>
-      </c>
       <c r="Y28" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="Z28" s="29" t="s">
-        <v>156</v>
-      </c>
-      <c r="AA28" s="29" t="str">
-        <f t="shared" ref="AA28" si="33">_xlfn.TRANSLATE(P28,"pt","en")</f>
-        <v>Sanitary Bowl</v>
-      </c>
-    </row>
-    <row r="29" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>181</v>
+      </c>
+      <c r="Z28" s="28" t="s">
+        <v>340</v>
+      </c>
+      <c r="AA28" s="28" t="s">
+        <v>182</v>
+      </c>
+      <c r="AB28" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="AC28" s="29" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="29" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="56">
         <v>29</v>
       </c>
       <c r="B29" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C29" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C29" s="41" t="s">
-        <v>246</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="E29" s="41" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F29" s="41" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G29" s="58" t="s">
         <v>9</v>
@@ -5026,15 +5346,15 @@
         <v>9</v>
       </c>
       <c r="L29" s="32" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M29" s="32" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="19"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N29" s="32" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v>Peças Sanitárias</v>
       </c>
       <c r="O29" s="29" t="str">
@@ -5042,64 +5362,68 @@
         <v>Banheira</v>
       </c>
       <c r="P29" s="51" t="s">
-        <v>173</v>
-      </c>
-      <c r="Q29" s="29" t="str">
-        <f t="shared" si="28"/>
-        <v>Bañera</v>
+        <v>171</v>
+      </c>
+      <c r="Q29" s="29" t="s">
+        <v>291</v>
       </c>
       <c r="R29" s="29" t="s">
-        <v>9</v>
+        <v>320</v>
       </c>
       <c r="S29" s="29" t="s">
-        <v>153</v>
+        <v>9</v>
       </c>
       <c r="T29" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="U29" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="V29" s="29" t="str">
+        <f t="shared" si="21"/>
+        <v>Peças.Sanitárias</v>
+      </c>
+      <c r="W29" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="U29" s="29" t="str">
-        <f t="shared" si="25"/>
-        <v>Peças.Sanitárias</v>
-      </c>
-      <c r="V29" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="W29" s="57" t="str">
+      <c r="X29" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-29</v>
       </c>
-      <c r="X29" s="28" t="s">
-        <v>183</v>
-      </c>
       <c r="Y29" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="Z29" s="29" t="s">
-        <v>156</v>
-      </c>
-      <c r="AA29" s="29" t="str">
-        <f t="shared" si="26"/>
-        <v>Bathtub</v>
-      </c>
-    </row>
-    <row r="30" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>181</v>
+      </c>
+      <c r="Z29" s="28" t="s">
+        <v>340</v>
+      </c>
+      <c r="AA29" s="28" t="s">
+        <v>182</v>
+      </c>
+      <c r="AB29" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="AC29" s="29" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="30" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="56">
         <v>30</v>
       </c>
       <c r="B30" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C30" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C30" s="41" t="s">
-        <v>246</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="E30" s="41" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F30" s="41" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G30" s="58" t="s">
         <v>9</v>
@@ -5117,15 +5441,15 @@
         <v>9</v>
       </c>
       <c r="L30" s="32" t="str">
-        <f t="shared" ref="L30" si="34">CONCATENATE("", C30)</f>
+        <f t="shared" ref="L30" si="26">CONCATENATE("", C30)</f>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M30" s="32" t="str">
-        <f t="shared" ref="M30" si="35">CONCATENATE("", D30)</f>
+        <f t="shared" ref="M30" si="27">CONCATENATE("", D30)</f>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N30" s="32" t="str">
-        <f t="shared" ref="N30" si="36">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E30),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N30" si="28">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E30),"."," ")," De "," de "))</f>
         <v>Esgoto Coletores</v>
       </c>
       <c r="O30" s="29" t="str">
@@ -5133,63 +5457,68 @@
         <v>Ventilação.Esgoto</v>
       </c>
       <c r="P30" s="51" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q30" s="51" t="s">
+        <v>149</v>
+      </c>
+      <c r="R30" s="29" t="s">
+        <v>321</v>
+      </c>
+      <c r="S30" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="T30" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="U30" s="29" t="s">
         <v>150</v>
       </c>
-      <c r="Q30" s="51" t="s">
-        <v>151</v>
-      </c>
-      <c r="R30" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="S30" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="T30" s="29" t="s">
+      <c r="V30" s="29" t="str">
+        <f t="shared" ref="V30" si="29">SUBSTITUTE(E30, "_", " ")</f>
+        <v>Esgoto.Coletores</v>
+      </c>
+      <c r="W30" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="U30" s="29" t="str">
-        <f t="shared" ref="U30" si="37">SUBSTITUTE(E30, "_", " ")</f>
-        <v>Esgoto.Coletores</v>
-      </c>
-      <c r="V30" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="W30" s="57" t="str">
+      <c r="X30" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-30</v>
       </c>
-      <c r="X30" s="28" t="s">
-        <v>249</v>
-      </c>
       <c r="Y30" s="28" t="s">
-        <v>250</v>
-      </c>
-      <c r="Z30" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="AA30" s="29" t="str">
-        <f>_xlfn.TRANSLATE(P30,"pt","en")</f>
-        <v>Sewer Ventilation</v>
-      </c>
-    </row>
-    <row r="31" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>247</v>
+      </c>
+      <c r="Z30" s="28" t="s">
+        <v>340</v>
+      </c>
+      <c r="AA30" s="28" t="s">
+        <v>248</v>
+      </c>
+      <c r="AB30" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="AC30" s="29" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="31" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="56">
         <v>31</v>
       </c>
       <c r="B31" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C31" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C31" s="41" t="s">
-        <v>246</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="E31" s="41" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F31" s="41" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G31" s="58" t="s">
         <v>9</v>
@@ -5207,15 +5536,15 @@
         <v>9</v>
       </c>
       <c r="L31" s="32" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M31" s="32" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="19"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N31" s="32" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v>Esgoto Coletores</v>
       </c>
       <c r="O31" s="29" t="str">
@@ -5223,63 +5552,68 @@
         <v>Ralo.Seco</v>
       </c>
       <c r="P31" s="51" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="Q31" s="29" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="R31" s="29" t="s">
-        <v>9</v>
+        <v>322</v>
       </c>
       <c r="S31" s="29" t="s">
-        <v>153</v>
+        <v>9</v>
       </c>
       <c r="T31" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="U31" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="V31" s="29" t="str">
+        <f t="shared" si="21"/>
+        <v>Esgoto.Coletores</v>
+      </c>
+      <c r="W31" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="U31" s="29" t="str">
-        <f t="shared" si="25"/>
-        <v>Esgoto.Coletores</v>
-      </c>
-      <c r="V31" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="W31" s="57" t="str">
+      <c r="X31" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-31</v>
       </c>
-      <c r="X31" s="28" t="s">
-        <v>249</v>
-      </c>
       <c r="Y31" s="28" t="s">
-        <v>250</v>
-      </c>
-      <c r="Z31" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="AA31" s="29" t="str">
-        <f t="shared" ref="AA31:AA41" si="38">_xlfn.TRANSLATE(P31,"pt","en")</f>
-        <v>Local Collector as a Dry Drain or Basin Valve</v>
-      </c>
-    </row>
-    <row r="32" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>247</v>
+      </c>
+      <c r="Z31" s="28" t="s">
+        <v>340</v>
+      </c>
+      <c r="AA31" s="28" t="s">
+        <v>248</v>
+      </c>
+      <c r="AB31" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="AC31" s="29" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="32" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="56">
         <v>32</v>
       </c>
       <c r="B32" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C32" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C32" s="41" t="s">
-        <v>246</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="E32" s="41" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F32" s="41" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G32" s="58" t="s">
         <v>9</v>
@@ -5297,15 +5631,15 @@
         <v>9</v>
       </c>
       <c r="L32" s="32" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M32" s="32" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="19"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N32" s="32" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v>Esgoto Coletores</v>
       </c>
       <c r="O32" s="29" t="str">
@@ -5313,63 +5647,68 @@
         <v>Ralo.Sifonado</v>
       </c>
       <c r="P32" s="51" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Q32" s="29" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="R32" s="29" t="s">
-        <v>9</v>
+        <v>323</v>
       </c>
       <c r="S32" s="29" t="s">
-        <v>153</v>
+        <v>9</v>
       </c>
       <c r="T32" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="U32" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="V32" s="29" t="str">
+        <f t="shared" si="21"/>
+        <v>Esgoto.Coletores</v>
+      </c>
+      <c r="W32" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="U32" s="29" t="str">
-        <f t="shared" si="25"/>
-        <v>Esgoto.Coletores</v>
-      </c>
-      <c r="V32" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="W32" s="57" t="str">
+      <c r="X32" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-32</v>
       </c>
-      <c r="X32" s="28" t="s">
-        <v>249</v>
-      </c>
       <c r="Y32" s="28" t="s">
-        <v>250</v>
-      </c>
-      <c r="Z32" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="AA32" s="29" t="str">
-        <f t="shared" si="38"/>
-        <v>Siphoned Collector as a Siphoned Drain</v>
-      </c>
-    </row>
-    <row r="33" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>247</v>
+      </c>
+      <c r="Z32" s="28" t="s">
+        <v>340</v>
+      </c>
+      <c r="AA32" s="28" t="s">
+        <v>248</v>
+      </c>
+      <c r="AB32" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="AC32" s="29" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="33" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="56">
         <v>33</v>
       </c>
       <c r="B33" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C33" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="D33" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C33" s="41" t="s">
-        <v>246</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="E33" s="41" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F33" s="41" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G33" s="58" t="s">
         <v>9</v>
@@ -5387,15 +5726,15 @@
         <v>9</v>
       </c>
       <c r="L33" s="32" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M33" s="32" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="19"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N33" s="32" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v>Esgoto Coletores</v>
       </c>
       <c r="O33" s="29" t="str">
@@ -5403,63 +5742,68 @@
         <v>Coletor.Andar</v>
       </c>
       <c r="P33" s="51" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="Q33" s="29" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="R33" s="29" t="s">
-        <v>9</v>
+        <v>324</v>
       </c>
       <c r="S33" s="29" t="s">
-        <v>153</v>
+        <v>9</v>
       </c>
       <c r="T33" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="U33" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="V33" s="29" t="str">
+        <f t="shared" si="21"/>
+        <v>Esgoto.Coletores</v>
+      </c>
+      <c r="W33" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="U33" s="29" t="str">
-        <f t="shared" si="25"/>
-        <v>Esgoto.Coletores</v>
-      </c>
-      <c r="V33" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="W33" s="57" t="str">
+      <c r="X33" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-33</v>
       </c>
-      <c r="X33" s="28" t="s">
-        <v>249</v>
-      </c>
       <c r="Y33" s="28" t="s">
-        <v>250</v>
-      </c>
-      <c r="Z33" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="AA33" s="29" t="str">
-        <f t="shared" si="38"/>
-        <v>Floor Horizontal Collection Branch</v>
-      </c>
-    </row>
-    <row r="34" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>247</v>
+      </c>
+      <c r="Z33" s="28" t="s">
+        <v>340</v>
+      </c>
+      <c r="AA33" s="28" t="s">
+        <v>248</v>
+      </c>
+      <c r="AB33" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="AC33" s="29" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="34" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="56">
         <v>34</v>
       </c>
       <c r="B34" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C34" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C34" s="41" t="s">
-        <v>246</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="E34" s="41" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F34" s="41" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G34" s="58" t="s">
         <v>9</v>
@@ -5477,15 +5821,15 @@
         <v>9</v>
       </c>
       <c r="L34" s="32" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M34" s="32" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="19"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N34" s="32" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v>Esgoto Coletores</v>
       </c>
       <c r="O34" s="29" t="str">
@@ -5493,63 +5837,68 @@
         <v>Coletor.Predial</v>
       </c>
       <c r="P34" s="51" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="Q34" s="29" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="R34" s="29" t="s">
-        <v>9</v>
+        <v>325</v>
       </c>
       <c r="S34" s="29" t="s">
-        <v>153</v>
+        <v>9</v>
       </c>
       <c r="T34" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="U34" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="V34" s="29" t="str">
+        <f t="shared" si="21"/>
+        <v>Esgoto.Coletores</v>
+      </c>
+      <c r="W34" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="U34" s="29" t="str">
-        <f t="shared" si="25"/>
-        <v>Esgoto.Coletores</v>
-      </c>
-      <c r="V34" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="W34" s="57" t="str">
+      <c r="X34" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-34</v>
       </c>
-      <c r="X34" s="28" t="s">
-        <v>249</v>
-      </c>
       <c r="Y34" s="28" t="s">
-        <v>250</v>
-      </c>
-      <c r="Z34" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="AA34" s="29" t="str">
-        <f t="shared" si="38"/>
-        <v>Horizontal collection branch of the building</v>
-      </c>
-    </row>
-    <row r="35" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>247</v>
+      </c>
+      <c r="Z34" s="28" t="s">
+        <v>340</v>
+      </c>
+      <c r="AA34" s="28" t="s">
+        <v>248</v>
+      </c>
+      <c r="AB34" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="AC34" s="29" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="35" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="56">
         <v>35</v>
       </c>
       <c r="B35" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C35" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="D35" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C35" s="41" t="s">
-        <v>246</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="E35" s="41" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F35" s="41" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G35" s="58" t="s">
         <v>9</v>
@@ -5567,15 +5916,15 @@
         <v>9</v>
       </c>
       <c r="L35" s="32" t="str">
-        <f t="shared" ref="L35" si="39">CONCATENATE("", C35)</f>
+        <f t="shared" ref="L35" si="30">CONCATENATE("", C35)</f>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M35" s="32" t="str">
-        <f t="shared" ref="M35" si="40">CONCATENATE("", D35)</f>
+        <f t="shared" ref="M35" si="31">CONCATENATE("", D35)</f>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N35" s="32" t="str">
-        <f t="shared" ref="N35" si="41">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E35),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N35" si="32">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E35),"."," ")," De "," de "))</f>
         <v>Esgoto Coletores</v>
       </c>
       <c r="O35" s="29" t="str">
@@ -5583,63 +5932,68 @@
         <v>Tubo.de.Queda</v>
       </c>
       <c r="P35" s="51" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="Q35" s="29" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="R35" s="29" t="s">
-        <v>9</v>
+        <v>326</v>
       </c>
       <c r="S35" s="29" t="s">
-        <v>153</v>
+        <v>9</v>
       </c>
       <c r="T35" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="U35" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="V35" s="29" t="str">
+        <f t="shared" ref="V35" si="33">SUBSTITUTE(E35, "_", " ")</f>
+        <v>Esgoto.Coletores</v>
+      </c>
+      <c r="W35" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="U35" s="29" t="str">
-        <f t="shared" ref="U35" si="42">SUBSTITUTE(E35, "_", " ")</f>
-        <v>Esgoto.Coletores</v>
-      </c>
-      <c r="V35" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="W35" s="57" t="str">
+      <c r="X35" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-35</v>
       </c>
-      <c r="X35" s="28" t="s">
-        <v>249</v>
-      </c>
       <c r="Y35" s="28" t="s">
-        <v>250</v>
-      </c>
-      <c r="Z35" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="AA35" s="29" t="str">
-        <f t="shared" si="38"/>
-        <v>Downpipe</v>
-      </c>
-    </row>
-    <row r="36" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>247</v>
+      </c>
+      <c r="Z35" s="28" t="s">
+        <v>340</v>
+      </c>
+      <c r="AA35" s="28" t="s">
+        <v>248</v>
+      </c>
+      <c r="AB35" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="AC35" s="29" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="36" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="56">
         <v>36</v>
       </c>
       <c r="B36" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C36" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C36" s="41" t="s">
-        <v>246</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="E36" s="41" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F36" s="41" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="G36" s="58" t="s">
         <v>9</v>
@@ -5657,15 +6011,15 @@
         <v>9</v>
       </c>
       <c r="L36" s="32" t="str">
-        <f t="shared" ref="L36" si="43">CONCATENATE("", C36)</f>
+        <f t="shared" ref="L36" si="34">CONCATENATE("", C36)</f>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M36" s="32" t="str">
-        <f t="shared" ref="M36" si="44">CONCATENATE("", D36)</f>
+        <f t="shared" ref="M36" si="35">CONCATENATE("", D36)</f>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N36" s="32" t="str">
-        <f t="shared" ref="N36" si="45">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E36),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N36" si="36">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E36),"."," ")," De "," de "))</f>
         <v>Esgoto Coletores</v>
       </c>
       <c r="O36" s="29" t="str">
@@ -5673,63 +6027,68 @@
         <v>Fecho.Hidráulico</v>
       </c>
       <c r="P36" s="51" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="Q36" s="29" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="R36" s="29" t="s">
-        <v>9</v>
+        <v>327</v>
       </c>
       <c r="S36" s="29" t="s">
-        <v>153</v>
+        <v>9</v>
       </c>
       <c r="T36" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="U36" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="V36" s="29" t="str">
+        <f t="shared" ref="V36" si="37">SUBSTITUTE(E36, "_", " ")</f>
+        <v>Esgoto.Coletores</v>
+      </c>
+      <c r="W36" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="U36" s="29" t="str">
-        <f t="shared" ref="U36" si="46">SUBSTITUTE(E36, "_", " ")</f>
-        <v>Esgoto.Coletores</v>
-      </c>
-      <c r="V36" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="W36" s="57" t="str">
+      <c r="X36" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-36</v>
       </c>
-      <c r="X36" s="28" t="s">
-        <v>249</v>
-      </c>
       <c r="Y36" s="28" t="s">
-        <v>250</v>
-      </c>
-      <c r="Z36" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="AA36" s="29" t="str">
-        <f t="shared" si="38"/>
-        <v>Siphons</v>
-      </c>
-    </row>
-    <row r="37" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>247</v>
+      </c>
+      <c r="Z36" s="28" t="s">
+        <v>340</v>
+      </c>
+      <c r="AA36" s="28" t="s">
+        <v>248</v>
+      </c>
+      <c r="AB36" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="AC36" s="29" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="37" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="56">
         <v>37</v>
       </c>
       <c r="B37" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C37" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="D37" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C37" s="41" t="s">
-        <v>246</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="E37" s="41" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F37" s="41" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G37" s="58" t="s">
         <v>9</v>
@@ -5747,15 +6106,15 @@
         <v>9</v>
       </c>
       <c r="L37" s="32" t="str">
-        <f t="shared" ref="L37:L41" si="47">CONCATENATE("", C37)</f>
+        <f t="shared" ref="L37:L41" si="38">CONCATENATE("", C37)</f>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M37" s="32" t="str">
-        <f t="shared" ref="M37:M41" si="48">CONCATENATE("", D37)</f>
+        <f t="shared" ref="M37:M41" si="39">CONCATENATE("", D37)</f>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N37" s="32" t="str">
-        <f t="shared" ref="N37:N41" si="49">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E37),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N37:N41" si="40">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E37),"."," ")," De "," de "))</f>
         <v>Esgoto Visitas</v>
       </c>
       <c r="O37" s="29" t="str">
@@ -5763,63 +6122,68 @@
         <v>Caixa.de.Areia</v>
       </c>
       <c r="P37" s="51" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="Q37" s="29" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="R37" s="29" t="s">
-        <v>9</v>
+        <v>328</v>
       </c>
       <c r="S37" s="29" t="s">
-        <v>153</v>
+        <v>9</v>
       </c>
       <c r="T37" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="U37" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="V37" s="29" t="str">
+        <f t="shared" ref="V37:V41" si="41">SUBSTITUTE(E37, "_", " ")</f>
+        <v>Esgoto.Visitas</v>
+      </c>
+      <c r="W37" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="U37" s="29" t="str">
-        <f t="shared" ref="U37:U41" si="50">SUBSTITUTE(E37, "_", " ")</f>
-        <v>Esgoto.Visitas</v>
-      </c>
-      <c r="V37" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="W37" s="57" t="str">
+      <c r="X37" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-37</v>
       </c>
-      <c r="X37" s="28" t="s">
-        <v>249</v>
-      </c>
       <c r="Y37" s="28" t="s">
-        <v>250</v>
-      </c>
-      <c r="Z37" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="AA37" s="29" t="str">
-        <f t="shared" si="38"/>
-        <v>Sandboxes</v>
-      </c>
-    </row>
-    <row r="38" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>247</v>
+      </c>
+      <c r="Z37" s="28" t="s">
+        <v>340</v>
+      </c>
+      <c r="AA37" s="28" t="s">
+        <v>248</v>
+      </c>
+      <c r="AB37" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="AC37" s="29" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="38" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="56">
         <v>38</v>
       </c>
       <c r="B38" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C38" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="D38" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C38" s="41" t="s">
-        <v>246</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="E38" s="41" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F38" s="41" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G38" s="58" t="s">
         <v>9</v>
@@ -5837,15 +6201,15 @@
         <v>9</v>
       </c>
       <c r="L38" s="32" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="38"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M38" s="32" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="39"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N38" s="32" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="40"/>
         <v>Esgoto Visitas</v>
       </c>
       <c r="O38" s="29" t="str">
@@ -5853,63 +6217,68 @@
         <v>Caixa.de.Gordura</v>
       </c>
       <c r="P38" s="51" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="Q38" s="29" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="R38" s="29" t="s">
-        <v>9</v>
+        <v>329</v>
       </c>
       <c r="S38" s="29" t="s">
-        <v>153</v>
+        <v>9</v>
       </c>
       <c r="T38" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="U38" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="V38" s="29" t="str">
+        <f t="shared" si="41"/>
+        <v>Esgoto.Visitas</v>
+      </c>
+      <c r="W38" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="U38" s="29" t="str">
-        <f t="shared" si="50"/>
-        <v>Esgoto.Visitas</v>
-      </c>
-      <c r="V38" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="W38" s="57" t="str">
+      <c r="X38" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-38</v>
       </c>
-      <c r="X38" s="28" t="s">
-        <v>249</v>
-      </c>
       <c r="Y38" s="28" t="s">
-        <v>250</v>
-      </c>
-      <c r="Z38" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="AA38" s="29" t="str">
-        <f t="shared" si="38"/>
-        <v>Grease Traps</v>
-      </c>
-    </row>
-    <row r="39" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>247</v>
+      </c>
+      <c r="Z38" s="28" t="s">
+        <v>340</v>
+      </c>
+      <c r="AA38" s="28" t="s">
+        <v>248</v>
+      </c>
+      <c r="AB38" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="AC38" s="29" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="39" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="56">
         <v>39</v>
       </c>
       <c r="B39" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C39" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C39" s="41" t="s">
-        <v>246</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="E39" s="41" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F39" s="41" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G39" s="58" t="s">
         <v>9</v>
@@ -5927,15 +6296,15 @@
         <v>9</v>
       </c>
       <c r="L39" s="32" t="str">
-        <f t="shared" ref="L39:L40" si="51">CONCATENATE("", C39)</f>
+        <f t="shared" ref="L39:L40" si="42">CONCATENATE("", C39)</f>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M39" s="32" t="str">
-        <f t="shared" ref="M39:M40" si="52">CONCATENATE("", D39)</f>
+        <f t="shared" ref="M39:M40" si="43">CONCATENATE("", D39)</f>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N39" s="32" t="str">
-        <f t="shared" ref="N39:N40" si="53">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E39),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N39:N40" si="44">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E39),"."," ")," De "," de "))</f>
         <v>Esgoto Visitas</v>
       </c>
       <c r="O39" s="29" t="str">
@@ -5943,63 +6312,68 @@
         <v>Caixa.de.Inspeção</v>
       </c>
       <c r="P39" s="51" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="Q39" s="29" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="R39" s="29" t="s">
-        <v>9</v>
+        <v>330</v>
       </c>
       <c r="S39" s="29" t="s">
-        <v>153</v>
+        <v>9</v>
       </c>
       <c r="T39" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="U39" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="V39" s="29" t="str">
+        <f t="shared" ref="V39:V40" si="45">SUBSTITUTE(E39, "_", " ")</f>
+        <v>Esgoto.Visitas</v>
+      </c>
+      <c r="W39" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="U39" s="29" t="str">
-        <f t="shared" ref="U39:U40" si="54">SUBSTITUTE(E39, "_", " ")</f>
-        <v>Esgoto.Visitas</v>
-      </c>
-      <c r="V39" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="W39" s="57" t="str">
+      <c r="X39" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-39</v>
       </c>
-      <c r="X39" s="28" t="s">
-        <v>249</v>
-      </c>
       <c r="Y39" s="28" t="s">
-        <v>250</v>
-      </c>
-      <c r="Z39" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="AA39" s="29" t="str">
-        <f t="shared" si="38"/>
-        <v>Manholes</v>
-      </c>
-    </row>
-    <row r="40" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>247</v>
+      </c>
+      <c r="Z39" s="28" t="s">
+        <v>340</v>
+      </c>
+      <c r="AA39" s="28" t="s">
+        <v>248</v>
+      </c>
+      <c r="AB39" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="AC39" s="29" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="40" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="56">
         <v>40</v>
       </c>
       <c r="B40" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C40" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="D40" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C40" s="41" t="s">
-        <v>246</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="E40" s="41" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F40" s="41" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G40" s="58" t="s">
         <v>9</v>
@@ -6017,15 +6391,15 @@
         <v>9</v>
       </c>
       <c r="L40" s="32" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="42"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M40" s="32" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="43"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N40" s="32" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="44"/>
         <v>Esgoto Visitas</v>
       </c>
       <c r="O40" s="29" t="str">
@@ -6033,63 +6407,68 @@
         <v>Caixa.Sifonada</v>
       </c>
       <c r="P40" s="51" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="Q40" s="29" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R40" s="29" t="s">
-        <v>9</v>
+        <v>331</v>
       </c>
       <c r="S40" s="29" t="s">
-        <v>153</v>
+        <v>9</v>
       </c>
       <c r="T40" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="U40" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="V40" s="29" t="str">
+        <f t="shared" si="45"/>
+        <v>Esgoto.Visitas</v>
+      </c>
+      <c r="W40" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="U40" s="29" t="str">
-        <f t="shared" si="54"/>
-        <v>Esgoto.Visitas</v>
-      </c>
-      <c r="V40" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="W40" s="57" t="str">
+      <c r="X40" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-40</v>
       </c>
-      <c r="X40" s="28" t="s">
-        <v>249</v>
-      </c>
       <c r="Y40" s="28" t="s">
-        <v>250</v>
-      </c>
-      <c r="Z40" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="AA40" s="29" t="str">
-        <f t="shared" si="38"/>
-        <v>Siphon Boxes</v>
-      </c>
-    </row>
-    <row r="41" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>247</v>
+      </c>
+      <c r="Z40" s="28" t="s">
+        <v>340</v>
+      </c>
+      <c r="AA40" s="28" t="s">
+        <v>248</v>
+      </c>
+      <c r="AB40" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="AC40" s="29" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="41" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="56">
         <v>41</v>
       </c>
       <c r="B41" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C41" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C41" s="41" t="s">
-        <v>246</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="E41" s="41" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F41" s="41" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G41" s="58" t="s">
         <v>9</v>
@@ -6107,15 +6486,15 @@
         <v>9</v>
       </c>
       <c r="L41" s="32" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="38"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M41" s="32" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="39"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N41" s="32" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="40"/>
         <v>Esgoto Visitas</v>
       </c>
       <c r="O41" s="29" t="str">
@@ -6123,63 +6502,68 @@
         <v>Poço.de.Visita</v>
       </c>
       <c r="P41" s="51" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q41" s="29" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="R41" s="29" t="s">
-        <v>9</v>
+        <v>330</v>
       </c>
       <c r="S41" s="29" t="s">
-        <v>153</v>
+        <v>9</v>
       </c>
       <c r="T41" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="U41" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="V41" s="29" t="str">
+        <f t="shared" si="41"/>
+        <v>Esgoto.Visitas</v>
+      </c>
+      <c r="W41" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="U41" s="29" t="str">
-        <f t="shared" si="50"/>
-        <v>Esgoto.Visitas</v>
-      </c>
-      <c r="V41" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="W41" s="57" t="str">
+      <c r="X41" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-41</v>
       </c>
-      <c r="X41" s="28" t="s">
-        <v>249</v>
-      </c>
       <c r="Y41" s="28" t="s">
-        <v>250</v>
-      </c>
-      <c r="Z41" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="AA41" s="29" t="str">
-        <f t="shared" si="38"/>
-        <v>Manholes</v>
-      </c>
-    </row>
-    <row r="42" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>247</v>
+      </c>
+      <c r="Z41" s="28" t="s">
+        <v>340</v>
+      </c>
+      <c r="AA41" s="28" t="s">
+        <v>248</v>
+      </c>
+      <c r="AB41" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="AC41" s="29" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="42" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="56">
         <v>42</v>
       </c>
       <c r="B42" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C42" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="D42" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C42" s="41" t="s">
-        <v>246</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="E42" s="41" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F42" s="41" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G42" s="58" t="s">
         <v>9</v>
@@ -6197,15 +6581,15 @@
         <v>9</v>
       </c>
       <c r="L42" s="32" t="str">
-        <f t="shared" ref="L42" si="55">CONCATENATE("", C42)</f>
+        <f t="shared" ref="L42" si="46">CONCATENATE("", C42)</f>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M42" s="32" t="str">
-        <f t="shared" ref="M42" si="56">CONCATENATE("", D42)</f>
+        <f t="shared" ref="M42" si="47">CONCATENATE("", D42)</f>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N42" s="32" t="str">
-        <f t="shared" ref="N42" si="57">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E42),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N42" si="48">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E42),"."," ")," De "," de "))</f>
         <v>Esgoto Acessórios</v>
       </c>
       <c r="O42" s="29" t="str">
@@ -6213,64 +6597,69 @@
         <v>Acessório.Sanitário</v>
       </c>
       <c r="P42" s="51" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="Q42" s="51" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="R42" s="29" t="s">
-        <v>9</v>
+        <v>332</v>
       </c>
       <c r="S42" s="29" t="s">
-        <v>153</v>
+        <v>9</v>
       </c>
       <c r="T42" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="U42" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="V42" s="29" t="str">
+        <f t="shared" ref="V42" si="49">SUBSTITUTE(E42, "_", " ")</f>
+        <v>Esgoto.Acessórios</v>
+      </c>
+      <c r="W42" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="U42" s="29" t="str">
-        <f t="shared" ref="U42" si="58">SUBSTITUTE(E42, "_", " ")</f>
-        <v>Esgoto.Acessórios</v>
-      </c>
-      <c r="V42" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="W42" s="57" t="str">
+      <c r="X42" s="57" t="str">
         <f t="shared" si="5"/>
         <v>Key-HIDR-42</v>
       </c>
-      <c r="X42" s="28" t="s">
-        <v>237</v>
-      </c>
       <c r="Y42" s="28" t="s">
-        <v>236</v>
-      </c>
-      <c r="Z42" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="AA42" s="29" t="str">
-        <f t="shared" ref="AA42" si="59">_xlfn.TRANSLATE(P42,"pt","en")</f>
-        <v>Sanitary sewer system accessory like brackets, hooks, pedestals, etc.</v>
-      </c>
-    </row>
-    <row r="43" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>235</v>
+      </c>
+      <c r="Z42" s="28" t="s">
+        <v>340</v>
+      </c>
+      <c r="AA42" s="28" t="s">
+        <v>234</v>
+      </c>
+      <c r="AB42" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="AC42" s="29" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="43" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="56">
         <v>43</v>
       </c>
       <c r="B43" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C43" s="41" t="s">
+        <v>270</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="E43" s="41" t="s">
+        <v>276</v>
+      </c>
+      <c r="F43" s="41" t="s">
         <v>271</v>
       </c>
-      <c r="C43" s="41" t="s">
-        <v>272</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="E43" s="41" t="s">
-        <v>278</v>
-      </c>
-      <c r="F43" s="41" t="s">
-        <v>273</v>
-      </c>
       <c r="G43" s="58" t="s">
         <v>9</v>
       </c>
@@ -6287,81 +6676,85 @@
         <v>9</v>
       </c>
       <c r="L43" s="32" t="str">
-        <f t="shared" ref="L43" si="60">CONCATENATE("", C43)</f>
+        <f t="shared" ref="L43" si="50">CONCATENATE("", C43)</f>
         <v>De.Tubulações</v>
       </c>
       <c r="M43" s="32" t="str">
-        <f t="shared" ref="M43" si="61">CONCATENATE("", D43)</f>
+        <f t="shared" ref="M43" si="51">CONCATENATE("", D43)</f>
         <v>Elementos.de.Instalações</v>
       </c>
       <c r="N43" s="32" t="str">
-        <f t="shared" ref="N43" si="62">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E43),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N43" si="52">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E43),"."," ")," De "," de "))</f>
         <v>Instalação De</v>
       </c>
       <c r="O43" s="29" t="str">
-        <f t="shared" ref="O43:P43" si="63">IF(ISNUMBER(FIND("Ifc",F43)),CONCATENATE("Classe IFC:   ",F43),CONCATENATE("",F43))</f>
+        <f t="shared" ref="O43" si="53">IF(ISNUMBER(FIND("Ifc",F43)),CONCATENATE("Classe IFC:   ",F43),CONCATENATE("",F43))</f>
         <v>Esgoto</v>
       </c>
       <c r="P43" s="51" t="s">
-        <v>281</v>
-      </c>
-      <c r="Q43" s="51" t="str">
-        <f>_xlfn.TRANSLATE(P43,"pt","es")</f>
-        <v>Instalación de alcantarillado</v>
+        <v>279</v>
+      </c>
+      <c r="Q43" s="51" t="s">
+        <v>292</v>
       </c>
       <c r="R43" s="29" t="s">
-        <v>9</v>
+        <v>333</v>
       </c>
       <c r="S43" s="29" t="s">
-        <v>153</v>
+        <v>9</v>
       </c>
       <c r="T43" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="U43" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="V43" s="29" t="str">
+        <f t="shared" ref="V43" si="54">SUBSTITUTE(E43, "_", " ")</f>
+        <v>Instalação.De</v>
+      </c>
+      <c r="W43" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="U43" s="29" t="str">
-        <f t="shared" ref="U43" si="64">SUBSTITUTE(E43, "_", " ")</f>
-        <v>Instalação.De</v>
-      </c>
-      <c r="V43" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="W43" s="57" t="str">
-        <f t="shared" ref="W43" si="65">CONCATENATE("Key-HIDR-",A43)</f>
+      <c r="X43" s="57" t="str">
+        <f t="shared" ref="X43" si="55">CONCATENATE("Key-HIDR-",A43)</f>
         <v>Key-HIDR-43</v>
       </c>
-      <c r="X43" s="28" t="s">
-        <v>249</v>
-      </c>
       <c r="Y43" s="28" t="s">
-        <v>250</v>
-      </c>
-      <c r="Z43" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="AA43" s="29" t="str">
-        <f t="shared" ref="AA43" si="66">_xlfn.TRANSLATE(P43,"pt","en")</f>
-        <v>Sewer Installation</v>
-      </c>
-    </row>
-    <row r="44" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>247</v>
+      </c>
+      <c r="Z43" s="28" t="s">
+        <v>340</v>
+      </c>
+      <c r="AA43" s="28" t="s">
+        <v>248</v>
+      </c>
+      <c r="AB43" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="AC43" s="29" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="44" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="56">
         <v>44</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C44" s="41" t="s">
+        <v>270</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="E44" s="41" t="s">
+        <v>276</v>
+      </c>
+      <c r="F44" s="41" t="s">
         <v>272</v>
       </c>
-      <c r="D44" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="E44" s="41" t="s">
-        <v>278</v>
-      </c>
-      <c r="F44" s="41" t="s">
-        <v>274</v>
-      </c>
       <c r="G44" s="58" t="s">
         <v>9</v>
       </c>
@@ -6378,80 +6771,84 @@
         <v>9</v>
       </c>
       <c r="L44" s="32" t="str">
-        <f t="shared" ref="L44:L46" si="67">CONCATENATE("", C44)</f>
+        <f t="shared" ref="L44:L46" si="56">CONCATENATE("", C44)</f>
         <v>De.Tubulações</v>
       </c>
       <c r="M44" s="32" t="str">
-        <f t="shared" ref="M44:M46" si="68">CONCATENATE("", D44)</f>
+        <f t="shared" ref="M44:M46" si="57">CONCATENATE("", D44)</f>
         <v>Elementos.de.Instalações</v>
       </c>
       <c r="N44" s="32" t="str">
-        <f t="shared" ref="N44:N46" si="69">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E44),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N44:N46" si="58">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E44),"."," ")," De "," de "))</f>
         <v>Instalação De</v>
       </c>
       <c r="O44" s="29" t="str">
-        <f t="shared" ref="O44:P46" si="70">IF(ISNUMBER(FIND("Ifc",F44)),CONCATENATE("Classe IFC:   ",F44),CONCATENATE("",F44))</f>
+        <f t="shared" ref="O44:O46" si="59">IF(ISNUMBER(FIND("Ifc",F44)),CONCATENATE("Classe IFC:   ",F44),CONCATENATE("",F44))</f>
         <v>AF</v>
       </c>
       <c r="P44" s="51" t="s">
-        <v>282</v>
-      </c>
-      <c r="Q44" s="51" t="str">
-        <f t="shared" ref="Q44:Q47" si="71">_xlfn.TRANSLATE(P44,"pt","es")</f>
-        <v>Instalación de agua fría</v>
+        <v>280</v>
+      </c>
+      <c r="Q44" s="51" t="s">
+        <v>293</v>
       </c>
       <c r="R44" s="29" t="s">
-        <v>9</v>
+        <v>334</v>
       </c>
       <c r="S44" s="29" t="s">
-        <v>153</v>
+        <v>9</v>
       </c>
       <c r="T44" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="U44" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="V44" s="29" t="str">
+        <f t="shared" ref="V44:V46" si="60">SUBSTITUTE(E44, "_", " ")</f>
+        <v>Instalação.De</v>
+      </c>
+      <c r="W44" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="U44" s="29" t="str">
-        <f t="shared" ref="U44:U46" si="72">SUBSTITUTE(E44, "_", " ")</f>
-        <v>Instalação.De</v>
-      </c>
-      <c r="V44" s="29" t="s">
+      <c r="X44" s="57" t="str">
+        <f t="shared" ref="X44:X46" si="61">CONCATENATE("Key-HIDR-",A44)</f>
+        <v>Key-HIDR-44</v>
+      </c>
+      <c r="Y44" s="28" t="s">
+        <v>247</v>
+      </c>
+      <c r="Z44" s="28" t="s">
+        <v>340</v>
+      </c>
+      <c r="AA44" s="28" t="s">
+        <v>248</v>
+      </c>
+      <c r="AB44" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="AC44" s="29" t="s">
         <v>154</v>
       </c>
-      <c r="W44" s="57" t="str">
-        <f t="shared" ref="W44:W46" si="73">CONCATENATE("Key-HIDR-",A44)</f>
-        <v>Key-HIDR-44</v>
-      </c>
-      <c r="X44" s="28" t="s">
-        <v>249</v>
-      </c>
-      <c r="Y44" s="28" t="s">
-        <v>250</v>
-      </c>
-      <c r="Z44" s="29" t="s">
-        <v>156</v>
-      </c>
-      <c r="AA44" s="29" t="str">
-        <f t="shared" ref="AA44:AA46" si="74">_xlfn.TRANSLATE(P44,"pt","en")</f>
-        <v>Cold water installation</v>
-      </c>
-    </row>
-    <row r="45" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="45" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="56">
         <v>45</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C45" s="41" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E45" s="41" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F45" s="41" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="G45" s="58" t="s">
         <v>9</v>
@@ -6469,80 +6866,84 @@
         <v>9</v>
       </c>
       <c r="L45" s="32" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="56"/>
         <v>De.Tubulações</v>
       </c>
       <c r="M45" s="32" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="57"/>
         <v>Elementos.de.Instalações</v>
       </c>
       <c r="N45" s="32" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="58"/>
         <v>Instalação De</v>
       </c>
       <c r="O45" s="29" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="59"/>
         <v>AQ</v>
       </c>
       <c r="P45" s="51" t="s">
-        <v>283</v>
-      </c>
-      <c r="Q45" s="51" t="str">
-        <f t="shared" si="71"/>
-        <v>Instalación de agua caliente</v>
+        <v>281</v>
+      </c>
+      <c r="Q45" s="51" t="s">
+        <v>294</v>
       </c>
       <c r="R45" s="29" t="s">
-        <v>9</v>
+        <v>335</v>
       </c>
       <c r="S45" s="29" t="s">
-        <v>153</v>
+        <v>9</v>
       </c>
       <c r="T45" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="U45" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="V45" s="29" t="str">
+        <f t="shared" si="60"/>
+        <v>Instalação.De</v>
+      </c>
+      <c r="W45" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="U45" s="29" t="str">
-        <f t="shared" si="72"/>
-        <v>Instalação.De</v>
-      </c>
-      <c r="V45" s="29" t="s">
+      <c r="X45" s="57" t="str">
+        <f t="shared" si="61"/>
+        <v>Key-HIDR-45</v>
+      </c>
+      <c r="Y45" s="28" t="s">
+        <v>247</v>
+      </c>
+      <c r="Z45" s="28" t="s">
+        <v>340</v>
+      </c>
+      <c r="AA45" s="28" t="s">
+        <v>248</v>
+      </c>
+      <c r="AB45" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="AC45" s="29" t="s">
         <v>154</v>
       </c>
-      <c r="W45" s="57" t="str">
-        <f t="shared" si="73"/>
-        <v>Key-HIDR-45</v>
-      </c>
-      <c r="X45" s="28" t="s">
-        <v>249</v>
-      </c>
-      <c r="Y45" s="28" t="s">
-        <v>250</v>
-      </c>
-      <c r="Z45" s="29" t="s">
-        <v>156</v>
-      </c>
-      <c r="AA45" s="29" t="str">
-        <f t="shared" si="74"/>
-        <v>Installation of hot water</v>
-      </c>
-    </row>
-    <row r="46" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="46" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="56">
         <v>46</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C46" s="41" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E46" s="41" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F46" s="41" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="G46" s="58" t="s">
         <v>9</v>
@@ -6560,217 +6961,235 @@
         <v>9</v>
       </c>
       <c r="L46" s="32" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="56"/>
         <v>De.Tubulações</v>
       </c>
       <c r="M46" s="32" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="57"/>
         <v>Elementos.de.Instalações</v>
       </c>
       <c r="N46" s="32" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="58"/>
         <v>Instalação De</v>
       </c>
       <c r="O46" s="29" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="59"/>
         <v>Pluvial</v>
       </c>
       <c r="P46" s="51" t="s">
-        <v>284</v>
-      </c>
-      <c r="Q46" s="51" t="str">
-        <f t="shared" si="71"/>
-        <v>Instalación de agua de lluvia.</v>
+        <v>282</v>
+      </c>
+      <c r="Q46" s="51" t="s">
+        <v>295</v>
       </c>
       <c r="R46" s="29" t="s">
-        <v>9</v>
+        <v>336</v>
       </c>
       <c r="S46" s="29" t="s">
-        <v>153</v>
+        <v>9</v>
       </c>
       <c r="T46" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="U46" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="V46" s="29" t="str">
+        <f t="shared" si="60"/>
+        <v>Instalação.De</v>
+      </c>
+      <c r="W46" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="U46" s="29" t="str">
-        <f t="shared" si="72"/>
-        <v>Instalação.De</v>
-      </c>
-      <c r="V46" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="W46" s="57" t="str">
-        <f t="shared" si="73"/>
+      <c r="X46" s="57" t="str">
+        <f t="shared" si="61"/>
         <v>Key-HIDR-46</v>
       </c>
-      <c r="X46" s="28" t="s">
-        <v>249</v>
-      </c>
       <c r="Y46" s="28" t="s">
-        <v>250</v>
-      </c>
-      <c r="Z46" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="AA46" s="29" t="str">
-        <f t="shared" si="74"/>
-        <v>Rainwater installation.</v>
-      </c>
-    </row>
-    <row r="47" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+        <v>247</v>
+      </c>
+      <c r="Z46" s="28" t="s">
+        <v>340</v>
+      </c>
+      <c r="AA46" s="28" t="s">
+        <v>248</v>
+      </c>
+      <c r="AB46" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="AC46" s="29" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="47" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="56">
         <v>47</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C47" s="41" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D47" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="E47" s="41" t="s">
+        <v>276</v>
+      </c>
+      <c r="F47" s="41" t="s">
         <v>277</v>
       </c>
-      <c r="E47" s="41" t="s">
+      <c r="G47" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H47" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I47" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J47" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K47" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="L47" s="32" t="str">
+        <f t="shared" ref="L47" si="62">CONCATENATE("", C47)</f>
+        <v>De.Tubulações</v>
+      </c>
+      <c r="M47" s="32" t="str">
+        <f t="shared" ref="M47" si="63">CONCATENATE("", D47)</f>
+        <v>Elementos.de.Instalações</v>
+      </c>
+      <c r="N47" s="32" t="str">
+        <f t="shared" ref="N47" si="64">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E47),"."," ")," De "," de "))</f>
+        <v>Instalação De</v>
+      </c>
+      <c r="O47" s="29" t="str">
+        <f t="shared" ref="O47" si="65">IF(ISNUMBER(FIND("Ifc",F47)),CONCATENATE("Classe IFC:   ",F47),CONCATENATE("",F47))</f>
+        <v>Ventilação</v>
+      </c>
+      <c r="P47" s="51" t="s">
         <v>278</v>
       </c>
-      <c r="F47" s="41" t="s">
-        <v>279</v>
-      </c>
-      <c r="G47" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="H47" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="I47" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="J47" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="K47" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="L47" s="32" t="str">
-        <f t="shared" ref="L47" si="75">CONCATENATE("", C47)</f>
-        <v>De.Tubulações</v>
-      </c>
-      <c r="M47" s="32" t="str">
-        <f t="shared" ref="M47" si="76">CONCATENATE("", D47)</f>
-        <v>Elementos.de.Instalações</v>
-      </c>
-      <c r="N47" s="32" t="str">
-        <f t="shared" ref="N47" si="77">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E47),"."," ")," De "," de "))</f>
-        <v>Instalação De</v>
-      </c>
-      <c r="O47" s="29" t="str">
-        <f t="shared" ref="O47:P47" si="78">IF(ISNUMBER(FIND("Ifc",F47)),CONCATENATE("Classe IFC:   ",F47),CONCATENATE("",F47))</f>
-        <v>Ventilação</v>
-      </c>
-      <c r="P47" s="51" t="s">
-        <v>280</v>
-      </c>
-      <c r="Q47" s="51" t="str">
-        <f t="shared" si="71"/>
-        <v>Ventilación de la instalación del desagüe.</v>
+      <c r="Q47" s="51" t="s">
+        <v>296</v>
       </c>
       <c r="R47" s="29" t="s">
-        <v>9</v>
+        <v>337</v>
       </c>
       <c r="S47" s="29" t="s">
-        <v>153</v>
+        <v>9</v>
       </c>
       <c r="T47" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="U47" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="V47" s="29" t="str">
+        <f t="shared" ref="V47" si="66">SUBSTITUTE(E47, "_", " ")</f>
+        <v>Instalação.De</v>
+      </c>
+      <c r="W47" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="U47" s="29" t="str">
-        <f t="shared" ref="U47" si="79">SUBSTITUTE(E47, "_", " ")</f>
-        <v>Instalação.De</v>
-      </c>
-      <c r="V47" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="W47" s="57" t="str">
-        <f t="shared" ref="W47" si="80">CONCATENATE("Key-HIDR-",A47)</f>
+      <c r="X47" s="57" t="str">
+        <f t="shared" ref="X47" si="67">CONCATENATE("Key-HIDR-",A47)</f>
         <v>Key-HIDR-47</v>
       </c>
-      <c r="X47" s="28" t="s">
-        <v>249</v>
-      </c>
       <c r="Y47" s="28" t="s">
-        <v>250</v>
-      </c>
-      <c r="Z47" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="AA47" s="29" t="str">
-        <f t="shared" ref="AA47" si="81">_xlfn.TRANSLATE(P47,"pt","en")</f>
-        <v>Ventilation of the drain installation.</v>
+        <v>247</v>
+      </c>
+      <c r="Z47" s="28" t="s">
+        <v>340</v>
+      </c>
+      <c r="AA47" s="28" t="s">
+        <v>248</v>
+      </c>
+      <c r="AB47" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="AC47" s="29" t="s">
+        <v>126</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:AA933">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:AC933">
     <sortCondition ref="F4:F933"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="AA2:AA47 A2:B47">
-    <cfRule type="cellIs" dxfId="0" priority="8" operator="equal">
+  <conditionalFormatting sqref="A2:B47">
+    <cfRule type="cellIs" dxfId="29" priority="10" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="27" priority="1496"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="1498"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F1048576">
-    <cfRule type="duplicateValues" dxfId="26" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F13">
-    <cfRule type="duplicateValues" dxfId="25" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F32">
-    <cfRule type="duplicateValues" dxfId="24" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F35 F14:F30 F37:F1048576 F1:F12">
-    <cfRule type="duplicateValues" dxfId="23" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F48:F1048576">
-    <cfRule type="duplicateValues" dxfId="22" priority="253"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="255"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="1468"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="1489"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="255"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="257"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="1470"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="1491"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:O1 A1:D1 Q1:X1">
-    <cfRule type="cellIs" dxfId="18" priority="60" operator="equal">
+  <conditionalFormatting sqref="F1:O1 A1:D1 Q1 S1:Z1">
+    <cfRule type="cellIs" dxfId="19" priority="62" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="P2:P6">
+    <cfRule type="duplicateValues" dxfId="18" priority="1523"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="P7:P12 P14:P23">
-    <cfRule type="duplicateValues" dxfId="17" priority="1509"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="1511"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P24:P29">
-    <cfRule type="duplicateValues" dxfId="16" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P30">
-    <cfRule type="duplicateValues" dxfId="15" priority="1502"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="1504"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2:Q5">
-    <cfRule type="duplicateValues" dxfId="14" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="32"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q6">
+    <cfRule type="duplicateValues" dxfId="13" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q23">
-    <cfRule type="duplicateValues" dxfId="13" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q30">
-    <cfRule type="duplicateValues" dxfId="12" priority="1503"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="1505"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z1:AA1">
-    <cfRule type="cellIs" dxfId="11" priority="25" operator="equal">
+  <conditionalFormatting sqref="AB1:AC1">
+    <cfRule type="cellIs" dxfId="10" priority="27" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q6">
-    <cfRule type="duplicateValues" dxfId="10" priority="1"/>
+  <conditionalFormatting sqref="R2:R47">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P6">
-    <cfRule type="duplicateValues" dxfId="1" priority="1521"/>
+  <conditionalFormatting sqref="R1">
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
@@ -6923,7 +7342,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="9" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7026,10 +7445,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C2" s="41" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D2" s="49" t="s">
         <v>9</v>
@@ -7041,7 +7460,7 @@
         <v>77</v>
       </c>
       <c r="G2" s="22" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="H2" s="48" t="s">
         <v>9</v>
@@ -7085,28 +7504,28 @@
         <v>2</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C3" s="41" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D3" s="49" t="s">
         <v>82</v>
       </c>
       <c r="E3" s="33" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F3" s="21" t="s">
         <v>77</v>
       </c>
       <c r="G3" s="22" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="H3" s="48" t="s">
         <v>77</v>
       </c>
       <c r="I3" s="23" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="J3" s="48" t="s">
         <v>9</v>
@@ -7124,7 +7543,7 @@
         <v>9</v>
       </c>
       <c r="O3" s="23" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="P3" s="48" t="s">
         <v>9</v>
@@ -7144,28 +7563,28 @@
         <v>3</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C4" s="41" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D4" s="49" t="s">
         <v>82</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F4" s="21" t="s">
         <v>77</v>
       </c>
       <c r="G4" s="22" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="H4" s="48" t="s">
         <v>77</v>
       </c>
       <c r="I4" s="23" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="J4" s="48" t="s">
         <v>9</v>
@@ -7183,7 +7602,7 @@
         <v>9</v>
       </c>
       <c r="O4" s="23" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="P4" s="48" t="s">
         <v>9</v>
@@ -7203,28 +7622,28 @@
         <v>4</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C5" s="41" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D5" s="49" t="s">
         <v>82</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F5" s="21" t="s">
         <v>77</v>
       </c>
       <c r="G5" s="22" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="H5" s="48" t="s">
         <v>77</v>
       </c>
       <c r="I5" s="23" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="J5" s="48" t="s">
         <v>9</v>
@@ -7242,7 +7661,7 @@
         <v>9</v>
       </c>
       <c r="O5" s="23" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="P5" s="48" t="s">
         <v>9</v>
@@ -7262,22 +7681,22 @@
         <v>5</v>
       </c>
       <c r="B6" s="46" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C6" s="41" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D6" s="49" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F6" s="21" t="s">
         <v>77</v>
       </c>
       <c r="G6" s="22" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H6" s="48" t="s">
         <v>9</v>
@@ -7286,34 +7705,34 @@
         <v>9</v>
       </c>
       <c r="J6" s="48" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="K6" s="23" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="L6" s="48" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="M6" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="N6" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="N6" s="48" t="s">
-        <v>100</v>
-      </c>
       <c r="O6" s="23" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="P6" s="48" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="Q6" s="23" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="R6" s="48" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="S6" s="23" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
@@ -7321,22 +7740,22 @@
         <v>6</v>
       </c>
       <c r="B7" s="46" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C7" s="41" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D7" s="49" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F7" s="21" t="s">
         <v>77</v>
       </c>
       <c r="G7" s="22" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H7" s="48" t="s">
         <v>9</v>
@@ -7345,34 +7764,34 @@
         <v>9</v>
       </c>
       <c r="J7" s="48" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="K7" s="23" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="L7" s="48" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="M7" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="N7" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="N7" s="48" t="s">
-        <v>100</v>
-      </c>
       <c r="O7" s="23" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="P7" s="48" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="Q7" s="23" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="R7" s="48" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="S7" s="23" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
@@ -7380,22 +7799,22 @@
         <v>7</v>
       </c>
       <c r="B8" s="46" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C8" s="41" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D8" s="49" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F8" s="21" t="s">
         <v>77</v>
       </c>
       <c r="G8" s="22" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="H8" s="48" t="s">
         <v>9</v>
@@ -7404,34 +7823,34 @@
         <v>9</v>
       </c>
       <c r="J8" s="48" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="K8" s="23" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="L8" s="48" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="M8" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="N8" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="N8" s="48" t="s">
-        <v>100</v>
-      </c>
       <c r="O8" s="23" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="P8" s="48" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="Q8" s="23" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="R8" s="48" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="S8" s="23" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="9" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
@@ -7439,22 +7858,22 @@
         <v>8</v>
       </c>
       <c r="B9" s="46" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C9" s="41" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D9" s="49" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E9" s="33" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F9" s="21" t="s">
         <v>77</v>
       </c>
       <c r="G9" s="22" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="H9" s="48" t="s">
         <v>9</v>
@@ -7463,34 +7882,34 @@
         <v>9</v>
       </c>
       <c r="J9" s="48" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="K9" s="23" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="L9" s="48" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="M9" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="N9" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="N9" s="48" t="s">
-        <v>100</v>
-      </c>
       <c r="O9" s="23" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="P9" s="48" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="Q9" s="23" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="R9" s="48" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="S9" s="23" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
@@ -7498,22 +7917,22 @@
         <v>9</v>
       </c>
       <c r="B10" s="46" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C10" s="41" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D10" s="49" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F10" s="21" t="s">
         <v>77</v>
       </c>
       <c r="G10" s="22" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="H10" s="48" t="s">
         <v>9</v>
@@ -7522,34 +7941,34 @@
         <v>9</v>
       </c>
       <c r="J10" s="48" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="K10" s="23" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="L10" s="48" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="M10" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="N10" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="N10" s="48" t="s">
-        <v>100</v>
-      </c>
       <c r="O10" s="23" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="P10" s="48" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="Q10" s="23" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="R10" s="48" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="S10" s="23" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
@@ -7557,22 +7976,22 @@
         <v>10</v>
       </c>
       <c r="B11" s="46" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C11" s="41" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E11" s="33" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F11" s="21" t="s">
         <v>77</v>
       </c>
       <c r="G11" s="22" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="H11" s="48" t="s">
         <v>9</v>
@@ -7581,34 +8000,34 @@
         <v>9</v>
       </c>
       <c r="J11" s="48" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="K11" s="23" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="L11" s="48" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="M11" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="N11" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="N11" s="48" t="s">
-        <v>100</v>
-      </c>
       <c r="O11" s="23" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="P11" s="48" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="Q11" s="23" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="R11" s="48" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="S11" s="23" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="12" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
@@ -7616,22 +8035,22 @@
         <v>11</v>
       </c>
       <c r="B12" s="46" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C12" s="41" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D12" s="49" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E12" s="33" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F12" s="21" t="s">
         <v>77</v>
       </c>
       <c r="G12" s="22" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="H12" s="48" t="s">
         <v>9</v>
@@ -7640,34 +8059,34 @@
         <v>9</v>
       </c>
       <c r="J12" s="48" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="K12" s="23" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="L12" s="48" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="M12" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="N12" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="N12" s="48" t="s">
-        <v>100</v>
-      </c>
       <c r="O12" s="23" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="P12" s="48" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="Q12" s="23" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="R12" s="48" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="S12" s="23" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="13" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
@@ -7675,22 +8094,22 @@
         <v>12</v>
       </c>
       <c r="B13" s="46" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C13" s="41" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D13" s="49" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E13" s="33" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F13" s="21" t="s">
         <v>77</v>
       </c>
       <c r="G13" s="22" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="H13" s="48" t="s">
         <v>9</v>
@@ -7699,34 +8118,34 @@
         <v>9</v>
       </c>
       <c r="J13" s="48" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="K13" s="23" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="L13" s="48" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="M13" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="N13" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="N13" s="48" t="s">
-        <v>100</v>
-      </c>
       <c r="O13" s="23" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="P13" s="48" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="Q13" s="23" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="R13" s="48" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="S13" s="23" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="14" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
@@ -7734,58 +8153,58 @@
         <v>13</v>
       </c>
       <c r="B14" s="46" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C14" s="41" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D14" s="49" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E14" s="33" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F14" s="21" t="s">
         <v>77</v>
       </c>
       <c r="G14" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="H14" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="I14" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="J14" s="48" t="s">
+        <v>241</v>
+      </c>
+      <c r="K14" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="L14" s="48" t="s">
+        <v>242</v>
+      </c>
+      <c r="M14" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="N14" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="O14" s="23" t="s">
+        <v>252</v>
+      </c>
+      <c r="P14" s="48" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q14" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="R14" s="48" t="s">
+        <v>95</v>
+      </c>
+      <c r="S14" s="23" t="s">
         <v>189</v>
-      </c>
-      <c r="H14" s="48" t="s">
-        <v>9</v>
-      </c>
-      <c r="I14" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="J14" s="48" t="s">
-        <v>243</v>
-      </c>
-      <c r="K14" s="23" t="s">
-        <v>129</v>
-      </c>
-      <c r="L14" s="48" t="s">
-        <v>244</v>
-      </c>
-      <c r="M14" s="23" t="s">
-        <v>98</v>
-      </c>
-      <c r="N14" s="48" t="s">
-        <v>100</v>
-      </c>
-      <c r="O14" s="23" t="s">
-        <v>254</v>
-      </c>
-      <c r="P14" s="48" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q14" s="23" t="s">
-        <v>255</v>
-      </c>
-      <c r="R14" s="48" t="s">
-        <v>97</v>
-      </c>
-      <c r="S14" s="23" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="15" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
@@ -7793,58 +8212,58 @@
         <v>14</v>
       </c>
       <c r="B15" s="46" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C15" s="41" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D15" s="49" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E15" s="33" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F15" s="21" t="s">
         <v>77</v>
       </c>
       <c r="G15" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="H15" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="I15" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="J15" s="48" t="s">
+        <v>241</v>
+      </c>
+      <c r="K15" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="L15" s="48" t="s">
+        <v>242</v>
+      </c>
+      <c r="M15" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="N15" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="O15" s="23" t="s">
+        <v>252</v>
+      </c>
+      <c r="P15" s="48" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q15" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="R15" s="48" t="s">
+        <v>95</v>
+      </c>
+      <c r="S15" s="23" t="s">
         <v>189</v>
-      </c>
-      <c r="H15" s="48" t="s">
-        <v>9</v>
-      </c>
-      <c r="I15" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="J15" s="48" t="s">
-        <v>243</v>
-      </c>
-      <c r="K15" s="23" t="s">
-        <v>129</v>
-      </c>
-      <c r="L15" s="48" t="s">
-        <v>244</v>
-      </c>
-      <c r="M15" s="23" t="s">
-        <v>98</v>
-      </c>
-      <c r="N15" s="48" t="s">
-        <v>100</v>
-      </c>
-      <c r="O15" s="23" t="s">
-        <v>254</v>
-      </c>
-      <c r="P15" s="48" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q15" s="23" t="s">
-        <v>255</v>
-      </c>
-      <c r="R15" s="48" t="s">
-        <v>97</v>
-      </c>
-      <c r="S15" s="23" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="16" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
@@ -7852,58 +8271,58 @@
         <v>15</v>
       </c>
       <c r="B16" s="46" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C16" s="41" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D16" s="49" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E16" s="33" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F16" s="21" t="s">
         <v>77</v>
       </c>
       <c r="G16" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="H16" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="I16" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="J16" s="48" t="s">
+        <v>241</v>
+      </c>
+      <c r="K16" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="L16" s="48" t="s">
+        <v>242</v>
+      </c>
+      <c r="M16" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="N16" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="O16" s="23" t="s">
+        <v>252</v>
+      </c>
+      <c r="P16" s="48" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q16" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="R16" s="48" t="s">
+        <v>95</v>
+      </c>
+      <c r="S16" s="23" t="s">
         <v>189</v>
-      </c>
-      <c r="H16" s="48" t="s">
-        <v>9</v>
-      </c>
-      <c r="I16" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="J16" s="48" t="s">
-        <v>243</v>
-      </c>
-      <c r="K16" s="23" t="s">
-        <v>129</v>
-      </c>
-      <c r="L16" s="48" t="s">
-        <v>244</v>
-      </c>
-      <c r="M16" s="23" t="s">
-        <v>98</v>
-      </c>
-      <c r="N16" s="48" t="s">
-        <v>100</v>
-      </c>
-      <c r="O16" s="23" t="s">
-        <v>254</v>
-      </c>
-      <c r="P16" s="48" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q16" s="23" t="s">
-        <v>255</v>
-      </c>
-      <c r="R16" s="48" t="s">
-        <v>97</v>
-      </c>
-      <c r="S16" s="23" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="17" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
@@ -7911,58 +8330,58 @@
         <v>16</v>
       </c>
       <c r="B17" s="46" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C17" s="41" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D17" s="49" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E17" s="33" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F17" s="21" t="s">
         <v>77</v>
       </c>
       <c r="G17" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="H17" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="I17" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="J17" s="48" t="s">
+        <v>241</v>
+      </c>
+      <c r="K17" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="L17" s="48" t="s">
+        <v>242</v>
+      </c>
+      <c r="M17" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="N17" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="O17" s="23" t="s">
+        <v>252</v>
+      </c>
+      <c r="P17" s="48" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q17" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="R17" s="48" t="s">
+        <v>95</v>
+      </c>
+      <c r="S17" s="23" t="s">
         <v>189</v>
-      </c>
-      <c r="H17" s="48" t="s">
-        <v>9</v>
-      </c>
-      <c r="I17" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="J17" s="48" t="s">
-        <v>243</v>
-      </c>
-      <c r="K17" s="23" t="s">
-        <v>129</v>
-      </c>
-      <c r="L17" s="48" t="s">
-        <v>244</v>
-      </c>
-      <c r="M17" s="23" t="s">
-        <v>98</v>
-      </c>
-      <c r="N17" s="48" t="s">
-        <v>100</v>
-      </c>
-      <c r="O17" s="23" t="s">
-        <v>254</v>
-      </c>
-      <c r="P17" s="48" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q17" s="23" t="s">
-        <v>255</v>
-      </c>
-      <c r="R17" s="48" t="s">
-        <v>97</v>
-      </c>
-      <c r="S17" s="23" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="18" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
@@ -7970,58 +8389,58 @@
         <v>17</v>
       </c>
       <c r="B18" s="46" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C18" s="41" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D18" s="49" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F18" s="21" t="s">
         <v>77</v>
       </c>
       <c r="G18" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="H18" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="I18" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="J18" s="48" t="s">
+        <v>241</v>
+      </c>
+      <c r="K18" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="L18" s="48" t="s">
+        <v>242</v>
+      </c>
+      <c r="M18" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="N18" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="O18" s="23" t="s">
+        <v>252</v>
+      </c>
+      <c r="P18" s="48" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q18" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="R18" s="48" t="s">
+        <v>95</v>
+      </c>
+      <c r="S18" s="23" t="s">
         <v>189</v>
-      </c>
-      <c r="H18" s="48" t="s">
-        <v>9</v>
-      </c>
-      <c r="I18" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="J18" s="48" t="s">
-        <v>243</v>
-      </c>
-      <c r="K18" s="23" t="s">
-        <v>129</v>
-      </c>
-      <c r="L18" s="48" t="s">
-        <v>244</v>
-      </c>
-      <c r="M18" s="23" t="s">
-        <v>98</v>
-      </c>
-      <c r="N18" s="48" t="s">
-        <v>100</v>
-      </c>
-      <c r="O18" s="23" t="s">
-        <v>254</v>
-      </c>
-      <c r="P18" s="48" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q18" s="23" t="s">
-        <v>255</v>
-      </c>
-      <c r="R18" s="48" t="s">
-        <v>97</v>
-      </c>
-      <c r="S18" s="23" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="19" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
@@ -8029,64 +8448,64 @@
         <v>18</v>
       </c>
       <c r="B19" s="46" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C19" s="41" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D19" s="49" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F19" s="21" t="s">
         <v>77</v>
       </c>
       <c r="G19" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="H19" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="I19" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="J19" s="48" t="s">
+        <v>241</v>
+      </c>
+      <c r="K19" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="L19" s="48" t="s">
+        <v>242</v>
+      </c>
+      <c r="M19" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="N19" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="O19" s="23" t="s">
+        <v>252</v>
+      </c>
+      <c r="P19" s="48" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q19" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="R19" s="48" t="s">
+        <v>95</v>
+      </c>
+      <c r="S19" s="23" t="s">
         <v>189</v>
-      </c>
-      <c r="H19" s="48" t="s">
-        <v>9</v>
-      </c>
-      <c r="I19" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="J19" s="48" t="s">
-        <v>243</v>
-      </c>
-      <c r="K19" s="23" t="s">
-        <v>129</v>
-      </c>
-      <c r="L19" s="48" t="s">
-        <v>244</v>
-      </c>
-      <c r="M19" s="23" t="s">
-        <v>98</v>
-      </c>
-      <c r="N19" s="48" t="s">
-        <v>100</v>
-      </c>
-      <c r="O19" s="23" t="s">
-        <v>254</v>
-      </c>
-      <c r="P19" s="48" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q19" s="23" t="s">
-        <v>255</v>
-      </c>
-      <c r="R19" s="48" t="s">
-        <v>97</v>
-      </c>
-      <c r="S19" s="23" t="s">
-        <v>191</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C3:C5">
-    <cfRule type="duplicateValues" dxfId="8" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8156,22 +8575,22 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:G1 B3:G1048576">
-    <cfRule type="containsText" dxfId="7" priority="5" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" dxfId="6" priority="1449"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="1450"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1449"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1450"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 A1:B1">
-    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 B1">
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:G2">
-    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",B2)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/SIS/Ontologia_Hidrossanitaria.xlsx
+++ b/Versão5/SIS/Ontologia_Hidrossanitaria.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\SIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB479118-CACE-4A09-891C-2E29A7E6996C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98A8AC81-4F95-4287-A03E-BB3001520330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1505" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1523" uniqueCount="347">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -1094,13 +1094,25 @@
     <t>Classe IFC</t>
   </si>
   <si>
-    <t>[ - ]</t>
-  </si>
-  <si>
     <t>Categoria Rvt</t>
   </si>
   <si>
     <t>Parâmetro Rvt</t>
+  </si>
+  <si>
+    <t>De.API</t>
+  </si>
+  <si>
+    <t>Métodos</t>
+  </si>
+  <si>
+    <t>Macros</t>
+  </si>
+  <si>
+    <t>API.Revit</t>
+  </si>
+  <si>
+    <t>Aplicação Revit</t>
   </si>
 </sst>
 </file>
@@ -1191,7 +1203,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="24">
+  <fills count="25">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1330,6 +1342,12 @@
         <bgColor rgb="FFD9F2D0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor rgb="FFFEF2CB"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="9">
     <border>
@@ -1443,7 +1461,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1620,11 +1638,132 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="30">
+  <dxfs count="39">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1697,14 +1836,6 @@
         <i/>
         <strike val="0"/>
         <color rgb="FFFFFFFF"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
     <dxf>
@@ -1900,14 +2031,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2342,15 +2465,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.69140625" style="54" customWidth="1"/>
-    <col min="2" max="2" width="40.15234375" style="54" customWidth="1"/>
-    <col min="3" max="3" width="3.3828125" style="40" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.15234375" style="54"/>
+    <col min="1" max="1" width="8.7109375" style="54" customWidth="1"/>
+    <col min="2" max="2" width="40.140625" style="54" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" style="40" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="54"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>44</v>
       </c>
@@ -2361,7 +2484,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>46</v>
       </c>
@@ -2372,7 +2495,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
         <v>48</v>
       </c>
@@ -2383,7 +2506,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
         <v>49</v>
       </c>
@@ -2394,7 +2517,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>50</v>
       </c>
@@ -2406,7 +2529,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
         <v>51</v>
       </c>
@@ -2418,7 +2541,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
         <v>52</v>
       </c>
@@ -2429,7 +2552,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="37" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" s="37" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="36" t="s">
         <v>54</v>
       </c>
@@ -2440,7 +2563,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>55</v>
       </c>
@@ -2451,7 +2574,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
         <v>57</v>
       </c>
@@ -2462,7 +2585,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
         <v>59</v>
       </c>
@@ -2473,7 +2596,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>60</v>
       </c>
@@ -2484,7 +2607,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
         <v>61</v>
       </c>
@@ -2495,7 +2618,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
         <v>62</v>
       </c>
@@ -2506,7 +2629,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>63</v>
       </c>
@@ -2517,7 +2640,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
         <v>64</v>
       </c>
@@ -2528,7 +2651,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
         <v>65</v>
       </c>
@@ -2539,19 +2662,19 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
         <v>66</v>
       </c>
       <c r="B18" s="14">
         <f ca="1">NOW()</f>
-        <v>46253.811862037037</v>
+        <v>46260.363235648147</v>
       </c>
       <c r="C18" s="39" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
         <v>67</v>
       </c>
@@ -2562,7 +2685,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
         <v>69</v>
       </c>
@@ -2573,7 +2696,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
         <v>70</v>
       </c>
@@ -2584,7 +2707,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
         <v>71</v>
       </c>
@@ -2595,7 +2718,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
         <v>72</v>
       </c>
@@ -2606,7 +2729,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="37" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" s="37" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
         <v>86</v>
       </c>
@@ -2626,38 +2749,38 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96052D63-9637-42D9-866B-0BB924A50D8C}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AC47"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:AC48"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.4609375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.23046875" style="52" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.07421875" style="52" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10" style="52" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.23046875" style="52" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.69140625" style="59" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="6.4609375" style="52" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.07421875" style="52" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10" style="52" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.3828125" style="52" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.69140625" style="52" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="31.3828125" style="52" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="29.3046875" style="52" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="26.4609375" style="52" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.69140625" style="52" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="6" style="52" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="4.69140625" style="52" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9.23046875" style="52" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="4.921875" style="52" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="5.61328125" style="52" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="52.3046875" style="52" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.765625" style="52" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="19.15234375" style="53" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="6" style="52" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="5" style="52" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.15234375" style="52"/>
+    <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.28515625" style="52" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10" style="52" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" style="52" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.28515625" style="52" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.140625" style="59" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="10.140625" style="52" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10" style="52" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="52" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.28515625" style="52" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.140625" style="52" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="44.42578125" style="52" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="41" style="52" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="37" style="52" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.7109375" style="52" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.7109375" style="52" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.85546875" style="52" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.28515625" style="52" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.7109375" style="52" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.85546875" style="52" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="45.5703125" style="52" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9.42578125" style="52" customWidth="1"/>
+    <col min="27" max="27" width="18.85546875" style="53" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="9.7109375" style="52" customWidth="1"/>
+    <col min="29" max="29" width="8.140625" style="52" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="52"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="38.6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:29" ht="38.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="42" t="s">
         <v>91</v>
       </c>
@@ -2731,10 +2854,10 @@
         <v>8</v>
       </c>
       <c r="Y1" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="Z1" s="34" t="s">
         <v>341</v>
-      </c>
-      <c r="Z1" s="34" t="s">
-        <v>342</v>
       </c>
       <c r="AA1" s="34" t="s">
         <v>339</v>
@@ -2746,7 +2869,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="56">
         <v>2</v>
       </c>
@@ -2828,20 +2951,20 @@
       <c r="Y2" s="28" t="s">
         <v>188</v>
       </c>
-      <c r="Z2" s="28" t="s">
-        <v>340</v>
+      <c r="Z2" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA2" s="28" t="s">
         <v>226</v>
       </c>
-      <c r="AB2" s="29" t="s">
-        <v>340</v>
+      <c r="AB2" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC2" s="29" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="56">
         <v>3</v>
       </c>
@@ -2923,20 +3046,20 @@
       <c r="Y3" s="28" t="s">
         <v>188</v>
       </c>
-      <c r="Z3" s="28" t="s">
-        <v>340</v>
+      <c r="Z3" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA3" s="28" t="s">
         <v>257</v>
       </c>
-      <c r="AB3" s="29" t="s">
-        <v>340</v>
+      <c r="AB3" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC3" s="29" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="56">
         <v>4</v>
       </c>
@@ -3018,20 +3141,20 @@
       <c r="Y4" s="28" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="28" t="s">
-        <v>340</v>
+      <c r="Z4" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA4" s="28" t="s">
         <v>224</v>
       </c>
-      <c r="AB4" s="29" t="s">
-        <v>340</v>
+      <c r="AB4" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC4" s="29" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="56">
         <v>5</v>
       </c>
@@ -3113,20 +3236,20 @@
       <c r="Y5" s="28" t="s">
         <v>188</v>
       </c>
-      <c r="Z5" s="28" t="s">
-        <v>340</v>
+      <c r="Z5" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA5" s="28" t="s">
         <v>225</v>
       </c>
-      <c r="AB5" s="29" t="s">
-        <v>340</v>
+      <c r="AB5" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC5" s="29" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="56">
         <v>6</v>
       </c>
@@ -3208,20 +3331,20 @@
       <c r="Y6" s="28" t="s">
         <v>188</v>
       </c>
-      <c r="Z6" s="28" t="s">
-        <v>340</v>
+      <c r="Z6" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA6" s="28" t="s">
         <v>257</v>
       </c>
-      <c r="AB6" s="29" t="s">
-        <v>340</v>
+      <c r="AB6" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC6" s="29" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="56">
         <v>7</v>
       </c>
@@ -3303,20 +3426,20 @@
       <c r="Y7" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="Z7" s="28" t="s">
-        <v>340</v>
+      <c r="Z7" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA7" s="28" t="s">
         <v>183</v>
       </c>
-      <c r="AB7" s="29" t="s">
-        <v>340</v>
+      <c r="AB7" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC7" s="29" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="56">
         <v>8</v>
       </c>
@@ -3398,20 +3521,20 @@
       <c r="Y8" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="Z8" s="28" t="s">
-        <v>340</v>
+      <c r="Z8" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA8" s="28" t="s">
         <v>183</v>
       </c>
-      <c r="AB8" s="29" t="s">
-        <v>340</v>
+      <c r="AB8" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC8" s="29" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="56">
         <v>9</v>
       </c>
@@ -3493,20 +3616,20 @@
       <c r="Y9" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="Z9" s="28" t="s">
-        <v>340</v>
+      <c r="Z9" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA9" s="28" t="s">
         <v>183</v>
       </c>
-      <c r="AB9" s="29" t="s">
-        <v>340</v>
+      <c r="AB9" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC9" s="29" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="56">
         <v>10</v>
       </c>
@@ -3588,20 +3711,20 @@
       <c r="Y10" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="Z10" s="28" t="s">
-        <v>340</v>
+      <c r="Z10" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA10" s="28" t="s">
         <v>183</v>
       </c>
-      <c r="AB10" s="29" t="s">
-        <v>340</v>
+      <c r="AB10" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC10" s="29" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="56">
         <v>11</v>
       </c>
@@ -3683,20 +3806,20 @@
       <c r="Y11" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="Z11" s="28" t="s">
-        <v>340</v>
+      <c r="Z11" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA11" s="28" t="s">
         <v>182</v>
       </c>
-      <c r="AB11" s="29" t="s">
-        <v>340</v>
+      <c r="AB11" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC11" s="29" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="56">
         <v>12</v>
       </c>
@@ -3778,20 +3901,20 @@
       <c r="Y12" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="Z12" s="28" t="s">
-        <v>340</v>
+      <c r="Z12" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA12" s="28" t="s">
         <v>182</v>
       </c>
-      <c r="AB12" s="29" t="s">
-        <v>340</v>
+      <c r="AB12" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC12" s="29" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="56">
         <v>13</v>
       </c>
@@ -3873,20 +3996,20 @@
       <c r="Y13" s="28" t="s">
         <v>240</v>
       </c>
-      <c r="Z13" s="28" t="s">
-        <v>340</v>
+      <c r="Z13" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA13" s="28" t="s">
         <v>229</v>
       </c>
-      <c r="AB13" s="29" t="s">
-        <v>340</v>
+      <c r="AB13" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC13" s="29" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="56">
         <v>14</v>
       </c>
@@ -3968,20 +4091,20 @@
       <c r="Y14" s="28" t="s">
         <v>235</v>
       </c>
-      <c r="Z14" s="28" t="s">
-        <v>340</v>
+      <c r="Z14" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA14" s="28" t="s">
         <v>234</v>
       </c>
-      <c r="AB14" s="29" t="s">
-        <v>340</v>
+      <c r="AB14" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC14" s="29" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="15" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="56">
         <v>15</v>
       </c>
@@ -4063,20 +4186,20 @@
       <c r="Y15" s="28" t="s">
         <v>247</v>
       </c>
-      <c r="Z15" s="28" t="s">
-        <v>340</v>
+      <c r="Z15" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA15" s="28" t="s">
         <v>184</v>
       </c>
-      <c r="AB15" s="29" t="s">
-        <v>340</v>
+      <c r="AB15" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC15" s="29" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="56">
         <v>16</v>
       </c>
@@ -4158,20 +4281,20 @@
       <c r="Y16" s="28" t="s">
         <v>247</v>
       </c>
-      <c r="Z16" s="28" t="s">
-        <v>340</v>
+      <c r="Z16" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA16" s="28" t="s">
         <v>184</v>
       </c>
-      <c r="AB16" s="29" t="s">
-        <v>340</v>
+      <c r="AB16" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC16" s="29" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="17" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="56">
         <v>17</v>
       </c>
@@ -4253,20 +4376,20 @@
       <c r="Y17" s="28" t="s">
         <v>247</v>
       </c>
-      <c r="Z17" s="28" t="s">
-        <v>340</v>
+      <c r="Z17" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA17" s="28" t="s">
         <v>184</v>
       </c>
-      <c r="AB17" s="29" t="s">
-        <v>340</v>
+      <c r="AB17" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC17" s="29" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="18" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="56">
         <v>18</v>
       </c>
@@ -4348,20 +4471,20 @@
       <c r="Y18" s="28" t="s">
         <v>247</v>
       </c>
-      <c r="Z18" s="28" t="s">
-        <v>340</v>
+      <c r="Z18" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA18" s="28" t="s">
         <v>248</v>
       </c>
-      <c r="AB18" s="29" t="s">
-        <v>340</v>
+      <c r="AB18" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC18" s="29" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="19" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="56">
         <v>19</v>
       </c>
@@ -4443,20 +4566,20 @@
       <c r="Y19" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="Z19" s="28" t="s">
-        <v>340</v>
+      <c r="Z19" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA19" s="28" t="s">
         <v>185</v>
       </c>
-      <c r="AB19" s="29" t="s">
-        <v>340</v>
+      <c r="AB19" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC19" s="29" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="20" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="56">
         <v>20</v>
       </c>
@@ -4538,20 +4661,20 @@
       <c r="Y20" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="Z20" s="28" t="s">
-        <v>340</v>
+      <c r="Z20" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA20" s="28" t="s">
         <v>185</v>
       </c>
-      <c r="AB20" s="29" t="s">
-        <v>340</v>
+      <c r="AB20" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC20" s="29" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="21" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="56">
         <v>21</v>
       </c>
@@ -4633,20 +4756,20 @@
       <c r="Y21" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="Z21" s="28" t="s">
-        <v>340</v>
+      <c r="Z21" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA21" s="28" t="s">
         <v>186</v>
       </c>
-      <c r="AB21" s="29" t="s">
-        <v>340</v>
+      <c r="AB21" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC21" s="29" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="22" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="56">
         <v>22</v>
       </c>
@@ -4728,20 +4851,20 @@
       <c r="Y22" s="28" t="s">
         <v>247</v>
       </c>
-      <c r="Z22" s="28" t="s">
-        <v>340</v>
+      <c r="Z22" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA22" s="28" t="s">
         <v>248</v>
       </c>
-      <c r="AB22" s="29" t="s">
-        <v>340</v>
+      <c r="AB22" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC22" s="29" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="23" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="56">
         <v>23</v>
       </c>
@@ -4823,20 +4946,20 @@
       <c r="Y23" s="28" t="s">
         <v>247</v>
       </c>
-      <c r="Z23" s="28" t="s">
-        <v>340</v>
+      <c r="Z23" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA23" s="28" t="s">
         <v>248</v>
       </c>
-      <c r="AB23" s="29" t="s">
-        <v>340</v>
+      <c r="AB23" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC23" s="29" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="24" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="56">
         <v>24</v>
       </c>
@@ -4918,20 +5041,20 @@
       <c r="Y24" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="Z24" s="28" t="s">
-        <v>340</v>
+      <c r="Z24" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA24" s="28" t="s">
         <v>182</v>
       </c>
-      <c r="AB24" s="29" t="s">
-        <v>340</v>
+      <c r="AB24" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC24" s="29" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="25" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="56">
         <v>25</v>
       </c>
@@ -5013,20 +5136,20 @@
       <c r="Y25" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="Z25" s="28" t="s">
-        <v>340</v>
+      <c r="Z25" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA25" s="28" t="s">
         <v>182</v>
       </c>
-      <c r="AB25" s="29" t="s">
-        <v>340</v>
+      <c r="AB25" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC25" s="29" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="26" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="56">
         <v>26</v>
       </c>
@@ -5108,20 +5231,20 @@
       <c r="Y26" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="Z26" s="28" t="s">
-        <v>340</v>
+      <c r="Z26" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA26" s="28" t="s">
         <v>182</v>
       </c>
-      <c r="AB26" s="29" t="s">
-        <v>340</v>
+      <c r="AB26" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC26" s="29" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="27" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="56">
         <v>27</v>
       </c>
@@ -5203,20 +5326,20 @@
       <c r="Y27" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="Z27" s="28" t="s">
-        <v>340</v>
+      <c r="Z27" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA27" s="28" t="s">
         <v>182</v>
       </c>
-      <c r="AB27" s="29" t="s">
-        <v>340</v>
+      <c r="AB27" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC27" s="29" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="28" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="56">
         <v>28</v>
       </c>
@@ -5298,20 +5421,20 @@
       <c r="Y28" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="Z28" s="28" t="s">
-        <v>340</v>
+      <c r="Z28" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA28" s="28" t="s">
         <v>182</v>
       </c>
-      <c r="AB28" s="29" t="s">
-        <v>340</v>
+      <c r="AB28" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC28" s="29" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="29" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="56">
         <v>29</v>
       </c>
@@ -5393,20 +5516,20 @@
       <c r="Y29" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="Z29" s="28" t="s">
-        <v>340</v>
+      <c r="Z29" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA29" s="28" t="s">
         <v>182</v>
       </c>
-      <c r="AB29" s="29" t="s">
-        <v>340</v>
+      <c r="AB29" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC29" s="29" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="30" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="56">
         <v>30</v>
       </c>
@@ -5488,20 +5611,20 @@
       <c r="Y30" s="28" t="s">
         <v>247</v>
       </c>
-      <c r="Z30" s="28" t="s">
-        <v>340</v>
+      <c r="Z30" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA30" s="28" t="s">
         <v>248</v>
       </c>
-      <c r="AB30" s="29" t="s">
-        <v>340</v>
+      <c r="AB30" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC30" s="29" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="31" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="56">
         <v>31</v>
       </c>
@@ -5583,20 +5706,20 @@
       <c r="Y31" s="28" t="s">
         <v>247</v>
       </c>
-      <c r="Z31" s="28" t="s">
-        <v>340</v>
+      <c r="Z31" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA31" s="28" t="s">
         <v>248</v>
       </c>
-      <c r="AB31" s="29" t="s">
-        <v>340</v>
+      <c r="AB31" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC31" s="29" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="32" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="56">
         <v>32</v>
       </c>
@@ -5678,20 +5801,20 @@
       <c r="Y32" s="28" t="s">
         <v>247</v>
       </c>
-      <c r="Z32" s="28" t="s">
-        <v>340</v>
+      <c r="Z32" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA32" s="28" t="s">
         <v>248</v>
       </c>
-      <c r="AB32" s="29" t="s">
-        <v>340</v>
+      <c r="AB32" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC32" s="29" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="33" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="56">
         <v>33</v>
       </c>
@@ -5773,20 +5896,20 @@
       <c r="Y33" s="28" t="s">
         <v>247</v>
       </c>
-      <c r="Z33" s="28" t="s">
-        <v>340</v>
+      <c r="Z33" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA33" s="28" t="s">
         <v>248</v>
       </c>
-      <c r="AB33" s="29" t="s">
-        <v>340</v>
+      <c r="AB33" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC33" s="29" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="34" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="56">
         <v>34</v>
       </c>
@@ -5868,20 +5991,20 @@
       <c r="Y34" s="28" t="s">
         <v>247</v>
       </c>
-      <c r="Z34" s="28" t="s">
-        <v>340</v>
+      <c r="Z34" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA34" s="28" t="s">
         <v>248</v>
       </c>
-      <c r="AB34" s="29" t="s">
-        <v>340</v>
+      <c r="AB34" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC34" s="29" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="35" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="56">
         <v>35</v>
       </c>
@@ -5963,20 +6086,20 @@
       <c r="Y35" s="28" t="s">
         <v>247</v>
       </c>
-      <c r="Z35" s="28" t="s">
-        <v>340</v>
+      <c r="Z35" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA35" s="28" t="s">
         <v>248</v>
       </c>
-      <c r="AB35" s="29" t="s">
-        <v>340</v>
+      <c r="AB35" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC35" s="29" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="36" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="56">
         <v>36</v>
       </c>
@@ -6058,20 +6181,20 @@
       <c r="Y36" s="28" t="s">
         <v>247</v>
       </c>
-      <c r="Z36" s="28" t="s">
-        <v>340</v>
+      <c r="Z36" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA36" s="28" t="s">
         <v>248</v>
       </c>
-      <c r="AB36" s="29" t="s">
-        <v>340</v>
+      <c r="AB36" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC36" s="29" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="37" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="56">
         <v>37</v>
       </c>
@@ -6153,20 +6276,20 @@
       <c r="Y37" s="28" t="s">
         <v>247</v>
       </c>
-      <c r="Z37" s="28" t="s">
-        <v>340</v>
+      <c r="Z37" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA37" s="28" t="s">
         <v>248</v>
       </c>
-      <c r="AB37" s="29" t="s">
-        <v>340</v>
+      <c r="AB37" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC37" s="29" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="38" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="56">
         <v>38</v>
       </c>
@@ -6248,20 +6371,20 @@
       <c r="Y38" s="28" t="s">
         <v>247</v>
       </c>
-      <c r="Z38" s="28" t="s">
-        <v>340</v>
+      <c r="Z38" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA38" s="28" t="s">
         <v>248</v>
       </c>
-      <c r="AB38" s="29" t="s">
-        <v>340</v>
+      <c r="AB38" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC38" s="29" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="39" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="56">
         <v>39</v>
       </c>
@@ -6343,20 +6466,20 @@
       <c r="Y39" s="28" t="s">
         <v>247</v>
       </c>
-      <c r="Z39" s="28" t="s">
-        <v>340</v>
+      <c r="Z39" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA39" s="28" t="s">
         <v>248</v>
       </c>
-      <c r="AB39" s="29" t="s">
-        <v>340</v>
+      <c r="AB39" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC39" s="29" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="40" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="56">
         <v>40</v>
       </c>
@@ -6438,20 +6561,20 @@
       <c r="Y40" s="28" t="s">
         <v>247</v>
       </c>
-      <c r="Z40" s="28" t="s">
-        <v>340</v>
+      <c r="Z40" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA40" s="28" t="s">
         <v>248</v>
       </c>
-      <c r="AB40" s="29" t="s">
-        <v>340</v>
+      <c r="AB40" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC40" s="29" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="41" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="56">
         <v>41</v>
       </c>
@@ -6533,20 +6656,20 @@
       <c r="Y41" s="28" t="s">
         <v>247</v>
       </c>
-      <c r="Z41" s="28" t="s">
-        <v>340</v>
+      <c r="Z41" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA41" s="28" t="s">
         <v>248</v>
       </c>
-      <c r="AB41" s="29" t="s">
-        <v>340</v>
+      <c r="AB41" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC41" s="29" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="42" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="56">
         <v>42</v>
       </c>
@@ -6628,20 +6751,20 @@
       <c r="Y42" s="28" t="s">
         <v>235</v>
       </c>
-      <c r="Z42" s="28" t="s">
-        <v>340</v>
+      <c r="Z42" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA42" s="28" t="s">
         <v>234</v>
       </c>
-      <c r="AB42" s="29" t="s">
-        <v>340</v>
+      <c r="AB42" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC42" s="29" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="43" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="56">
         <v>43</v>
       </c>
@@ -6723,20 +6846,20 @@
       <c r="Y43" s="28" t="s">
         <v>247</v>
       </c>
-      <c r="Z43" s="28" t="s">
-        <v>340</v>
+      <c r="Z43" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA43" s="28" t="s">
         <v>248</v>
       </c>
-      <c r="AB43" s="29" t="s">
-        <v>340</v>
+      <c r="AB43" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC43" s="29" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="44" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="56">
         <v>44</v>
       </c>
@@ -6812,26 +6935,26 @@
         <v>152</v>
       </c>
       <c r="X44" s="57" t="str">
-        <f t="shared" ref="X44:X46" si="61">CONCATENATE("Key-HIDR-",A44)</f>
+        <f t="shared" ref="X44:X48" si="61">CONCATENATE("Key-HIDR-",A44)</f>
         <v>Key-HIDR-44</v>
       </c>
       <c r="Y44" s="28" t="s">
         <v>247</v>
       </c>
-      <c r="Z44" s="28" t="s">
-        <v>340</v>
+      <c r="Z44" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA44" s="28" t="s">
         <v>248</v>
       </c>
-      <c r="AB44" s="29" t="s">
-        <v>340</v>
+      <c r="AB44" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC44" s="29" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="45" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="56">
         <v>45</v>
       </c>
@@ -6913,20 +7036,20 @@
       <c r="Y45" s="28" t="s">
         <v>247</v>
       </c>
-      <c r="Z45" s="28" t="s">
-        <v>340</v>
+      <c r="Z45" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA45" s="28" t="s">
         <v>248</v>
       </c>
-      <c r="AB45" s="29" t="s">
-        <v>340</v>
+      <c r="AB45" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC45" s="29" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="46" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="56">
         <v>46</v>
       </c>
@@ -7008,20 +7131,20 @@
       <c r="Y46" s="28" t="s">
         <v>247</v>
       </c>
-      <c r="Z46" s="28" t="s">
-        <v>340</v>
+      <c r="Z46" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA46" s="28" t="s">
         <v>248</v>
       </c>
-      <c r="AB46" s="29" t="s">
-        <v>340</v>
+      <c r="AB46" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC46" s="29" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="47" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="56">
         <v>47</v>
       </c>
@@ -7097,23 +7220,122 @@
         <v>152</v>
       </c>
       <c r="X47" s="57" t="str">
-        <f t="shared" ref="X47" si="67">CONCATENATE("Key-HIDR-",A47)</f>
+        <f t="shared" si="61"/>
         <v>Key-HIDR-47</v>
       </c>
       <c r="Y47" s="28" t="s">
         <v>247</v>
       </c>
-      <c r="Z47" s="28" t="s">
-        <v>340</v>
+      <c r="Z47" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AA47" s="28" t="s">
         <v>248</v>
       </c>
-      <c r="AB47" s="29" t="s">
-        <v>340</v>
+      <c r="AB47" s="62" t="s">
+        <v>9</v>
       </c>
       <c r="AC47" s="29" t="s">
         <v>126</v>
+      </c>
+    </row>
+    <row r="48" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="56">
+        <v>48</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C48" s="64" t="s">
+        <v>342</v>
+      </c>
+      <c r="D48" s="64" t="s">
+        <v>343</v>
+      </c>
+      <c r="E48" s="64" t="s">
+        <v>344</v>
+      </c>
+      <c r="F48" s="64" t="s">
+        <v>345</v>
+      </c>
+      <c r="G48" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H48" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I48" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J48" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K48" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="L48" s="32" t="str">
+        <f t="shared" ref="L48:O48" si="67">SUBSTITUTE(CONCATENATE("", C48), ".", " ")</f>
+        <v>De API</v>
+      </c>
+      <c r="M48" s="32" t="str">
+        <f t="shared" si="67"/>
+        <v>Métodos</v>
+      </c>
+      <c r="N48" s="32" t="str">
+        <f t="shared" si="67"/>
+        <v>Macros</v>
+      </c>
+      <c r="O48" s="32" t="str">
+        <f t="shared" si="67"/>
+        <v>API Revit</v>
+      </c>
+      <c r="P48" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="Q48" s="60" t="str">
+        <f t="shared" ref="Q48" si="68">_xlfn.TRANSLATE(P48,"pt","es")</f>
+        <v>Aplicación Revit</v>
+      </c>
+      <c r="R48" s="60" t="str">
+        <f t="shared" ref="R48" si="69">_xlfn.TRANSLATE(P48,"pt","en")</f>
+        <v>Revit App</v>
+      </c>
+      <c r="S48" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="T48" s="29" t="str">
+        <f t="shared" ref="T48:V48" si="70">SUBSTITUTE(C48, ".", " ")</f>
+        <v>De API</v>
+      </c>
+      <c r="U48" s="29" t="str">
+        <f t="shared" si="70"/>
+        <v>Métodos</v>
+      </c>
+      <c r="V48" s="61" t="str">
+        <f t="shared" si="70"/>
+        <v>Macros</v>
+      </c>
+      <c r="W48" s="29" t="s">
+        <v>152</v>
+      </c>
+      <c r="X48" s="57" t="str">
+        <f t="shared" si="61"/>
+        <v>Key-HIDR-48</v>
+      </c>
+      <c r="Y48" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z48" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA48" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB48" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC48" s="62" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -7121,75 +7343,90 @@
     <sortCondition ref="F4:F933"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:B47">
-    <cfRule type="cellIs" dxfId="29" priority="10" operator="equal">
+  <conditionalFormatting sqref="A2:B47 A48">
+    <cfRule type="cellIs" dxfId="0" priority="20" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="28" priority="1498"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="1508"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F1048576">
-    <cfRule type="duplicateValues" dxfId="27" priority="26"/>
+  <conditionalFormatting sqref="F1:F47 F49:F1048576">
+    <cfRule type="duplicateValues" dxfId="37" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F13">
-    <cfRule type="duplicateValues" dxfId="26" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F32">
-    <cfRule type="duplicateValues" dxfId="25" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="58"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F35 F14:F30 F37:F1048576 F1:F12">
-    <cfRule type="duplicateValues" dxfId="24" priority="50"/>
+  <conditionalFormatting sqref="F35 F14:F30 F37:F47 F1:F12 F49:F1048576">
+    <cfRule type="duplicateValues" dxfId="34" priority="60"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F48:F1048576">
-    <cfRule type="duplicateValues" dxfId="23" priority="255"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="257"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="1470"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="1491"/>
+  <conditionalFormatting sqref="F49:F1048576">
+    <cfRule type="duplicateValues" dxfId="33" priority="265"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="267"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="1480"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="1501"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:O1 A1:D1 Q1 S1:Z1">
-    <cfRule type="cellIs" dxfId="19" priority="62" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="72" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:P6">
-    <cfRule type="duplicateValues" dxfId="18" priority="1523"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="1533"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P7:P12 P14:P23">
-    <cfRule type="duplicateValues" dxfId="17" priority="1511"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="1521"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P24:P29">
-    <cfRule type="duplicateValues" dxfId="16" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P30">
-    <cfRule type="duplicateValues" dxfId="15" priority="1504"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="1514"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2:Q5">
-    <cfRule type="duplicateValues" dxfId="14" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q6">
-    <cfRule type="duplicateValues" dxfId="13" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q23">
-    <cfRule type="duplicateValues" dxfId="12" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q30">
-    <cfRule type="duplicateValues" dxfId="11" priority="1505"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="1515"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AB1:AC1">
-    <cfRule type="cellIs" dxfId="10" priority="27" operator="equal">
+  <conditionalFormatting sqref="R1:R47">
+    <cfRule type="cellIs" dxfId="20" priority="11" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R47">
-    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
+  <conditionalFormatting sqref="AB1:AC1">
+    <cfRule type="cellIs" dxfId="19" priority="37" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R1">
-    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
+  <conditionalFormatting sqref="B48">
+    <cfRule type="cellIs" dxfId="10" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F48">
+    <cfRule type="duplicateValues" dxfId="9" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q48">
+    <cfRule type="duplicateValues" dxfId="8" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R48">
+    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
@@ -7202,15 +7439,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.84375" style="9" customWidth="1"/>
-    <col min="2" max="10" width="6.53515625" style="10" customWidth="1"/>
-    <col min="11" max="21" width="6.53515625" style="8" customWidth="1"/>
-    <col min="22" max="16384" width="11.15234375" style="8"/>
+    <col min="1" max="1" width="2.85546875" style="9" customWidth="1"/>
+    <col min="2" max="10" width="6.5703125" style="10" customWidth="1"/>
+    <col min="11" max="21" width="6.5703125" style="8" customWidth="1"/>
+    <col min="22" max="16384" width="11.140625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -7275,7 +7512,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -7342,7 +7579,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7358,30 +7595,30 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38CB0525-EDFB-44CB-9009-6752AEDD7340}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:S19"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.3046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.3046875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.69140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.84375" customWidth="1"/>
+    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.85546875" customWidth="1"/>
     <col min="6" max="6" width="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="60.15234375" customWidth="1"/>
+    <col min="7" max="7" width="60.140625" customWidth="1"/>
     <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.3828125" customWidth="1"/>
-    <col min="10" max="10" width="8.3046875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.84375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.3828125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.42578125" customWidth="1"/>
+    <col min="10" max="10" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.42578125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="24" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.3828125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="23.84375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.69140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="19.69140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.3046875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.3828125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="14.7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:19" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>10</v>
       </c>
@@ -7440,7 +7677,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="19">
         <v>1</v>
       </c>
@@ -7499,7 +7736,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="19">
         <v>2</v>
       </c>
@@ -7558,7 +7795,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="19">
         <v>3</v>
       </c>
@@ -7617,7 +7854,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="19">
         <v>4</v>
       </c>
@@ -7676,7 +7913,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="19">
         <v>5</v>
       </c>
@@ -7735,7 +7972,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="19">
         <v>6</v>
       </c>
@@ -7794,7 +8031,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="19">
         <v>7</v>
       </c>
@@ -7853,7 +8090,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="19">
         <v>8</v>
       </c>
@@ -7912,7 +8149,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="19">
         <v>9</v>
       </c>
@@ -7971,7 +8208,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="19">
         <v>10</v>
       </c>
@@ -8030,7 +8267,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="19">
         <v>11</v>
       </c>
@@ -8089,7 +8326,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="19">
         <v>12</v>
       </c>
@@ -8148,7 +8385,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="19">
         <v>13</v>
       </c>
@@ -8207,7 +8444,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="19">
         <v>14</v>
       </c>
@@ -8266,7 +8503,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="19">
         <v>15</v>
       </c>
@@ -8325,7 +8562,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="19">
         <v>16</v>
       </c>
@@ -8384,7 +8621,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="19">
         <v>17</v>
       </c>
@@ -8443,7 +8680,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="19">
         <v>18</v>
       </c>
@@ -8505,7 +8742,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C3:C5">
-    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8515,15 +8752,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5FE5EC8-1387-4A67-960C-C64BD1326958}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.15234375" style="25" customWidth="1"/>
-    <col min="2" max="2" width="5.84375" style="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.3046875" style="24" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.84375" style="24" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.140625" style="25" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" style="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" style="24" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.85546875" style="24" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="30">
         <v>0</v>
       </c>
@@ -8546,7 +8783,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="31">
         <v>2</v>
       </c>
@@ -8575,22 +8812,22 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:G1 B3:G1048576">
-    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="16" priority="5" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" dxfId="4" priority="1449"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="1450"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="1449"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="1450"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 A1:B1">
-    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 B1">
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:G2">
-    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="11" priority="2" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",B2)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/SIS/Ontologia_Hidrossanitaria.xlsx
+++ b/Versão5/SIS/Ontologia_Hidrossanitaria.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\SIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98A8AC81-4F95-4287-A03E-BB3001520330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4A9DB90-DFF5-4B69-A3CF-D95D95BFFE72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -1657,113 +1657,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="39">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="38">
     <dxf>
       <font>
         <b val="0"/>
@@ -1848,11 +1742,91 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <b val="0"/>
         <i/>
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2031,6 +2005,24 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2465,15 +2457,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="54" customWidth="1"/>
-    <col min="2" max="2" width="40.140625" style="54" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="40" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="54"/>
+    <col min="1" max="1" width="8.69140625" style="54" customWidth="1"/>
+    <col min="2" max="2" width="40.15234375" style="54" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="40" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.15234375" style="54"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="11" t="s">
         <v>44</v>
       </c>
@@ -2484,7 +2476,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="12" t="s">
         <v>46</v>
       </c>
@@ -2495,7 +2487,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="12" t="s">
         <v>48</v>
       </c>
@@ -2506,7 +2498,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="13" t="s">
         <v>49</v>
       </c>
@@ -2517,7 +2509,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="13" t="s">
         <v>50</v>
       </c>
@@ -2529,7 +2521,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="13" t="s">
         <v>51</v>
       </c>
@@ -2541,7 +2533,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="13" t="s">
         <v>52</v>
       </c>
@@ -2552,7 +2544,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="37" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" s="37" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="36" t="s">
         <v>54</v>
       </c>
@@ -2563,7 +2555,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="13" t="s">
         <v>55</v>
       </c>
@@ -2574,7 +2566,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="13" t="s">
         <v>57</v>
       </c>
@@ -2585,7 +2577,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="13" t="s">
         <v>59</v>
       </c>
@@ -2596,7 +2588,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="13" t="s">
         <v>60</v>
       </c>
@@ -2607,7 +2599,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="13" t="s">
         <v>61</v>
       </c>
@@ -2618,7 +2610,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="13" t="s">
         <v>62</v>
       </c>
@@ -2629,7 +2621,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="13" t="s">
         <v>63</v>
       </c>
@@ -2640,7 +2632,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="13" t="s">
         <v>64</v>
       </c>
@@ -2651,7 +2643,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="13" t="s">
         <v>65</v>
       </c>
@@ -2662,19 +2654,19 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="13" t="s">
         <v>66</v>
       </c>
       <c r="B18" s="14">
         <f ca="1">NOW()</f>
-        <v>46260.363235648147</v>
+        <v>46264.571302893521</v>
       </c>
       <c r="C18" s="39" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="13" t="s">
         <v>67</v>
       </c>
@@ -2685,7 +2677,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="13" t="s">
         <v>69</v>
       </c>
@@ -2696,7 +2688,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="13" t="s">
         <v>70</v>
       </c>
@@ -2707,7 +2699,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="13" t="s">
         <v>71</v>
       </c>
@@ -2718,7 +2710,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="13" t="s">
         <v>72</v>
       </c>
@@ -2729,7 +2721,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="37" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" s="37" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="13" t="s">
         <v>86</v>
       </c>
@@ -2750,37 +2742,37 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96052D63-9637-42D9-866B-0BB924A50D8C}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AC48"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.28515625" style="52" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.3828125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.3046875" style="52" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="52" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="52" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.28515625" style="52" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.140625" style="59" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="10.140625" style="52" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.3828125" style="52" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.3046875" style="52" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.15234375" style="59" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="10.15234375" style="52" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="10" style="52" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="52" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.28515625" style="52" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.140625" style="52" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="44.42578125" style="52" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.3828125" style="52" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.3046875" style="52" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.15234375" style="52" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="44.3828125" style="52" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="41" style="52" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="37" style="52" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.7109375" style="52" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.7109375" style="52" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="6.85546875" style="52" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.28515625" style="52" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="6.7109375" style="52" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="7.85546875" style="52" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="45.5703125" style="52" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="9.42578125" style="52" customWidth="1"/>
-    <col min="27" max="27" width="18.85546875" style="53" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="9.7109375" style="52" customWidth="1"/>
-    <col min="29" max="29" width="8.140625" style="52" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="52"/>
+    <col min="19" max="19" width="3.69140625" style="52" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.69140625" style="52" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.84375" style="52" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.3046875" style="52" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.69140625" style="52" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.84375" style="52" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="45.53515625" style="52" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9.3828125" style="52" customWidth="1"/>
+    <col min="27" max="27" width="18.84375" style="53" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="9.69140625" style="52" customWidth="1"/>
+    <col min="29" max="29" width="8.15234375" style="52" customWidth="1"/>
+    <col min="30" max="16384" width="9.15234375" style="52"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="38.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" ht="38.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="42" t="s">
         <v>91</v>
       </c>
@@ -2869,7 +2861,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="56">
         <v>2</v>
       </c>
@@ -2964,7 +2956,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="56">
         <v>3</v>
       </c>
@@ -3059,7 +3051,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="56">
         <v>4</v>
       </c>
@@ -3154,7 +3146,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="56">
         <v>5</v>
       </c>
@@ -3249,7 +3241,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="56">
         <v>6</v>
       </c>
@@ -3344,7 +3336,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="56">
         <v>7</v>
       </c>
@@ -3439,7 +3431,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="56">
         <v>8</v>
       </c>
@@ -3534,7 +3526,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="56">
         <v>9</v>
       </c>
@@ -3629,7 +3621,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="56">
         <v>10</v>
       </c>
@@ -3724,7 +3716,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="56">
         <v>11</v>
       </c>
@@ -3819,7 +3811,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="56">
         <v>12</v>
       </c>
@@ -3914,7 +3906,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="56">
         <v>13</v>
       </c>
@@ -4009,7 +4001,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="56">
         <v>14</v>
       </c>
@@ -4104,7 +4096,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="15" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="56">
         <v>15</v>
       </c>
@@ -4199,7 +4191,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="56">
         <v>16</v>
       </c>
@@ -4294,7 +4286,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="17" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="56">
         <v>17</v>
       </c>
@@ -4389,7 +4381,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="18" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="56">
         <v>18</v>
       </c>
@@ -4484,7 +4476,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="19" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="56">
         <v>19</v>
       </c>
@@ -4579,7 +4571,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="20" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="56">
         <v>20</v>
       </c>
@@ -4674,7 +4666,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="21" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="56">
         <v>21</v>
       </c>
@@ -4769,7 +4761,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="22" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="56">
         <v>22</v>
       </c>
@@ -4864,7 +4856,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="23" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="56">
         <v>23</v>
       </c>
@@ -4959,7 +4951,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="24" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="56">
         <v>24</v>
       </c>
@@ -5054,7 +5046,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="25" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="56">
         <v>25</v>
       </c>
@@ -5149,7 +5141,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="26" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="56">
         <v>26</v>
       </c>
@@ -5244,7 +5236,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="27" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="56">
         <v>27</v>
       </c>
@@ -5339,7 +5331,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="28" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="56">
         <v>28</v>
       </c>
@@ -5434,7 +5426,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="29" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="56">
         <v>29</v>
       </c>
@@ -5529,7 +5521,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="30" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="56">
         <v>30</v>
       </c>
@@ -5624,7 +5616,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="31" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="56">
         <v>31</v>
       </c>
@@ -5719,7 +5711,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="32" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="56">
         <v>32</v>
       </c>
@@ -5814,7 +5806,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="33" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="56">
         <v>33</v>
       </c>
@@ -5909,7 +5901,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="34" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="56">
         <v>34</v>
       </c>
@@ -6004,7 +5996,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="35" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="56">
         <v>35</v>
       </c>
@@ -6099,7 +6091,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="36" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="56">
         <v>36</v>
       </c>
@@ -6194,7 +6186,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="37" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="56">
         <v>37</v>
       </c>
@@ -6289,7 +6281,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="38" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="56">
         <v>38</v>
       </c>
@@ -6384,7 +6376,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="39" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="56">
         <v>39</v>
       </c>
@@ -6479,7 +6471,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="40" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="56">
         <v>40</v>
       </c>
@@ -6574,7 +6566,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="41" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="56">
         <v>41</v>
       </c>
@@ -6669,7 +6661,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="42" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="56">
         <v>42</v>
       </c>
@@ -6764,7 +6756,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="43" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="56">
         <v>43</v>
       </c>
@@ -6859,7 +6851,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="44" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="56">
         <v>44</v>
       </c>
@@ -6954,7 +6946,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="45" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="56">
         <v>45</v>
       </c>
@@ -7049,7 +7041,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="46" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="56">
         <v>46</v>
       </c>
@@ -7144,7 +7136,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="47" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="56">
         <v>47</v>
       </c>
@@ -7239,7 +7231,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="48" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="56">
         <v>48</v>
       </c>
@@ -7250,10 +7242,10 @@
         <v>342</v>
       </c>
       <c r="D48" s="64" t="s">
+        <v>344</v>
+      </c>
+      <c r="E48" s="64" t="s">
         <v>343</v>
-      </c>
-      <c r="E48" s="64" t="s">
-        <v>344</v>
       </c>
       <c r="F48" s="64" t="s">
         <v>345</v>
@@ -7279,11 +7271,11 @@
       </c>
       <c r="M48" s="32" t="str">
         <f t="shared" si="67"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="N48" s="32" t="str">
         <f t="shared" si="67"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="O48" s="32" t="str">
         <f t="shared" si="67"/>
@@ -7309,11 +7301,11 @@
       </c>
       <c r="U48" s="29" t="str">
         <f t="shared" si="70"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="V48" s="61" t="str">
         <f t="shared" si="70"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="W48" s="29" t="s">
         <v>152</v>
@@ -7343,90 +7335,85 @@
     <sortCondition ref="F4:F933"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:B47 A48">
-    <cfRule type="cellIs" dxfId="0" priority="20" operator="equal">
+  <conditionalFormatting sqref="A2:B48">
+    <cfRule type="cellIs" dxfId="37" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="38" priority="1508"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="1508"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F47 F49:F1048576">
-    <cfRule type="duplicateValues" dxfId="37" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F13">
-    <cfRule type="duplicateValues" dxfId="36" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F32">
-    <cfRule type="duplicateValues" dxfId="35" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="58"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F35 F14:F30 F37:F47 F1:F12 F49:F1048576">
-    <cfRule type="duplicateValues" dxfId="34" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="60"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F48">
+    <cfRule type="duplicateValues" dxfId="31" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F49:F1048576">
-    <cfRule type="duplicateValues" dxfId="33" priority="265"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="267"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="1480"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="1501"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="265"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="267"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="1480"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="1501"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:O1 A1:D1 Q1 S1:Z1">
-    <cfRule type="cellIs" dxfId="29" priority="72" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="72" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:P6">
-    <cfRule type="duplicateValues" dxfId="28" priority="1533"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="1533"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P7:P12 P14:P23">
-    <cfRule type="duplicateValues" dxfId="27" priority="1521"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="1521"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P24:P29">
-    <cfRule type="duplicateValues" dxfId="26" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P30">
-    <cfRule type="duplicateValues" dxfId="25" priority="1514"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="1514"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2:Q5">
-    <cfRule type="duplicateValues" dxfId="24" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q6">
-    <cfRule type="duplicateValues" dxfId="23" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q23">
-    <cfRule type="duplicateValues" dxfId="22" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q30">
-    <cfRule type="duplicateValues" dxfId="21" priority="1515"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="1515"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q48">
+    <cfRule type="duplicateValues" dxfId="17" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:R47">
-    <cfRule type="cellIs" dxfId="20" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="11" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="R48">
+    <cfRule type="duplicateValues" dxfId="12" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="4"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="AB1:AC1">
-    <cfRule type="cellIs" dxfId="19" priority="37" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="37" operator="equal">
       <formula>"null"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B48">
-    <cfRule type="cellIs" dxfId="10" priority="5" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F48">
-    <cfRule type="duplicateValues" dxfId="9" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q48">
-    <cfRule type="duplicateValues" dxfId="8" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R48">
-    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
@@ -7439,15 +7426,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" style="9" customWidth="1"/>
-    <col min="2" max="10" width="6.5703125" style="10" customWidth="1"/>
-    <col min="11" max="21" width="6.5703125" style="8" customWidth="1"/>
-    <col min="22" max="16384" width="11.140625" style="8"/>
+    <col min="1" max="1" width="2.84375" style="9" customWidth="1"/>
+    <col min="2" max="10" width="6.53515625" style="10" customWidth="1"/>
+    <col min="11" max="21" width="6.53515625" style="8" customWidth="1"/>
+    <col min="22" max="16384" width="11.15234375" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -7512,7 +7499,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -7579,7 +7566,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="18" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7595,30 +7582,30 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38CB0525-EDFB-44CB-9009-6752AEDD7340}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:S19"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.85546875" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.3046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.3046875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.69140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.84375" customWidth="1"/>
     <col min="6" max="6" width="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="60.140625" customWidth="1"/>
+    <col min="7" max="7" width="60.15234375" customWidth="1"/>
     <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.42578125" customWidth="1"/>
-    <col min="10" max="10" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.3828125" customWidth="1"/>
+    <col min="10" max="10" width="8.3046875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.84375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.3828125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="24" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="23.85546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.3828125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="23.84375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.69140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="19.69140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.3046875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.3828125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="14.7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="16" t="s">
         <v>10</v>
       </c>
@@ -7677,7 +7664,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="19">
         <v>1</v>
       </c>
@@ -7736,7 +7723,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="19">
         <v>2</v>
       </c>
@@ -7795,7 +7782,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="19">
         <v>3</v>
       </c>
@@ -7854,7 +7841,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="19">
         <v>4</v>
       </c>
@@ -7913,7 +7900,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="19">
         <v>5</v>
       </c>
@@ -7972,7 +7959,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="19">
         <v>6</v>
       </c>
@@ -8031,7 +8018,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="19">
         <v>7</v>
       </c>
@@ -8090,7 +8077,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="19">
         <v>8</v>
       </c>
@@ -8149,7 +8136,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="19">
         <v>9</v>
       </c>
@@ -8208,7 +8195,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="19">
         <v>10</v>
       </c>
@@ -8267,7 +8254,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="19">
         <v>11</v>
       </c>
@@ -8326,7 +8313,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="19">
         <v>12</v>
       </c>
@@ -8385,7 +8372,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="19">
         <v>13</v>
       </c>
@@ -8444,7 +8431,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="19">
         <v>14</v>
       </c>
@@ -8503,7 +8490,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="19">
         <v>15</v>
       </c>
@@ -8562,7 +8549,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="19">
         <v>16</v>
       </c>
@@ -8621,7 +8608,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="19">
         <v>17</v>
       </c>
@@ -8680,7 +8667,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="19">
         <v>18</v>
       </c>
@@ -8742,7 +8729,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C3:C5">
-    <cfRule type="duplicateValues" dxfId="17" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8752,15 +8739,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5FE5EC8-1387-4A67-960C-C64BD1326958}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.140625" style="25" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" style="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" style="24" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.85546875" style="24" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.15234375" style="25" customWidth="1"/>
+    <col min="2" max="2" width="5.84375" style="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.3046875" style="24" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.84375" style="24" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="30">
         <v>0</v>
       </c>
@@ -8783,7 +8770,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="31">
         <v>2</v>
       </c>
@@ -8812,22 +8799,22 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:G1 B3:G1048576">
-    <cfRule type="containsText" dxfId="16" priority="5" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" dxfId="15" priority="1449"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="1450"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1449"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1450"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 A1:B1">
-    <cfRule type="duplicateValues" dxfId="13" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 B1">
-    <cfRule type="duplicateValues" dxfId="12" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:G2">
-    <cfRule type="containsText" dxfId="11" priority="2" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",B2)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/SIS/Ontologia_Hidrossanitaria.xlsx
+++ b/Versão5/SIS/Ontologia_Hidrossanitaria.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\SIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4A9DB90-DFF5-4B69-A3CF-D95D95BFFE72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94F0091A-C804-4263-B50B-E16A38C11EAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1523" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1657" uniqueCount="367">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -1109,10 +1109,70 @@
     <t>Macros</t>
   </si>
   <si>
-    <t>API.Revit</t>
-  </si>
-  <si>
-    <t>Aplicação Revit</t>
+    <t>Função.Auxiliar</t>
+  </si>
+  <si>
+    <t>Define uma Função Auxiliar (helper) numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol de ayudante en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Helper Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Global</t>
+  </si>
+  <si>
+    <t>Define uma Função Global numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol global en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Global Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Local</t>
+  </si>
+  <si>
+    <t>Define uma Função Local numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol local en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Local Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Filtro</t>
+  </si>
+  <si>
+    <t>Define uma Função para filtrar objetos numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina una función para filtrar objetos en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Function to filter objects in an application</t>
+  </si>
+  <si>
+    <t>Códigos.Visuais</t>
+  </si>
+  <si>
+    <t>Bloco.de.Código</t>
+  </si>
+  <si>
+    <t>Define um Código escrito em sistemas de programação visual</t>
+  </si>
+  <si>
+    <t>Define un código escrito en sistemas de programación visual</t>
+  </si>
+  <si>
+    <t>Defines a Code written in visual programming systems</t>
+  </si>
+  <si>
+    <t>KML</t>
   </si>
 </sst>
 </file>
@@ -1461,7 +1521,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1639,9 +1699,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="24" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1657,7 +1714,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="38">
+  <dxfs count="31">
     <dxf>
       <font>
         <b val="0"/>
@@ -1739,46 +1796,6 @@
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -1870,13 +1887,11 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
       </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -1887,34 +1902,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -2457,15 +2444,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.69140625" style="54" customWidth="1"/>
-    <col min="2" max="2" width="40.15234375" style="54" customWidth="1"/>
-    <col min="3" max="3" width="3.3828125" style="40" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.15234375" style="54"/>
+    <col min="1" max="1" width="8.7109375" style="54" customWidth="1"/>
+    <col min="2" max="2" width="40.140625" style="54" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" style="40" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="54"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>44</v>
       </c>
@@ -2476,7 +2463,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>46</v>
       </c>
@@ -2487,7 +2474,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
         <v>48</v>
       </c>
@@ -2498,7 +2485,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
         <v>49</v>
       </c>
@@ -2509,7 +2496,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>50</v>
       </c>
@@ -2521,7 +2508,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
         <v>51</v>
       </c>
@@ -2533,7 +2520,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
         <v>52</v>
       </c>
@@ -2544,7 +2531,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="37" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" s="37" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="36" t="s">
         <v>54</v>
       </c>
@@ -2555,7 +2542,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>55</v>
       </c>
@@ -2566,7 +2553,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
         <v>57</v>
       </c>
@@ -2577,7 +2564,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
         <v>59</v>
       </c>
@@ -2588,7 +2575,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>60</v>
       </c>
@@ -2599,7 +2586,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
         <v>61</v>
       </c>
@@ -2610,7 +2597,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
         <v>62</v>
       </c>
@@ -2621,7 +2608,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>63</v>
       </c>
@@ -2632,7 +2619,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
         <v>64</v>
       </c>
@@ -2643,7 +2630,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
         <v>65</v>
       </c>
@@ -2654,19 +2641,19 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
         <v>66</v>
       </c>
       <c r="B18" s="14">
         <f ca="1">NOW()</f>
-        <v>46264.571302893521</v>
+        <v>46268.700805787033</v>
       </c>
       <c r="C18" s="39" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
         <v>67</v>
       </c>
@@ -2677,7 +2664,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
         <v>69</v>
       </c>
@@ -2688,7 +2675,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
         <v>70</v>
       </c>
@@ -2699,7 +2686,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
         <v>71</v>
       </c>
@@ -2710,7 +2697,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
         <v>72</v>
       </c>
@@ -2721,7 +2708,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="37" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" s="37" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
         <v>86</v>
       </c>
@@ -2741,38 +2728,38 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96052D63-9637-42D9-866B-0BB924A50D8C}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AC48"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:AD52"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.3828125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.3046875" style="52" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.28515625" style="52" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="52" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.3828125" style="52" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.3046875" style="52" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.15234375" style="59" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="10.15234375" style="52" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" style="52" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.28515625" style="52" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.140625" style="59" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="10.140625" style="52" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="10" style="52" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.3828125" style="52" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.3046875" style="52" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.15234375" style="52" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="44.3828125" style="52" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="52" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.28515625" style="52" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.140625" style="52" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="44.42578125" style="52" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="41" style="52" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="37" style="52" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.69140625" style="52" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.69140625" style="52" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="6.84375" style="52" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.3046875" style="52" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="6.69140625" style="52" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="7.84375" style="52" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="45.53515625" style="52" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="9.3828125" style="52" customWidth="1"/>
-    <col min="27" max="27" width="18.84375" style="53" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="9.69140625" style="52" customWidth="1"/>
-    <col min="29" max="29" width="8.15234375" style="52" customWidth="1"/>
-    <col min="30" max="16384" width="9.15234375" style="52"/>
+    <col min="19" max="19" width="3.7109375" style="52" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.7109375" style="52" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.85546875" style="52" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.28515625" style="52" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.7109375" style="52" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.85546875" style="52" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="45.5703125" style="52" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9.42578125" style="52" customWidth="1"/>
+    <col min="27" max="27" width="22.140625" style="53" customWidth="1"/>
+    <col min="28" max="28" width="9.7109375" style="52" customWidth="1"/>
+    <col min="29" max="29" width="8.140625" style="52" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="52"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="38.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:30" ht="38.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="42" t="s">
         <v>91</v>
       </c>
@@ -2860,8 +2847,11 @@
       <c r="AC1" s="34" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="2" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD1" s="34" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="2" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="56">
         <v>2</v>
       </c>
@@ -2943,20 +2933,23 @@
       <c r="Y2" s="28" t="s">
         <v>188</v>
       </c>
-      <c r="Z2" s="62" t="s">
+      <c r="Z2" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA2" s="28" t="s">
         <v>226</v>
       </c>
-      <c r="AB2" s="62" t="s">
+      <c r="AB2" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC2" s="29" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="3" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD2" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="56">
         <v>3</v>
       </c>
@@ -3038,20 +3031,23 @@
       <c r="Y3" s="28" t="s">
         <v>188</v>
       </c>
-      <c r="Z3" s="62" t="s">
+      <c r="Z3" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA3" s="28" t="s">
         <v>257</v>
       </c>
-      <c r="AB3" s="62" t="s">
+      <c r="AB3" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC3" s="29" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="4" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD3" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="56">
         <v>4</v>
       </c>
@@ -3133,20 +3129,23 @@
       <c r="Y4" s="28" t="s">
         <v>188</v>
       </c>
-      <c r="Z4" s="62" t="s">
+      <c r="Z4" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA4" s="28" t="s">
         <v>224</v>
       </c>
-      <c r="AB4" s="62" t="s">
+      <c r="AB4" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC4" s="29" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="5" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD4" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="56">
         <v>5</v>
       </c>
@@ -3228,20 +3227,23 @@
       <c r="Y5" s="28" t="s">
         <v>188</v>
       </c>
-      <c r="Z5" s="62" t="s">
+      <c r="Z5" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA5" s="28" t="s">
         <v>225</v>
       </c>
-      <c r="AB5" s="62" t="s">
+      <c r="AB5" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC5" s="29" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="6" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD5" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="56">
         <v>6</v>
       </c>
@@ -3323,20 +3325,23 @@
       <c r="Y6" s="28" t="s">
         <v>188</v>
       </c>
-      <c r="Z6" s="62" t="s">
+      <c r="Z6" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA6" s="28" t="s">
         <v>257</v>
       </c>
-      <c r="AB6" s="62" t="s">
+      <c r="AB6" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC6" s="29" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="7" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD6" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="56">
         <v>7</v>
       </c>
@@ -3418,20 +3423,23 @@
       <c r="Y7" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="Z7" s="62" t="s">
+      <c r="Z7" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA7" s="28" t="s">
         <v>183</v>
       </c>
-      <c r="AB7" s="62" t="s">
+      <c r="AB7" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC7" s="29" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="8" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD7" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="56">
         <v>8</v>
       </c>
@@ -3513,20 +3521,23 @@
       <c r="Y8" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="Z8" s="62" t="s">
+      <c r="Z8" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA8" s="28" t="s">
         <v>183</v>
       </c>
-      <c r="AB8" s="62" t="s">
+      <c r="AB8" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC8" s="29" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="9" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD8" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="56">
         <v>9</v>
       </c>
@@ -3608,20 +3619,23 @@
       <c r="Y9" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="Z9" s="62" t="s">
+      <c r="Z9" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA9" s="28" t="s">
         <v>183</v>
       </c>
-      <c r="AB9" s="62" t="s">
+      <c r="AB9" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC9" s="29" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD9" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="56">
         <v>10</v>
       </c>
@@ -3703,20 +3717,23 @@
       <c r="Y10" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="Z10" s="62" t="s">
+      <c r="Z10" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA10" s="28" t="s">
         <v>183</v>
       </c>
-      <c r="AB10" s="62" t="s">
+      <c r="AB10" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC10" s="29" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD10" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="56">
         <v>11</v>
       </c>
@@ -3798,20 +3815,23 @@
       <c r="Y11" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="Z11" s="62" t="s">
+      <c r="Z11" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA11" s="28" t="s">
         <v>182</v>
       </c>
-      <c r="AB11" s="62" t="s">
+      <c r="AB11" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC11" s="29" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="12" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD11" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="56">
         <v>12</v>
       </c>
@@ -3893,20 +3913,23 @@
       <c r="Y12" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="Z12" s="62" t="s">
+      <c r="Z12" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA12" s="28" t="s">
         <v>182</v>
       </c>
-      <c r="AB12" s="62" t="s">
+      <c r="AB12" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC12" s="29" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD12" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="56">
         <v>13</v>
       </c>
@@ -3988,20 +4011,23 @@
       <c r="Y13" s="28" t="s">
         <v>240</v>
       </c>
-      <c r="Z13" s="62" t="s">
+      <c r="Z13" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA13" s="28" t="s">
         <v>229</v>
       </c>
-      <c r="AB13" s="62" t="s">
+      <c r="AB13" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC13" s="29" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD13" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="56">
         <v>14</v>
       </c>
@@ -4083,20 +4109,23 @@
       <c r="Y14" s="28" t="s">
         <v>235</v>
       </c>
-      <c r="Z14" s="62" t="s">
+      <c r="Z14" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA14" s="28" t="s">
         <v>234</v>
       </c>
-      <c r="AB14" s="62" t="s">
+      <c r="AB14" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC14" s="29" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD14" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="56">
         <v>15</v>
       </c>
@@ -4178,20 +4207,23 @@
       <c r="Y15" s="28" t="s">
         <v>247</v>
       </c>
-      <c r="Z15" s="62" t="s">
+      <c r="Z15" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA15" s="28" t="s">
         <v>184</v>
       </c>
-      <c r="AB15" s="62" t="s">
+      <c r="AB15" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC15" s="29" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD15" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="56">
         <v>16</v>
       </c>
@@ -4273,20 +4305,23 @@
       <c r="Y16" s="28" t="s">
         <v>247</v>
       </c>
-      <c r="Z16" s="62" t="s">
+      <c r="Z16" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA16" s="28" t="s">
         <v>184</v>
       </c>
-      <c r="AB16" s="62" t="s">
+      <c r="AB16" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC16" s="29" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="17" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD16" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="56">
         <v>17</v>
       </c>
@@ -4368,20 +4403,23 @@
       <c r="Y17" s="28" t="s">
         <v>247</v>
       </c>
-      <c r="Z17" s="62" t="s">
+      <c r="Z17" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA17" s="28" t="s">
         <v>184</v>
       </c>
-      <c r="AB17" s="62" t="s">
+      <c r="AB17" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC17" s="29" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="18" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD17" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="56">
         <v>18</v>
       </c>
@@ -4463,20 +4501,23 @@
       <c r="Y18" s="28" t="s">
         <v>247</v>
       </c>
-      <c r="Z18" s="62" t="s">
+      <c r="Z18" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA18" s="28" t="s">
         <v>248</v>
       </c>
-      <c r="AB18" s="62" t="s">
+      <c r="AB18" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC18" s="29" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="19" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD18" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="56">
         <v>19</v>
       </c>
@@ -4558,20 +4599,23 @@
       <c r="Y19" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="Z19" s="62" t="s">
+      <c r="Z19" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA19" s="28" t="s">
         <v>185</v>
       </c>
-      <c r="AB19" s="62" t="s">
+      <c r="AB19" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC19" s="29" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="20" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD19" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="56">
         <v>20</v>
       </c>
@@ -4653,20 +4697,23 @@
       <c r="Y20" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="Z20" s="62" t="s">
+      <c r="Z20" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA20" s="28" t="s">
         <v>185</v>
       </c>
-      <c r="AB20" s="62" t="s">
+      <c r="AB20" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC20" s="29" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="21" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD20" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="56">
         <v>21</v>
       </c>
@@ -4748,20 +4795,23 @@
       <c r="Y21" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="Z21" s="62" t="s">
+      <c r="Z21" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA21" s="28" t="s">
         <v>186</v>
       </c>
-      <c r="AB21" s="62" t="s">
+      <c r="AB21" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC21" s="29" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="22" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD21" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="56">
         <v>22</v>
       </c>
@@ -4843,20 +4893,23 @@
       <c r="Y22" s="28" t="s">
         <v>247</v>
       </c>
-      <c r="Z22" s="62" t="s">
+      <c r="Z22" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA22" s="28" t="s">
         <v>248</v>
       </c>
-      <c r="AB22" s="62" t="s">
+      <c r="AB22" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC22" s="29" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="23" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD22" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="56">
         <v>23</v>
       </c>
@@ -4938,20 +4991,23 @@
       <c r="Y23" s="28" t="s">
         <v>247</v>
       </c>
-      <c r="Z23" s="62" t="s">
+      <c r="Z23" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA23" s="28" t="s">
         <v>248</v>
       </c>
-      <c r="AB23" s="62" t="s">
+      <c r="AB23" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC23" s="29" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="24" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD23" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="56">
         <v>24</v>
       </c>
@@ -5033,20 +5089,23 @@
       <c r="Y24" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="Z24" s="62" t="s">
+      <c r="Z24" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA24" s="28" t="s">
         <v>182</v>
       </c>
-      <c r="AB24" s="62" t="s">
+      <c r="AB24" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC24" s="29" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="25" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD24" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="56">
         <v>25</v>
       </c>
@@ -5128,20 +5187,23 @@
       <c r="Y25" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="Z25" s="62" t="s">
+      <c r="Z25" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA25" s="28" t="s">
         <v>182</v>
       </c>
-      <c r="AB25" s="62" t="s">
+      <c r="AB25" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC25" s="29" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="26" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD25" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="56">
         <v>26</v>
       </c>
@@ -5223,20 +5285,23 @@
       <c r="Y26" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="Z26" s="62" t="s">
+      <c r="Z26" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA26" s="28" t="s">
         <v>182</v>
       </c>
-      <c r="AB26" s="62" t="s">
+      <c r="AB26" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC26" s="29" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="27" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD26" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="56">
         <v>27</v>
       </c>
@@ -5318,20 +5383,23 @@
       <c r="Y27" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="Z27" s="62" t="s">
+      <c r="Z27" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA27" s="28" t="s">
         <v>182</v>
       </c>
-      <c r="AB27" s="62" t="s">
+      <c r="AB27" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC27" s="29" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="28" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD27" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="56">
         <v>28</v>
       </c>
@@ -5413,20 +5481,23 @@
       <c r="Y28" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="Z28" s="62" t="s">
+      <c r="Z28" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA28" s="28" t="s">
         <v>182</v>
       </c>
-      <c r="AB28" s="62" t="s">
+      <c r="AB28" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC28" s="29" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="29" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD28" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="56">
         <v>29</v>
       </c>
@@ -5508,20 +5579,23 @@
       <c r="Y29" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="Z29" s="62" t="s">
+      <c r="Z29" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA29" s="28" t="s">
         <v>182</v>
       </c>
-      <c r="AB29" s="62" t="s">
+      <c r="AB29" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC29" s="29" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="30" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD29" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="56">
         <v>30</v>
       </c>
@@ -5603,20 +5677,23 @@
       <c r="Y30" s="28" t="s">
         <v>247</v>
       </c>
-      <c r="Z30" s="62" t="s">
+      <c r="Z30" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA30" s="28" t="s">
         <v>248</v>
       </c>
-      <c r="AB30" s="62" t="s">
+      <c r="AB30" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC30" s="29" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="31" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD30" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="56">
         <v>31</v>
       </c>
@@ -5698,20 +5775,23 @@
       <c r="Y31" s="28" t="s">
         <v>247</v>
       </c>
-      <c r="Z31" s="62" t="s">
+      <c r="Z31" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA31" s="28" t="s">
         <v>248</v>
       </c>
-      <c r="AB31" s="62" t="s">
+      <c r="AB31" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC31" s="29" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="32" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD31" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="56">
         <v>32</v>
       </c>
@@ -5793,20 +5873,23 @@
       <c r="Y32" s="28" t="s">
         <v>247</v>
       </c>
-      <c r="Z32" s="62" t="s">
+      <c r="Z32" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA32" s="28" t="s">
         <v>248</v>
       </c>
-      <c r="AB32" s="62" t="s">
+      <c r="AB32" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC32" s="29" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="33" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD32" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="56">
         <v>33</v>
       </c>
@@ -5888,20 +5971,23 @@
       <c r="Y33" s="28" t="s">
         <v>247</v>
       </c>
-      <c r="Z33" s="62" t="s">
+      <c r="Z33" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA33" s="28" t="s">
         <v>248</v>
       </c>
-      <c r="AB33" s="62" t="s">
+      <c r="AB33" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC33" s="29" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="34" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD33" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="56">
         <v>34</v>
       </c>
@@ -5983,20 +6069,23 @@
       <c r="Y34" s="28" t="s">
         <v>247</v>
       </c>
-      <c r="Z34" s="62" t="s">
+      <c r="Z34" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA34" s="28" t="s">
         <v>248</v>
       </c>
-      <c r="AB34" s="62" t="s">
+      <c r="AB34" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC34" s="29" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="35" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD34" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="56">
         <v>35</v>
       </c>
@@ -6078,20 +6167,23 @@
       <c r="Y35" s="28" t="s">
         <v>247</v>
       </c>
-      <c r="Z35" s="62" t="s">
+      <c r="Z35" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA35" s="28" t="s">
         <v>248</v>
       </c>
-      <c r="AB35" s="62" t="s">
+      <c r="AB35" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC35" s="29" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="36" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD35" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="56">
         <v>36</v>
       </c>
@@ -6173,20 +6265,23 @@
       <c r="Y36" s="28" t="s">
         <v>247</v>
       </c>
-      <c r="Z36" s="62" t="s">
+      <c r="Z36" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA36" s="28" t="s">
         <v>248</v>
       </c>
-      <c r="AB36" s="62" t="s">
+      <c r="AB36" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC36" s="29" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="37" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD36" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="56">
         <v>37</v>
       </c>
@@ -6268,20 +6363,23 @@
       <c r="Y37" s="28" t="s">
         <v>247</v>
       </c>
-      <c r="Z37" s="62" t="s">
+      <c r="Z37" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA37" s="28" t="s">
         <v>248</v>
       </c>
-      <c r="AB37" s="62" t="s">
+      <c r="AB37" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC37" s="29" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="38" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD37" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="56">
         <v>38</v>
       </c>
@@ -6363,20 +6461,23 @@
       <c r="Y38" s="28" t="s">
         <v>247</v>
       </c>
-      <c r="Z38" s="62" t="s">
+      <c r="Z38" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA38" s="28" t="s">
         <v>248</v>
       </c>
-      <c r="AB38" s="62" t="s">
+      <c r="AB38" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC38" s="29" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="39" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD38" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="56">
         <v>39</v>
       </c>
@@ -6458,20 +6559,23 @@
       <c r="Y39" s="28" t="s">
         <v>247</v>
       </c>
-      <c r="Z39" s="62" t="s">
+      <c r="Z39" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA39" s="28" t="s">
         <v>248</v>
       </c>
-      <c r="AB39" s="62" t="s">
+      <c r="AB39" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC39" s="29" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="40" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD39" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="56">
         <v>40</v>
       </c>
@@ -6553,20 +6657,23 @@
       <c r="Y40" s="28" t="s">
         <v>247</v>
       </c>
-      <c r="Z40" s="62" t="s">
+      <c r="Z40" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA40" s="28" t="s">
         <v>248</v>
       </c>
-      <c r="AB40" s="62" t="s">
+      <c r="AB40" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC40" s="29" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="41" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD40" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="56">
         <v>41</v>
       </c>
@@ -6648,20 +6755,23 @@
       <c r="Y41" s="28" t="s">
         <v>247</v>
       </c>
-      <c r="Z41" s="62" t="s">
+      <c r="Z41" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA41" s="28" t="s">
         <v>248</v>
       </c>
-      <c r="AB41" s="62" t="s">
+      <c r="AB41" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC41" s="29" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="42" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD41" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="56">
         <v>42</v>
       </c>
@@ -6743,20 +6853,23 @@
       <c r="Y42" s="28" t="s">
         <v>235</v>
       </c>
-      <c r="Z42" s="62" t="s">
+      <c r="Z42" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA42" s="28" t="s">
         <v>234</v>
       </c>
-      <c r="AB42" s="62" t="s">
+      <c r="AB42" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC42" s="29" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="43" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD42" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="56">
         <v>43</v>
       </c>
@@ -6838,20 +6951,23 @@
       <c r="Y43" s="28" t="s">
         <v>247</v>
       </c>
-      <c r="Z43" s="62" t="s">
+      <c r="Z43" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA43" s="28" t="s">
         <v>248</v>
       </c>
-      <c r="AB43" s="62" t="s">
+      <c r="AB43" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC43" s="29" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="44" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD43" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="56">
         <v>44</v>
       </c>
@@ -6927,26 +7043,29 @@
         <v>152</v>
       </c>
       <c r="X44" s="57" t="str">
-        <f t="shared" ref="X44:X48" si="61">CONCATENATE("Key-HIDR-",A44)</f>
+        <f t="shared" ref="X44:X52" si="61">CONCATENATE("Key-HIDR-",A44)</f>
         <v>Key-HIDR-44</v>
       </c>
       <c r="Y44" s="28" t="s">
         <v>247</v>
       </c>
-      <c r="Z44" s="62" t="s">
+      <c r="Z44" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA44" s="28" t="s">
         <v>248</v>
       </c>
-      <c r="AB44" s="62" t="s">
+      <c r="AB44" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC44" s="29" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="45" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD44" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="56">
         <v>45</v>
       </c>
@@ -7028,20 +7147,23 @@
       <c r="Y45" s="28" t="s">
         <v>247</v>
       </c>
-      <c r="Z45" s="62" t="s">
+      <c r="Z45" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA45" s="28" t="s">
         <v>248</v>
       </c>
-      <c r="AB45" s="62" t="s">
+      <c r="AB45" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC45" s="29" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="46" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD45" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="56">
         <v>46</v>
       </c>
@@ -7123,20 +7245,23 @@
       <c r="Y46" s="28" t="s">
         <v>247</v>
       </c>
-      <c r="Z46" s="62" t="s">
+      <c r="Z46" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA46" s="28" t="s">
         <v>248</v>
       </c>
-      <c r="AB46" s="62" t="s">
+      <c r="AB46" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC46" s="29" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="47" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD46" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="47" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="56">
         <v>47</v>
       </c>
@@ -7218,36 +7343,39 @@
       <c r="Y47" s="28" t="s">
         <v>247</v>
       </c>
-      <c r="Z47" s="62" t="s">
+      <c r="Z47" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA47" s="28" t="s">
         <v>248</v>
       </c>
-      <c r="AB47" s="62" t="s">
+      <c r="AB47" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC47" s="29" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="48" spans="1:29" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AD47" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="48" spans="1:30" s="62" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="56">
         <v>48</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="C48" s="64" t="s">
+      <c r="C48" s="63" t="s">
         <v>342</v>
       </c>
-      <c r="D48" s="64" t="s">
+      <c r="D48" s="63" t="s">
         <v>344</v>
       </c>
-      <c r="E48" s="64" t="s">
+      <c r="E48" s="63" t="s">
         <v>343</v>
       </c>
-      <c r="F48" s="64" t="s">
+      <c r="F48" s="63" t="s">
         <v>345</v>
       </c>
       <c r="G48" s="58" t="s">
@@ -7266,7 +7394,7 @@
         <v>9</v>
       </c>
       <c r="L48" s="32" t="str">
-        <f t="shared" ref="L48:O48" si="67">SUBSTITUTE(CONCATENATE("", C48), ".", " ")</f>
+        <f t="shared" ref="L48:O52" si="67">SUBSTITUTE(CONCATENATE("", C48), ".", " ")</f>
         <v>De API</v>
       </c>
       <c r="M48" s="32" t="str">
@@ -7279,32 +7407,30 @@
       </c>
       <c r="O48" s="32" t="str">
         <f t="shared" si="67"/>
-        <v>API Revit</v>
+        <v>Função Auxiliar</v>
       </c>
       <c r="P48" s="29" t="s">
         <v>346</v>
       </c>
-      <c r="Q48" s="60" t="str">
-        <f t="shared" ref="Q48" si="68">_xlfn.TRANSLATE(P48,"pt","es")</f>
-        <v>Aplicación Revit</v>
-      </c>
-      <c r="R48" s="60" t="str">
-        <f t="shared" ref="R48" si="69">_xlfn.TRANSLATE(P48,"pt","en")</f>
-        <v>Revit App</v>
+      <c r="Q48" s="29" t="s">
+        <v>347</v>
+      </c>
+      <c r="R48" s="29" t="s">
+        <v>348</v>
       </c>
       <c r="S48" s="29" t="s">
         <v>9</v>
       </c>
       <c r="T48" s="29" t="str">
-        <f t="shared" ref="T48:V48" si="70">SUBSTITUTE(C48, ".", " ")</f>
+        <f t="shared" ref="T48:V52" si="68">SUBSTITUTE(C48, ".", " ")</f>
         <v>De API</v>
       </c>
       <c r="U48" s="29" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="68"/>
         <v>Macros</v>
       </c>
-      <c r="V48" s="61" t="str">
-        <f t="shared" si="70"/>
+      <c r="V48" s="60" t="str">
+        <f t="shared" si="68"/>
         <v>Métodos</v>
       </c>
       <c r="W48" s="29" t="s">
@@ -7314,19 +7440,422 @@
         <f t="shared" si="61"/>
         <v>Key-HIDR-48</v>
       </c>
-      <c r="Y48" s="62" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z48" s="62" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA48" s="62" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB48" s="62" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC48" s="62" t="s">
+      <c r="Y48" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z48" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA48" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB48" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC48" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD48" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="49" spans="1:30" s="62" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="56">
+        <v>49</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C49" s="63" t="s">
+        <v>342</v>
+      </c>
+      <c r="D49" s="63" t="s">
+        <v>344</v>
+      </c>
+      <c r="E49" s="63" t="s">
+        <v>343</v>
+      </c>
+      <c r="F49" s="63" t="s">
+        <v>349</v>
+      </c>
+      <c r="G49" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H49" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I49" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J49" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K49" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="L49" s="32" t="str">
+        <f t="shared" si="67"/>
+        <v>De API</v>
+      </c>
+      <c r="M49" s="32" t="str">
+        <f t="shared" si="67"/>
+        <v>Macros</v>
+      </c>
+      <c r="N49" s="32" t="str">
+        <f t="shared" si="67"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O49" s="32" t="str">
+        <f t="shared" si="67"/>
+        <v>Função Global</v>
+      </c>
+      <c r="P49" s="29" t="s">
+        <v>350</v>
+      </c>
+      <c r="Q49" s="29" t="s">
+        <v>351</v>
+      </c>
+      <c r="R49" s="29" t="s">
+        <v>352</v>
+      </c>
+      <c r="S49" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="T49" s="29" t="str">
+        <f t="shared" si="68"/>
+        <v>De API</v>
+      </c>
+      <c r="U49" s="29" t="str">
+        <f t="shared" si="68"/>
+        <v>Macros</v>
+      </c>
+      <c r="V49" s="60" t="str">
+        <f t="shared" si="68"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W49" s="29" t="s">
+        <v>152</v>
+      </c>
+      <c r="X49" s="57" t="str">
+        <f t="shared" si="61"/>
+        <v>Key-HIDR-49</v>
+      </c>
+      <c r="Y49" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z49" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA49" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB49" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC49" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD49" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="50" spans="1:30" s="62" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="56">
+        <v>50</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C50" s="63" t="s">
+        <v>342</v>
+      </c>
+      <c r="D50" s="63" t="s">
+        <v>344</v>
+      </c>
+      <c r="E50" s="63" t="s">
+        <v>343</v>
+      </c>
+      <c r="F50" s="63" t="s">
+        <v>353</v>
+      </c>
+      <c r="G50" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H50" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I50" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J50" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K50" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="L50" s="32" t="str">
+        <f t="shared" si="67"/>
+        <v>De API</v>
+      </c>
+      <c r="M50" s="32" t="str">
+        <f t="shared" si="67"/>
+        <v>Macros</v>
+      </c>
+      <c r="N50" s="32" t="str">
+        <f t="shared" si="67"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O50" s="32" t="str">
+        <f t="shared" si="67"/>
+        <v>Função Local</v>
+      </c>
+      <c r="P50" s="29" t="s">
+        <v>354</v>
+      </c>
+      <c r="Q50" s="29" t="s">
+        <v>355</v>
+      </c>
+      <c r="R50" s="29" t="s">
+        <v>356</v>
+      </c>
+      <c r="S50" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="T50" s="29" t="str">
+        <f t="shared" si="68"/>
+        <v>De API</v>
+      </c>
+      <c r="U50" s="29" t="str">
+        <f t="shared" si="68"/>
+        <v>Macros</v>
+      </c>
+      <c r="V50" s="60" t="str">
+        <f t="shared" si="68"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W50" s="29" t="s">
+        <v>152</v>
+      </c>
+      <c r="X50" s="57" t="str">
+        <f t="shared" si="61"/>
+        <v>Key-HIDR-50</v>
+      </c>
+      <c r="Y50" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z50" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA50" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB50" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC50" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD50" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="51" spans="1:30" s="62" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="56">
+        <v>51</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C51" s="63" t="s">
+        <v>342</v>
+      </c>
+      <c r="D51" s="63" t="s">
+        <v>344</v>
+      </c>
+      <c r="E51" s="63" t="s">
+        <v>343</v>
+      </c>
+      <c r="F51" s="63" t="s">
+        <v>357</v>
+      </c>
+      <c r="G51" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H51" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I51" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J51" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K51" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="L51" s="32" t="str">
+        <f t="shared" si="67"/>
+        <v>De API</v>
+      </c>
+      <c r="M51" s="32" t="str">
+        <f t="shared" si="67"/>
+        <v>Macros</v>
+      </c>
+      <c r="N51" s="32" t="str">
+        <f t="shared" si="67"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O51" s="32" t="str">
+        <f t="shared" si="67"/>
+        <v>Função Filtro</v>
+      </c>
+      <c r="P51" s="29" t="s">
+        <v>358</v>
+      </c>
+      <c r="Q51" s="29" t="s">
+        <v>359</v>
+      </c>
+      <c r="R51" s="29" t="s">
+        <v>360</v>
+      </c>
+      <c r="S51" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="T51" s="29" t="str">
+        <f t="shared" si="68"/>
+        <v>De API</v>
+      </c>
+      <c r="U51" s="29" t="str">
+        <f t="shared" si="68"/>
+        <v>Macros</v>
+      </c>
+      <c r="V51" s="60" t="str">
+        <f t="shared" si="68"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W51" s="29" t="s">
+        <v>152</v>
+      </c>
+      <c r="X51" s="57" t="str">
+        <f t="shared" si="61"/>
+        <v>Key-HIDR-51</v>
+      </c>
+      <c r="Y51" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z51" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA51" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB51" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC51" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD51" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="52" spans="1:30" s="62" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="56">
+        <v>52</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C52" s="63" t="s">
+        <v>342</v>
+      </c>
+      <c r="D52" s="63" t="s">
+        <v>344</v>
+      </c>
+      <c r="E52" s="63" t="s">
+        <v>361</v>
+      </c>
+      <c r="F52" s="63" t="s">
+        <v>362</v>
+      </c>
+      <c r="G52" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H52" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I52" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J52" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K52" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="L52" s="32" t="str">
+        <f t="shared" si="67"/>
+        <v>De API</v>
+      </c>
+      <c r="M52" s="32" t="str">
+        <f t="shared" si="67"/>
+        <v>Macros</v>
+      </c>
+      <c r="N52" s="32" t="str">
+        <f t="shared" si="67"/>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="O52" s="32" t="str">
+        <f t="shared" si="67"/>
+        <v>Bloco de Código</v>
+      </c>
+      <c r="P52" s="29" t="s">
+        <v>363</v>
+      </c>
+      <c r="Q52" s="29" t="s">
+        <v>364</v>
+      </c>
+      <c r="R52" s="29" t="s">
+        <v>365</v>
+      </c>
+      <c r="S52" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="T52" s="29" t="str">
+        <f t="shared" si="68"/>
+        <v>De API</v>
+      </c>
+      <c r="U52" s="29" t="str">
+        <f t="shared" si="68"/>
+        <v>Macros</v>
+      </c>
+      <c r="V52" s="60" t="str">
+        <f t="shared" si="68"/>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="W52" s="29" t="s">
+        <v>152</v>
+      </c>
+      <c r="X52" s="57" t="str">
+        <f t="shared" si="61"/>
+        <v>Key-HIDR-52</v>
+      </c>
+      <c r="Y52" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z52" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA52" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB52" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC52" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD52" s="61" t="s">
         <v>9</v>
       </c>
     </row>
@@ -7335,83 +7864,74 @@
     <sortCondition ref="F4:F933"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:B48">
-    <cfRule type="cellIs" dxfId="37" priority="5" operator="equal">
+  <conditionalFormatting sqref="A2:B52">
+    <cfRule type="cellIs" dxfId="30" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E52:F52">
+    <cfRule type="duplicateValues" dxfId="29" priority="2"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="36" priority="1508"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="1512"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F47 F49:F1048576">
-    <cfRule type="duplicateValues" dxfId="35" priority="36"/>
+  <conditionalFormatting sqref="F1:F47 F53:F1048576">
+    <cfRule type="duplicateValues" dxfId="27" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F13">
-    <cfRule type="duplicateValues" dxfId="34" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F32">
-    <cfRule type="duplicateValues" dxfId="33" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="62"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F35 F14:F30 F37:F47 F1:F12 F49:F1048576">
-    <cfRule type="duplicateValues" dxfId="32" priority="60"/>
+  <conditionalFormatting sqref="F35 F14:F30 F37:F47 F1:F12 F53:F1048576">
+    <cfRule type="duplicateValues" dxfId="24" priority="64"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F48">
-    <cfRule type="duplicateValues" dxfId="31" priority="6"/>
+  <conditionalFormatting sqref="F48:F51">
+    <cfRule type="duplicateValues" dxfId="23" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F49:F1048576">
-    <cfRule type="duplicateValues" dxfId="30" priority="265"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="267"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="1480"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="1501"/>
+  <conditionalFormatting sqref="F53:F1048576">
+    <cfRule type="duplicateValues" dxfId="22" priority="269"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="271"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="1484"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="1505"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:O1 A1:D1 Q1 S1:Z1">
-    <cfRule type="cellIs" dxfId="26" priority="72" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="76" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P2:P6">
-    <cfRule type="duplicateValues" dxfId="25" priority="1533"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="1537"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P7:P12 P14:P23">
-    <cfRule type="duplicateValues" dxfId="24" priority="1521"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="1525"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P24:P29">
-    <cfRule type="duplicateValues" dxfId="23" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P30">
-    <cfRule type="duplicateValues" dxfId="22" priority="1514"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="1518"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2:Q5">
-    <cfRule type="duplicateValues" dxfId="21" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="46"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q6">
-    <cfRule type="duplicateValues" dxfId="20" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q23">
-    <cfRule type="duplicateValues" dxfId="19" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q30">
-    <cfRule type="duplicateValues" dxfId="18" priority="1515"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q48">
-    <cfRule type="duplicateValues" dxfId="17" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="1519"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:R47">
-    <cfRule type="cellIs" dxfId="13" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="15" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R48">
-    <cfRule type="duplicateValues" dxfId="12" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AB1:AC1">
-    <cfRule type="cellIs" dxfId="8" priority="37" operator="equal">
+  <conditionalFormatting sqref="AB1:AD1">
+    <cfRule type="cellIs" dxfId="8" priority="41" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7426,15 +7946,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.84375" style="9" customWidth="1"/>
-    <col min="2" max="10" width="6.53515625" style="10" customWidth="1"/>
-    <col min="11" max="21" width="6.53515625" style="8" customWidth="1"/>
-    <col min="22" max="16384" width="11.15234375" style="8"/>
+    <col min="1" max="1" width="2.85546875" style="9" customWidth="1"/>
+    <col min="2" max="10" width="6.5703125" style="10" customWidth="1"/>
+    <col min="11" max="21" width="6.5703125" style="8" customWidth="1"/>
+    <col min="22" max="16384" width="11.140625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -7499,7 +8019,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -7582,30 +8102,30 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38CB0525-EDFB-44CB-9009-6752AEDD7340}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:S19"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.3046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.3046875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.69140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.84375" customWidth="1"/>
+    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.85546875" customWidth="1"/>
     <col min="6" max="6" width="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="60.15234375" customWidth="1"/>
+    <col min="7" max="7" width="60.140625" customWidth="1"/>
     <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.3828125" customWidth="1"/>
-    <col min="10" max="10" width="8.3046875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.84375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.3828125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.42578125" customWidth="1"/>
+    <col min="10" max="10" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.42578125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="24" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.3828125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="23.84375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.69140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="19.69140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.3046875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.3828125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="14.7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:19" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>10</v>
       </c>
@@ -7664,7 +8184,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="19">
         <v>1</v>
       </c>
@@ -7723,7 +8243,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="19">
         <v>2</v>
       </c>
@@ -7782,7 +8302,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="19">
         <v>3</v>
       </c>
@@ -7841,7 +8361,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="19">
         <v>4</v>
       </c>
@@ -7900,7 +8420,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="19">
         <v>5</v>
       </c>
@@ -7959,7 +8479,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="19">
         <v>6</v>
       </c>
@@ -8018,7 +8538,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="19">
         <v>7</v>
       </c>
@@ -8077,7 +8597,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="19">
         <v>8</v>
       </c>
@@ -8136,7 +8656,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="19">
         <v>9</v>
       </c>
@@ -8195,7 +8715,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="19">
         <v>10</v>
       </c>
@@ -8254,7 +8774,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="19">
         <v>11</v>
       </c>
@@ -8313,7 +8833,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="19">
         <v>12</v>
       </c>
@@ -8372,7 +8892,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="19">
         <v>13</v>
       </c>
@@ -8431,7 +8951,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="19">
         <v>14</v>
       </c>
@@ -8490,7 +9010,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="19">
         <v>15</v>
       </c>
@@ -8549,7 +9069,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="19">
         <v>16</v>
       </c>
@@ -8608,7 +9128,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="19">
         <v>17</v>
       </c>
@@ -8667,7 +9187,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="19">
         <v>18</v>
       </c>
@@ -8739,15 +9259,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5FE5EC8-1387-4A67-960C-C64BD1326958}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.15234375" style="25" customWidth="1"/>
-    <col min="2" max="2" width="5.84375" style="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.3046875" style="24" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.84375" style="24" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.140625" style="25" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" style="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" style="24" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.85546875" style="24" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="30">
         <v>0</v>
       </c>
@@ -8770,7 +9290,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="31">
         <v>2</v>
       </c>

--- a/Versão5/SIS/Ontologia_Hidrossanitaria.xlsx
+++ b/Versão5/SIS/Ontologia_Hidrossanitaria.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\SIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94F0091A-C804-4263-B50B-E16A38C11EAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1F27868-1640-4764-A4D6-B7B38292D61D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1657" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1846" uniqueCount="414">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -1173,6 +1173,147 @@
   </si>
   <si>
     <t>KML</t>
+  </si>
+  <si>
+    <t>De.Materialidade</t>
+  </si>
+  <si>
+    <t>Materialidades</t>
+  </si>
+  <si>
+    <t>Materiais</t>
+  </si>
+  <si>
+    <t>Tubo.de.Aço</t>
+  </si>
+  <si>
+    <t>Tubo de aço para canalizações.</t>
+  </si>
+  <si>
+    <t>Tubería de acero para fontanería.</t>
+  </si>
+  <si>
+    <t>Steel pipe for plumbing.</t>
+  </si>
+  <si>
+    <t>[ OST_Materials : OST_PipeMaterials ]</t>
+  </si>
+  <si>
+    <t>[ IfcMaterial ]</t>
+  </si>
+  <si>
+    <t>[ 0M.20.20.01.01 ]</t>
+  </si>
+  <si>
+    <t>Tubo.de.Aço.Costura</t>
+  </si>
+  <si>
+    <t>Tubo de aço com costura (especificações NBR 5580 ou NBR 5590).</t>
+  </si>
+  <si>
+    <t>Tubería de acero soldada (especificaciones NBR 5580 o NBR 5590).</t>
+  </si>
+  <si>
+    <t>Welded steel pipe (NBR 5580 or NBR 5590 specifications).</t>
+  </si>
+  <si>
+    <t>Tubo.de.Cobre</t>
+  </si>
+  <si>
+    <t>Tubo de cobre para redes de água quente ou gás.</t>
+  </si>
+  <si>
+    <t>Tubería de cobre para agua caliente o redes de gas.</t>
+  </si>
+  <si>
+    <t>Copper pipe for hot water or gas networks.</t>
+  </si>
+  <si>
+    <t>[ 0M.20.20.05 ]</t>
+  </si>
+  <si>
+    <t>Tubo.de.FoFo</t>
+  </si>
+  <si>
+    <t>Tubo de Ferro Fundido para redes de agua e esgoto de saneamento básico.</t>
+  </si>
+  <si>
+    <t>Tubería de hierro fundido para redes de agua y alcantarillado de saneamiento básico.</t>
+  </si>
+  <si>
+    <t>Cast Iron Pipe for water and sewage networks of basic sanitation.</t>
+  </si>
+  <si>
+    <t>[ 0M.20.20.01.07.03 ]</t>
+  </si>
+  <si>
+    <t>Tubo.de.Latão</t>
+  </si>
+  <si>
+    <t>Tubo de latão para redes de água.</t>
+  </si>
+  <si>
+    <t>Tubería de latón para redes de agua.</t>
+  </si>
+  <si>
+    <t>Brass pipe for water networks.</t>
+  </si>
+  <si>
+    <t>[ 0M.20.20.05.01 ]</t>
+  </si>
+  <si>
+    <t>Tubo.de.PEAD</t>
+  </si>
+  <si>
+    <t>Tubo de termofusão PEAD (Polietileno de Alta Densidade).</t>
+  </si>
+  <si>
+    <t>Tubo de termofusión HDPE (Polietileno de Alta Densidad).</t>
+  </si>
+  <si>
+    <t>HDPE (High Density Polyethylene) thermofusion tube.</t>
+  </si>
+  <si>
+    <t>[ 0M.20.60.07.09 ]</t>
+  </si>
+  <si>
+    <t>Tubo.de.PVC</t>
+  </si>
+  <si>
+    <t>Tubo de PVC (Policloreto de Vinila) para redes de agua e esgoto doméstica.</t>
+  </si>
+  <si>
+    <t>Tubería de PVC (cloruro de polivinilo) para redes domésticas de agua y alcantarillado.</t>
+  </si>
+  <si>
+    <t>PVC (Polyvinyl Chloride) pipe for domestic water and sewage networks.</t>
+  </si>
+  <si>
+    <t>[ 0M.20.60.07.16 ]</t>
+  </si>
+  <si>
+    <t>Tubo.de.PVCO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tubo de PVC Orientado (Policloreto de Vinila). Material mais resistente que PVC normal para redes de água e esgoto. </t>
+  </si>
+  <si>
+    <t>Tubería de PVC orientada (cloruro de polivinilo). Material más resistente que el PVC normal para redes de agua y alcantarillado.</t>
+  </si>
+  <si>
+    <t>Oriented PVC Pipe (Polyvinyl Chloride). Material more resistant than normal PVC for water and sewage networks.</t>
+  </si>
+  <si>
+    <t>Tubo.Multicamada</t>
+  </si>
+  <si>
+    <t>Tubo composto por uma camada interna de plástico (PEX), uma camada intermediária de alumínio contínuo (Al) e uma camada externa de plástico protetor. Tubo flexível conectado por crimpagem.</t>
+  </si>
+  <si>
+    <t>Tubo compuesto por una capa interior de plástico (PEX), una capa intermedia de aluminio continuo (Al) y una capa exterior de plástico protector. Tubo flexible conectado mediante crimping.</t>
+  </si>
+  <si>
+    <t>Tube composed of an inner layer of plastic (PEX), a middle layer of continuous aluminium (Al) and an outer layer of protective plastic. Flexible tube connected by crimping.</t>
   </si>
 </sst>
 </file>
@@ -1521,7 +1662,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1710,11 +1851,17 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="31">
+  <dxfs count="47">
     <dxf>
       <font>
         <b val="0"/>
@@ -1787,6 +1934,14 @@
         <i/>
         <strike val="0"/>
         <color rgb="FFFFFFFF"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
     <dxf>
@@ -1892,6 +2047,156 @@
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2444,15 +2749,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="9.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="54" customWidth="1"/>
-    <col min="2" max="2" width="40.140625" style="54" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="40" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="54"/>
+    <col min="1" max="1" width="8.69140625" style="54" customWidth="1"/>
+    <col min="2" max="2" width="40.15234375" style="54" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="40" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.15234375" style="54"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="11" t="s">
         <v>44</v>
       </c>
@@ -2463,7 +2768,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="12" t="s">
         <v>46</v>
       </c>
@@ -2474,7 +2779,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="12" t="s">
         <v>48</v>
       </c>
@@ -2485,7 +2790,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="13" t="s">
         <v>49</v>
       </c>
@@ -2496,7 +2801,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="13" t="s">
         <v>50</v>
       </c>
@@ -2508,7 +2813,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="13" t="s">
         <v>51</v>
       </c>
@@ -2520,7 +2825,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="13" t="s">
         <v>52</v>
       </c>
@@ -2531,7 +2836,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="37" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" s="37" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="36" t="s">
         <v>54</v>
       </c>
@@ -2542,7 +2847,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="13" t="s">
         <v>55</v>
       </c>
@@ -2553,7 +2858,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="13" t="s">
         <v>57</v>
       </c>
@@ -2564,7 +2869,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="13" t="s">
         <v>59</v>
       </c>
@@ -2575,7 +2880,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="13" t="s">
         <v>60</v>
       </c>
@@ -2586,7 +2891,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="13" t="s">
         <v>61</v>
       </c>
@@ -2597,7 +2902,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="13" t="s">
         <v>62</v>
       </c>
@@ -2608,7 +2913,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="13" t="s">
         <v>63</v>
       </c>
@@ -2619,7 +2924,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="13" t="s">
         <v>64</v>
       </c>
@@ -2630,7 +2935,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="13" t="s">
         <v>65</v>
       </c>
@@ -2641,19 +2946,19 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="13" t="s">
         <v>66</v>
       </c>
       <c r="B18" s="14">
         <f ca="1">NOW()</f>
-        <v>46268.700805787033</v>
+        <v>46270.887384027781</v>
       </c>
       <c r="C18" s="39" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="13" t="s">
         <v>67</v>
       </c>
@@ -2664,7 +2969,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="13" t="s">
         <v>69</v>
       </c>
@@ -2675,7 +2980,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="13" t="s">
         <v>70</v>
       </c>
@@ -2686,7 +2991,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="13" t="s">
         <v>71</v>
       </c>
@@ -2697,7 +3002,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="13" t="s">
         <v>72</v>
       </c>
@@ -2708,7 +3013,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="37" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" s="37" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="13" t="s">
         <v>86</v>
       </c>
@@ -2728,38 +3033,38 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96052D63-9637-42D9-866B-0BB924A50D8C}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AD52"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AD61"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.28515625" style="52" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.3828125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.3046875" style="52" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="52" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="52" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.28515625" style="52" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.140625" style="59" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="10.140625" style="52" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.3828125" style="52" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.3046875" style="52" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.15234375" style="59" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="10.15234375" style="52" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="10" style="52" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="52" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.28515625" style="52" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.140625" style="52" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="44.42578125" style="52" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.3828125" style="52" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.3046875" style="52" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.15234375" style="52" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="44.3828125" style="52" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="41" style="52" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="37" style="52" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.7109375" style="52" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.7109375" style="52" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="6.85546875" style="52" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.28515625" style="52" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="6.7109375" style="52" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="7.85546875" style="52" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="45.5703125" style="52" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="9.42578125" style="52" customWidth="1"/>
-    <col min="27" max="27" width="22.140625" style="53" customWidth="1"/>
-    <col min="28" max="28" width="9.7109375" style="52" customWidth="1"/>
-    <col min="29" max="29" width="8.140625" style="52" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="52"/>
+    <col min="19" max="19" width="3.69140625" style="52" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.69140625" style="52" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.84375" style="52" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.3046875" style="52" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.69140625" style="52" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.84375" style="52" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="45.53515625" style="52" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9.3828125" style="52" customWidth="1"/>
+    <col min="27" max="27" width="22.15234375" style="53" customWidth="1"/>
+    <col min="28" max="28" width="9.69140625" style="52" customWidth="1"/>
+    <col min="29" max="29" width="8.15234375" style="52" customWidth="1"/>
+    <col min="30" max="16384" width="9.15234375" style="52"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="38.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" ht="38.700000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="42" t="s">
         <v>91</v>
       </c>
@@ -2851,24 +3156,24 @@
         <v>366</v>
       </c>
     </row>
-    <row r="2" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="56">
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="C2" s="41" t="s">
-        <v>244</v>
-      </c>
-      <c r="D2" s="41" t="s">
-        <v>246</v>
-      </c>
-      <c r="E2" s="41" t="s">
-        <v>254</v>
-      </c>
-      <c r="F2" s="41" t="s">
-        <v>153</v>
+      <c r="C2" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="F2" s="64" t="s">
+        <v>370</v>
       </c>
       <c r="G2" s="58" t="s">
         <v>9</v>
@@ -2886,87 +3191,89 @@
         <v>9</v>
       </c>
       <c r="L2" s="32" t="str">
-        <f t="shared" ref="L2:L3" si="0">CONCATENATE("", C2)</f>
-        <v>Sistemas.Prediais</v>
+        <f t="shared" ref="L2:O10" si="0">SUBSTITUTE(CONCATENATE("", C2), ".", " ")</f>
+        <v>De Materialidade</v>
       </c>
       <c r="M2" s="32" t="str">
-        <f t="shared" ref="M2:M3" si="1">CONCATENATE("", D2)</f>
-        <v>Sistemas.Hidrossanitários</v>
+        <f t="shared" si="0"/>
+        <v>Materialidades</v>
       </c>
       <c r="N2" s="32" t="str">
-        <f t="shared" ref="N2:N3" si="2">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E2),"."," ")," De "," de "))</f>
-        <v>Sistemas Sanitários</v>
-      </c>
-      <c r="O2" s="29" t="str">
-        <f t="shared" ref="O2:O3" si="3">IF(ISNUMBER(FIND("Ifc",F2)),CONCATENATE("Classe IFC:   ",F2),CONCATENATE("",F2))</f>
-        <v>Sistema.ESG</v>
-      </c>
-      <c r="P2" s="51" t="s">
-        <v>265</v>
-      </c>
-      <c r="Q2" s="51" t="s">
-        <v>259</v>
+        <f t="shared" si="0"/>
+        <v>Materiais</v>
+      </c>
+      <c r="O2" s="32" t="str">
+        <f t="shared" si="0"/>
+        <v>Tubo de Aço</v>
+      </c>
+      <c r="P2" s="65" t="s">
+        <v>371</v>
+      </c>
+      <c r="Q2" s="29" t="s">
+        <v>372</v>
       </c>
       <c r="R2" s="29" t="s">
-        <v>297</v>
+        <v>373</v>
       </c>
       <c r="S2" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="T2" s="29" t="s">
-        <v>151</v>
-      </c>
-      <c r="U2" s="29" t="s">
-        <v>150</v>
+      <c r="T2" s="29" t="str">
+        <f t="shared" ref="T2:V10" si="1">SUBSTITUTE(C2, ".", " ")</f>
+        <v>De Materialidade</v>
+      </c>
+      <c r="U2" s="29" t="str">
+        <f t="shared" si="1"/>
+        <v>Materialidades</v>
       </c>
       <c r="V2" s="29" t="str">
-        <f t="shared" ref="V2:V3" si="4">SUBSTITUTE(E2, "_", " ")</f>
-        <v>Sistemas.Sanitários</v>
+        <f t="shared" si="1"/>
+        <v>Materiais</v>
       </c>
       <c r="W2" s="29" t="s">
         <v>152</v>
       </c>
       <c r="X2" s="57" t="str">
-        <f t="shared" ref="X2:X42" si="5">CONCATENATE("Key-HIDR-",A2)</f>
+        <f t="shared" ref="X2:X10" si="2">CONCATENATE("Key-HIDR-",A2)</f>
         <v>Key-HIDR-2</v>
       </c>
-      <c r="Y2" s="28" t="s">
-        <v>188</v>
+      <c r="Y2" s="29" t="s">
+        <v>374</v>
       </c>
       <c r="Z2" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AA2" s="28" t="s">
-        <v>226</v>
+      <c r="AA2" s="29" t="s">
+        <v>375</v>
       </c>
       <c r="AB2" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC2" s="29" t="s">
-        <v>126</v>
+        <v>376</v>
       </c>
       <c r="AD2" s="61" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="56">
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="C3" s="41" t="s">
-        <v>244</v>
-      </c>
-      <c r="D3" s="41" t="s">
-        <v>246</v>
-      </c>
-      <c r="E3" s="41" t="s">
-        <v>254</v>
-      </c>
-      <c r="F3" s="41" t="s">
-        <v>256</v>
+      <c r="C3" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="F3" s="64" t="s">
+        <v>377</v>
       </c>
       <c r="G3" s="58" t="s">
         <v>9</v>
@@ -2985,86 +3292,88 @@
       </c>
       <c r="L3" s="32" t="str">
         <f t="shared" si="0"/>
-        <v>Sistemas.Prediais</v>
+        <v>De Materialidade</v>
       </c>
       <c r="M3" s="32" t="str">
+        <f t="shared" si="0"/>
+        <v>Materialidades</v>
+      </c>
+      <c r="N3" s="32" t="str">
+        <f t="shared" si="0"/>
+        <v>Materiais</v>
+      </c>
+      <c r="O3" s="32" t="str">
+        <f t="shared" si="0"/>
+        <v>Tubo de Aço Costura</v>
+      </c>
+      <c r="P3" s="65" t="s">
+        <v>378</v>
+      </c>
+      <c r="Q3" s="29" t="s">
+        <v>379</v>
+      </c>
+      <c r="R3" s="29" t="s">
+        <v>380</v>
+      </c>
+      <c r="S3" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="T3" s="29" t="str">
         <f t="shared" si="1"/>
-        <v>Sistemas.Hidrossanitários</v>
-      </c>
-      <c r="N3" s="32" t="str">
-        <f t="shared" si="2"/>
-        <v>Sistemas Sanitários</v>
-      </c>
-      <c r="O3" s="29" t="str">
-        <f t="shared" si="3"/>
-        <v>Sistema.VEN</v>
-      </c>
-      <c r="P3" s="51" t="s">
-        <v>264</v>
-      </c>
-      <c r="Q3" s="51" t="s">
-        <v>258</v>
-      </c>
-      <c r="R3" s="29" t="s">
-        <v>298</v>
-      </c>
-      <c r="S3" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="T3" s="29" t="s">
-        <v>151</v>
-      </c>
-      <c r="U3" s="29" t="s">
-        <v>150</v>
+        <v>De Materialidade</v>
+      </c>
+      <c r="U3" s="29" t="str">
+        <f t="shared" si="1"/>
+        <v>Materialidades</v>
       </c>
       <c r="V3" s="29" t="str">
-        <f t="shared" si="4"/>
-        <v>Sistemas.Sanitários</v>
+        <f t="shared" si="1"/>
+        <v>Materiais</v>
       </c>
       <c r="W3" s="29" t="s">
         <v>152</v>
       </c>
       <c r="X3" s="57" t="str">
-        <f t="shared" ref="X3" si="6">CONCATENATE("Key-HIDR-",A3)</f>
+        <f t="shared" si="2"/>
         <v>Key-HIDR-3</v>
       </c>
-      <c r="Y3" s="28" t="s">
-        <v>188</v>
+      <c r="Y3" s="29" t="s">
+        <v>374</v>
       </c>
       <c r="Z3" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AA3" s="28" t="s">
-        <v>257</v>
+      <c r="AA3" s="29" t="s">
+        <v>375</v>
       </c>
       <c r="AB3" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC3" s="29" t="s">
-        <v>126</v>
+        <v>376</v>
       </c>
       <c r="AD3" s="61" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="56">
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="C4" s="41" t="s">
-        <v>244</v>
-      </c>
-      <c r="D4" s="41" t="s">
-        <v>246</v>
-      </c>
-      <c r="E4" s="41" t="s">
-        <v>255</v>
-      </c>
-      <c r="F4" s="41" t="s">
-        <v>219</v>
+      <c r="C4" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="F4" s="64" t="s">
+        <v>381</v>
       </c>
       <c r="G4" s="58" t="s">
         <v>9</v>
@@ -3082,87 +3391,89 @@
         <v>9</v>
       </c>
       <c r="L4" s="32" t="str">
-        <f t="shared" ref="L4:L14" si="7">CONCATENATE("", C4)</f>
-        <v>Sistemas.Prediais</v>
+        <f t="shared" si="0"/>
+        <v>De Materialidade</v>
       </c>
       <c r="M4" s="32" t="str">
-        <f t="shared" ref="M4:M14" si="8">CONCATENATE("", D4)</f>
-        <v>Sistemas.Hidrossanitários</v>
+        <f t="shared" si="0"/>
+        <v>Materialidades</v>
       </c>
       <c r="N4" s="32" t="str">
-        <f t="shared" ref="N4:N14" si="9">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E4),"."," ")," De "," de "))</f>
-        <v>Sistemas Hidráulicos</v>
-      </c>
-      <c r="O4" s="29" t="str">
-        <f t="shared" ref="O4:O42" si="10">IF(ISNUMBER(FIND("Ifc",F4)),CONCATENATE("Classe IFC:   ",F4),CONCATENATE("",F4))</f>
-        <v>Sistema.AFR</v>
-      </c>
-      <c r="P4" s="51" t="s">
-        <v>266</v>
-      </c>
-      <c r="Q4" s="51" t="s">
-        <v>260</v>
+        <f t="shared" si="0"/>
+        <v>Materiais</v>
+      </c>
+      <c r="O4" s="32" t="str">
+        <f t="shared" si="0"/>
+        <v>Tubo de Cobre</v>
+      </c>
+      <c r="P4" s="65" t="s">
+        <v>382</v>
+      </c>
+      <c r="Q4" s="29" t="s">
+        <v>383</v>
       </c>
       <c r="R4" s="29" t="s">
-        <v>299</v>
+        <v>384</v>
       </c>
       <c r="S4" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="T4" s="29" t="s">
-        <v>151</v>
-      </c>
-      <c r="U4" s="29" t="s">
-        <v>150</v>
+      <c r="T4" s="29" t="str">
+        <f t="shared" si="1"/>
+        <v>De Materialidade</v>
+      </c>
+      <c r="U4" s="29" t="str">
+        <f t="shared" si="1"/>
+        <v>Materialidades</v>
       </c>
       <c r="V4" s="29" t="str">
-        <f t="shared" ref="V4:V14" si="11">SUBSTITUTE(E4, "_", " ")</f>
-        <v>Sistemas.Hidráulicos</v>
+        <f t="shared" si="1"/>
+        <v>Materiais</v>
       </c>
       <c r="W4" s="29" t="s">
         <v>152</v>
       </c>
       <c r="X4" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>Key-HIDR-4</v>
       </c>
-      <c r="Y4" s="28" t="s">
-        <v>188</v>
+      <c r="Y4" s="29" t="s">
+        <v>374</v>
       </c>
       <c r="Z4" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AA4" s="28" t="s">
-        <v>224</v>
+      <c r="AA4" s="29" t="s">
+        <v>375</v>
       </c>
       <c r="AB4" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC4" s="29" t="s">
-        <v>154</v>
+        <v>385</v>
       </c>
       <c r="AD4" s="61" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="56">
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="C5" s="41" t="s">
-        <v>244</v>
-      </c>
-      <c r="D5" s="41" t="s">
-        <v>246</v>
-      </c>
-      <c r="E5" s="41" t="s">
-        <v>255</v>
-      </c>
-      <c r="F5" s="41" t="s">
-        <v>220</v>
+      <c r="C5" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="F5" s="64" t="s">
+        <v>386</v>
       </c>
       <c r="G5" s="58" t="s">
         <v>9</v>
@@ -3180,87 +3491,89 @@
         <v>9</v>
       </c>
       <c r="L5" s="32" t="str">
-        <f t="shared" si="7"/>
-        <v>Sistemas.Prediais</v>
+        <f t="shared" si="0"/>
+        <v>De Materialidade</v>
       </c>
       <c r="M5" s="32" t="str">
-        <f t="shared" si="8"/>
-        <v>Sistemas.Hidrossanitários</v>
+        <f t="shared" si="0"/>
+        <v>Materialidades</v>
       </c>
       <c r="N5" s="32" t="str">
-        <f t="shared" si="9"/>
-        <v>Sistemas Hidráulicos</v>
-      </c>
-      <c r="O5" s="29" t="str">
-        <f t="shared" si="10"/>
-        <v>Sistema.AQT</v>
-      </c>
-      <c r="P5" s="51" t="s">
-        <v>267</v>
-      </c>
-      <c r="Q5" s="51" t="s">
-        <v>261</v>
+        <f t="shared" si="0"/>
+        <v>Materiais</v>
+      </c>
+      <c r="O5" s="32" t="str">
+        <f t="shared" si="0"/>
+        <v>Tubo de FoFo</v>
+      </c>
+      <c r="P5" s="65" t="s">
+        <v>387</v>
+      </c>
+      <c r="Q5" s="29" t="s">
+        <v>388</v>
       </c>
       <c r="R5" s="29" t="s">
-        <v>300</v>
+        <v>389</v>
       </c>
       <c r="S5" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="T5" s="29" t="s">
-        <v>151</v>
-      </c>
-      <c r="U5" s="29" t="s">
-        <v>150</v>
+      <c r="T5" s="29" t="str">
+        <f t="shared" si="1"/>
+        <v>De Materialidade</v>
+      </c>
+      <c r="U5" s="29" t="str">
+        <f t="shared" si="1"/>
+        <v>Materialidades</v>
       </c>
       <c r="V5" s="29" t="str">
-        <f t="shared" si="11"/>
-        <v>Sistemas.Hidráulicos</v>
+        <f t="shared" si="1"/>
+        <v>Materiais</v>
       </c>
       <c r="W5" s="29" t="s">
         <v>152</v>
       </c>
       <c r="X5" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>Key-HIDR-5</v>
       </c>
-      <c r="Y5" s="28" t="s">
-        <v>188</v>
+      <c r="Y5" s="29" t="s">
+        <v>374</v>
       </c>
       <c r="Z5" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AA5" s="28" t="s">
-        <v>225</v>
+      <c r="AA5" s="29" t="s">
+        <v>375</v>
       </c>
       <c r="AB5" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC5" s="29" t="s">
-        <v>154</v>
+        <v>390</v>
       </c>
       <c r="AD5" s="61" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="56">
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="C6" s="41" t="s">
-        <v>244</v>
-      </c>
-      <c r="D6" s="41" t="s">
-        <v>246</v>
-      </c>
-      <c r="E6" s="41" t="s">
-        <v>268</v>
-      </c>
-      <c r="F6" s="41" t="s">
-        <v>262</v>
+      <c r="C6" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="F6" s="64" t="s">
+        <v>391</v>
       </c>
       <c r="G6" s="58" t="s">
         <v>9</v>
@@ -3278,87 +3591,89 @@
         <v>9</v>
       </c>
       <c r="L6" s="32" t="str">
-        <f t="shared" si="7"/>
-        <v>Sistemas.Prediais</v>
+        <f t="shared" si="0"/>
+        <v>De Materialidade</v>
       </c>
       <c r="M6" s="32" t="str">
-        <f t="shared" si="8"/>
-        <v>Sistemas.Hidrossanitários</v>
+        <f t="shared" si="0"/>
+        <v>Materialidades</v>
       </c>
       <c r="N6" s="32" t="str">
-        <f t="shared" si="9"/>
-        <v>Sistemas Pluviais</v>
-      </c>
-      <c r="O6" s="29" t="str">
-        <f t="shared" ref="O6" si="12">IF(ISNUMBER(FIND("Ifc",F6)),CONCATENATE("Classe IFC:   ",F6),CONCATENATE("",F6))</f>
-        <v>Sistema.PLU</v>
-      </c>
-      <c r="P6" s="51" t="s">
-        <v>263</v>
-      </c>
-      <c r="Q6" s="51" t="s">
-        <v>263</v>
+        <f t="shared" si="0"/>
+        <v>Materiais</v>
+      </c>
+      <c r="O6" s="32" t="str">
+        <f t="shared" si="0"/>
+        <v>Tubo de Latão</v>
+      </c>
+      <c r="P6" s="65" t="s">
+        <v>392</v>
+      </c>
+      <c r="Q6" s="29" t="s">
+        <v>393</v>
       </c>
       <c r="R6" s="29" t="s">
-        <v>301</v>
+        <v>394</v>
       </c>
       <c r="S6" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="T6" s="29" t="s">
-        <v>151</v>
-      </c>
-      <c r="U6" s="29" t="s">
-        <v>150</v>
+      <c r="T6" s="29" t="str">
+        <f t="shared" si="1"/>
+        <v>De Materialidade</v>
+      </c>
+      <c r="U6" s="29" t="str">
+        <f t="shared" si="1"/>
+        <v>Materialidades</v>
       </c>
       <c r="V6" s="29" t="str">
-        <f t="shared" si="11"/>
-        <v>Sistemas.Pluviais</v>
+        <f t="shared" si="1"/>
+        <v>Materiais</v>
       </c>
       <c r="W6" s="29" t="s">
         <v>152</v>
       </c>
       <c r="X6" s="57" t="str">
-        <f t="shared" ref="X6" si="13">CONCATENATE("Key-HIDR-",A6)</f>
+        <f t="shared" si="2"/>
         <v>Key-HIDR-6</v>
       </c>
-      <c r="Y6" s="28" t="s">
-        <v>188</v>
+      <c r="Y6" s="29" t="s">
+        <v>374</v>
       </c>
       <c r="Z6" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AA6" s="28" t="s">
-        <v>257</v>
+      <c r="AA6" s="29" t="s">
+        <v>375</v>
       </c>
       <c r="AB6" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC6" s="29" t="s">
-        <v>126</v>
+        <v>395</v>
       </c>
       <c r="AD6" s="61" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="56">
         <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="C7" s="41" t="s">
-        <v>244</v>
+      <c r="C7" s="1" t="s">
+        <v>367</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="E7" s="41" t="s">
-        <v>218</v>
-      </c>
-      <c r="F7" s="41" t="s">
-        <v>162</v>
+        <v>368</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="F7" s="64" t="s">
+        <v>396</v>
       </c>
       <c r="G7" s="58" t="s">
         <v>9</v>
@@ -3376,87 +3691,89 @@
         <v>9</v>
       </c>
       <c r="L7" s="32" t="str">
-        <f t="shared" si="7"/>
-        <v>Sistemas.Prediais</v>
+        <f t="shared" si="0"/>
+        <v>De Materialidade</v>
       </c>
       <c r="M7" s="32" t="str">
-        <f t="shared" si="8"/>
-        <v>Elementos.Hidráulicos</v>
+        <f t="shared" si="0"/>
+        <v>Materialidades</v>
       </c>
       <c r="N7" s="32" t="str">
-        <f t="shared" si="9"/>
-        <v>Peças Hidráulicas</v>
-      </c>
-      <c r="O7" s="29" t="str">
-        <f t="shared" si="10"/>
-        <v>Torneira</v>
-      </c>
-      <c r="P7" s="51" t="s">
-        <v>162</v>
+        <f t="shared" si="0"/>
+        <v>Materiais</v>
+      </c>
+      <c r="O7" s="32" t="str">
+        <f t="shared" si="0"/>
+        <v>Tubo de PEAD</v>
+      </c>
+      <c r="P7" s="65" t="s">
+        <v>397</v>
       </c>
       <c r="Q7" s="29" t="s">
-        <v>174</v>
+        <v>398</v>
       </c>
       <c r="R7" s="29" t="s">
-        <v>302</v>
+        <v>399</v>
       </c>
       <c r="S7" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="T7" s="29" t="s">
-        <v>151</v>
-      </c>
-      <c r="U7" s="29" t="s">
-        <v>150</v>
+      <c r="T7" s="29" t="str">
+        <f t="shared" si="1"/>
+        <v>De Materialidade</v>
+      </c>
+      <c r="U7" s="29" t="str">
+        <f t="shared" si="1"/>
+        <v>Materialidades</v>
       </c>
       <c r="V7" s="29" t="str">
-        <f t="shared" si="11"/>
-        <v>Peças.Hidráulicas</v>
+        <f t="shared" si="1"/>
+        <v>Materiais</v>
       </c>
       <c r="W7" s="29" t="s">
         <v>152</v>
       </c>
       <c r="X7" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>Key-HIDR-7</v>
       </c>
-      <c r="Y7" s="28" t="s">
-        <v>181</v>
+      <c r="Y7" s="29" t="s">
+        <v>374</v>
       </c>
       <c r="Z7" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AA7" s="28" t="s">
-        <v>183</v>
+      <c r="AA7" s="29" t="s">
+        <v>375</v>
       </c>
       <c r="AB7" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC7" s="29" t="s">
-        <v>154</v>
+        <v>400</v>
       </c>
       <c r="AD7" s="61" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="56">
         <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="C8" s="41" t="s">
-        <v>244</v>
+      <c r="C8" s="1" t="s">
+        <v>367</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="E8" s="41" t="s">
-        <v>218</v>
-      </c>
-      <c r="F8" s="41" t="s">
-        <v>163</v>
+        <v>368</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="F8" s="64" t="s">
+        <v>401</v>
       </c>
       <c r="G8" s="58" t="s">
         <v>9</v>
@@ -3474,87 +3791,89 @@
         <v>9</v>
       </c>
       <c r="L8" s="32" t="str">
-        <f t="shared" si="7"/>
-        <v>Sistemas.Prediais</v>
+        <f t="shared" si="0"/>
+        <v>De Materialidade</v>
       </c>
       <c r="M8" s="32" t="str">
-        <f t="shared" si="8"/>
-        <v>Elementos.Hidráulicos</v>
+        <f t="shared" si="0"/>
+        <v>Materialidades</v>
       </c>
       <c r="N8" s="32" t="str">
-        <f t="shared" si="9"/>
-        <v>Peças Hidráulicas</v>
-      </c>
-      <c r="O8" s="29" t="str">
-        <f t="shared" si="10"/>
-        <v>Misturador</v>
-      </c>
-      <c r="P8" s="51" t="s">
-        <v>163</v>
+        <f t="shared" si="0"/>
+        <v>Materiais</v>
+      </c>
+      <c r="O8" s="32" t="str">
+        <f t="shared" si="0"/>
+        <v>Tubo de PVC</v>
+      </c>
+      <c r="P8" s="65" t="s">
+        <v>402</v>
       </c>
       <c r="Q8" s="29" t="s">
-        <v>283</v>
+        <v>403</v>
       </c>
       <c r="R8" s="29" t="s">
-        <v>303</v>
+        <v>404</v>
       </c>
       <c r="S8" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="T8" s="29" t="s">
-        <v>151</v>
-      </c>
-      <c r="U8" s="29" t="s">
-        <v>150</v>
+      <c r="T8" s="29" t="str">
+        <f t="shared" si="1"/>
+        <v>De Materialidade</v>
+      </c>
+      <c r="U8" s="29" t="str">
+        <f t="shared" si="1"/>
+        <v>Materialidades</v>
       </c>
       <c r="V8" s="29" t="str">
-        <f t="shared" si="11"/>
-        <v>Peças.Hidráulicas</v>
+        <f t="shared" si="1"/>
+        <v>Materiais</v>
       </c>
       <c r="W8" s="29" t="s">
         <v>152</v>
       </c>
       <c r="X8" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>Key-HIDR-8</v>
       </c>
-      <c r="Y8" s="28" t="s">
-        <v>181</v>
+      <c r="Y8" s="29" t="s">
+        <v>374</v>
       </c>
       <c r="Z8" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AA8" s="28" t="s">
-        <v>183</v>
+      <c r="AA8" s="29" t="s">
+        <v>375</v>
       </c>
       <c r="AB8" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC8" s="29" t="s">
-        <v>154</v>
+        <v>405</v>
       </c>
       <c r="AD8" s="61" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="56">
         <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="C9" s="41" t="s">
-        <v>244</v>
+      <c r="C9" s="1" t="s">
+        <v>367</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="E9" s="41" t="s">
-        <v>218</v>
-      </c>
-      <c r="F9" s="41" t="s">
-        <v>165</v>
+        <v>368</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="F9" s="64" t="s">
+        <v>406</v>
       </c>
       <c r="G9" s="58" t="s">
         <v>9</v>
@@ -3572,87 +3891,89 @@
         <v>9</v>
       </c>
       <c r="L9" s="32" t="str">
-        <f t="shared" si="7"/>
-        <v>Sistemas.Prediais</v>
+        <f t="shared" si="0"/>
+        <v>De Materialidade</v>
       </c>
       <c r="M9" s="32" t="str">
-        <f t="shared" si="8"/>
-        <v>Elementos.Hidráulicos</v>
+        <f t="shared" si="0"/>
+        <v>Materialidades</v>
       </c>
       <c r="N9" s="32" t="str">
-        <f t="shared" si="9"/>
-        <v>Peças Hidráulicas</v>
-      </c>
-      <c r="O9" s="29" t="str">
-        <f t="shared" si="10"/>
-        <v>Registro</v>
-      </c>
-      <c r="P9" s="51" t="s">
-        <v>165</v>
+        <f t="shared" si="0"/>
+        <v>Materiais</v>
+      </c>
+      <c r="O9" s="32" t="str">
+        <f t="shared" si="0"/>
+        <v>Tubo de PVCO</v>
+      </c>
+      <c r="P9" s="65" t="s">
+        <v>407</v>
       </c>
       <c r="Q9" s="29" t="s">
-        <v>165</v>
+        <v>408</v>
       </c>
       <c r="R9" s="29" t="s">
-        <v>304</v>
+        <v>409</v>
       </c>
       <c r="S9" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="T9" s="29" t="s">
-        <v>151</v>
-      </c>
-      <c r="U9" s="29" t="s">
-        <v>150</v>
+      <c r="T9" s="29" t="str">
+        <f t="shared" si="1"/>
+        <v>De Materialidade</v>
+      </c>
+      <c r="U9" s="29" t="str">
+        <f t="shared" si="1"/>
+        <v>Materialidades</v>
       </c>
       <c r="V9" s="29" t="str">
-        <f t="shared" si="11"/>
-        <v>Peças.Hidráulicas</v>
+        <f t="shared" si="1"/>
+        <v>Materiais</v>
       </c>
       <c r="W9" s="29" t="s">
         <v>152</v>
       </c>
       <c r="X9" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>Key-HIDR-9</v>
       </c>
-      <c r="Y9" s="28" t="s">
-        <v>181</v>
+      <c r="Y9" s="29" t="s">
+        <v>374</v>
       </c>
       <c r="Z9" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AA9" s="28" t="s">
-        <v>183</v>
+      <c r="AA9" s="29" t="s">
+        <v>375</v>
       </c>
       <c r="AB9" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC9" s="29" t="s">
-        <v>154</v>
+        <v>405</v>
       </c>
       <c r="AD9" s="61" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="56">
         <v>10</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="C10" s="41" t="s">
-        <v>244</v>
+      <c r="C10" s="1" t="s">
+        <v>367</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="E10" s="41" t="s">
-        <v>218</v>
-      </c>
-      <c r="F10" s="41" t="s">
-        <v>164</v>
+        <v>368</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="F10" s="64" t="s">
+        <v>410</v>
       </c>
       <c r="G10" s="58" t="s">
         <v>9</v>
@@ -3670,70 +3991,72 @@
         <v>9</v>
       </c>
       <c r="L10" s="32" t="str">
-        <f t="shared" si="7"/>
-        <v>Sistemas.Prediais</v>
+        <f t="shared" si="0"/>
+        <v>De Materialidade</v>
       </c>
       <c r="M10" s="32" t="str">
-        <f t="shared" si="8"/>
-        <v>Elementos.Hidráulicos</v>
+        <f t="shared" si="0"/>
+        <v>Materialidades</v>
       </c>
       <c r="N10" s="32" t="str">
-        <f t="shared" si="9"/>
-        <v>Peças Hidráulicas</v>
-      </c>
-      <c r="O10" s="29" t="str">
-        <f t="shared" si="10"/>
-        <v>Válvula</v>
-      </c>
-      <c r="P10" s="51" t="s">
-        <v>164</v>
+        <f t="shared" si="0"/>
+        <v>Materiais</v>
+      </c>
+      <c r="O10" s="32" t="str">
+        <f t="shared" si="0"/>
+        <v>Tubo Multicamada</v>
+      </c>
+      <c r="P10" s="65" t="s">
+        <v>411</v>
       </c>
       <c r="Q10" s="29" t="s">
-        <v>164</v>
+        <v>412</v>
       </c>
       <c r="R10" s="29" t="s">
-        <v>305</v>
+        <v>413</v>
       </c>
       <c r="S10" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="T10" s="29" t="s">
-        <v>151</v>
-      </c>
-      <c r="U10" s="29" t="s">
-        <v>150</v>
+      <c r="T10" s="29" t="str">
+        <f t="shared" si="1"/>
+        <v>De Materialidade</v>
+      </c>
+      <c r="U10" s="29" t="str">
+        <f t="shared" si="1"/>
+        <v>Materialidades</v>
       </c>
       <c r="V10" s="29" t="str">
-        <f t="shared" si="11"/>
-        <v>Peças.Hidráulicas</v>
+        <f t="shared" si="1"/>
+        <v>Materiais</v>
       </c>
       <c r="W10" s="29" t="s">
         <v>152</v>
       </c>
       <c r="X10" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="2"/>
         <v>Key-HIDR-10</v>
       </c>
-      <c r="Y10" s="28" t="s">
-        <v>181</v>
+      <c r="Y10" s="29" t="s">
+        <v>374</v>
       </c>
       <c r="Z10" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AA10" s="28" t="s">
-        <v>183</v>
+      <c r="AA10" s="29" t="s">
+        <v>375</v>
       </c>
       <c r="AB10" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC10" s="29" t="s">
-        <v>154</v>
+        <v>400</v>
       </c>
       <c r="AD10" s="61" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="56">
         <v>11</v>
       </c>
@@ -3743,14 +4066,14 @@
       <c r="C11" s="41" t="s">
         <v>244</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>245</v>
+      <c r="D11" s="41" t="s">
+        <v>246</v>
       </c>
       <c r="E11" s="41" t="s">
-        <v>218</v>
+        <v>254</v>
       </c>
       <c r="F11" s="41" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="G11" s="58" t="s">
         <v>9</v>
@@ -3768,29 +4091,29 @@
         <v>9</v>
       </c>
       <c r="L11" s="32" t="str">
-        <f t="shared" ref="L11:L13" si="14">CONCATENATE("", C11)</f>
+        <f t="shared" ref="L11:L12" si="3">CONCATENATE("", C11)</f>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M11" s="32" t="str">
-        <f t="shared" ref="M11:M13" si="15">CONCATENATE("", D11)</f>
-        <v>Elementos.Hidráulicos</v>
+        <f t="shared" ref="M11:M12" si="4">CONCATENATE("", D11)</f>
+        <v>Sistemas.Hidrossanitários</v>
       </c>
       <c r="N11" s="32" t="str">
-        <f t="shared" ref="N11:N13" si="16">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E11),"."," ")," De "," de "))</f>
-        <v>Peças Hidráulicas</v>
+        <f t="shared" ref="N11:N12" si="5">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E11),"."," ")," De "," de "))</f>
+        <v>Sistemas Sanitários</v>
       </c>
       <c r="O11" s="29" t="str">
-        <f t="shared" si="10"/>
-        <v>Chuveiro</v>
+        <f t="shared" ref="O11:O12" si="6">IF(ISNUMBER(FIND("Ifc",F11)),CONCATENATE("Classe IFC:   ",F11),CONCATENATE("",F11))</f>
+        <v>Sistema.ESG</v>
       </c>
       <c r="P11" s="51" t="s">
-        <v>161</v>
-      </c>
-      <c r="Q11" s="29" t="s">
-        <v>172</v>
+        <v>265</v>
+      </c>
+      <c r="Q11" s="51" t="s">
+        <v>259</v>
       </c>
       <c r="R11" s="29" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="S11" s="29" t="s">
         <v>9</v>
@@ -3802,36 +4125,36 @@
         <v>150</v>
       </c>
       <c r="V11" s="29" t="str">
-        <f t="shared" ref="V11:V13" si="17">SUBSTITUTE(E11, "_", " ")</f>
-        <v>Peças.Hidráulicas</v>
+        <f t="shared" ref="V11:V12" si="7">SUBSTITUTE(E11, "_", " ")</f>
+        <v>Sistemas.Sanitários</v>
       </c>
       <c r="W11" s="29" t="s">
         <v>152</v>
       </c>
       <c r="X11" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="X11:X51" si="8">CONCATENATE("Key-HIDR-",A11)</f>
         <v>Key-HIDR-11</v>
       </c>
       <c r="Y11" s="28" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="Z11" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA11" s="28" t="s">
-        <v>182</v>
+        <v>226</v>
       </c>
       <c r="AB11" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC11" s="29" t="s">
-        <v>154</v>
+        <v>126</v>
       </c>
       <c r="AD11" s="61" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="56">
         <v>12</v>
       </c>
@@ -3841,14 +4164,14 @@
       <c r="C12" s="41" t="s">
         <v>244</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>245</v>
+      <c r="D12" s="41" t="s">
+        <v>246</v>
       </c>
       <c r="E12" s="41" t="s">
-        <v>218</v>
+        <v>254</v>
       </c>
       <c r="F12" s="41" t="s">
-        <v>172</v>
+        <v>256</v>
       </c>
       <c r="G12" s="58" t="s">
         <v>9</v>
@@ -3866,29 +4189,29 @@
         <v>9</v>
       </c>
       <c r="L12" s="32" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="3"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M12" s="32" t="str">
-        <f t="shared" si="15"/>
-        <v>Elementos.Hidráulicos</v>
+        <f t="shared" si="4"/>
+        <v>Sistemas.Hidrossanitários</v>
       </c>
       <c r="N12" s="32" t="str">
-        <f t="shared" si="16"/>
-        <v>Peças Hidráulicas</v>
+        <f t="shared" si="5"/>
+        <v>Sistemas Sanitários</v>
       </c>
       <c r="O12" s="29" t="str">
-        <f t="shared" si="10"/>
-        <v>Ducha</v>
+        <f t="shared" si="6"/>
+        <v>Sistema.VEN</v>
       </c>
       <c r="P12" s="51" t="s">
-        <v>173</v>
-      </c>
-      <c r="Q12" s="29" t="s">
-        <v>173</v>
+        <v>264</v>
+      </c>
+      <c r="Q12" s="51" t="s">
+        <v>258</v>
       </c>
       <c r="R12" s="29" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="S12" s="29" t="s">
         <v>9</v>
@@ -3900,36 +4223,36 @@
         <v>150</v>
       </c>
       <c r="V12" s="29" t="str">
-        <f t="shared" si="17"/>
-        <v>Peças.Hidráulicas</v>
+        <f t="shared" si="7"/>
+        <v>Sistemas.Sanitários</v>
       </c>
       <c r="W12" s="29" t="s">
         <v>152</v>
       </c>
       <c r="X12" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="X12" si="9">CONCATENATE("Key-HIDR-",A12)</f>
         <v>Key-HIDR-12</v>
       </c>
       <c r="Y12" s="28" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="Z12" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA12" s="28" t="s">
-        <v>182</v>
+        <v>257</v>
       </c>
       <c r="AB12" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC12" s="29" t="s">
-        <v>154</v>
+        <v>126</v>
       </c>
       <c r="AD12" s="61" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="56">
         <v>13</v>
       </c>
@@ -3939,14 +4262,14 @@
       <c r="C13" s="41" t="s">
         <v>244</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>245</v>
+      <c r="D13" s="41" t="s">
+        <v>246</v>
       </c>
       <c r="E13" s="41" t="s">
-        <v>218</v>
+        <v>255</v>
       </c>
       <c r="F13" s="41" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="G13" s="58" t="s">
         <v>9</v>
@@ -3964,29 +4287,29 @@
         <v>9</v>
       </c>
       <c r="L13" s="32" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="L13:L23" si="10">CONCATENATE("", C13)</f>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M13" s="32" t="str">
-        <f t="shared" si="15"/>
-        <v>Elementos.Hidráulicos</v>
+        <f t="shared" ref="M13:M23" si="11">CONCATENATE("", D13)</f>
+        <v>Sistemas.Hidrossanitários</v>
       </c>
       <c r="N13" s="32" t="str">
-        <f t="shared" si="16"/>
-        <v>Peças Hidráulicas</v>
+        <f t="shared" ref="N13:N23" si="12">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E13),"."," ")," De "," de "))</f>
+        <v>Sistemas Hidráulicos</v>
       </c>
       <c r="O13" s="29" t="str">
-        <f t="shared" si="10"/>
-        <v>Medidor.de.Água</v>
+        <f t="shared" ref="O13:O51" si="13">IF(ISNUMBER(FIND("Ifc",F13)),CONCATENATE("Classe IFC:   ",F13),CONCATENATE("",F13))</f>
+        <v>Sistema.AFR</v>
       </c>
       <c r="P13" s="51" t="s">
-        <v>231</v>
+        <v>266</v>
       </c>
       <c r="Q13" s="51" t="s">
-        <v>232</v>
+        <v>260</v>
       </c>
       <c r="R13" s="29" t="s">
-        <v>233</v>
+        <v>299</v>
       </c>
       <c r="S13" s="29" t="s">
         <v>9</v>
@@ -3998,24 +4321,24 @@
         <v>150</v>
       </c>
       <c r="V13" s="29" t="str">
-        <f t="shared" si="17"/>
-        <v>Peças.Hidráulicas</v>
+        <f t="shared" ref="V13:V23" si="14">SUBSTITUTE(E13, "_", " ")</f>
+        <v>Sistemas.Hidráulicos</v>
       </c>
       <c r="W13" s="29" t="s">
         <v>152</v>
       </c>
       <c r="X13" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>Key-HIDR-13</v>
       </c>
       <c r="Y13" s="28" t="s">
-        <v>240</v>
+        <v>188</v>
       </c>
       <c r="Z13" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA13" s="28" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="AB13" s="61" t="s">
         <v>9</v>
@@ -4027,7 +4350,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="56">
         <v>14</v>
       </c>
@@ -4037,14 +4360,14 @@
       <c r="C14" s="41" t="s">
         <v>244</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>245</v>
+      <c r="D14" s="41" t="s">
+        <v>246</v>
       </c>
       <c r="E14" s="41" t="s">
-        <v>218</v>
+        <v>255</v>
       </c>
       <c r="F14" s="41" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="G14" s="58" t="s">
         <v>9</v>
@@ -4062,29 +4385,29 @@
         <v>9</v>
       </c>
       <c r="L14" s="32" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M14" s="32" t="str">
-        <f t="shared" si="8"/>
-        <v>Elementos.Hidráulicos</v>
+        <f t="shared" si="11"/>
+        <v>Sistemas.Hidrossanitários</v>
       </c>
       <c r="N14" s="32" t="str">
-        <f t="shared" si="9"/>
-        <v>Peças Hidráulicas</v>
+        <f t="shared" si="12"/>
+        <v>Sistemas Hidráulicos</v>
       </c>
       <c r="O14" s="29" t="str">
-        <f t="shared" si="10"/>
-        <v>Acessório.Hidraúlico</v>
+        <f t="shared" si="13"/>
+        <v>Sistema.AQT</v>
       </c>
       <c r="P14" s="51" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q14" s="29" t="s">
-        <v>284</v>
+        <v>267</v>
+      </c>
+      <c r="Q14" s="51" t="s">
+        <v>261</v>
       </c>
       <c r="R14" s="29" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="S14" s="29" t="s">
         <v>9</v>
@@ -4096,24 +4419,24 @@
         <v>150</v>
       </c>
       <c r="V14" s="29" t="str">
-        <f t="shared" si="11"/>
-        <v>Peças.Hidráulicas</v>
+        <f t="shared" si="14"/>
+        <v>Sistemas.Hidráulicos</v>
       </c>
       <c r="W14" s="29" t="s">
         <v>152</v>
       </c>
       <c r="X14" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>Key-HIDR-14</v>
       </c>
       <c r="Y14" s="28" t="s">
-        <v>235</v>
+        <v>188</v>
       </c>
       <c r="Z14" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA14" s="28" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="AB14" s="61" t="s">
         <v>9</v>
@@ -4125,7 +4448,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="56">
         <v>15</v>
       </c>
@@ -4135,14 +4458,14 @@
       <c r="C15" s="41" t="s">
         <v>244</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>245</v>
+      <c r="D15" s="41" t="s">
+        <v>246</v>
       </c>
       <c r="E15" s="41" t="s">
-        <v>212</v>
+        <v>268</v>
       </c>
       <c r="F15" s="41" t="s">
-        <v>132</v>
+        <v>262</v>
       </c>
       <c r="G15" s="58" t="s">
         <v>9</v>
@@ -4160,29 +4483,29 @@
         <v>9</v>
       </c>
       <c r="L15" s="32" t="str">
-        <f t="shared" ref="L15:L34" si="18">CONCATENATE("", C15)</f>
+        <f t="shared" si="10"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M15" s="32" t="str">
-        <f t="shared" ref="M15:M34" si="19">CONCATENATE("", D15)</f>
-        <v>Elementos.Hidráulicos</v>
+        <f t="shared" si="11"/>
+        <v>Sistemas.Hidrossanitários</v>
       </c>
       <c r="N15" s="32" t="str">
-        <f t="shared" ref="N15:N34" si="20">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E15),"."," ")," De "," de "))</f>
-        <v>Tubulação Agua Fria</v>
+        <f t="shared" si="12"/>
+        <v>Sistemas Pluviais</v>
       </c>
       <c r="O15" s="29" t="str">
-        <f t="shared" si="10"/>
-        <v>Cisterna.Superior</v>
+        <f t="shared" ref="O15" si="15">IF(ISNUMBER(FIND("Ifc",F15)),CONCATENATE("Classe IFC:   ",F15),CONCATENATE("",F15))</f>
+        <v>Sistema.PLU</v>
       </c>
       <c r="P15" s="51" t="s">
-        <v>138</v>
-      </c>
-      <c r="Q15" s="29" t="s">
-        <v>138</v>
+        <v>263</v>
+      </c>
+      <c r="Q15" s="51" t="s">
+        <v>263</v>
       </c>
       <c r="R15" s="29" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="S15" s="29" t="s">
         <v>9</v>
@@ -4194,36 +4517,36 @@
         <v>150</v>
       </c>
       <c r="V15" s="29" t="str">
-        <f t="shared" ref="V15:V34" si="21">SUBSTITUTE(E15, "_", " ")</f>
-        <v>Tubulação.Agua.Fria</v>
+        <f t="shared" si="14"/>
+        <v>Sistemas.Pluviais</v>
       </c>
       <c r="W15" s="29" t="s">
         <v>152</v>
       </c>
       <c r="X15" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="X15" si="16">CONCATENATE("Key-HIDR-",A15)</f>
         <v>Key-HIDR-15</v>
       </c>
       <c r="Y15" s="28" t="s">
-        <v>247</v>
+        <v>188</v>
       </c>
       <c r="Z15" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA15" s="28" t="s">
-        <v>184</v>
+        <v>257</v>
       </c>
       <c r="AB15" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC15" s="29" t="s">
-        <v>154</v>
+        <v>126</v>
       </c>
       <c r="AD15" s="61" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="56">
         <v>16</v>
       </c>
@@ -4237,10 +4560,10 @@
         <v>245</v>
       </c>
       <c r="E16" s="41" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F16" s="41" t="s">
-        <v>228</v>
+        <v>162</v>
       </c>
       <c r="G16" s="58" t="s">
         <v>9</v>
@@ -4258,29 +4581,29 @@
         <v>9</v>
       </c>
       <c r="L16" s="32" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="10"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M16" s="32" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="11"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N16" s="32" t="str">
-        <f t="shared" si="20"/>
-        <v>Tubulação Agua Fria</v>
+        <f t="shared" si="12"/>
+        <v>Peças Hidráulicas</v>
       </c>
       <c r="O16" s="29" t="str">
-        <f t="shared" si="10"/>
-        <v>Cisterna.Intermediária</v>
+        <f t="shared" si="13"/>
+        <v>Torneira</v>
       </c>
       <c r="P16" s="51" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="Q16" s="29" t="s">
-        <v>285</v>
+        <v>174</v>
       </c>
       <c r="R16" s="29" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="S16" s="29" t="s">
         <v>9</v>
@@ -4292,24 +4615,24 @@
         <v>150</v>
       </c>
       <c r="V16" s="29" t="str">
-        <f t="shared" si="21"/>
-        <v>Tubulação.Agua.Fria</v>
+        <f t="shared" si="14"/>
+        <v>Peças.Hidráulicas</v>
       </c>
       <c r="W16" s="29" t="s">
         <v>152</v>
       </c>
       <c r="X16" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>Key-HIDR-16</v>
       </c>
       <c r="Y16" s="28" t="s">
-        <v>247</v>
+        <v>181</v>
       </c>
       <c r="Z16" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA16" s="28" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AB16" s="61" t="s">
         <v>9</v>
@@ -4321,7 +4644,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="56">
         <v>17</v>
       </c>
@@ -4335,10 +4658,10 @@
         <v>245</v>
       </c>
       <c r="E17" s="41" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F17" s="41" t="s">
-        <v>133</v>
+        <v>163</v>
       </c>
       <c r="G17" s="58" t="s">
         <v>9</v>
@@ -4356,29 +4679,29 @@
         <v>9</v>
       </c>
       <c r="L17" s="32" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="10"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M17" s="32" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="11"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N17" s="32" t="str">
-        <f t="shared" si="20"/>
-        <v>Tubulação Agua Fria</v>
+        <f t="shared" si="12"/>
+        <v>Peças Hidráulicas</v>
       </c>
       <c r="O17" s="29" t="str">
-        <f t="shared" si="10"/>
-        <v>Cisterna.Inferior</v>
+        <f t="shared" si="13"/>
+        <v>Misturador</v>
       </c>
       <c r="P17" s="51" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="Q17" s="29" t="s">
-        <v>139</v>
+        <v>283</v>
       </c>
       <c r="R17" s="29" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="S17" s="29" t="s">
         <v>9</v>
@@ -4390,24 +4713,24 @@
         <v>150</v>
       </c>
       <c r="V17" s="29" t="str">
-        <f t="shared" si="21"/>
-        <v>Tubulação.Agua.Fria</v>
+        <f t="shared" si="14"/>
+        <v>Peças.Hidráulicas</v>
       </c>
       <c r="W17" s="29" t="s">
         <v>152</v>
       </c>
       <c r="X17" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>Key-HIDR-17</v>
       </c>
       <c r="Y17" s="28" t="s">
-        <v>247</v>
+        <v>181</v>
       </c>
       <c r="Z17" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA17" s="28" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AB17" s="61" t="s">
         <v>9</v>
@@ -4419,7 +4742,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="56">
         <v>18</v>
       </c>
@@ -4433,10 +4756,10 @@
         <v>245</v>
       </c>
       <c r="E18" s="41" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F18" s="41" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="G18" s="58" t="s">
         <v>9</v>
@@ -4454,29 +4777,29 @@
         <v>9</v>
       </c>
       <c r="L18" s="32" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="10"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M18" s="32" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="11"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N18" s="32" t="str">
-        <f t="shared" si="20"/>
-        <v>Tubulação Agua Fria</v>
+        <f t="shared" si="12"/>
+        <v>Peças Hidráulicas</v>
       </c>
       <c r="O18" s="29" t="str">
-        <f t="shared" si="10"/>
-        <v>Tubulação.AF</v>
+        <f t="shared" si="13"/>
+        <v>Registro</v>
       </c>
       <c r="P18" s="51" t="s">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="Q18" s="29" t="s">
-        <v>286</v>
+        <v>165</v>
       </c>
       <c r="R18" s="29" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="S18" s="29" t="s">
         <v>9</v>
@@ -4488,24 +4811,24 @@
         <v>150</v>
       </c>
       <c r="V18" s="29" t="str">
-        <f t="shared" si="21"/>
-        <v>Tubulação.Agua.Fria</v>
+        <f t="shared" si="14"/>
+        <v>Peças.Hidráulicas</v>
       </c>
       <c r="W18" s="29" t="s">
         <v>152</v>
       </c>
       <c r="X18" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>Key-HIDR-18</v>
       </c>
       <c r="Y18" s="28" t="s">
-        <v>247</v>
+        <v>181</v>
       </c>
       <c r="Z18" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA18" s="28" t="s">
-        <v>248</v>
+        <v>183</v>
       </c>
       <c r="AB18" s="61" t="s">
         <v>9</v>
@@ -4517,7 +4840,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="56">
         <v>19</v>
       </c>
@@ -4531,10 +4854,10 @@
         <v>245</v>
       </c>
       <c r="E19" s="41" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="F19" s="41" t="s">
-        <v>140</v>
+        <v>164</v>
       </c>
       <c r="G19" s="58" t="s">
         <v>9</v>
@@ -4552,29 +4875,29 @@
         <v>9</v>
       </c>
       <c r="L19" s="32" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="10"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M19" s="32" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="11"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N19" s="32" t="str">
-        <f t="shared" si="20"/>
-        <v>Tubulação Agua Quente</v>
+        <f t="shared" si="12"/>
+        <v>Peças Hidráulicas</v>
       </c>
       <c r="O19" s="29" t="str">
-        <f t="shared" si="10"/>
-        <v>Aquecedor.de.Agua</v>
+        <f t="shared" si="13"/>
+        <v>Válvula</v>
       </c>
       <c r="P19" s="51" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="Q19" s="29" t="s">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="R19" s="29" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="S19" s="29" t="s">
         <v>9</v>
@@ -4586,14 +4909,14 @@
         <v>150</v>
       </c>
       <c r="V19" s="29" t="str">
-        <f t="shared" si="21"/>
-        <v>Tubulação.Agua.Quente</v>
+        <f t="shared" si="14"/>
+        <v>Peças.Hidráulicas</v>
       </c>
       <c r="W19" s="29" t="s">
         <v>152</v>
       </c>
       <c r="X19" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>Key-HIDR-19</v>
       </c>
       <c r="Y19" s="28" t="s">
@@ -4603,7 +4926,7 @@
         <v>9</v>
       </c>
       <c r="AA19" s="28" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="AB19" s="61" t="s">
         <v>9</v>
@@ -4615,7 +4938,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="56">
         <v>20</v>
       </c>
@@ -4629,10 +4952,10 @@
         <v>245</v>
       </c>
       <c r="E20" s="41" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="F20" s="41" t="s">
-        <v>134</v>
+        <v>161</v>
       </c>
       <c r="G20" s="58" t="s">
         <v>9</v>
@@ -4650,29 +4973,29 @@
         <v>9</v>
       </c>
       <c r="L20" s="32" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" ref="L20:L22" si="17">CONCATENATE("", C20)</f>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M20" s="32" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="M20:M22" si="18">CONCATENATE("", D20)</f>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N20" s="32" t="str">
-        <f t="shared" si="20"/>
-        <v>Tubulação Agua Quente</v>
+        <f t="shared" ref="N20:N22" si="19">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E20),"."," ")," De "," de "))</f>
+        <v>Peças Hidráulicas</v>
       </c>
       <c r="O20" s="29" t="str">
-        <f t="shared" si="10"/>
-        <v>Boiler</v>
+        <f t="shared" si="13"/>
+        <v>Chuveiro</v>
       </c>
       <c r="P20" s="51" t="s">
-        <v>134</v>
+        <v>161</v>
       </c>
       <c r="Q20" s="29" t="s">
-        <v>134</v>
+        <v>172</v>
       </c>
       <c r="R20" s="29" t="s">
-        <v>134</v>
+        <v>306</v>
       </c>
       <c r="S20" s="29" t="s">
         <v>9</v>
@@ -4684,14 +5007,14 @@
         <v>150</v>
       </c>
       <c r="V20" s="29" t="str">
-        <f t="shared" si="21"/>
-        <v>Tubulação.Agua.Quente</v>
+        <f t="shared" ref="V20:V22" si="20">SUBSTITUTE(E20, "_", " ")</f>
+        <v>Peças.Hidráulicas</v>
       </c>
       <c r="W20" s="29" t="s">
         <v>152</v>
       </c>
       <c r="X20" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>Key-HIDR-20</v>
       </c>
       <c r="Y20" s="28" t="s">
@@ -4701,7 +5024,7 @@
         <v>9</v>
       </c>
       <c r="AA20" s="28" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="AB20" s="61" t="s">
         <v>9</v>
@@ -4713,7 +5036,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="56">
         <v>21</v>
       </c>
@@ -4727,10 +5050,10 @@
         <v>245</v>
       </c>
       <c r="E21" s="41" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="F21" s="41" t="s">
-        <v>135</v>
+        <v>172</v>
       </c>
       <c r="G21" s="58" t="s">
         <v>9</v>
@@ -4748,29 +5071,29 @@
         <v>9</v>
       </c>
       <c r="L21" s="32" t="str">
+        <f t="shared" si="17"/>
+        <v>Sistemas.Prediais</v>
+      </c>
+      <c r="M21" s="32" t="str">
         <f t="shared" si="18"/>
-        <v>Sistemas.Prediais</v>
-      </c>
-      <c r="M21" s="32" t="str">
+        <v>Elementos.Hidráulicos</v>
+      </c>
+      <c r="N21" s="32" t="str">
         <f t="shared" si="19"/>
-        <v>Elementos.Hidráulicos</v>
-      </c>
-      <c r="N21" s="32" t="str">
-        <f t="shared" si="20"/>
-        <v>Tubulação Agua Quente</v>
+        <v>Peças Hidráulicas</v>
       </c>
       <c r="O21" s="29" t="str">
-        <f t="shared" si="10"/>
-        <v>Caldeira</v>
+        <f t="shared" si="13"/>
+        <v>Ducha</v>
       </c>
       <c r="P21" s="51" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="Q21" s="29" t="s">
-        <v>287</v>
+        <v>173</v>
       </c>
       <c r="R21" s="29" t="s">
-        <v>134</v>
+        <v>307</v>
       </c>
       <c r="S21" s="29" t="s">
         <v>9</v>
@@ -4782,14 +5105,14 @@
         <v>150</v>
       </c>
       <c r="V21" s="29" t="str">
-        <f t="shared" si="21"/>
-        <v>Tubulação.Agua.Quente</v>
+        <f t="shared" si="20"/>
+        <v>Peças.Hidráulicas</v>
       </c>
       <c r="W21" s="29" t="s">
         <v>152</v>
       </c>
       <c r="X21" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>Key-HIDR-21</v>
       </c>
       <c r="Y21" s="28" t="s">
@@ -4799,7 +5122,7 @@
         <v>9</v>
       </c>
       <c r="AA21" s="28" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="AB21" s="61" t="s">
         <v>9</v>
@@ -4811,7 +5134,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="56">
         <v>22</v>
       </c>
@@ -4825,10 +5148,10 @@
         <v>245</v>
       </c>
       <c r="E22" s="41" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="F22" s="41" t="s">
-        <v>136</v>
+        <v>230</v>
       </c>
       <c r="G22" s="58" t="s">
         <v>9</v>
@@ -4846,29 +5169,29 @@
         <v>9</v>
       </c>
       <c r="L22" s="32" t="str">
+        <f t="shared" si="17"/>
+        <v>Sistemas.Prediais</v>
+      </c>
+      <c r="M22" s="32" t="str">
         <f t="shared" si="18"/>
-        <v>Sistemas.Prediais</v>
-      </c>
-      <c r="M22" s="32" t="str">
+        <v>Elementos.Hidráulicos</v>
+      </c>
+      <c r="N22" s="32" t="str">
         <f t="shared" si="19"/>
-        <v>Elementos.Hidráulicos</v>
-      </c>
-      <c r="N22" s="32" t="str">
-        <f t="shared" si="20"/>
-        <v>Tubulação Agua Quente</v>
+        <v>Peças Hidráulicas</v>
       </c>
       <c r="O22" s="29" t="str">
-        <f t="shared" si="10"/>
-        <v>Tubulação.AQ</v>
+        <f t="shared" si="13"/>
+        <v>Medidor.de.Água</v>
       </c>
       <c r="P22" s="51" t="s">
-        <v>143</v>
-      </c>
-      <c r="Q22" s="29" t="s">
-        <v>288</v>
+        <v>231</v>
+      </c>
+      <c r="Q22" s="51" t="s">
+        <v>232</v>
       </c>
       <c r="R22" s="29" t="s">
-        <v>314</v>
+        <v>233</v>
       </c>
       <c r="S22" s="29" t="s">
         <v>9</v>
@@ -4880,24 +5203,24 @@
         <v>150</v>
       </c>
       <c r="V22" s="29" t="str">
-        <f t="shared" si="21"/>
-        <v>Tubulação.Agua.Quente</v>
+        <f t="shared" si="20"/>
+        <v>Peças.Hidráulicas</v>
       </c>
       <c r="W22" s="29" t="s">
         <v>152</v>
       </c>
       <c r="X22" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>Key-HIDR-22</v>
       </c>
       <c r="Y22" s="28" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="Z22" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA22" s="28" t="s">
-        <v>248</v>
+        <v>229</v>
       </c>
       <c r="AB22" s="61" t="s">
         <v>9</v>
@@ -4909,7 +5232,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="56">
         <v>23</v>
       </c>
@@ -4923,10 +5246,10 @@
         <v>245</v>
       </c>
       <c r="E23" s="41" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="F23" s="41" t="s">
-        <v>131</v>
+        <v>211</v>
       </c>
       <c r="G23" s="58" t="s">
         <v>9</v>
@@ -4944,29 +5267,29 @@
         <v>9</v>
       </c>
       <c r="L23" s="32" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="10"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M23" s="32" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="11"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N23" s="32" t="str">
-        <f t="shared" si="20"/>
-        <v>Tubulação Agua Quente</v>
+        <f t="shared" si="12"/>
+        <v>Peças Hidráulicas</v>
       </c>
       <c r="O23" s="29" t="str">
-        <f t="shared" si="10"/>
-        <v>Tubulação.Reuso</v>
+        <f t="shared" si="13"/>
+        <v>Acessório.Hidraúlico</v>
       </c>
       <c r="P23" s="51" t="s">
-        <v>144</v>
-      </c>
-      <c r="Q23" s="51" t="s">
-        <v>145</v>
+        <v>222</v>
+      </c>
+      <c r="Q23" s="29" t="s">
+        <v>284</v>
       </c>
       <c r="R23" s="29" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="S23" s="29" t="s">
         <v>9</v>
@@ -4978,24 +5301,24 @@
         <v>150</v>
       </c>
       <c r="V23" s="29" t="str">
-        <f t="shared" si="21"/>
-        <v>Tubulação.Agua.Quente</v>
+        <f t="shared" si="14"/>
+        <v>Peças.Hidráulicas</v>
       </c>
       <c r="W23" s="29" t="s">
         <v>152</v>
       </c>
       <c r="X23" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>Key-HIDR-23</v>
       </c>
       <c r="Y23" s="28" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="Z23" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA23" s="28" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="AB23" s="61" t="s">
         <v>9</v>
@@ -5007,7 +5330,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="56">
         <v>24</v>
       </c>
@@ -5021,10 +5344,10 @@
         <v>245</v>
       </c>
       <c r="E24" s="41" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F24" s="41" t="s">
-        <v>168</v>
+        <v>132</v>
       </c>
       <c r="G24" s="58" t="s">
         <v>9</v>
@@ -5042,29 +5365,29 @@
         <v>9</v>
       </c>
       <c r="L24" s="32" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" ref="L24:L43" si="21">CONCATENATE("", C24)</f>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M24" s="32" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="M24:M43" si="22">CONCATENATE("", D24)</f>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N24" s="32" t="str">
-        <f t="shared" si="20"/>
-        <v>Peças Sanitárias</v>
+        <f t="shared" ref="N24:N43" si="23">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E24),"."," ")," De "," de "))</f>
+        <v>Tubulação Agua Fria</v>
       </c>
       <c r="O24" s="29" t="str">
-        <f t="shared" si="10"/>
-        <v>Vaso.Sanitário</v>
+        <f t="shared" si="13"/>
+        <v>Cisterna.Superior</v>
       </c>
       <c r="P24" s="51" t="s">
-        <v>175</v>
+        <v>138</v>
       </c>
       <c r="Q24" s="29" t="s">
-        <v>178</v>
+        <v>138</v>
       </c>
       <c r="R24" s="29" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="S24" s="29" t="s">
         <v>9</v>
@@ -5076,24 +5399,24 @@
         <v>150</v>
       </c>
       <c r="V24" s="29" t="str">
-        <f t="shared" si="21"/>
-        <v>Peças.Sanitárias</v>
+        <f t="shared" ref="V24:V43" si="24">SUBSTITUTE(E24, "_", " ")</f>
+        <v>Tubulação.Agua.Fria</v>
       </c>
       <c r="W24" s="29" t="s">
         <v>152</v>
       </c>
       <c r="X24" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>Key-HIDR-24</v>
       </c>
       <c r="Y24" s="28" t="s">
-        <v>181</v>
+        <v>247</v>
       </c>
       <c r="Z24" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA24" s="28" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="AB24" s="61" t="s">
         <v>9</v>
@@ -5105,7 +5428,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="56">
         <v>25</v>
       </c>
@@ -5119,10 +5442,10 @@
         <v>245</v>
       </c>
       <c r="E25" s="41" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F25" s="41" t="s">
-        <v>167</v>
+        <v>228</v>
       </c>
       <c r="G25" s="58" t="s">
         <v>9</v>
@@ -5140,29 +5463,29 @@
         <v>9</v>
       </c>
       <c r="L25" s="32" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M25" s="32" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N25" s="32" t="str">
-        <f t="shared" si="20"/>
-        <v>Peças Sanitárias</v>
+        <f t="shared" si="23"/>
+        <v>Tubulação Agua Fria</v>
       </c>
       <c r="O25" s="29" t="str">
-        <f t="shared" si="10"/>
-        <v>Bidet</v>
+        <f t="shared" si="13"/>
+        <v>Cisterna.Intermediária</v>
       </c>
       <c r="P25" s="51" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="Q25" s="29" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="R25" s="29" t="s">
-        <v>167</v>
+        <v>310</v>
       </c>
       <c r="S25" s="29" t="s">
         <v>9</v>
@@ -5174,24 +5497,24 @@
         <v>150</v>
       </c>
       <c r="V25" s="29" t="str">
-        <f t="shared" si="21"/>
-        <v>Peças.Sanitárias</v>
+        <f t="shared" si="24"/>
+        <v>Tubulação.Agua.Fria</v>
       </c>
       <c r="W25" s="29" t="s">
         <v>152</v>
       </c>
       <c r="X25" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>Key-HIDR-25</v>
       </c>
       <c r="Y25" s="28" t="s">
-        <v>181</v>
+        <v>247</v>
       </c>
       <c r="Z25" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA25" s="28" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="AB25" s="61" t="s">
         <v>9</v>
@@ -5203,7 +5526,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="56">
         <v>26</v>
       </c>
@@ -5217,10 +5540,10 @@
         <v>245</v>
       </c>
       <c r="E26" s="41" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F26" s="41" t="s">
-        <v>170</v>
+        <v>133</v>
       </c>
       <c r="G26" s="58" t="s">
         <v>9</v>
@@ -5238,29 +5561,29 @@
         <v>9</v>
       </c>
       <c r="L26" s="32" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M26" s="32" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N26" s="32" t="str">
-        <f t="shared" si="20"/>
-        <v>Peças Sanitárias</v>
+        <f t="shared" si="23"/>
+        <v>Tubulação Agua Fria</v>
       </c>
       <c r="O26" s="29" t="str">
-        <f t="shared" si="10"/>
-        <v>Pia.Sanitária</v>
+        <f t="shared" si="13"/>
+        <v>Cisterna.Inferior</v>
       </c>
       <c r="P26" s="51" t="s">
-        <v>176</v>
+        <v>139</v>
       </c>
       <c r="Q26" s="29" t="s">
-        <v>180</v>
+        <v>139</v>
       </c>
       <c r="R26" s="29" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="S26" s="29" t="s">
         <v>9</v>
@@ -5272,24 +5595,24 @@
         <v>150</v>
       </c>
       <c r="V26" s="29" t="str">
-        <f t="shared" si="21"/>
-        <v>Peças.Sanitárias</v>
+        <f t="shared" si="24"/>
+        <v>Tubulação.Agua.Fria</v>
       </c>
       <c r="W26" s="29" t="s">
         <v>152</v>
       </c>
       <c r="X26" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>Key-HIDR-26</v>
       </c>
       <c r="Y26" s="28" t="s">
-        <v>181</v>
+        <v>247</v>
       </c>
       <c r="Z26" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA26" s="28" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="AB26" s="61" t="s">
         <v>9</v>
@@ -5301,7 +5624,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="56">
         <v>27</v>
       </c>
@@ -5315,10 +5638,10 @@
         <v>245</v>
       </c>
       <c r="E27" s="41" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F27" s="41" t="s">
-        <v>166</v>
+        <v>137</v>
       </c>
       <c r="G27" s="58" t="s">
         <v>9</v>
@@ -5336,29 +5659,29 @@
         <v>9</v>
       </c>
       <c r="L27" s="32" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M27" s="32" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N27" s="32" t="str">
-        <f t="shared" si="20"/>
-        <v>Peças Sanitárias</v>
+        <f t="shared" si="23"/>
+        <v>Tubulação Agua Fria</v>
       </c>
       <c r="O27" s="29" t="str">
-        <f t="shared" si="10"/>
-        <v>Lavatório</v>
+        <f t="shared" si="13"/>
+        <v>Tubulação.AF</v>
       </c>
       <c r="P27" s="51" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="Q27" s="29" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="R27" s="29" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="S27" s="29" t="s">
         <v>9</v>
@@ -5370,24 +5693,24 @@
         <v>150</v>
       </c>
       <c r="V27" s="29" t="str">
-        <f t="shared" si="21"/>
-        <v>Peças.Sanitárias</v>
+        <f t="shared" si="24"/>
+        <v>Tubulação.Agua.Fria</v>
       </c>
       <c r="W27" s="29" t="s">
         <v>152</v>
       </c>
       <c r="X27" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>Key-HIDR-27</v>
       </c>
       <c r="Y27" s="28" t="s">
-        <v>181</v>
+        <v>247</v>
       </c>
       <c r="Z27" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA27" s="28" t="s">
-        <v>182</v>
+        <v>248</v>
       </c>
       <c r="AB27" s="61" t="s">
         <v>9</v>
@@ -5399,7 +5722,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="56">
         <v>28</v>
       </c>
@@ -5413,10 +5736,10 @@
         <v>245</v>
       </c>
       <c r="E28" s="41" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F28" s="41" t="s">
-        <v>169</v>
+        <v>140</v>
       </c>
       <c r="G28" s="58" t="s">
         <v>9</v>
@@ -5434,29 +5757,29 @@
         <v>9</v>
       </c>
       <c r="L28" s="32" t="str">
-        <f t="shared" ref="L28" si="22">CONCATENATE("", C28)</f>
+        <f t="shared" si="21"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M28" s="32" t="str">
-        <f t="shared" ref="M28" si="23">CONCATENATE("", D28)</f>
+        <f t="shared" si="22"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N28" s="32" t="str">
-        <f t="shared" ref="N28" si="24">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E28),"."," ")," De "," de "))</f>
-        <v>Peças Sanitárias</v>
+        <f t="shared" si="23"/>
+        <v>Tubulação Agua Quente</v>
       </c>
       <c r="O28" s="29" t="str">
-        <f t="shared" si="10"/>
-        <v>Cuba.Sanitária</v>
+        <f t="shared" si="13"/>
+        <v>Aquecedor.de.Agua</v>
       </c>
       <c r="P28" s="51" t="s">
-        <v>177</v>
+        <v>141</v>
       </c>
       <c r="Q28" s="29" t="s">
-        <v>179</v>
+        <v>146</v>
       </c>
       <c r="R28" s="29" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="S28" s="29" t="s">
         <v>9</v>
@@ -5468,14 +5791,14 @@
         <v>150</v>
       </c>
       <c r="V28" s="29" t="str">
-        <f t="shared" ref="V28" si="25">SUBSTITUTE(E28, "_", " ")</f>
-        <v>Peças.Sanitárias</v>
+        <f t="shared" si="24"/>
+        <v>Tubulação.Agua.Quente</v>
       </c>
       <c r="W28" s="29" t="s">
         <v>152</v>
       </c>
       <c r="X28" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>Key-HIDR-28</v>
       </c>
       <c r="Y28" s="28" t="s">
@@ -5485,7 +5808,7 @@
         <v>9</v>
       </c>
       <c r="AA28" s="28" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="AB28" s="61" t="s">
         <v>9</v>
@@ -5497,7 +5820,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="56">
         <v>29</v>
       </c>
@@ -5511,10 +5834,10 @@
         <v>245</v>
       </c>
       <c r="E29" s="41" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F29" s="41" t="s">
-        <v>171</v>
+        <v>134</v>
       </c>
       <c r="G29" s="58" t="s">
         <v>9</v>
@@ -5532,29 +5855,29 @@
         <v>9</v>
       </c>
       <c r="L29" s="32" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M29" s="32" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N29" s="32" t="str">
-        <f t="shared" si="20"/>
-        <v>Peças Sanitárias</v>
+        <f t="shared" si="23"/>
+        <v>Tubulação Agua Quente</v>
       </c>
       <c r="O29" s="29" t="str">
-        <f t="shared" si="10"/>
-        <v>Banheira</v>
+        <f t="shared" si="13"/>
+        <v>Boiler</v>
       </c>
       <c r="P29" s="51" t="s">
-        <v>171</v>
+        <v>134</v>
       </c>
       <c r="Q29" s="29" t="s">
-        <v>291</v>
+        <v>134</v>
       </c>
       <c r="R29" s="29" t="s">
-        <v>320</v>
+        <v>134</v>
       </c>
       <c r="S29" s="29" t="s">
         <v>9</v>
@@ -5566,14 +5889,14 @@
         <v>150</v>
       </c>
       <c r="V29" s="29" t="str">
-        <f t="shared" si="21"/>
-        <v>Peças.Sanitárias</v>
+        <f t="shared" si="24"/>
+        <v>Tubulação.Agua.Quente</v>
       </c>
       <c r="W29" s="29" t="s">
         <v>152</v>
       </c>
       <c r="X29" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>Key-HIDR-29</v>
       </c>
       <c r="Y29" s="28" t="s">
@@ -5583,7 +5906,7 @@
         <v>9</v>
       </c>
       <c r="AA29" s="28" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="AB29" s="61" t="s">
         <v>9</v>
@@ -5595,7 +5918,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="56">
         <v>30</v>
       </c>
@@ -5609,10 +5932,10 @@
         <v>245</v>
       </c>
       <c r="E30" s="41" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F30" s="41" t="s">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="G30" s="58" t="s">
         <v>9</v>
@@ -5630,29 +5953,29 @@
         <v>9</v>
       </c>
       <c r="L30" s="32" t="str">
-        <f t="shared" ref="L30" si="26">CONCATENATE("", C30)</f>
+        <f t="shared" si="21"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M30" s="32" t="str">
-        <f t="shared" ref="M30" si="27">CONCATENATE("", D30)</f>
+        <f t="shared" si="22"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N30" s="32" t="str">
-        <f t="shared" ref="N30" si="28">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E30),"."," ")," De "," de "))</f>
-        <v>Esgoto Coletores</v>
+        <f t="shared" si="23"/>
+        <v>Tubulação Agua Quente</v>
       </c>
       <c r="O30" s="29" t="str">
-        <f t="shared" si="10"/>
-        <v>Ventilação.Esgoto</v>
+        <f t="shared" si="13"/>
+        <v>Caldeira</v>
       </c>
       <c r="P30" s="51" t="s">
-        <v>148</v>
-      </c>
-      <c r="Q30" s="51" t="s">
-        <v>149</v>
+        <v>135</v>
+      </c>
+      <c r="Q30" s="29" t="s">
+        <v>287</v>
       </c>
       <c r="R30" s="29" t="s">
-        <v>321</v>
+        <v>134</v>
       </c>
       <c r="S30" s="29" t="s">
         <v>9</v>
@@ -5664,36 +5987,36 @@
         <v>150</v>
       </c>
       <c r="V30" s="29" t="str">
-        <f t="shared" ref="V30" si="29">SUBSTITUTE(E30, "_", " ")</f>
-        <v>Esgoto.Coletores</v>
+        <f t="shared" si="24"/>
+        <v>Tubulação.Agua.Quente</v>
       </c>
       <c r="W30" s="29" t="s">
         <v>152</v>
       </c>
       <c r="X30" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>Key-HIDR-30</v>
       </c>
       <c r="Y30" s="28" t="s">
-        <v>247</v>
+        <v>181</v>
       </c>
       <c r="Z30" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA30" s="28" t="s">
-        <v>248</v>
+        <v>186</v>
       </c>
       <c r="AB30" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC30" s="29" t="s">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="AD30" s="61" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="56">
         <v>31</v>
       </c>
@@ -5707,10 +6030,10 @@
         <v>245</v>
       </c>
       <c r="E31" s="41" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F31" s="41" t="s">
-        <v>160</v>
+        <v>136</v>
       </c>
       <c r="G31" s="58" t="s">
         <v>9</v>
@@ -5728,29 +6051,29 @@
         <v>9</v>
       </c>
       <c r="L31" s="32" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M31" s="32" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N31" s="32" t="str">
-        <f t="shared" si="20"/>
-        <v>Esgoto Coletores</v>
+        <f t="shared" si="23"/>
+        <v>Tubulação Agua Quente</v>
       </c>
       <c r="O31" s="29" t="str">
-        <f t="shared" si="10"/>
-        <v>Ralo.Seco</v>
+        <f t="shared" si="13"/>
+        <v>Tubulação.AQ</v>
       </c>
       <c r="P31" s="51" t="s">
-        <v>109</v>
+        <v>143</v>
       </c>
       <c r="Q31" s="29" t="s">
-        <v>119</v>
+        <v>288</v>
       </c>
       <c r="R31" s="29" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="S31" s="29" t="s">
         <v>9</v>
@@ -5762,14 +6085,14 @@
         <v>150</v>
       </c>
       <c r="V31" s="29" t="str">
-        <f t="shared" si="21"/>
-        <v>Esgoto.Coletores</v>
+        <f t="shared" si="24"/>
+        <v>Tubulação.Agua.Quente</v>
       </c>
       <c r="W31" s="29" t="s">
         <v>152</v>
       </c>
       <c r="X31" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>Key-HIDR-31</v>
       </c>
       <c r="Y31" s="28" t="s">
@@ -5785,13 +6108,13 @@
         <v>9</v>
       </c>
       <c r="AC31" s="29" t="s">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="AD31" s="61" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="56">
         <v>32</v>
       </c>
@@ -5805,10 +6128,10 @@
         <v>245</v>
       </c>
       <c r="E32" s="41" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F32" s="41" t="s">
-        <v>159</v>
+        <v>131</v>
       </c>
       <c r="G32" s="58" t="s">
         <v>9</v>
@@ -5826,29 +6149,29 @@
         <v>9</v>
       </c>
       <c r="L32" s="32" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M32" s="32" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N32" s="32" t="str">
-        <f t="shared" si="20"/>
-        <v>Esgoto Coletores</v>
+        <f t="shared" si="23"/>
+        <v>Tubulação Agua Quente</v>
       </c>
       <c r="O32" s="29" t="str">
-        <f t="shared" si="10"/>
-        <v>Ralo.Sifonado</v>
+        <f t="shared" si="13"/>
+        <v>Tubulação.Reuso</v>
       </c>
       <c r="P32" s="51" t="s">
-        <v>108</v>
-      </c>
-      <c r="Q32" s="29" t="s">
-        <v>120</v>
+        <v>144</v>
+      </c>
+      <c r="Q32" s="51" t="s">
+        <v>145</v>
       </c>
       <c r="R32" s="29" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="S32" s="29" t="s">
         <v>9</v>
@@ -5860,14 +6183,14 @@
         <v>150</v>
       </c>
       <c r="V32" s="29" t="str">
-        <f t="shared" si="21"/>
-        <v>Esgoto.Coletores</v>
+        <f t="shared" si="24"/>
+        <v>Tubulação.Agua.Quente</v>
       </c>
       <c r="W32" s="29" t="s">
         <v>152</v>
       </c>
       <c r="X32" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>Key-HIDR-32</v>
       </c>
       <c r="Y32" s="28" t="s">
@@ -5883,13 +6206,13 @@
         <v>9</v>
       </c>
       <c r="AC32" s="29" t="s">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="AD32" s="61" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="56">
         <v>33</v>
       </c>
@@ -5903,10 +6226,10 @@
         <v>245</v>
       </c>
       <c r="E33" s="41" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F33" s="41" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="G33" s="58" t="s">
         <v>9</v>
@@ -5924,29 +6247,29 @@
         <v>9</v>
       </c>
       <c r="L33" s="32" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M33" s="32" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N33" s="32" t="str">
-        <f t="shared" si="20"/>
-        <v>Esgoto Coletores</v>
+        <f t="shared" si="23"/>
+        <v>Peças Sanitárias</v>
       </c>
       <c r="O33" s="29" t="str">
-        <f t="shared" si="10"/>
-        <v>Coletor.Andar</v>
+        <f t="shared" si="13"/>
+        <v>Vaso.Sanitário</v>
       </c>
       <c r="P33" s="51" t="s">
-        <v>110</v>
+        <v>175</v>
       </c>
       <c r="Q33" s="29" t="s">
-        <v>237</v>
+        <v>178</v>
       </c>
       <c r="R33" s="29" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="S33" s="29" t="s">
         <v>9</v>
@@ -5958,36 +6281,36 @@
         <v>150</v>
       </c>
       <c r="V33" s="29" t="str">
-        <f t="shared" si="21"/>
-        <v>Esgoto.Coletores</v>
+        <f t="shared" si="24"/>
+        <v>Peças.Sanitárias</v>
       </c>
       <c r="W33" s="29" t="s">
         <v>152</v>
       </c>
       <c r="X33" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>Key-HIDR-33</v>
       </c>
       <c r="Y33" s="28" t="s">
-        <v>247</v>
+        <v>181</v>
       </c>
       <c r="Z33" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA33" s="28" t="s">
-        <v>248</v>
+        <v>182</v>
       </c>
       <c r="AB33" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC33" s="29" t="s">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="AD33" s="61" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="56">
         <v>34</v>
       </c>
@@ -6001,10 +6324,10 @@
         <v>245</v>
       </c>
       <c r="E34" s="41" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F34" s="41" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="G34" s="58" t="s">
         <v>9</v>
@@ -6022,29 +6345,29 @@
         <v>9</v>
       </c>
       <c r="L34" s="32" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M34" s="32" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="22"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N34" s="32" t="str">
-        <f t="shared" si="20"/>
-        <v>Esgoto Coletores</v>
+        <f t="shared" si="23"/>
+        <v>Peças Sanitárias</v>
       </c>
       <c r="O34" s="29" t="str">
-        <f t="shared" si="10"/>
-        <v>Coletor.Predial</v>
+        <f t="shared" si="13"/>
+        <v>Bidet</v>
       </c>
       <c r="P34" s="51" t="s">
-        <v>111</v>
+        <v>167</v>
       </c>
       <c r="Q34" s="29" t="s">
-        <v>238</v>
+        <v>289</v>
       </c>
       <c r="R34" s="29" t="s">
-        <v>325</v>
+        <v>167</v>
       </c>
       <c r="S34" s="29" t="s">
         <v>9</v>
@@ -6056,36 +6379,36 @@
         <v>150</v>
       </c>
       <c r="V34" s="29" t="str">
-        <f t="shared" si="21"/>
-        <v>Esgoto.Coletores</v>
+        <f t="shared" si="24"/>
+        <v>Peças.Sanitárias</v>
       </c>
       <c r="W34" s="29" t="s">
         <v>152</v>
       </c>
       <c r="X34" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>Key-HIDR-34</v>
       </c>
       <c r="Y34" s="28" t="s">
-        <v>247</v>
+        <v>181</v>
       </c>
       <c r="Z34" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA34" s="28" t="s">
-        <v>248</v>
+        <v>182</v>
       </c>
       <c r="AB34" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC34" s="29" t="s">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="AD34" s="61" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="56">
         <v>35</v>
       </c>
@@ -6099,10 +6422,10 @@
         <v>245</v>
       </c>
       <c r="E35" s="41" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F35" s="41" t="s">
-        <v>101</v>
+        <v>170</v>
       </c>
       <c r="G35" s="58" t="s">
         <v>9</v>
@@ -6120,29 +6443,29 @@
         <v>9</v>
       </c>
       <c r="L35" s="32" t="str">
-        <f t="shared" ref="L35" si="30">CONCATENATE("", C35)</f>
+        <f t="shared" si="21"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M35" s="32" t="str">
-        <f t="shared" ref="M35" si="31">CONCATENATE("", D35)</f>
+        <f t="shared" si="22"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N35" s="32" t="str">
-        <f t="shared" ref="N35" si="32">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E35),"."," ")," De "," de "))</f>
-        <v>Esgoto Coletores</v>
+        <f t="shared" si="23"/>
+        <v>Peças Sanitárias</v>
       </c>
       <c r="O35" s="29" t="str">
-        <f t="shared" si="10"/>
-        <v>Tubo.de.Queda</v>
+        <f t="shared" si="13"/>
+        <v>Pia.Sanitária</v>
       </c>
       <c r="P35" s="51" t="s">
-        <v>112</v>
+        <v>176</v>
       </c>
       <c r="Q35" s="29" t="s">
-        <v>239</v>
+        <v>180</v>
       </c>
       <c r="R35" s="29" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="S35" s="29" t="s">
         <v>9</v>
@@ -6154,36 +6477,36 @@
         <v>150</v>
       </c>
       <c r="V35" s="29" t="str">
-        <f t="shared" ref="V35" si="33">SUBSTITUTE(E35, "_", " ")</f>
-        <v>Esgoto.Coletores</v>
+        <f t="shared" si="24"/>
+        <v>Peças.Sanitárias</v>
       </c>
       <c r="W35" s="29" t="s">
         <v>152</v>
       </c>
       <c r="X35" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>Key-HIDR-35</v>
       </c>
       <c r="Y35" s="28" t="s">
-        <v>247</v>
+        <v>181</v>
       </c>
       <c r="Z35" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA35" s="28" t="s">
-        <v>248</v>
+        <v>182</v>
       </c>
       <c r="AB35" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC35" s="29" t="s">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="AD35" s="61" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="56">
         <v>36</v>
       </c>
@@ -6197,10 +6520,10 @@
         <v>245</v>
       </c>
       <c r="E36" s="41" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F36" s="41" t="s">
-        <v>210</v>
+        <v>166</v>
       </c>
       <c r="G36" s="58" t="s">
         <v>9</v>
@@ -6218,29 +6541,29 @@
         <v>9</v>
       </c>
       <c r="L36" s="32" t="str">
-        <f t="shared" ref="L36" si="34">CONCATENATE("", C36)</f>
+        <f t="shared" si="21"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M36" s="32" t="str">
-        <f t="shared" ref="M36" si="35">CONCATENATE("", D36)</f>
+        <f t="shared" si="22"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N36" s="32" t="str">
-        <f t="shared" ref="N36" si="36">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E36),"."," ")," De "," de "))</f>
-        <v>Esgoto Coletores</v>
+        <f t="shared" si="23"/>
+        <v>Peças Sanitárias</v>
       </c>
       <c r="O36" s="29" t="str">
-        <f t="shared" si="10"/>
-        <v>Fecho.Hidráulico</v>
+        <f t="shared" si="13"/>
+        <v>Lavatório</v>
       </c>
       <c r="P36" s="51" t="s">
-        <v>113</v>
+        <v>166</v>
       </c>
       <c r="Q36" s="29" t="s">
-        <v>121</v>
+        <v>290</v>
       </c>
       <c r="R36" s="29" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="S36" s="29" t="s">
         <v>9</v>
@@ -6252,36 +6575,36 @@
         <v>150</v>
       </c>
       <c r="V36" s="29" t="str">
-        <f t="shared" ref="V36" si="37">SUBSTITUTE(E36, "_", " ")</f>
-        <v>Esgoto.Coletores</v>
+        <f t="shared" si="24"/>
+        <v>Peças.Sanitárias</v>
       </c>
       <c r="W36" s="29" t="s">
         <v>152</v>
       </c>
       <c r="X36" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>Key-HIDR-36</v>
       </c>
       <c r="Y36" s="28" t="s">
-        <v>247</v>
+        <v>181</v>
       </c>
       <c r="Z36" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA36" s="28" t="s">
-        <v>248</v>
+        <v>182</v>
       </c>
       <c r="AB36" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC36" s="29" t="s">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="AD36" s="61" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="56">
         <v>37</v>
       </c>
@@ -6295,10 +6618,10 @@
         <v>245</v>
       </c>
       <c r="E37" s="41" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F37" s="41" t="s">
-        <v>105</v>
+        <v>169</v>
       </c>
       <c r="G37" s="58" t="s">
         <v>9</v>
@@ -6316,29 +6639,29 @@
         <v>9</v>
       </c>
       <c r="L37" s="32" t="str">
-        <f t="shared" ref="L37:L41" si="38">CONCATENATE("", C37)</f>
+        <f t="shared" ref="L37" si="25">CONCATENATE("", C37)</f>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M37" s="32" t="str">
-        <f t="shared" ref="M37:M41" si="39">CONCATENATE("", D37)</f>
+        <f t="shared" ref="M37" si="26">CONCATENATE("", D37)</f>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N37" s="32" t="str">
-        <f t="shared" ref="N37:N41" si="40">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E37),"."," ")," De "," de "))</f>
-        <v>Esgoto Visitas</v>
+        <f t="shared" ref="N37" si="27">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E37),"."," ")," De "," de "))</f>
+        <v>Peças Sanitárias</v>
       </c>
       <c r="O37" s="29" t="str">
-        <f t="shared" si="10"/>
-        <v>Caixa.de.Areia</v>
+        <f t="shared" si="13"/>
+        <v>Cuba.Sanitária</v>
       </c>
       <c r="P37" s="51" t="s">
-        <v>114</v>
+        <v>177</v>
       </c>
       <c r="Q37" s="29" t="s">
-        <v>122</v>
+        <v>179</v>
       </c>
       <c r="R37" s="29" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="S37" s="29" t="s">
         <v>9</v>
@@ -6350,36 +6673,36 @@
         <v>150</v>
       </c>
       <c r="V37" s="29" t="str">
-        <f t="shared" ref="V37:V41" si="41">SUBSTITUTE(E37, "_", " ")</f>
-        <v>Esgoto.Visitas</v>
+        <f t="shared" ref="V37" si="28">SUBSTITUTE(E37, "_", " ")</f>
+        <v>Peças.Sanitárias</v>
       </c>
       <c r="W37" s="29" t="s">
         <v>152</v>
       </c>
       <c r="X37" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>Key-HIDR-37</v>
       </c>
       <c r="Y37" s="28" t="s">
-        <v>247</v>
+        <v>181</v>
       </c>
       <c r="Z37" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA37" s="28" t="s">
-        <v>248</v>
+        <v>182</v>
       </c>
       <c r="AB37" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC37" s="29" t="s">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="AD37" s="61" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="56">
         <v>38</v>
       </c>
@@ -6393,10 +6716,10 @@
         <v>245</v>
       </c>
       <c r="E38" s="41" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F38" s="41" t="s">
-        <v>104</v>
+        <v>171</v>
       </c>
       <c r="G38" s="58" t="s">
         <v>9</v>
@@ -6414,29 +6737,29 @@
         <v>9</v>
       </c>
       <c r="L38" s="32" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="21"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M38" s="32" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="22"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N38" s="32" t="str">
-        <f t="shared" si="40"/>
-        <v>Esgoto Visitas</v>
+        <f t="shared" si="23"/>
+        <v>Peças Sanitárias</v>
       </c>
       <c r="O38" s="29" t="str">
-        <f t="shared" si="10"/>
-        <v>Caixa.de.Gordura</v>
+        <f t="shared" si="13"/>
+        <v>Banheira</v>
       </c>
       <c r="P38" s="51" t="s">
-        <v>115</v>
+        <v>171</v>
       </c>
       <c r="Q38" s="29" t="s">
-        <v>123</v>
+        <v>291</v>
       </c>
       <c r="R38" s="29" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="S38" s="29" t="s">
         <v>9</v>
@@ -6448,36 +6771,36 @@
         <v>150</v>
       </c>
       <c r="V38" s="29" t="str">
-        <f t="shared" si="41"/>
-        <v>Esgoto.Visitas</v>
+        <f t="shared" si="24"/>
+        <v>Peças.Sanitárias</v>
       </c>
       <c r="W38" s="29" t="s">
         <v>152</v>
       </c>
       <c r="X38" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>Key-HIDR-38</v>
       </c>
       <c r="Y38" s="28" t="s">
-        <v>247</v>
+        <v>181</v>
       </c>
       <c r="Z38" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA38" s="28" t="s">
-        <v>248</v>
+        <v>182</v>
       </c>
       <c r="AB38" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AC38" s="29" t="s">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="AD38" s="61" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="56">
         <v>39</v>
       </c>
@@ -6491,10 +6814,10 @@
         <v>245</v>
       </c>
       <c r="E39" s="41" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F39" s="41" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G39" s="58" t="s">
         <v>9</v>
@@ -6512,29 +6835,29 @@
         <v>9</v>
       </c>
       <c r="L39" s="32" t="str">
-        <f t="shared" ref="L39:L40" si="42">CONCATENATE("", C39)</f>
+        <f t="shared" ref="L39" si="29">CONCATENATE("", C39)</f>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M39" s="32" t="str">
-        <f t="shared" ref="M39:M40" si="43">CONCATENATE("", D39)</f>
+        <f t="shared" ref="M39" si="30">CONCATENATE("", D39)</f>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N39" s="32" t="str">
-        <f t="shared" ref="N39:N40" si="44">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E39),"."," ")," De "," de "))</f>
-        <v>Esgoto Visitas</v>
+        <f t="shared" ref="N39" si="31">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E39),"."," ")," De "," de "))</f>
+        <v>Esgoto Coletores</v>
       </c>
       <c r="O39" s="29" t="str">
-        <f t="shared" si="10"/>
-        <v>Caixa.de.Inspeção</v>
+        <f t="shared" si="13"/>
+        <v>Ventilação.Esgoto</v>
       </c>
       <c r="P39" s="51" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q39" s="29" t="s">
-        <v>236</v>
+        <v>148</v>
+      </c>
+      <c r="Q39" s="51" t="s">
+        <v>149</v>
       </c>
       <c r="R39" s="29" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="S39" s="29" t="s">
         <v>9</v>
@@ -6546,14 +6869,14 @@
         <v>150</v>
       </c>
       <c r="V39" s="29" t="str">
-        <f t="shared" ref="V39:V40" si="45">SUBSTITUTE(E39, "_", " ")</f>
-        <v>Esgoto.Visitas</v>
+        <f t="shared" ref="V39" si="32">SUBSTITUTE(E39, "_", " ")</f>
+        <v>Esgoto.Coletores</v>
       </c>
       <c r="W39" s="29" t="s">
         <v>152</v>
       </c>
       <c r="X39" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>Key-HIDR-39</v>
       </c>
       <c r="Y39" s="28" t="s">
@@ -6575,7 +6898,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="56">
         <v>40</v>
       </c>
@@ -6589,10 +6912,10 @@
         <v>245</v>
       </c>
       <c r="E40" s="41" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F40" s="41" t="s">
-        <v>106</v>
+        <v>160</v>
       </c>
       <c r="G40" s="58" t="s">
         <v>9</v>
@@ -6610,29 +6933,29 @@
         <v>9</v>
       </c>
       <c r="L40" s="32" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="21"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M40" s="32" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="22"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N40" s="32" t="str">
-        <f t="shared" si="44"/>
-        <v>Esgoto Visitas</v>
+        <f t="shared" si="23"/>
+        <v>Esgoto Coletores</v>
       </c>
       <c r="O40" s="29" t="str">
-        <f t="shared" si="10"/>
-        <v>Caixa.Sifonada</v>
+        <f t="shared" si="13"/>
+        <v>Ralo.Seco</v>
       </c>
       <c r="P40" s="51" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="Q40" s="29" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="R40" s="29" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="S40" s="29" t="s">
         <v>9</v>
@@ -6644,14 +6967,14 @@
         <v>150</v>
       </c>
       <c r="V40" s="29" t="str">
-        <f t="shared" si="45"/>
-        <v>Esgoto.Visitas</v>
+        <f t="shared" si="24"/>
+        <v>Esgoto.Coletores</v>
       </c>
       <c r="W40" s="29" t="s">
         <v>152</v>
       </c>
       <c r="X40" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>Key-HIDR-40</v>
       </c>
       <c r="Y40" s="28" t="s">
@@ -6673,7 +6996,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="56">
         <v>41</v>
       </c>
@@ -6687,10 +7010,10 @@
         <v>245</v>
       </c>
       <c r="E41" s="41" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F41" s="41" t="s">
-        <v>103</v>
+        <v>159</v>
       </c>
       <c r="G41" s="58" t="s">
         <v>9</v>
@@ -6708,29 +7031,29 @@
         <v>9</v>
       </c>
       <c r="L41" s="32" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="21"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M41" s="32" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="22"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N41" s="32" t="str">
-        <f t="shared" si="40"/>
-        <v>Esgoto Visitas</v>
+        <f t="shared" si="23"/>
+        <v>Esgoto Coletores</v>
       </c>
       <c r="O41" s="29" t="str">
-        <f t="shared" si="10"/>
-        <v>Poço.de.Visita</v>
+        <f t="shared" si="13"/>
+        <v>Ralo.Sifonado</v>
       </c>
       <c r="P41" s="51" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="Q41" s="29" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="R41" s="29" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="S41" s="29" t="s">
         <v>9</v>
@@ -6742,14 +7065,14 @@
         <v>150</v>
       </c>
       <c r="V41" s="29" t="str">
-        <f t="shared" si="41"/>
-        <v>Esgoto.Visitas</v>
+        <f t="shared" si="24"/>
+        <v>Esgoto.Coletores</v>
       </c>
       <c r="W41" s="29" t="s">
         <v>152</v>
       </c>
       <c r="X41" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>Key-HIDR-41</v>
       </c>
       <c r="Y41" s="28" t="s">
@@ -6771,7 +7094,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="56">
         <v>42</v>
       </c>
@@ -6785,10 +7108,10 @@
         <v>245</v>
       </c>
       <c r="E42" s="41" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F42" s="41" t="s">
-        <v>155</v>
+        <v>100</v>
       </c>
       <c r="G42" s="58" t="s">
         <v>9</v>
@@ -6806,29 +7129,29 @@
         <v>9</v>
       </c>
       <c r="L42" s="32" t="str">
-        <f t="shared" ref="L42" si="46">CONCATENATE("", C42)</f>
+        <f t="shared" si="21"/>
         <v>Sistemas.Prediais</v>
       </c>
       <c r="M42" s="32" t="str">
-        <f t="shared" ref="M42" si="47">CONCATENATE("", D42)</f>
+        <f t="shared" si="22"/>
         <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N42" s="32" t="str">
-        <f t="shared" ref="N42" si="48">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E42),"."," ")," De "," de "))</f>
-        <v>Esgoto Acessórios</v>
+        <f t="shared" si="23"/>
+        <v>Esgoto Coletores</v>
       </c>
       <c r="O42" s="29" t="str">
-        <f t="shared" si="10"/>
-        <v>Acessório.Sanitário</v>
+        <f t="shared" si="13"/>
+        <v>Coletor.Andar</v>
       </c>
       <c r="P42" s="51" t="s">
-        <v>223</v>
-      </c>
-      <c r="Q42" s="51" t="s">
-        <v>156</v>
+        <v>110</v>
+      </c>
+      <c r="Q42" s="29" t="s">
+        <v>237</v>
       </c>
       <c r="R42" s="29" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="S42" s="29" t="s">
         <v>9</v>
@@ -6840,24 +7163,24 @@
         <v>150</v>
       </c>
       <c r="V42" s="29" t="str">
-        <f t="shared" ref="V42" si="49">SUBSTITUTE(E42, "_", " ")</f>
-        <v>Esgoto.Acessórios</v>
+        <f t="shared" si="24"/>
+        <v>Esgoto.Coletores</v>
       </c>
       <c r="W42" s="29" t="s">
         <v>152</v>
       </c>
       <c r="X42" s="57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>Key-HIDR-42</v>
       </c>
       <c r="Y42" s="28" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="Z42" s="61" t="s">
         <v>9</v>
       </c>
       <c r="AA42" s="28" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="AB42" s="61" t="s">
         <v>9</v>
@@ -6869,24 +7192,24 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="56">
         <v>43</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>269</v>
+        <v>243</v>
       </c>
       <c r="C43" s="41" t="s">
-        <v>270</v>
+        <v>244</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>275</v>
+        <v>245</v>
       </c>
       <c r="E43" s="41" t="s">
-        <v>276</v>
+        <v>215</v>
       </c>
       <c r="F43" s="41" t="s">
-        <v>271</v>
+        <v>99</v>
       </c>
       <c r="G43" s="58" t="s">
         <v>9</v>
@@ -6904,29 +7227,29 @@
         <v>9</v>
       </c>
       <c r="L43" s="32" t="str">
-        <f t="shared" ref="L43" si="50">CONCATENATE("", C43)</f>
-        <v>De.Tubulações</v>
+        <f t="shared" si="21"/>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M43" s="32" t="str">
-        <f t="shared" ref="M43" si="51">CONCATENATE("", D43)</f>
-        <v>Elementos.de.Instalações</v>
+        <f t="shared" si="22"/>
+        <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N43" s="32" t="str">
-        <f t="shared" ref="N43" si="52">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E43),"."," ")," De "," de "))</f>
-        <v>Instalação De</v>
+        <f t="shared" si="23"/>
+        <v>Esgoto Coletores</v>
       </c>
       <c r="O43" s="29" t="str">
-        <f t="shared" ref="O43" si="53">IF(ISNUMBER(FIND("Ifc",F43)),CONCATENATE("Classe IFC:   ",F43),CONCATENATE("",F43))</f>
-        <v>Esgoto</v>
+        <f t="shared" si="13"/>
+        <v>Coletor.Predial</v>
       </c>
       <c r="P43" s="51" t="s">
-        <v>279</v>
-      </c>
-      <c r="Q43" s="51" t="s">
-        <v>292</v>
+        <v>111</v>
+      </c>
+      <c r="Q43" s="29" t="s">
+        <v>238</v>
       </c>
       <c r="R43" s="29" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="S43" s="29" t="s">
         <v>9</v>
@@ -6938,14 +7261,14 @@
         <v>150</v>
       </c>
       <c r="V43" s="29" t="str">
-        <f t="shared" ref="V43" si="54">SUBSTITUTE(E43, "_", " ")</f>
-        <v>Instalação.De</v>
+        <f t="shared" si="24"/>
+        <v>Esgoto.Coletores</v>
       </c>
       <c r="W43" s="29" t="s">
         <v>152</v>
       </c>
       <c r="X43" s="57" t="str">
-        <f t="shared" ref="X43" si="55">CONCATENATE("Key-HIDR-",A43)</f>
+        <f t="shared" si="8"/>
         <v>Key-HIDR-43</v>
       </c>
       <c r="Y43" s="28" t="s">
@@ -6967,24 +7290,24 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="56">
         <v>44</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>269</v>
+        <v>243</v>
       </c>
       <c r="C44" s="41" t="s">
-        <v>270</v>
+        <v>244</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>275</v>
+        <v>245</v>
       </c>
       <c r="E44" s="41" t="s">
-        <v>276</v>
+        <v>215</v>
       </c>
       <c r="F44" s="41" t="s">
-        <v>272</v>
+        <v>101</v>
       </c>
       <c r="G44" s="58" t="s">
         <v>9</v>
@@ -7002,29 +7325,29 @@
         <v>9</v>
       </c>
       <c r="L44" s="32" t="str">
-        <f t="shared" ref="L44:L46" si="56">CONCATENATE("", C44)</f>
-        <v>De.Tubulações</v>
+        <f t="shared" ref="L44" si="33">CONCATENATE("", C44)</f>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M44" s="32" t="str">
-        <f t="shared" ref="M44:M46" si="57">CONCATENATE("", D44)</f>
-        <v>Elementos.de.Instalações</v>
+        <f t="shared" ref="M44" si="34">CONCATENATE("", D44)</f>
+        <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N44" s="32" t="str">
-        <f t="shared" ref="N44:N46" si="58">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E44),"."," ")," De "," de "))</f>
-        <v>Instalação De</v>
+        <f t="shared" ref="N44" si="35">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E44),"."," ")," De "," de "))</f>
+        <v>Esgoto Coletores</v>
       </c>
       <c r="O44" s="29" t="str">
-        <f t="shared" ref="O44:O46" si="59">IF(ISNUMBER(FIND("Ifc",F44)),CONCATENATE("Classe IFC:   ",F44),CONCATENATE("",F44))</f>
-        <v>AF</v>
+        <f t="shared" si="13"/>
+        <v>Tubo.de.Queda</v>
       </c>
       <c r="P44" s="51" t="s">
-        <v>280</v>
-      </c>
-      <c r="Q44" s="51" t="s">
-        <v>293</v>
+        <v>112</v>
+      </c>
+      <c r="Q44" s="29" t="s">
+        <v>239</v>
       </c>
       <c r="R44" s="29" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="S44" s="29" t="s">
         <v>9</v>
@@ -7036,14 +7359,14 @@
         <v>150</v>
       </c>
       <c r="V44" s="29" t="str">
-        <f t="shared" ref="V44:V46" si="60">SUBSTITUTE(E44, "_", " ")</f>
-        <v>Instalação.De</v>
+        <f t="shared" ref="V44" si="36">SUBSTITUTE(E44, "_", " ")</f>
+        <v>Esgoto.Coletores</v>
       </c>
       <c r="W44" s="29" t="s">
         <v>152</v>
       </c>
       <c r="X44" s="57" t="str">
-        <f t="shared" ref="X44:X52" si="61">CONCATENATE("Key-HIDR-",A44)</f>
+        <f t="shared" si="8"/>
         <v>Key-HIDR-44</v>
       </c>
       <c r="Y44" s="28" t="s">
@@ -7059,30 +7382,30 @@
         <v>9</v>
       </c>
       <c r="AC44" s="29" t="s">
-        <v>154</v>
+        <v>126</v>
       </c>
       <c r="AD44" s="61" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="56">
         <v>45</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>269</v>
+        <v>243</v>
       </c>
       <c r="C45" s="41" t="s">
-        <v>270</v>
+        <v>244</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>275</v>
+        <v>245</v>
       </c>
       <c r="E45" s="41" t="s">
-        <v>276</v>
+        <v>215</v>
       </c>
       <c r="F45" s="41" t="s">
-        <v>273</v>
+        <v>210</v>
       </c>
       <c r="G45" s="58" t="s">
         <v>9</v>
@@ -7100,29 +7423,29 @@
         <v>9</v>
       </c>
       <c r="L45" s="32" t="str">
-        <f t="shared" si="56"/>
-        <v>De.Tubulações</v>
+        <f t="shared" ref="L45" si="37">CONCATENATE("", C45)</f>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M45" s="32" t="str">
-        <f t="shared" si="57"/>
-        <v>Elementos.de.Instalações</v>
+        <f t="shared" ref="M45" si="38">CONCATENATE("", D45)</f>
+        <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N45" s="32" t="str">
-        <f t="shared" si="58"/>
-        <v>Instalação De</v>
+        <f t="shared" ref="N45" si="39">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E45),"."," ")," De "," de "))</f>
+        <v>Esgoto Coletores</v>
       </c>
       <c r="O45" s="29" t="str">
-        <f t="shared" si="59"/>
-        <v>AQ</v>
+        <f t="shared" si="13"/>
+        <v>Fecho.Hidráulico</v>
       </c>
       <c r="P45" s="51" t="s">
-        <v>281</v>
-      </c>
-      <c r="Q45" s="51" t="s">
-        <v>294</v>
+        <v>113</v>
+      </c>
+      <c r="Q45" s="29" t="s">
+        <v>121</v>
       </c>
       <c r="R45" s="29" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="S45" s="29" t="s">
         <v>9</v>
@@ -7134,14 +7457,14 @@
         <v>150</v>
       </c>
       <c r="V45" s="29" t="str">
-        <f t="shared" si="60"/>
-        <v>Instalação.De</v>
+        <f t="shared" ref="V45" si="40">SUBSTITUTE(E45, "_", " ")</f>
+        <v>Esgoto.Coletores</v>
       </c>
       <c r="W45" s="29" t="s">
         <v>152</v>
       </c>
       <c r="X45" s="57" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="8"/>
         <v>Key-HIDR-45</v>
       </c>
       <c r="Y45" s="28" t="s">
@@ -7157,30 +7480,30 @@
         <v>9</v>
       </c>
       <c r="AC45" s="29" t="s">
-        <v>154</v>
+        <v>126</v>
       </c>
       <c r="AD45" s="61" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="56">
         <v>46</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>269</v>
+        <v>243</v>
       </c>
       <c r="C46" s="41" t="s">
-        <v>270</v>
+        <v>244</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>275</v>
+        <v>245</v>
       </c>
       <c r="E46" s="41" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="F46" s="41" t="s">
-        <v>274</v>
+        <v>105</v>
       </c>
       <c r="G46" s="58" t="s">
         <v>9</v>
@@ -7198,29 +7521,29 @@
         <v>9</v>
       </c>
       <c r="L46" s="32" t="str">
-        <f t="shared" si="56"/>
-        <v>De.Tubulações</v>
+        <f t="shared" ref="L46:L50" si="41">CONCATENATE("", C46)</f>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M46" s="32" t="str">
-        <f t="shared" si="57"/>
-        <v>Elementos.de.Instalações</v>
+        <f t="shared" ref="M46:M50" si="42">CONCATENATE("", D46)</f>
+        <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N46" s="32" t="str">
-        <f t="shared" si="58"/>
-        <v>Instalação De</v>
+        <f t="shared" ref="N46:N50" si="43">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E46),"."," ")," De "," de "))</f>
+        <v>Esgoto Visitas</v>
       </c>
       <c r="O46" s="29" t="str">
-        <f t="shared" si="59"/>
-        <v>Pluvial</v>
+        <f t="shared" si="13"/>
+        <v>Caixa.de.Areia</v>
       </c>
       <c r="P46" s="51" t="s">
-        <v>282</v>
-      </c>
-      <c r="Q46" s="51" t="s">
-        <v>295</v>
+        <v>114</v>
+      </c>
+      <c r="Q46" s="29" t="s">
+        <v>122</v>
       </c>
       <c r="R46" s="29" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="S46" s="29" t="s">
         <v>9</v>
@@ -7232,14 +7555,14 @@
         <v>150</v>
       </c>
       <c r="V46" s="29" t="str">
-        <f t="shared" si="60"/>
-        <v>Instalação.De</v>
+        <f t="shared" ref="V46:V50" si="44">SUBSTITUTE(E46, "_", " ")</f>
+        <v>Esgoto.Visitas</v>
       </c>
       <c r="W46" s="29" t="s">
         <v>152</v>
       </c>
       <c r="X46" s="57" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="8"/>
         <v>Key-HIDR-46</v>
       </c>
       <c r="Y46" s="28" t="s">
@@ -7261,24 +7584,24 @@
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="56">
         <v>47</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>269</v>
+        <v>243</v>
       </c>
       <c r="C47" s="41" t="s">
-        <v>270</v>
+        <v>244</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>275</v>
+        <v>245</v>
       </c>
       <c r="E47" s="41" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="F47" s="41" t="s">
-        <v>277</v>
+        <v>104</v>
       </c>
       <c r="G47" s="58" t="s">
         <v>9</v>
@@ -7296,29 +7619,29 @@
         <v>9</v>
       </c>
       <c r="L47" s="32" t="str">
-        <f t="shared" ref="L47" si="62">CONCATENATE("", C47)</f>
-        <v>De.Tubulações</v>
+        <f t="shared" si="41"/>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M47" s="32" t="str">
-        <f t="shared" ref="M47" si="63">CONCATENATE("", D47)</f>
-        <v>Elementos.de.Instalações</v>
+        <f t="shared" si="42"/>
+        <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N47" s="32" t="str">
-        <f t="shared" ref="N47" si="64">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E47),"."," ")," De "," de "))</f>
-        <v>Instalação De</v>
+        <f t="shared" si="43"/>
+        <v>Esgoto Visitas</v>
       </c>
       <c r="O47" s="29" t="str">
-        <f t="shared" ref="O47" si="65">IF(ISNUMBER(FIND("Ifc",F47)),CONCATENATE("Classe IFC:   ",F47),CONCATENATE("",F47))</f>
-        <v>Ventilação</v>
+        <f t="shared" si="13"/>
+        <v>Caixa.de.Gordura</v>
       </c>
       <c r="P47" s="51" t="s">
-        <v>278</v>
-      </c>
-      <c r="Q47" s="51" t="s">
-        <v>296</v>
+        <v>115</v>
+      </c>
+      <c r="Q47" s="29" t="s">
+        <v>123</v>
       </c>
       <c r="R47" s="29" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="S47" s="29" t="s">
         <v>9</v>
@@ -7330,14 +7653,14 @@
         <v>150</v>
       </c>
       <c r="V47" s="29" t="str">
-        <f t="shared" ref="V47" si="66">SUBSTITUTE(E47, "_", " ")</f>
-        <v>Instalação.De</v>
+        <f t="shared" si="44"/>
+        <v>Esgoto.Visitas</v>
       </c>
       <c r="W47" s="29" t="s">
         <v>152</v>
       </c>
       <c r="X47" s="57" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="8"/>
         <v>Key-HIDR-47</v>
       </c>
       <c r="Y47" s="28" t="s">
@@ -7359,24 +7682,24 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:30" s="62" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="56">
         <v>48</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="C48" s="63" t="s">
-        <v>342</v>
-      </c>
-      <c r="D48" s="63" t="s">
-        <v>344</v>
-      </c>
-      <c r="E48" s="63" t="s">
-        <v>343</v>
-      </c>
-      <c r="F48" s="63" t="s">
-        <v>345</v>
+        <v>243</v>
+      </c>
+      <c r="C48" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="E48" s="41" t="s">
+        <v>216</v>
+      </c>
+      <c r="F48" s="41" t="s">
+        <v>102</v>
       </c>
       <c r="G48" s="58" t="s">
         <v>9</v>
@@ -7394,89 +7717,87 @@
         <v>9</v>
       </c>
       <c r="L48" s="32" t="str">
-        <f t="shared" ref="L48:O52" si="67">SUBSTITUTE(CONCATENATE("", C48), ".", " ")</f>
-        <v>De API</v>
+        <f t="shared" ref="L48:L49" si="45">CONCATENATE("", C48)</f>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M48" s="32" t="str">
-        <f t="shared" si="67"/>
-        <v>Macros</v>
+        <f t="shared" ref="M48:M49" si="46">CONCATENATE("", D48)</f>
+        <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N48" s="32" t="str">
-        <f t="shared" si="67"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O48" s="32" t="str">
-        <f t="shared" si="67"/>
-        <v>Função Auxiliar</v>
-      </c>
-      <c r="P48" s="29" t="s">
-        <v>346</v>
+        <f t="shared" ref="N48:N49" si="47">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E48),"."," ")," De "," de "))</f>
+        <v>Esgoto Visitas</v>
+      </c>
+      <c r="O48" s="29" t="str">
+        <f t="shared" si="13"/>
+        <v>Caixa.de.Inspeção</v>
+      </c>
+      <c r="P48" s="51" t="s">
+        <v>116</v>
       </c>
       <c r="Q48" s="29" t="s">
-        <v>347</v>
+        <v>236</v>
       </c>
       <c r="R48" s="29" t="s">
-        <v>348</v>
+        <v>330</v>
       </c>
       <c r="S48" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="T48" s="29" t="str">
-        <f t="shared" ref="T48:V52" si="68">SUBSTITUTE(C48, ".", " ")</f>
-        <v>De API</v>
-      </c>
-      <c r="U48" s="29" t="str">
-        <f t="shared" si="68"/>
-        <v>Macros</v>
-      </c>
-      <c r="V48" s="60" t="str">
-        <f t="shared" si="68"/>
-        <v>Métodos</v>
+      <c r="T48" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="U48" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="V48" s="29" t="str">
+        <f t="shared" ref="V48:V49" si="48">SUBSTITUTE(E48, "_", " ")</f>
+        <v>Esgoto.Visitas</v>
       </c>
       <c r="W48" s="29" t="s">
         <v>152</v>
       </c>
       <c r="X48" s="57" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="8"/>
         <v>Key-HIDR-48</v>
       </c>
-      <c r="Y48" s="61" t="s">
-        <v>9</v>
+      <c r="Y48" s="28" t="s">
+        <v>247</v>
       </c>
       <c r="Z48" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AA48" s="61" t="s">
-        <v>9</v>
+      <c r="AA48" s="28" t="s">
+        <v>248</v>
       </c>
       <c r="AB48" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AC48" s="61" t="s">
-        <v>9</v>
+      <c r="AC48" s="29" t="s">
+        <v>126</v>
       </c>
       <c r="AD48" s="61" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:30" s="62" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="56">
         <v>49</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="C49" s="63" t="s">
-        <v>342</v>
-      </c>
-      <c r="D49" s="63" t="s">
-        <v>344</v>
-      </c>
-      <c r="E49" s="63" t="s">
-        <v>343</v>
-      </c>
-      <c r="F49" s="63" t="s">
-        <v>349</v>
+        <v>243</v>
+      </c>
+      <c r="C49" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="E49" s="41" t="s">
+        <v>216</v>
+      </c>
+      <c r="F49" s="41" t="s">
+        <v>106</v>
       </c>
       <c r="G49" s="58" t="s">
         <v>9</v>
@@ -7494,89 +7815,87 @@
         <v>9</v>
       </c>
       <c r="L49" s="32" t="str">
-        <f t="shared" si="67"/>
-        <v>De API</v>
+        <f t="shared" si="45"/>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M49" s="32" t="str">
-        <f t="shared" si="67"/>
-        <v>Macros</v>
+        <f t="shared" si="46"/>
+        <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N49" s="32" t="str">
-        <f t="shared" si="67"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O49" s="32" t="str">
-        <f t="shared" si="67"/>
-        <v>Função Global</v>
-      </c>
-      <c r="P49" s="29" t="s">
-        <v>350</v>
+        <f t="shared" si="47"/>
+        <v>Esgoto Visitas</v>
+      </c>
+      <c r="O49" s="29" t="str">
+        <f t="shared" si="13"/>
+        <v>Caixa.Sifonada</v>
+      </c>
+      <c r="P49" s="51" t="s">
+        <v>117</v>
       </c>
       <c r="Q49" s="29" t="s">
-        <v>351</v>
+        <v>124</v>
       </c>
       <c r="R49" s="29" t="s">
-        <v>352</v>
+        <v>331</v>
       </c>
       <c r="S49" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="T49" s="29" t="str">
-        <f t="shared" si="68"/>
-        <v>De API</v>
-      </c>
-      <c r="U49" s="29" t="str">
-        <f t="shared" si="68"/>
-        <v>Macros</v>
-      </c>
-      <c r="V49" s="60" t="str">
-        <f t="shared" si="68"/>
-        <v>Métodos</v>
+      <c r="T49" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="U49" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="V49" s="29" t="str">
+        <f t="shared" si="48"/>
+        <v>Esgoto.Visitas</v>
       </c>
       <c r="W49" s="29" t="s">
         <v>152</v>
       </c>
       <c r="X49" s="57" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="8"/>
         <v>Key-HIDR-49</v>
       </c>
-      <c r="Y49" s="61" t="s">
-        <v>9</v>
+      <c r="Y49" s="28" t="s">
+        <v>247</v>
       </c>
       <c r="Z49" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AA49" s="61" t="s">
-        <v>9</v>
+      <c r="AA49" s="28" t="s">
+        <v>248</v>
       </c>
       <c r="AB49" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AC49" s="61" t="s">
-        <v>9</v>
+      <c r="AC49" s="29" t="s">
+        <v>126</v>
       </c>
       <c r="AD49" s="61" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="1:30" s="62" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="56">
         <v>50</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="C50" s="63" t="s">
-        <v>342</v>
-      </c>
-      <c r="D50" s="63" t="s">
-        <v>344</v>
-      </c>
-      <c r="E50" s="63" t="s">
-        <v>343</v>
-      </c>
-      <c r="F50" s="63" t="s">
-        <v>353</v>
+        <v>243</v>
+      </c>
+      <c r="C50" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="E50" s="41" t="s">
+        <v>216</v>
+      </c>
+      <c r="F50" s="41" t="s">
+        <v>103</v>
       </c>
       <c r="G50" s="58" t="s">
         <v>9</v>
@@ -7594,89 +7913,87 @@
         <v>9</v>
       </c>
       <c r="L50" s="32" t="str">
-        <f t="shared" si="67"/>
-        <v>De API</v>
+        <f t="shared" si="41"/>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M50" s="32" t="str">
-        <f t="shared" si="67"/>
-        <v>Macros</v>
+        <f t="shared" si="42"/>
+        <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N50" s="32" t="str">
-        <f t="shared" si="67"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O50" s="32" t="str">
-        <f t="shared" si="67"/>
-        <v>Função Local</v>
-      </c>
-      <c r="P50" s="29" t="s">
-        <v>354</v>
+        <f t="shared" si="43"/>
+        <v>Esgoto Visitas</v>
+      </c>
+      <c r="O50" s="29" t="str">
+        <f t="shared" si="13"/>
+        <v>Poço.de.Visita</v>
+      </c>
+      <c r="P50" s="51" t="s">
+        <v>118</v>
       </c>
       <c r="Q50" s="29" t="s">
-        <v>355</v>
+        <v>125</v>
       </c>
       <c r="R50" s="29" t="s">
-        <v>356</v>
+        <v>330</v>
       </c>
       <c r="S50" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="T50" s="29" t="str">
-        <f t="shared" si="68"/>
-        <v>De API</v>
-      </c>
-      <c r="U50" s="29" t="str">
-        <f t="shared" si="68"/>
-        <v>Macros</v>
-      </c>
-      <c r="V50" s="60" t="str">
-        <f t="shared" si="68"/>
-        <v>Métodos</v>
+      <c r="T50" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="U50" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="V50" s="29" t="str">
+        <f t="shared" si="44"/>
+        <v>Esgoto.Visitas</v>
       </c>
       <c r="W50" s="29" t="s">
         <v>152</v>
       </c>
       <c r="X50" s="57" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="8"/>
         <v>Key-HIDR-50</v>
       </c>
-      <c r="Y50" s="61" t="s">
-        <v>9</v>
+      <c r="Y50" s="28" t="s">
+        <v>247</v>
       </c>
       <c r="Z50" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AA50" s="61" t="s">
-        <v>9</v>
+      <c r="AA50" s="28" t="s">
+        <v>248</v>
       </c>
       <c r="AB50" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AC50" s="61" t="s">
-        <v>9</v>
+      <c r="AC50" s="29" t="s">
+        <v>126</v>
       </c>
       <c r="AD50" s="61" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:30" s="62" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="56">
         <v>51</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="C51" s="63" t="s">
-        <v>342</v>
-      </c>
-      <c r="D51" s="63" t="s">
-        <v>344</v>
-      </c>
-      <c r="E51" s="63" t="s">
-        <v>343</v>
-      </c>
-      <c r="F51" s="63" t="s">
-        <v>357</v>
+        <v>243</v>
+      </c>
+      <c r="C51" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="E51" s="41" t="s">
+        <v>217</v>
+      </c>
+      <c r="F51" s="41" t="s">
+        <v>155</v>
       </c>
       <c r="G51" s="58" t="s">
         <v>9</v>
@@ -7694,89 +8011,87 @@
         <v>9</v>
       </c>
       <c r="L51" s="32" t="str">
-        <f t="shared" si="67"/>
-        <v>De API</v>
+        <f t="shared" ref="L51" si="49">CONCATENATE("", C51)</f>
+        <v>Sistemas.Prediais</v>
       </c>
       <c r="M51" s="32" t="str">
-        <f t="shared" si="67"/>
-        <v>Macros</v>
+        <f t="shared" ref="M51" si="50">CONCATENATE("", D51)</f>
+        <v>Elementos.Hidráulicos</v>
       </c>
       <c r="N51" s="32" t="str">
-        <f t="shared" si="67"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O51" s="32" t="str">
-        <f t="shared" si="67"/>
-        <v>Função Filtro</v>
-      </c>
-      <c r="P51" s="29" t="s">
-        <v>358</v>
-      </c>
-      <c r="Q51" s="29" t="s">
-        <v>359</v>
+        <f t="shared" ref="N51" si="51">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E51),"."," ")," De "," de "))</f>
+        <v>Esgoto Acessórios</v>
+      </c>
+      <c r="O51" s="29" t="str">
+        <f t="shared" si="13"/>
+        <v>Acessório.Sanitário</v>
+      </c>
+      <c r="P51" s="51" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q51" s="51" t="s">
+        <v>156</v>
       </c>
       <c r="R51" s="29" t="s">
-        <v>360</v>
+        <v>332</v>
       </c>
       <c r="S51" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="T51" s="29" t="str">
-        <f t="shared" si="68"/>
-        <v>De API</v>
-      </c>
-      <c r="U51" s="29" t="str">
-        <f t="shared" si="68"/>
-        <v>Macros</v>
-      </c>
-      <c r="V51" s="60" t="str">
-        <f t="shared" si="68"/>
-        <v>Métodos</v>
+      <c r="T51" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="U51" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="V51" s="29" t="str">
+        <f t="shared" ref="V51" si="52">SUBSTITUTE(E51, "_", " ")</f>
+        <v>Esgoto.Acessórios</v>
       </c>
       <c r="W51" s="29" t="s">
         <v>152</v>
       </c>
       <c r="X51" s="57" t="str">
-        <f t="shared" si="61"/>
+        <f t="shared" si="8"/>
         <v>Key-HIDR-51</v>
       </c>
-      <c r="Y51" s="61" t="s">
-        <v>9</v>
+      <c r="Y51" s="28" t="s">
+        <v>235</v>
       </c>
       <c r="Z51" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AA51" s="61" t="s">
-        <v>9</v>
+      <c r="AA51" s="28" t="s">
+        <v>234</v>
       </c>
       <c r="AB51" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AC51" s="61" t="s">
-        <v>9</v>
+      <c r="AC51" s="29" t="s">
+        <v>126</v>
       </c>
       <c r="AD51" s="61" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:30" s="62" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="56">
         <v>52</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="C52" s="63" t="s">
-        <v>342</v>
-      </c>
-      <c r="D52" s="63" t="s">
-        <v>344</v>
-      </c>
-      <c r="E52" s="63" t="s">
-        <v>361</v>
-      </c>
-      <c r="F52" s="63" t="s">
-        <v>362</v>
+      <c r="C52" s="41" t="s">
+        <v>270</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="E52" s="41" t="s">
+        <v>276</v>
+      </c>
+      <c r="F52" s="41" t="s">
+        <v>271</v>
       </c>
       <c r="G52" s="58" t="s">
         <v>9</v>
@@ -7794,144 +8109,1060 @@
         <v>9</v>
       </c>
       <c r="L52" s="32" t="str">
-        <f t="shared" si="67"/>
-        <v>De API</v>
+        <f t="shared" ref="L52" si="53">CONCATENATE("", C52)</f>
+        <v>De.Tubulações</v>
       </c>
       <c r="M52" s="32" t="str">
-        <f t="shared" si="67"/>
-        <v>Macros</v>
+        <f t="shared" ref="M52" si="54">CONCATENATE("", D52)</f>
+        <v>Elementos.de.Instalações</v>
       </c>
       <c r="N52" s="32" t="str">
-        <f t="shared" si="67"/>
-        <v>Códigos Visuais</v>
-      </c>
-      <c r="O52" s="32" t="str">
-        <f t="shared" si="67"/>
-        <v>Bloco de Código</v>
-      </c>
-      <c r="P52" s="29" t="s">
-        <v>363</v>
-      </c>
-      <c r="Q52" s="29" t="s">
-        <v>364</v>
+        <f t="shared" ref="N52" si="55">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E52),"."," ")," De "," de "))</f>
+        <v>Instalação De</v>
+      </c>
+      <c r="O52" s="29" t="str">
+        <f t="shared" ref="O52" si="56">IF(ISNUMBER(FIND("Ifc",F52)),CONCATENATE("Classe IFC:   ",F52),CONCATENATE("",F52))</f>
+        <v>Esgoto</v>
+      </c>
+      <c r="P52" s="51" t="s">
+        <v>279</v>
+      </c>
+      <c r="Q52" s="51" t="s">
+        <v>292</v>
       </c>
       <c r="R52" s="29" t="s">
-        <v>365</v>
+        <v>333</v>
       </c>
       <c r="S52" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="T52" s="29" t="str">
-        <f t="shared" si="68"/>
-        <v>De API</v>
-      </c>
-      <c r="U52" s="29" t="str">
-        <f t="shared" si="68"/>
-        <v>Macros</v>
-      </c>
-      <c r="V52" s="60" t="str">
-        <f t="shared" si="68"/>
-        <v>Códigos Visuais</v>
+      <c r="T52" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="U52" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="V52" s="29" t="str">
+        <f t="shared" ref="V52" si="57">SUBSTITUTE(E52, "_", " ")</f>
+        <v>Instalação.De</v>
       </c>
       <c r="W52" s="29" t="s">
         <v>152</v>
       </c>
       <c r="X52" s="57" t="str">
+        <f t="shared" ref="X52" si="58">CONCATENATE("Key-HIDR-",A52)</f>
+        <v>Key-HIDR-52</v>
+      </c>
+      <c r="Y52" s="28" t="s">
+        <v>247</v>
+      </c>
+      <c r="Z52" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA52" s="28" t="s">
+        <v>248</v>
+      </c>
+      <c r="AB52" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC52" s="29" t="s">
+        <v>126</v>
+      </c>
+      <c r="AD52" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="53" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A53" s="56">
+        <v>53</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C53" s="41" t="s">
+        <v>270</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="E53" s="41" t="s">
+        <v>276</v>
+      </c>
+      <c r="F53" s="41" t="s">
+        <v>272</v>
+      </c>
+      <c r="G53" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H53" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I53" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J53" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K53" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="L53" s="32" t="str">
+        <f t="shared" ref="L53:L55" si="59">CONCATENATE("", C53)</f>
+        <v>De.Tubulações</v>
+      </c>
+      <c r="M53" s="32" t="str">
+        <f t="shared" ref="M53:M55" si="60">CONCATENATE("", D53)</f>
+        <v>Elementos.de.Instalações</v>
+      </c>
+      <c r="N53" s="32" t="str">
+        <f t="shared" ref="N53:N55" si="61">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E53),"."," ")," De "," de "))</f>
+        <v>Instalação De</v>
+      </c>
+      <c r="O53" s="29" t="str">
+        <f t="shared" ref="O53:O55" si="62">IF(ISNUMBER(FIND("Ifc",F53)),CONCATENATE("Classe IFC:   ",F53),CONCATENATE("",F53))</f>
+        <v>AF</v>
+      </c>
+      <c r="P53" s="51" t="s">
+        <v>280</v>
+      </c>
+      <c r="Q53" s="51" t="s">
+        <v>293</v>
+      </c>
+      <c r="R53" s="29" t="s">
+        <v>334</v>
+      </c>
+      <c r="S53" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="T53" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="U53" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="V53" s="29" t="str">
+        <f t="shared" ref="V53:V55" si="63">SUBSTITUTE(E53, "_", " ")</f>
+        <v>Instalação.De</v>
+      </c>
+      <c r="W53" s="29" t="s">
+        <v>152</v>
+      </c>
+      <c r="X53" s="57" t="str">
+        <f t="shared" ref="X53:X61" si="64">CONCATENATE("Key-HIDR-",A53)</f>
+        <v>Key-HIDR-53</v>
+      </c>
+      <c r="Y53" s="28" t="s">
+        <v>247</v>
+      </c>
+      <c r="Z53" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA53" s="28" t="s">
+        <v>248</v>
+      </c>
+      <c r="AB53" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC53" s="29" t="s">
+        <v>154</v>
+      </c>
+      <c r="AD53" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="54" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A54" s="56">
+        <v>54</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C54" s="41" t="s">
+        <v>270</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="E54" s="41" t="s">
+        <v>276</v>
+      </c>
+      <c r="F54" s="41" t="s">
+        <v>273</v>
+      </c>
+      <c r="G54" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H54" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I54" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J54" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K54" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="L54" s="32" t="str">
+        <f t="shared" si="59"/>
+        <v>De.Tubulações</v>
+      </c>
+      <c r="M54" s="32" t="str">
+        <f t="shared" si="60"/>
+        <v>Elementos.de.Instalações</v>
+      </c>
+      <c r="N54" s="32" t="str">
         <f t="shared" si="61"/>
-        <v>Key-HIDR-52</v>
-      </c>
-      <c r="Y52" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z52" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA52" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB52" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC52" s="61" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD52" s="61" t="s">
+        <v>Instalação De</v>
+      </c>
+      <c r="O54" s="29" t="str">
+        <f t="shared" si="62"/>
+        <v>AQ</v>
+      </c>
+      <c r="P54" s="51" t="s">
+        <v>281</v>
+      </c>
+      <c r="Q54" s="51" t="s">
+        <v>294</v>
+      </c>
+      <c r="R54" s="29" t="s">
+        <v>335</v>
+      </c>
+      <c r="S54" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="T54" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="U54" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="V54" s="29" t="str">
+        <f t="shared" si="63"/>
+        <v>Instalação.De</v>
+      </c>
+      <c r="W54" s="29" t="s">
+        <v>152</v>
+      </c>
+      <c r="X54" s="57" t="str">
+        <f t="shared" si="64"/>
+        <v>Key-HIDR-54</v>
+      </c>
+      <c r="Y54" s="28" t="s">
+        <v>247</v>
+      </c>
+      <c r="Z54" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA54" s="28" t="s">
+        <v>248</v>
+      </c>
+      <c r="AB54" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC54" s="29" t="s">
+        <v>154</v>
+      </c>
+      <c r="AD54" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="55" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A55" s="56">
+        <v>55</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C55" s="41" t="s">
+        <v>270</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="E55" s="41" t="s">
+        <v>276</v>
+      </c>
+      <c r="F55" s="41" t="s">
+        <v>274</v>
+      </c>
+      <c r="G55" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H55" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I55" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J55" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K55" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="L55" s="32" t="str">
+        <f t="shared" si="59"/>
+        <v>De.Tubulações</v>
+      </c>
+      <c r="M55" s="32" t="str">
+        <f t="shared" si="60"/>
+        <v>Elementos.de.Instalações</v>
+      </c>
+      <c r="N55" s="32" t="str">
+        <f t="shared" si="61"/>
+        <v>Instalação De</v>
+      </c>
+      <c r="O55" s="29" t="str">
+        <f t="shared" si="62"/>
+        <v>Pluvial</v>
+      </c>
+      <c r="P55" s="51" t="s">
+        <v>282</v>
+      </c>
+      <c r="Q55" s="51" t="s">
+        <v>295</v>
+      </c>
+      <c r="R55" s="29" t="s">
+        <v>336</v>
+      </c>
+      <c r="S55" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="T55" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="U55" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="V55" s="29" t="str">
+        <f t="shared" si="63"/>
+        <v>Instalação.De</v>
+      </c>
+      <c r="W55" s="29" t="s">
+        <v>152</v>
+      </c>
+      <c r="X55" s="57" t="str">
+        <f t="shared" si="64"/>
+        <v>Key-HIDR-55</v>
+      </c>
+      <c r="Y55" s="28" t="s">
+        <v>247</v>
+      </c>
+      <c r="Z55" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA55" s="28" t="s">
+        <v>248</v>
+      </c>
+      <c r="AB55" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC55" s="29" t="s">
+        <v>126</v>
+      </c>
+      <c r="AD55" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="56" spans="1:30" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A56" s="56">
+        <v>56</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C56" s="41" t="s">
+        <v>270</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="E56" s="41" t="s">
+        <v>276</v>
+      </c>
+      <c r="F56" s="41" t="s">
+        <v>277</v>
+      </c>
+      <c r="G56" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H56" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I56" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J56" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K56" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="L56" s="32" t="str">
+        <f t="shared" ref="L56" si="65">CONCATENATE("", C56)</f>
+        <v>De.Tubulações</v>
+      </c>
+      <c r="M56" s="32" t="str">
+        <f t="shared" ref="M56" si="66">CONCATENATE("", D56)</f>
+        <v>Elementos.de.Instalações</v>
+      </c>
+      <c r="N56" s="32" t="str">
+        <f t="shared" ref="N56" si="67">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E56),"."," ")," De "," de "))</f>
+        <v>Instalação De</v>
+      </c>
+      <c r="O56" s="29" t="str">
+        <f t="shared" ref="O56" si="68">IF(ISNUMBER(FIND("Ifc",F56)),CONCATENATE("Classe IFC:   ",F56),CONCATENATE("",F56))</f>
+        <v>Ventilação</v>
+      </c>
+      <c r="P56" s="51" t="s">
+        <v>278</v>
+      </c>
+      <c r="Q56" s="51" t="s">
+        <v>296</v>
+      </c>
+      <c r="R56" s="29" t="s">
+        <v>337</v>
+      </c>
+      <c r="S56" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="T56" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="U56" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="V56" s="29" t="str">
+        <f t="shared" ref="V56" si="69">SUBSTITUTE(E56, "_", " ")</f>
+        <v>Instalação.De</v>
+      </c>
+      <c r="W56" s="29" t="s">
+        <v>152</v>
+      </c>
+      <c r="X56" s="57" t="str">
+        <f t="shared" si="64"/>
+        <v>Key-HIDR-56</v>
+      </c>
+      <c r="Y56" s="28" t="s">
+        <v>247</v>
+      </c>
+      <c r="Z56" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA56" s="28" t="s">
+        <v>248</v>
+      </c>
+      <c r="AB56" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC56" s="29" t="s">
+        <v>126</v>
+      </c>
+      <c r="AD56" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="57" spans="1:30" s="62" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="56">
+        <v>57</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C57" s="63" t="s">
+        <v>342</v>
+      </c>
+      <c r="D57" s="63" t="s">
+        <v>344</v>
+      </c>
+      <c r="E57" s="63" t="s">
+        <v>343</v>
+      </c>
+      <c r="F57" s="63" t="s">
+        <v>345</v>
+      </c>
+      <c r="G57" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H57" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I57" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J57" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K57" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="L57" s="32" t="str">
+        <f t="shared" ref="L57:O61" si="70">SUBSTITUTE(CONCATENATE("", C57), ".", " ")</f>
+        <v>De API</v>
+      </c>
+      <c r="M57" s="32" t="str">
+        <f t="shared" si="70"/>
+        <v>Macros</v>
+      </c>
+      <c r="N57" s="32" t="str">
+        <f t="shared" si="70"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O57" s="32" t="str">
+        <f t="shared" si="70"/>
+        <v>Função Auxiliar</v>
+      </c>
+      <c r="P57" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="Q57" s="29" t="s">
+        <v>347</v>
+      </c>
+      <c r="R57" s="29" t="s">
+        <v>348</v>
+      </c>
+      <c r="S57" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="T57" s="29" t="str">
+        <f t="shared" ref="T57:V61" si="71">SUBSTITUTE(C57, ".", " ")</f>
+        <v>De API</v>
+      </c>
+      <c r="U57" s="29" t="str">
+        <f t="shared" si="71"/>
+        <v>Macros</v>
+      </c>
+      <c r="V57" s="60" t="str">
+        <f t="shared" si="71"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W57" s="29" t="s">
+        <v>152</v>
+      </c>
+      <c r="X57" s="57" t="str">
+        <f t="shared" si="64"/>
+        <v>Key-HIDR-57</v>
+      </c>
+      <c r="Y57" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z57" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA57" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB57" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC57" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD57" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="58" spans="1:30" s="62" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="56">
+        <v>58</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C58" s="63" t="s">
+        <v>342</v>
+      </c>
+      <c r="D58" s="63" t="s">
+        <v>344</v>
+      </c>
+      <c r="E58" s="63" t="s">
+        <v>343</v>
+      </c>
+      <c r="F58" s="63" t="s">
+        <v>349</v>
+      </c>
+      <c r="G58" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H58" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I58" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J58" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K58" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="L58" s="32" t="str">
+        <f t="shared" si="70"/>
+        <v>De API</v>
+      </c>
+      <c r="M58" s="32" t="str">
+        <f t="shared" si="70"/>
+        <v>Macros</v>
+      </c>
+      <c r="N58" s="32" t="str">
+        <f t="shared" si="70"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O58" s="32" t="str">
+        <f t="shared" si="70"/>
+        <v>Função Global</v>
+      </c>
+      <c r="P58" s="29" t="s">
+        <v>350</v>
+      </c>
+      <c r="Q58" s="29" t="s">
+        <v>351</v>
+      </c>
+      <c r="R58" s="29" t="s">
+        <v>352</v>
+      </c>
+      <c r="S58" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="T58" s="29" t="str">
+        <f t="shared" si="71"/>
+        <v>De API</v>
+      </c>
+      <c r="U58" s="29" t="str">
+        <f t="shared" si="71"/>
+        <v>Macros</v>
+      </c>
+      <c r="V58" s="60" t="str">
+        <f t="shared" si="71"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W58" s="29" t="s">
+        <v>152</v>
+      </c>
+      <c r="X58" s="57" t="str">
+        <f t="shared" si="64"/>
+        <v>Key-HIDR-58</v>
+      </c>
+      <c r="Y58" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z58" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA58" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB58" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC58" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD58" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="59" spans="1:30" s="62" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="56">
+        <v>59</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C59" s="63" t="s">
+        <v>342</v>
+      </c>
+      <c r="D59" s="63" t="s">
+        <v>344</v>
+      </c>
+      <c r="E59" s="63" t="s">
+        <v>343</v>
+      </c>
+      <c r="F59" s="63" t="s">
+        <v>353</v>
+      </c>
+      <c r="G59" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H59" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I59" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J59" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K59" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="L59" s="32" t="str">
+        <f t="shared" si="70"/>
+        <v>De API</v>
+      </c>
+      <c r="M59" s="32" t="str">
+        <f t="shared" si="70"/>
+        <v>Macros</v>
+      </c>
+      <c r="N59" s="32" t="str">
+        <f t="shared" si="70"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O59" s="32" t="str">
+        <f t="shared" si="70"/>
+        <v>Função Local</v>
+      </c>
+      <c r="P59" s="29" t="s">
+        <v>354</v>
+      </c>
+      <c r="Q59" s="29" t="s">
+        <v>355</v>
+      </c>
+      <c r="R59" s="29" t="s">
+        <v>356</v>
+      </c>
+      <c r="S59" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="T59" s="29" t="str">
+        <f t="shared" si="71"/>
+        <v>De API</v>
+      </c>
+      <c r="U59" s="29" t="str">
+        <f t="shared" si="71"/>
+        <v>Macros</v>
+      </c>
+      <c r="V59" s="60" t="str">
+        <f t="shared" si="71"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W59" s="29" t="s">
+        <v>152</v>
+      </c>
+      <c r="X59" s="57" t="str">
+        <f t="shared" si="64"/>
+        <v>Key-HIDR-59</v>
+      </c>
+      <c r="Y59" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z59" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA59" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB59" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC59" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD59" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="60" spans="1:30" s="62" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="56">
+        <v>60</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C60" s="63" t="s">
+        <v>342</v>
+      </c>
+      <c r="D60" s="63" t="s">
+        <v>344</v>
+      </c>
+      <c r="E60" s="63" t="s">
+        <v>343</v>
+      </c>
+      <c r="F60" s="63" t="s">
+        <v>357</v>
+      </c>
+      <c r="G60" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H60" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I60" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J60" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K60" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="L60" s="32" t="str">
+        <f t="shared" si="70"/>
+        <v>De API</v>
+      </c>
+      <c r="M60" s="32" t="str">
+        <f t="shared" si="70"/>
+        <v>Macros</v>
+      </c>
+      <c r="N60" s="32" t="str">
+        <f t="shared" si="70"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O60" s="32" t="str">
+        <f t="shared" si="70"/>
+        <v>Função Filtro</v>
+      </c>
+      <c r="P60" s="29" t="s">
+        <v>358</v>
+      </c>
+      <c r="Q60" s="29" t="s">
+        <v>359</v>
+      </c>
+      <c r="R60" s="29" t="s">
+        <v>360</v>
+      </c>
+      <c r="S60" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="T60" s="29" t="str">
+        <f t="shared" si="71"/>
+        <v>De API</v>
+      </c>
+      <c r="U60" s="29" t="str">
+        <f t="shared" si="71"/>
+        <v>Macros</v>
+      </c>
+      <c r="V60" s="60" t="str">
+        <f t="shared" si="71"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W60" s="29" t="s">
+        <v>152</v>
+      </c>
+      <c r="X60" s="57" t="str">
+        <f t="shared" si="64"/>
+        <v>Key-HIDR-60</v>
+      </c>
+      <c r="Y60" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z60" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA60" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB60" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC60" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD60" s="61" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="61" spans="1:30" s="62" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="56">
+        <v>61</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C61" s="63" t="s">
+        <v>342</v>
+      </c>
+      <c r="D61" s="63" t="s">
+        <v>344</v>
+      </c>
+      <c r="E61" s="63" t="s">
+        <v>361</v>
+      </c>
+      <c r="F61" s="63" t="s">
+        <v>362</v>
+      </c>
+      <c r="G61" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H61" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="I61" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J61" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K61" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="L61" s="32" t="str">
+        <f t="shared" si="70"/>
+        <v>De API</v>
+      </c>
+      <c r="M61" s="32" t="str">
+        <f t="shared" si="70"/>
+        <v>Macros</v>
+      </c>
+      <c r="N61" s="32" t="str">
+        <f t="shared" si="70"/>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="O61" s="32" t="str">
+        <f t="shared" si="70"/>
+        <v>Bloco de Código</v>
+      </c>
+      <c r="P61" s="29" t="s">
+        <v>363</v>
+      </c>
+      <c r="Q61" s="29" t="s">
+        <v>364</v>
+      </c>
+      <c r="R61" s="29" t="s">
+        <v>365</v>
+      </c>
+      <c r="S61" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="T61" s="29" t="str">
+        <f t="shared" si="71"/>
+        <v>De API</v>
+      </c>
+      <c r="U61" s="29" t="str">
+        <f t="shared" si="71"/>
+        <v>Macros</v>
+      </c>
+      <c r="V61" s="60" t="str">
+        <f t="shared" si="71"/>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="W61" s="29" t="s">
+        <v>152</v>
+      </c>
+      <c r="X61" s="57" t="str">
+        <f t="shared" si="64"/>
+        <v>Key-HIDR-61</v>
+      </c>
+      <c r="Y61" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z61" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA61" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB61" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC61" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD61" s="61" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:AC933">
-    <sortCondition ref="F4:F933"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A13:AC942">
+    <sortCondition ref="F13:F942"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:B52">
-    <cfRule type="cellIs" dxfId="30" priority="1" operator="equal">
+  <conditionalFormatting sqref="A2:B61">
+    <cfRule type="cellIs" dxfId="46" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E52:F52">
-    <cfRule type="duplicateValues" dxfId="29" priority="2"/>
+  <conditionalFormatting sqref="E61:F61">
+    <cfRule type="duplicateValues" dxfId="45" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="28" priority="1512"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="1529"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F47 F53:F1048576">
-    <cfRule type="duplicateValues" dxfId="27" priority="40"/>
+  <conditionalFormatting sqref="F2:F7">
+    <cfRule type="duplicateValues" dxfId="43" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F13">
-    <cfRule type="duplicateValues" dxfId="26" priority="42"/>
+  <conditionalFormatting sqref="F8:F9">
+    <cfRule type="duplicateValues" dxfId="38" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F32">
-    <cfRule type="duplicateValues" dxfId="25" priority="62"/>
+  <conditionalFormatting sqref="F10">
+    <cfRule type="duplicateValues" dxfId="33" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="17"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F35 F14:F30 F37:F47 F1:F12 F53:F1048576">
-    <cfRule type="duplicateValues" dxfId="24" priority="64"/>
+  <conditionalFormatting sqref="F22">
+    <cfRule type="duplicateValues" dxfId="28" priority="59"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F48:F51">
-    <cfRule type="duplicateValues" dxfId="23" priority="3"/>
+  <conditionalFormatting sqref="F41">
+    <cfRule type="duplicateValues" dxfId="27" priority="79"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F53:F1048576">
-    <cfRule type="duplicateValues" dxfId="22" priority="269"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="271"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="1484"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="1505"/>
+  <conditionalFormatting sqref="F44 F23:F39 F46:F56 F1 F62:F1048576 F11:F21">
+    <cfRule type="duplicateValues" dxfId="26" priority="81"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:O1 A1:D1 Q1 S1:Z1">
-    <cfRule type="cellIs" dxfId="18" priority="76" operator="equal">
+  <conditionalFormatting sqref="F57:F60">
+    <cfRule type="duplicateValues" dxfId="25" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F62:F1048576 F1 F11:F56">
+    <cfRule type="duplicateValues" dxfId="24" priority="57"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F62:F1048576">
+    <cfRule type="duplicateValues" dxfId="23" priority="286"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="288"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="1501"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="1522"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F1:O1 A1:D1">
+    <cfRule type="cellIs" dxfId="19" priority="93" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P6">
-    <cfRule type="duplicateValues" dxfId="17" priority="1537"/>
+  <conditionalFormatting sqref="P11:P15">
+    <cfRule type="duplicateValues" dxfId="18" priority="1554"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P7:P12 P14:P23">
-    <cfRule type="duplicateValues" dxfId="16" priority="1525"/>
+  <conditionalFormatting sqref="P16:P21 P23:P32">
+    <cfRule type="duplicateValues" dxfId="17" priority="1542"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P24:P29">
-    <cfRule type="duplicateValues" dxfId="15" priority="45"/>
+  <conditionalFormatting sqref="P33:P38">
+    <cfRule type="duplicateValues" dxfId="16" priority="62"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P30">
-    <cfRule type="duplicateValues" dxfId="14" priority="1518"/>
+  <conditionalFormatting sqref="P39">
+    <cfRule type="duplicateValues" dxfId="15" priority="1535"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q5">
-    <cfRule type="duplicateValues" dxfId="13" priority="46"/>
+  <conditionalFormatting sqref="Q11:Q14">
+    <cfRule type="duplicateValues" dxfId="14" priority="63"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q6">
-    <cfRule type="duplicateValues" dxfId="12" priority="17"/>
+  <conditionalFormatting sqref="Q15">
+    <cfRule type="duplicateValues" dxfId="13" priority="34"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q23">
-    <cfRule type="duplicateValues" dxfId="11" priority="48"/>
+  <conditionalFormatting sqref="Q32">
+    <cfRule type="duplicateValues" dxfId="12" priority="65"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q30">
-    <cfRule type="duplicateValues" dxfId="10" priority="1519"/>
+  <conditionalFormatting sqref="Q39">
+    <cfRule type="duplicateValues" dxfId="11" priority="1536"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R1:R47">
-    <cfRule type="cellIs" dxfId="9" priority="15" operator="equal">
+  <conditionalFormatting sqref="Q1:Z1">
+    <cfRule type="cellIs" dxfId="10" priority="32" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y2:Y10 AA2:AA10 AC2:AC10 R2:R56">
+    <cfRule type="cellIs" dxfId="9" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB1:AD1">
-    <cfRule type="cellIs" dxfId="8" priority="41" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="58" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7946,15 +9177,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" style="9" customWidth="1"/>
-    <col min="2" max="10" width="6.5703125" style="10" customWidth="1"/>
-    <col min="11" max="21" width="6.5703125" style="8" customWidth="1"/>
-    <col min="22" max="16384" width="11.140625" style="8"/>
+    <col min="1" max="1" width="2.84375" style="9" customWidth="1"/>
+    <col min="2" max="10" width="6.53515625" style="10" customWidth="1"/>
+    <col min="11" max="21" width="6.53515625" style="8" customWidth="1"/>
+    <col min="22" max="16384" width="11.15234375" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -8019,7 +9250,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -8102,30 +9333,30 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38CB0525-EDFB-44CB-9009-6752AEDD7340}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:S19"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.85546875" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.3046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.3046875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.69140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.84375" customWidth="1"/>
     <col min="6" max="6" width="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="60.140625" customWidth="1"/>
+    <col min="7" max="7" width="60.15234375" customWidth="1"/>
     <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.42578125" customWidth="1"/>
-    <col min="10" max="10" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.3828125" customWidth="1"/>
+    <col min="10" max="10" width="8.3046875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.84375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.3828125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="24" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="23.85546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.3828125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="23.84375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.69140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="19.69140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.3046875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.3828125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="14.7" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="16" t="s">
         <v>10</v>
       </c>
@@ -8184,7 +9415,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="19">
         <v>1</v>
       </c>
@@ -8243,7 +9474,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="19">
         <v>2</v>
       </c>
@@ -8302,7 +9533,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="19">
         <v>3</v>
       </c>
@@ -8361,7 +9592,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="19">
         <v>4</v>
       </c>
@@ -8420,7 +9651,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="19">
         <v>5</v>
       </c>
@@ -8479,7 +9710,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="19">
         <v>6</v>
       </c>
@@ -8538,7 +9769,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="19">
         <v>7</v>
       </c>
@@ -8597,7 +9828,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="19">
         <v>8</v>
       </c>
@@ -8656,7 +9887,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="19">
         <v>9</v>
       </c>
@@ -8715,7 +9946,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="19">
         <v>10</v>
       </c>
@@ -8774,7 +10005,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="19">
         <v>11</v>
       </c>
@@ -8833,7 +10064,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="19">
         <v>12</v>
       </c>
@@ -8892,7 +10123,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="19">
         <v>13</v>
       </c>
@@ -8951,7 +10182,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="19">
         <v>14</v>
       </c>
@@ -9010,7 +10241,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="19">
         <v>15</v>
       </c>
@@ -9069,7 +10300,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="19">
         <v>16</v>
       </c>
@@ -9128,7 +10359,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="19">
         <v>17</v>
       </c>
@@ -9187,7 +10418,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="19">
         <v>18</v>
       </c>
@@ -9259,15 +10490,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5FE5EC8-1387-4A67-960C-C64BD1326958}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.140625" style="25" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" style="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" style="24" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.85546875" style="24" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.15234375" style="25" customWidth="1"/>
+    <col min="2" max="2" width="5.84375" style="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.3046875" style="24" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.84375" style="24" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="30">
         <v>0</v>
       </c>
@@ -9290,7 +10521,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="31">
         <v>2</v>
       </c>
